--- a/upload/case-mix-2025.xlsx
+++ b/upload/case-mix-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D725"/>
+  <dimension ref="A1:D734"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1560,21 +1560,21 @@
         <v>3</v>
       </c>
       <c r="D84" s="3">
-        <v>1.6600999999999999</v>
+        <v>1.5893999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B85" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C85" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D85" s="3">
-        <v>0.32269999999999999</v>
+        <v>1.5334000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1585,10 +1585,10 @@
         <v>2019</v>
       </c>
       <c r="C86" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D86" s="3">
-        <v>2.4020999999999999</v>
+        <v>0.32269999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1596,13 +1596,13 @@
         <v>5</v>
       </c>
       <c r="B87" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C87" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D87" s="3">
-        <v>2.0989</v>
+        <v>2.4020999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1613,10 +1613,10 @@
         <v>2020</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" s="3">
-        <v>1.9497</v>
+        <v>2.0989</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1627,10 +1627,10 @@
         <v>2020</v>
       </c>
       <c r="C89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" s="3">
-        <v>2.1490999999999998</v>
+        <v>1.9497</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1641,10 +1641,10 @@
         <v>2020</v>
       </c>
       <c r="C90" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" s="3">
-        <v>1.6907000000000001</v>
+        <v>2.1490999999999998</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1655,10 +1655,10 @@
         <v>2020</v>
       </c>
       <c r="C91" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" s="3">
-        <v>2.1762999999999999</v>
+        <v>1.6907000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1669,10 +1669,10 @@
         <v>2020</v>
       </c>
       <c r="C92" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D92" s="3">
-        <v>2.3714</v>
+        <v>2.1762999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1683,10 +1683,10 @@
         <v>2020</v>
       </c>
       <c r="C93" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D93" s="3">
-        <v>2.6513</v>
+        <v>2.3714</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1697,10 +1697,10 @@
         <v>2020</v>
       </c>
       <c r="C94" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" s="3">
-        <v>2.3975</v>
+        <v>2.6513</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1711,10 +1711,10 @@
         <v>2020</v>
       </c>
       <c r="C95" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D95" s="3">
-        <v>3.2244999999999999</v>
+        <v>2.3975</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1725,10 +1725,10 @@
         <v>2020</v>
       </c>
       <c r="C96" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D96" s="3">
-        <v>2.0931000000000002</v>
+        <v>3.2244999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1739,10 +1739,10 @@
         <v>2020</v>
       </c>
       <c r="C97" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D97" s="3">
-        <v>2.1968000000000001</v>
+        <v>2.0931000000000002</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1753,10 +1753,10 @@
         <v>2020</v>
       </c>
       <c r="C98" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D98" s="3">
-        <v>2.0958999999999999</v>
+        <v>2.1968000000000001</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1764,13 +1764,13 @@
         <v>5</v>
       </c>
       <c r="B99" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D99" s="3">
-        <v>2.4843000000000002</v>
+        <v>2.0958999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1781,10 +1781,10 @@
         <v>2021</v>
       </c>
       <c r="C100" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" s="3">
-        <v>2.3409</v>
+        <v>2.4843000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1795,10 +1795,10 @@
         <v>2021</v>
       </c>
       <c r="C101" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" s="3">
-        <v>2.7355999999999998</v>
+        <v>2.3409</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1809,10 +1809,10 @@
         <v>2021</v>
       </c>
       <c r="C102" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D102" s="3">
-        <v>2.8948</v>
+        <v>2.7355999999999998</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1823,10 +1823,10 @@
         <v>2021</v>
       </c>
       <c r="C103" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D103" s="3">
-        <v>2.7456</v>
+        <v>2.8948</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>2021</v>
       </c>
       <c r="C104" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" s="3">
-        <v>2.5648</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1851,10 +1851,10 @@
         <v>2021</v>
       </c>
       <c r="C105" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105" s="3">
-        <v>2.5844</v>
+        <v>2.5648</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1865,10 +1865,10 @@
         <v>2021</v>
       </c>
       <c r="C106" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D106" s="3">
-        <v>2.8304999999999998</v>
+        <v>2.5844</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1879,10 +1879,10 @@
         <v>2021</v>
       </c>
       <c r="C107" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D107" s="3">
-        <v>2.0144000000000002</v>
+        <v>2.8304999999999998</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1893,10 +1893,10 @@
         <v>2021</v>
       </c>
       <c r="C108" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D108" s="3">
-        <v>1.9097</v>
+        <v>2.0144000000000002</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1907,10 +1907,10 @@
         <v>2021</v>
       </c>
       <c r="C109" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D109" s="3">
-        <v>2.3733</v>
+        <v>1.9097</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1921,10 +1921,10 @@
         <v>2021</v>
       </c>
       <c r="C110" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D110" s="3">
-        <v>2.0158999999999998</v>
+        <v>2.3733</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1932,13 +1932,13 @@
         <v>5</v>
       </c>
       <c r="B111" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C111" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D111" s="3">
-        <v>2.0093999999999999</v>
+        <v>2.0158999999999998</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1949,10 +1949,10 @@
         <v>2022</v>
       </c>
       <c r="C112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" s="3">
-        <v>3.6905000000000001</v>
+        <v>2.0093999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1963,10 +1963,10 @@
         <v>2022</v>
       </c>
       <c r="C113" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D113" s="3">
-        <v>2.6345000000000001</v>
+        <v>3.6905000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1977,10 +1977,10 @@
         <v>2022</v>
       </c>
       <c r="C114" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D114" s="3">
-        <v>2.0619999999999998</v>
+        <v>2.6345000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1991,10 +1991,10 @@
         <v>2022</v>
       </c>
       <c r="C115" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D115" s="3">
-        <v>1.9186000000000001</v>
+        <v>2.0619999999999998</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2005,10 +2005,10 @@
         <v>2022</v>
       </c>
       <c r="C116" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D116" s="3">
-        <v>2.0594000000000001</v>
+        <v>1.9186000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>2022</v>
       </c>
       <c r="C117" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D117" s="3">
-        <v>2.1585999999999999</v>
+        <v>2.0594000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2033,10 +2033,10 @@
         <v>2022</v>
       </c>
       <c r="C118" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D118" s="3">
-        <v>1.6135999999999999</v>
+        <v>2.1585999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2047,10 +2047,10 @@
         <v>2022</v>
       </c>
       <c r="C119" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D119" s="3">
-        <v>1.5652000000000001</v>
+        <v>1.6135999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2061,10 +2061,10 @@
         <v>2022</v>
       </c>
       <c r="C120" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D120" s="3">
-        <v>1.4952000000000001</v>
+        <v>1.5652000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2075,10 +2075,10 @@
         <v>2022</v>
       </c>
       <c r="C121" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D121" s="3">
-        <v>1.7753000000000001</v>
+        <v>1.4952000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2089,10 +2089,10 @@
         <v>2022</v>
       </c>
       <c r="C122" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D122" s="3">
-        <v>1.9029</v>
+        <v>1.7753000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2100,13 +2100,13 @@
         <v>5</v>
       </c>
       <c r="B123" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D123" s="3">
-        <v>1.5787</v>
+        <v>1.9029</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2117,10 +2117,10 @@
         <v>2023</v>
       </c>
       <c r="C124" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3">
-        <v>1.8613999999999999</v>
+        <v>1.5787</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2131,10 +2131,10 @@
         <v>2023</v>
       </c>
       <c r="C125" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125" s="3">
-        <v>1.6684000000000001</v>
+        <v>1.8613999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2145,10 +2145,10 @@
         <v>2023</v>
       </c>
       <c r="C126" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D126" s="3">
-        <v>1.5757000000000001</v>
+        <v>1.6684000000000001</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2159,10 +2159,10 @@
         <v>2023</v>
       </c>
       <c r="C127" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D127" s="3">
-        <v>2.0183</v>
+        <v>1.5757000000000001</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2173,10 +2173,10 @@
         <v>2023</v>
       </c>
       <c r="C128" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D128" s="3">
-        <v>1.6662999999999997</v>
+        <v>2.0183</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2187,10 +2187,10 @@
         <v>2023</v>
       </c>
       <c r="C129" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D129" s="3">
-        <v>1.9484999999999999</v>
+        <v>1.6662999999999997</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2201,10 +2201,10 @@
         <v>2023</v>
       </c>
       <c r="C130" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130" s="3">
-        <v>2.0987</v>
+        <v>1.9484999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2215,10 +2215,10 @@
         <v>2023</v>
       </c>
       <c r="C131" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D131" s="3">
-        <v>1.9556999999999998</v>
+        <v>2.0987</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2229,10 +2229,10 @@
         <v>2023</v>
       </c>
       <c r="C132" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D132" s="3">
-        <v>2.331</v>
+        <v>1.9556999999999998</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2243,10 +2243,10 @@
         <v>2023</v>
       </c>
       <c r="C133" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133" s="3">
-        <v>1.7165999999999999</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2257,10 +2257,10 @@
         <v>2023</v>
       </c>
       <c r="C134" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D134" s="3">
-        <v>1.6557999999999999</v>
+        <v>1.7165999999999999</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2268,13 +2268,13 @@
         <v>5</v>
       </c>
       <c r="B135" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C135" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D135" s="3">
-        <v>0.99390000000000001</v>
+        <v>1.6557999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2285,10 +2285,10 @@
         <v>2024</v>
       </c>
       <c r="C136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2299,10 +2299,10 @@
         <v>2024</v>
       </c>
       <c r="C137" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" s="3">
-        <v>0.88229999999999997</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2313,10 +2313,10 @@
         <v>2024</v>
       </c>
       <c r="C138" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D138" s="3">
-        <v>0.82889999999999997</v>
+        <v>0.88229999999999997</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2327,10 +2327,10 @@
         <v>2024</v>
       </c>
       <c r="C139" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D139" s="3">
-        <v>1.113</v>
+        <v>0.82889999999999997</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2341,10 +2341,10 @@
         <v>2024</v>
       </c>
       <c r="C140" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" s="3">
-        <v>1.7364999999999999</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2355,10 +2355,10 @@
         <v>2024</v>
       </c>
       <c r="C141" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D141" s="3">
-        <v>1.6022000000000001</v>
+        <v>1.7364999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2369,10 +2369,10 @@
         <v>2024</v>
       </c>
       <c r="C142" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D142" s="3">
-        <v>2.0381999999999998</v>
+        <v>1.6022000000000001</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2383,10 +2383,10 @@
         <v>2024</v>
       </c>
       <c r="C143" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D143" s="3">
-        <v>2.2471000000000001</v>
+        <v>2.0381999999999998</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2397,10 +2397,10 @@
         <v>2024</v>
       </c>
       <c r="C144" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D144" s="3">
-        <v>1.7967000000000002</v>
+        <v>2.2471000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2411,10 +2411,10 @@
         <v>2024</v>
       </c>
       <c r="C145" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D145" s="3">
-        <v>2.1593</v>
+        <v>1.7967000000000002</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2425,10 +2425,10 @@
         <v>2024</v>
       </c>
       <c r="C146" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D146" s="3">
-        <v>1.8868000000000003</v>
+        <v>2.1593</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2436,13 +2436,13 @@
         <v>5</v>
       </c>
       <c r="B147" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C147" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D147" s="3">
-        <v>1.7827999999999999</v>
+        <v>1.8868000000000003</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2453,10 +2453,10 @@
         <v>2025</v>
       </c>
       <c r="C148" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" s="3">
-        <v>2.1297999999999999</v>
+        <v>1.7827999999999999</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2467,10 +2467,10 @@
         <v>2025</v>
       </c>
       <c r="C149" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D149" s="3">
-        <v>2.4182999999999999</v>
+        <v>2.1297999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2481,10 +2481,10 @@
         <v>2025</v>
       </c>
       <c r="C150" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D150" s="3">
-        <v>1.9123000000000001</v>
+        <v>2.4182999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2495,10 +2495,10 @@
         <v>2025</v>
       </c>
       <c r="C151" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D151" s="3">
-        <v>1.6870000000000001</v>
+        <v>1.9123000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2509,10 +2509,10 @@
         <v>2025</v>
       </c>
       <c r="C152" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D152" s="3">
-        <v>2.0131000000000001</v>
+        <v>1.6870000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2523,10 +2523,10 @@
         <v>2025</v>
       </c>
       <c r="C153" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D153" s="3">
-        <v>1.8540000000000001</v>
+        <v>2.0131000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2537,10 +2537,10 @@
         <v>2025</v>
       </c>
       <c r="C154" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154" s="3">
-        <v>2.1894999999999998</v>
+        <v>1.8540000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2551,10 +2551,10 @@
         <v>2025</v>
       </c>
       <c r="C155" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D155" s="3">
-        <v>2.0306999999999999</v>
+        <v>2.1894999999999998</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2565,10 +2565,10 @@
         <v>2025</v>
       </c>
       <c r="C156" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D156" s="3">
-        <v>2.2544</v>
+        <v>2.0306999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2579,10 +2579,10 @@
         <v>2025</v>
       </c>
       <c r="C157" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D157" s="3">
-        <v>2.1646000000000001</v>
+        <v>2.2544</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2593,10 +2593,10 @@
         <v>2025</v>
       </c>
       <c r="C158" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D158" s="3">
-        <v>1.6874000000000002</v>
+        <v>2.1646000000000001</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2604,13 +2604,13 @@
         <v>5</v>
       </c>
       <c r="B159" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C159" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D159" s="3">
-        <v>1.7944</v>
+        <v>1.7296</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2621,10 +2621,10 @@
         <v>2026</v>
       </c>
       <c r="C160" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" s="3">
-        <v>1.5825</v>
+        <v>1.7944</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2635,38 +2635,38 @@
         <v>2026</v>
       </c>
       <c r="C161" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" s="3">
-        <v>1.4955000000000001</v>
+        <v>1.5825</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B162" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C162" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D162" s="3">
-        <v>0.76870000000000005</v>
+        <v>1.5029000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B163" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C163" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D163" s="3">
-        <v>0.73919999999999997</v>
+        <v>1.5125</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2677,10 +2677,10 @@
         <v>2019</v>
       </c>
       <c r="C164" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D164" s="3">
-        <v>0.40439999999999998</v>
+        <v>0.76870000000000005</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2691,10 +2691,10 @@
         <v>2019</v>
       </c>
       <c r="C165" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D165" s="3">
-        <v>0.91849999999999998</v>
+        <v>0.73919999999999997</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2702,13 +2702,13 @@
         <v>6</v>
       </c>
       <c r="B166" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D166" s="3">
-        <v>0.91590000000000005</v>
+        <v>0.40439999999999998</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2716,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="B167" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C167" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D167" s="3">
-        <v>0.91639999999999999</v>
+        <v>0.91849999999999998</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2733,10 +2733,10 @@
         <v>2020</v>
       </c>
       <c r="C168" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" s="3">
-        <v>0.71460000000000001</v>
+        <v>0.91590000000000005</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2747,10 +2747,10 @@
         <v>2020</v>
       </c>
       <c r="C169" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D169" s="3">
-        <v>0.99629999999999985</v>
+        <v>0.91639999999999999</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2761,10 +2761,10 @@
         <v>2020</v>
       </c>
       <c r="C170" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D170" s="3">
-        <v>1.0396000000000001</v>
+        <v>0.71460000000000001</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2775,10 +2775,10 @@
         <v>2020</v>
       </c>
       <c r="C171" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D171" s="3">
-        <v>0.70820000000000005</v>
+        <v>0.99629999999999985</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2789,10 +2789,10 @@
         <v>2020</v>
       </c>
       <c r="C172" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D172" s="3">
-        <v>1.5511999999999999</v>
+        <v>1.0396000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2803,10 +2803,10 @@
         <v>2020</v>
       </c>
       <c r="C173" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D173" s="3">
-        <v>1.117</v>
+        <v>0.70820000000000005</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2817,10 +2817,10 @@
         <v>2020</v>
       </c>
       <c r="C174" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D174" s="3">
-        <v>1.1403000000000001</v>
+        <v>1.5511999999999999</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2831,10 +2831,10 @@
         <v>2020</v>
       </c>
       <c r="C175" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D175" s="3">
-        <v>1.431</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2845,10 +2845,10 @@
         <v>2020</v>
       </c>
       <c r="C176" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D176" s="3">
-        <v>1.3353999999999999</v>
+        <v>1.1403000000000001</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2859,10 +2859,10 @@
         <v>2020</v>
       </c>
       <c r="C177" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D177" s="3">
-        <v>1.8660000000000001</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2870,13 +2870,13 @@
         <v>6</v>
       </c>
       <c r="B178" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C178" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D178" s="3">
-        <v>1.4126000000000001</v>
+        <v>1.3353999999999999</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2884,13 +2884,13 @@
         <v>6</v>
       </c>
       <c r="B179" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C179" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D179" s="3">
-        <v>1.2838000000000001</v>
+        <v>1.8660000000000001</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2901,10 +2901,10 @@
         <v>2021</v>
       </c>
       <c r="C180" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D180" s="3">
-        <v>1.0382</v>
+        <v>1.4126000000000001</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2915,10 +2915,10 @@
         <v>2021</v>
       </c>
       <c r="C181" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D181" s="3">
-        <v>1.4381999999999999</v>
+        <v>1.2838000000000001</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2929,10 +2929,10 @@
         <v>2021</v>
       </c>
       <c r="C182" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D182" s="3">
-        <v>1.1092</v>
+        <v>1.0382</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2943,10 +2943,10 @@
         <v>2021</v>
       </c>
       <c r="C183" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D183" s="3">
-        <v>0.93130000000000002</v>
+        <v>1.4381999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2957,10 +2957,10 @@
         <v>2021</v>
       </c>
       <c r="C184" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D184" s="3">
-        <v>1.4892000000000001</v>
+        <v>1.1092</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2971,10 +2971,10 @@
         <v>2021</v>
       </c>
       <c r="C185" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D185" s="3">
-        <v>1.1386000000000001</v>
+        <v>0.93130000000000002</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2985,10 +2985,10 @@
         <v>2021</v>
       </c>
       <c r="C186" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D186" s="3">
-        <v>1.1675</v>
+        <v>1.4892000000000001</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2999,10 +2999,10 @@
         <v>2021</v>
       </c>
       <c r="C187" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D187" s="3">
-        <v>1.2996000000000001</v>
+        <v>1.1386000000000001</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3013,10 +3013,10 @@
         <v>2021</v>
       </c>
       <c r="C188" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D188" s="3">
-        <v>1.0663</v>
+        <v>1.1675</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3024,13 +3024,13 @@
         <v>6</v>
       </c>
       <c r="B189" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C189" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D189" s="3">
-        <v>1.0550999999999999</v>
+        <v>1.2996000000000001</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3038,13 +3038,13 @@
         <v>6</v>
       </c>
       <c r="B190" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C190" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D190" s="3">
-        <v>1.0621</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3055,10 +3055,10 @@
         <v>2022</v>
       </c>
       <c r="C191" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D191" s="3">
-        <v>1.0516000000000001</v>
+        <v>1.0550999999999999</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3069,10 +3069,10 @@
         <v>2022</v>
       </c>
       <c r="C192" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D192" s="3">
-        <v>1.0001</v>
+        <v>1.0621</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3083,10 +3083,10 @@
         <v>2022</v>
       </c>
       <c r="C193" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D193" s="3">
-        <v>1.4765999999999999</v>
+        <v>1.0516000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3097,10 +3097,10 @@
         <v>2022</v>
       </c>
       <c r="C194" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D194" s="3">
-        <v>1.0939000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3111,10 +3111,10 @@
         <v>2022</v>
       </c>
       <c r="C195" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D195" s="3">
-        <v>1.2916000000000001</v>
+        <v>1.4765999999999999</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3125,10 +3125,10 @@
         <v>2022</v>
       </c>
       <c r="C196" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D196" s="3">
-        <v>1.2714000000000001</v>
+        <v>1.0939000000000001</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3139,10 +3139,10 @@
         <v>2022</v>
       </c>
       <c r="C197" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D197" s="3">
-        <v>1.2466999999999999</v>
+        <v>1.2916000000000001</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3153,10 +3153,10 @@
         <v>2022</v>
       </c>
       <c r="C198" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D198" s="3">
-        <v>1.0482</v>
+        <v>1.2714000000000001</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3167,10 +3167,10 @@
         <v>2022</v>
       </c>
       <c r="C199" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D199" s="3">
-        <v>1.0491999999999999</v>
+        <v>1.2466999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3181,10 +3181,10 @@
         <v>2022</v>
       </c>
       <c r="C200" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D200" s="3">
-        <v>1.2296</v>
+        <v>1.0482</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3192,13 +3192,13 @@
         <v>6</v>
       </c>
       <c r="B201" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C201" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D201" s="3">
-        <v>1.2606999999999999</v>
+        <v>1.0491999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3206,13 +3206,13 @@
         <v>6</v>
       </c>
       <c r="B202" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C202" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D202" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.2296</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3223,10 +3223,10 @@
         <v>2023</v>
       </c>
       <c r="C203" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D203" s="3">
-        <v>1.5298</v>
+        <v>1.2606999999999999</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3237,10 +3237,10 @@
         <v>2023</v>
       </c>
       <c r="C204" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D204" s="3">
-        <v>1.1073</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3251,10 +3251,10 @@
         <v>2023</v>
       </c>
       <c r="C205" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D205" s="3">
-        <v>1.0602</v>
+        <v>1.5298</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3265,10 +3265,10 @@
         <v>2023</v>
       </c>
       <c r="C206" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D206" s="3">
-        <v>1.3539999999999999</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3279,10 +3279,10 @@
         <v>2023</v>
       </c>
       <c r="C207" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D207" s="3">
-        <v>1.3968</v>
+        <v>1.0602</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3293,10 +3293,10 @@
         <v>2023</v>
       </c>
       <c r="C208" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D208" s="3">
-        <v>1.2923</v>
+        <v>1.3539999999999999</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3307,10 +3307,10 @@
         <v>2023</v>
       </c>
       <c r="C209" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D209" s="3">
-        <v>1.0855999999999999</v>
+        <v>1.3968</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3321,10 +3321,10 @@
         <v>2023</v>
       </c>
       <c r="C210" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D210" s="3">
-        <v>1.2621</v>
+        <v>1.2923</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3335,10 +3335,10 @@
         <v>2023</v>
       </c>
       <c r="C211" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D211" s="3">
-        <v>1.1758</v>
+        <v>1.0855999999999999</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3349,10 +3349,10 @@
         <v>2023</v>
       </c>
       <c r="C212" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D212" s="3">
-        <v>1.3091999999999999</v>
+        <v>1.2621</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3360,13 +3360,13 @@
         <v>6</v>
       </c>
       <c r="B213" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C213" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D213" s="3">
-        <v>1.5447</v>
+        <v>1.1758</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3374,13 +3374,13 @@
         <v>6</v>
       </c>
       <c r="B214" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C214" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D214" s="3">
-        <v>1.087</v>
+        <v>1.3091999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3391,10 +3391,10 @@
         <v>2024</v>
       </c>
       <c r="C215" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" s="3">
-        <v>0.89500000000000002</v>
+        <v>1.5447</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3405,10 +3405,10 @@
         <v>2024</v>
       </c>
       <c r="C216" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D216" s="3">
-        <v>1.0757000000000001</v>
+        <v>1.087</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3419,10 +3419,10 @@
         <v>2024</v>
       </c>
       <c r="C217" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D217" s="3">
-        <v>1.2897000000000001</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3433,10 +3433,10 @@
         <v>2024</v>
       </c>
       <c r="C218" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D218" s="3">
-        <v>1.3664000000000001</v>
+        <v>1.0757000000000001</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3447,10 +3447,10 @@
         <v>2024</v>
       </c>
       <c r="C219" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D219" s="3">
-        <v>1.2185999999999999</v>
+        <v>1.2897000000000001</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3461,10 +3461,10 @@
         <v>2024</v>
       </c>
       <c r="C220" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D220" s="3">
-        <v>1.2690999999999999</v>
+        <v>1.3664000000000001</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3475,10 +3475,10 @@
         <v>2024</v>
       </c>
       <c r="C221" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D221" s="3">
-        <v>1.0383</v>
+        <v>1.2185999999999999</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>2024</v>
       </c>
       <c r="C222" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D222" s="3">
-        <v>1.1085</v>
+        <v>1.2690999999999999</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3503,10 +3503,10 @@
         <v>2024</v>
       </c>
       <c r="C223" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D223" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.0390999999999999</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3517,10 +3517,10 @@
         <v>2024</v>
       </c>
       <c r="C224" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D224" s="3">
-        <v>1.0940000000000001</v>
+        <v>1.1085</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3528,13 +3528,13 @@
         <v>6</v>
       </c>
       <c r="B225" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C225" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D225" s="3">
-        <v>0.94689999999999996</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3542,13 +3542,13 @@
         <v>6</v>
       </c>
       <c r="B226" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C226" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D226" s="3">
-        <v>0.95220000000000005</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3559,10 +3559,10 @@
         <v>2025</v>
       </c>
       <c r="C227" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D227" s="3">
-        <v>0.95209999999999995</v>
+        <v>0.94689999999999996</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3573,10 +3573,10 @@
         <v>2025</v>
       </c>
       <c r="C228" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D228" s="3">
-        <v>1.0407999999999999</v>
+        <v>0.95220000000000005</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3587,10 +3587,10 @@
         <v>2025</v>
       </c>
       <c r="C229" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D229" s="3">
-        <v>1.1001000000000001</v>
+        <v>0.95209999999999995</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3601,10 +3601,10 @@
         <v>2025</v>
       </c>
       <c r="C230" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D230" s="3">
-        <v>1.0804</v>
+        <v>1.0407999999999999</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3615,10 +3615,10 @@
         <v>2025</v>
       </c>
       <c r="C231" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D231" s="3">
-        <v>1.1061000000000001</v>
+        <v>1.1001000000000001</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3629,10 +3629,10 @@
         <v>2025</v>
       </c>
       <c r="C232" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D232" s="3">
-        <v>0.98920000000000008</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3643,10 +3643,10 @@
         <v>2025</v>
       </c>
       <c r="C233" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D233" s="3">
-        <v>1.1734</v>
+        <v>1.1061000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3657,10 +3657,10 @@
         <v>2025</v>
       </c>
       <c r="C234" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D234" s="3">
-        <v>0.94899999999999995</v>
+        <v>0.98920000000000008</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3671,10 +3671,10 @@
         <v>2025</v>
       </c>
       <c r="C235" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D235" s="3">
-        <v>1.0885</v>
+        <v>1.1734</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3685,10 +3685,10 @@
         <v>2025</v>
       </c>
       <c r="C236" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D236" s="3">
-        <v>1.0085999999999999</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3696,13 +3696,13 @@
         <v>6</v>
       </c>
       <c r="B237" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C237" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D237" s="3">
-        <v>0.98619999999999997</v>
+        <v>1.0885</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3710,13 +3710,13 @@
         <v>6</v>
       </c>
       <c r="B238" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C238" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D238" s="3">
-        <v>0.87270000000000003</v>
+        <v>1.0073000000000001</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3727,52 +3727,52 @@
         <v>2026</v>
       </c>
       <c r="C239" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D239" s="3">
-        <v>0.93989999999999996</v>
+        <v>0.98619999999999997</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B240" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C240" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D240" s="3">
-        <v>0.3634</v>
+        <v>0.87270000000000003</v>
       </c>
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B241" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C241" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D241" s="3">
-        <v>1.1855</v>
+        <v>0.93330000000000013</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B242" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C242" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D242" s="3">
-        <v>0.55079999999999996</v>
+        <v>0.89370000000000016</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3783,10 +3783,10 @@
         <v>2019</v>
       </c>
       <c r="C243" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D243" s="3">
-        <v>1.544</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3797,10 +3797,10 @@
         <v>2019</v>
       </c>
       <c r="C244" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D244" s="3">
-        <v>1.5068999999999997</v>
+        <v>1.1855</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3808,13 +3808,13 @@
         <v>7</v>
       </c>
       <c r="B245" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C245" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D245" s="3">
-        <v>0.94199999999999995</v>
+        <v>0.55079999999999996</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3822,13 +3822,13 @@
         <v>7</v>
       </c>
       <c r="B246" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C246" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D246" s="3">
-        <v>1.0011000000000001</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3836,13 +3836,13 @@
         <v>7</v>
       </c>
       <c r="B247" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C247" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D247" s="3">
-        <v>0.96850000000000003</v>
+        <v>1.5068999999999997</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3853,10 +3853,10 @@
         <v>2020</v>
       </c>
       <c r="C248" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D248" s="3">
-        <v>1.0559000000000001</v>
+        <v>0.94199999999999995</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3867,10 +3867,10 @@
         <v>2020</v>
       </c>
       <c r="C249" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D249" s="3">
-        <v>0.91450000000000009</v>
+        <v>1.0011000000000001</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3881,10 +3881,10 @@
         <v>2020</v>
       </c>
       <c r="C250" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D250" s="3">
-        <v>1.0116000000000001</v>
+        <v>0.96850000000000003</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3895,10 +3895,10 @@
         <v>2020</v>
       </c>
       <c r="C251" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D251" s="3">
-        <v>1.3797999999999999</v>
+        <v>1.0559000000000001</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3909,10 +3909,10 @@
         <v>2020</v>
       </c>
       <c r="C252" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3">
-        <v>1.4618</v>
+        <v>0.91450000000000009</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3923,10 +3923,10 @@
         <v>2020</v>
       </c>
       <c r="C253" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D253" s="3">
-        <v>1.2636000000000001</v>
+        <v>1.0116000000000001</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3937,10 +3937,10 @@
         <v>2020</v>
       </c>
       <c r="C254" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D254" s="3">
-        <v>1.0907</v>
+        <v>1.3797999999999999</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3951,10 +3951,10 @@
         <v>2020</v>
       </c>
       <c r="C255" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D255" s="3">
-        <v>1.1226</v>
+        <v>1.4618</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3965,10 +3965,10 @@
         <v>2020</v>
       </c>
       <c r="C256" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D256" s="3">
-        <v>1.1798999999999999</v>
+        <v>1.2636000000000001</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3976,13 +3976,13 @@
         <v>7</v>
       </c>
       <c r="B257" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C257" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D257" s="3">
-        <v>1.3149999999999999</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3990,13 +3990,13 @@
         <v>7</v>
       </c>
       <c r="B258" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C258" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D258" s="3">
-        <v>1.2918000000000001</v>
+        <v>1.1226</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4004,13 +4004,13 @@
         <v>7</v>
       </c>
       <c r="B259" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C259" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D259" s="3">
-        <v>1.3935</v>
+        <v>1.1798999999999999</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4021,10 +4021,10 @@
         <v>2021</v>
       </c>
       <c r="C260" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D260" s="3">
-        <v>1.6409</v>
+        <v>1.3149999999999999</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4035,10 +4035,10 @@
         <v>2021</v>
       </c>
       <c r="C261" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D261" s="3">
-        <v>1.5944</v>
+        <v>1.2918000000000001</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4049,10 +4049,10 @@
         <v>2021</v>
       </c>
       <c r="C262" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D262" s="3">
-        <v>1.5669999999999999</v>
+        <v>1.3935</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4063,10 +4063,10 @@
         <v>2021</v>
       </c>
       <c r="C263" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D263" s="3">
-        <v>1.276</v>
+        <v>1.6409</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4077,10 +4077,10 @@
         <v>2021</v>
       </c>
       <c r="C264" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D264" s="3">
-        <v>1.1046</v>
+        <v>1.5944</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4091,10 +4091,10 @@
         <v>2021</v>
       </c>
       <c r="C265" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D265" s="3">
-        <v>1.0746</v>
+        <v>1.5669999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4105,10 +4105,10 @@
         <v>2021</v>
       </c>
       <c r="C266" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D266" s="3">
-        <v>0.95230000000000004</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4119,10 +4119,10 @@
         <v>2021</v>
       </c>
       <c r="C267" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D267" s="3">
-        <v>0.93070000000000008</v>
+        <v>1.1046</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4133,10 +4133,10 @@
         <v>2021</v>
       </c>
       <c r="C268" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D268" s="3">
-        <v>1.0242</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4144,13 +4144,13 @@
         <v>7</v>
       </c>
       <c r="B269" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C269" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D269" s="3">
-        <v>0.95179999999999998</v>
+        <v>0.95230000000000004</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4158,13 +4158,13 @@
         <v>7</v>
       </c>
       <c r="B270" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C270" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D270" s="3">
-        <v>1.1564000000000001</v>
+        <v>0.93070000000000008</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4172,13 +4172,13 @@
         <v>7</v>
       </c>
       <c r="B271" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C271" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D271" s="3">
-        <v>0.93640000000000001</v>
+        <v>1.0242</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4189,10 +4189,10 @@
         <v>2022</v>
       </c>
       <c r="C272" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D272" s="3">
-        <v>0.86789999999999989</v>
+        <v>0.95179999999999998</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4203,10 +4203,10 @@
         <v>2022</v>
       </c>
       <c r="C273" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D273" s="3">
-        <v>0.89589999999999992</v>
+        <v>1.1564000000000001</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4217,10 +4217,10 @@
         <v>2022</v>
       </c>
       <c r="C274" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D274" s="3">
-        <v>0.97230000000000005</v>
+        <v>0.93640000000000001</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4231,10 +4231,10 @@
         <v>2022</v>
       </c>
       <c r="C275" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D275" s="3">
-        <v>1.0585</v>
+        <v>0.86789999999999989</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4245,10 +4245,10 @@
         <v>2022</v>
       </c>
       <c r="C276" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D276" s="3">
-        <v>0.91169999999999995</v>
+        <v>0.89589999999999992</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4259,10 +4259,10 @@
         <v>2022</v>
       </c>
       <c r="C277" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D277" s="3">
-        <v>0.77860000000000007</v>
+        <v>0.97230000000000005</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4273,10 +4273,10 @@
         <v>2022</v>
       </c>
       <c r="C278" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D278" s="3">
-        <v>0.98480000000000001</v>
+        <v>1.0585</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4287,10 +4287,10 @@
         <v>2022</v>
       </c>
       <c r="C279" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D279" s="3">
-        <v>0.96220000000000006</v>
+        <v>0.91169999999999995</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4301,10 +4301,10 @@
         <v>2022</v>
       </c>
       <c r="C280" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D280" s="3">
-        <v>0.89329999999999998</v>
+        <v>0.77860000000000007</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4312,13 +4312,13 @@
         <v>7</v>
       </c>
       <c r="B281" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C281" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D281" s="3">
-        <v>0.99390000000000001</v>
+        <v>0.98480000000000001</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4326,13 +4326,13 @@
         <v>7</v>
       </c>
       <c r="B282" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C282" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D282" s="3">
-        <v>1.0999000000000001</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4340,13 +4340,13 @@
         <v>7</v>
       </c>
       <c r="B283" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C283" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D283" s="3">
-        <v>1.1256999999999999</v>
+        <v>0.89329999999999998</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4357,10 +4357,10 @@
         <v>2023</v>
       </c>
       <c r="C284" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D284" s="3">
-        <v>1.0003</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4371,10 +4371,10 @@
         <v>2023</v>
       </c>
       <c r="C285" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D285" s="3">
-        <v>1.1068</v>
+        <v>1.0999000000000001</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4385,10 +4385,10 @@
         <v>2023</v>
       </c>
       <c r="C286" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D286" s="3">
-        <v>1.0865</v>
+        <v>1.1256999999999999</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4399,10 +4399,10 @@
         <v>2023</v>
       </c>
       <c r="C287" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D287" s="3">
-        <v>0.97589999999999999</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4413,10 +4413,10 @@
         <v>2023</v>
       </c>
       <c r="C288" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D288" s="3">
-        <v>1.0511999999999999</v>
+        <v>1.1068</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4427,10 +4427,10 @@
         <v>2023</v>
       </c>
       <c r="C289" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D289" s="3">
-        <v>1.0577000000000001</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4441,10 +4441,10 @@
         <v>2023</v>
       </c>
       <c r="C290" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D290" s="3">
-        <v>0.97499999999999987</v>
+        <v>0.97589999999999999</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4455,10 +4455,10 @@
         <v>2023</v>
       </c>
       <c r="C291" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D291" s="3">
-        <v>1.0082</v>
+        <v>1.0511999999999999</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4469,10 +4469,10 @@
         <v>2023</v>
       </c>
       <c r="C292" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D292" s="3">
-        <v>1.0295000000000001</v>
+        <v>1.0577000000000001</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4480,13 +4480,13 @@
         <v>7</v>
       </c>
       <c r="B293" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C293" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D293" s="3">
-        <v>0.87479999999999991</v>
+        <v>0.97499999999999987</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4494,13 +4494,13 @@
         <v>7</v>
       </c>
       <c r="B294" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C294" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D294" s="3">
-        <v>0.8629</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4508,13 +4508,13 @@
         <v>7</v>
       </c>
       <c r="B295" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C295" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D295" s="3">
-        <v>0.87240000000000006</v>
+        <v>1.0295000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4525,10 +4525,10 @@
         <v>2024</v>
       </c>
       <c r="C296" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D296" s="3">
-        <v>1.1091</v>
+        <v>0.87479999999999991</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4539,10 +4539,10 @@
         <v>2024</v>
       </c>
       <c r="C297" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D297" s="3">
-        <v>1.0685</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4553,10 +4553,10 @@
         <v>2024</v>
       </c>
       <c r="C298" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D298" s="3">
-        <v>1.0423</v>
+        <v>0.87240000000000006</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4567,10 +4567,10 @@
         <v>2024</v>
       </c>
       <c r="C299" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D299" s="3">
-        <v>1.1042000000000001</v>
+        <v>1.1091</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4581,10 +4581,10 @@
         <v>2024</v>
       </c>
       <c r="C300" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D300" s="3">
-        <v>1.1225000000000001</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4595,10 +4595,10 @@
         <v>2024</v>
       </c>
       <c r="C301" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D301" s="3">
-        <v>1.2110000000000001</v>
+        <v>1.0423</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4609,10 +4609,10 @@
         <v>2024</v>
       </c>
       <c r="C302" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D302" s="3">
-        <v>1.2477</v>
+        <v>1.1042000000000001</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4623,10 +4623,10 @@
         <v>2024</v>
       </c>
       <c r="C303" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D303" s="3">
-        <v>1.1498999999999999</v>
+        <v>1.1225000000000001</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4637,10 +4637,10 @@
         <v>2024</v>
       </c>
       <c r="C304" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D304" s="3">
-        <v>1.2698</v>
+        <v>1.2110000000000001</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4648,13 +4648,13 @@
         <v>7</v>
       </c>
       <c r="B305" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C305" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D305" s="3">
-        <v>1.0690999999999999</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4662,13 +4662,13 @@
         <v>7</v>
       </c>
       <c r="B306" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C306" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D306" s="3">
-        <v>1.0788</v>
+        <v>1.1498999999999999</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4676,13 +4676,13 @@
         <v>7</v>
       </c>
       <c r="B307" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C307" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D307" s="3">
-        <v>1.206</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4693,10 +4693,10 @@
         <v>2025</v>
       </c>
       <c r="C308" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D308" s="3">
-        <v>1.1214999999999999</v>
+        <v>1.0690999999999999</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4707,10 +4707,10 @@
         <v>2025</v>
       </c>
       <c r="C309" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D309" s="3">
-        <v>1.1589</v>
+        <v>1.0788</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4721,10 +4721,10 @@
         <v>2025</v>
       </c>
       <c r="C310" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D310" s="3">
-        <v>1.2847999999999999</v>
+        <v>1.206</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4735,10 +4735,10 @@
         <v>2025</v>
       </c>
       <c r="C311" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D311" s="3">
-        <v>1.3216000000000001</v>
+        <v>1.1214999999999999</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4749,10 +4749,10 @@
         <v>2025</v>
       </c>
       <c r="C312" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D312" s="3">
-        <v>1.1874</v>
+        <v>1.1348</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4763,10 +4763,10 @@
         <v>2025</v>
       </c>
       <c r="C313" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D313" s="3">
-        <v>1.1946000000000001</v>
+        <v>1.2157000000000002</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4777,10 +4777,10 @@
         <v>2025</v>
       </c>
       <c r="C314" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D314" s="3">
-        <v>1.355</v>
+        <v>1.3216000000000001</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4791,10 +4791,10 @@
         <v>2025</v>
       </c>
       <c r="C315" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D315" s="3">
-        <v>1.3225</v>
+        <v>1.1874</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4805,10 +4805,10 @@
         <v>2025</v>
       </c>
       <c r="C316" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D316" s="3">
-        <v>1.1868000000000001</v>
+        <v>1.1946000000000001</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4816,13 +4816,13 @@
         <v>7</v>
       </c>
       <c r="B317" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C317" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D317" s="3">
-        <v>1.1228</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4830,13 +4830,13 @@
         <v>7</v>
       </c>
       <c r="B318" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C318" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D318" s="3">
-        <v>1.2611000000000001</v>
+        <v>1.3223</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4844,69 +4844,69 @@
         <v>7</v>
       </c>
       <c r="B319" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C319" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D319" s="3">
-        <v>1.8919999999999999</v>
+        <v>1.1866000000000001</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B320" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C320" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D320" s="3">
-        <v>0.46260000000000001</v>
+        <v>1.1228</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B321" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C321" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D321" s="3">
-        <v>2.5009999999999999</v>
+        <v>1.2611000000000001</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B322" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C322" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D322" s="3">
-        <v>0.60919999999999996</v>
+        <v>1.8692</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B323" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C323" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D323" s="3">
-        <v>0.43890000000000001</v>
+        <v>1.2091000000000001</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4914,13 +4914,13 @@
         <v>8</v>
       </c>
       <c r="B324" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C324" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D324" s="3">
-        <v>0.58919999999999995</v>
+        <v>0.46260000000000001</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4928,13 +4928,13 @@
         <v>8</v>
       </c>
       <c r="B325" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C325" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D325" s="3">
-        <v>1.8193999999999997</v>
+        <v>2.5009999999999999</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4942,13 +4942,13 @@
         <v>8</v>
       </c>
       <c r="B326" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C326" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D326" s="3">
-        <v>1.2989999999999999</v>
+        <v>0.60919999999999996</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4959,10 +4959,10 @@
         <v>2020</v>
       </c>
       <c r="C327" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D327" s="3">
-        <v>1.3857999999999999</v>
+        <v>0.43890000000000001</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4973,10 +4973,10 @@
         <v>2020</v>
       </c>
       <c r="C328" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D328" s="3">
-        <v>1.9608000000000001</v>
+        <v>0.58919999999999995</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4987,10 +4987,10 @@
         <v>2020</v>
       </c>
       <c r="C329" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D329" s="3">
-        <v>1.8338000000000001</v>
+        <v>1.8193999999999997</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5001,10 +5001,10 @@
         <v>2020</v>
       </c>
       <c r="C330" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D330" s="3">
-        <v>1.7322999999999997</v>
+        <v>1.2989999999999999</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5015,10 +5015,10 @@
         <v>2020</v>
       </c>
       <c r="C331" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D331" s="3">
-        <v>1.8411999999999999</v>
+        <v>1.3857999999999999</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5029,10 +5029,10 @@
         <v>2020</v>
       </c>
       <c r="C332" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D332" s="3">
-        <v>1.8994</v>
+        <v>1.9608000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5043,10 +5043,10 @@
         <v>2020</v>
       </c>
       <c r="C333" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D333" s="3">
-        <v>1.7765999999999997</v>
+        <v>1.8338000000000001</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5054,13 +5054,13 @@
         <v>8</v>
       </c>
       <c r="B334" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C334" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D334" s="3">
-        <v>1.5302</v>
+        <v>1.7322999999999997</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5068,13 +5068,13 @@
         <v>8</v>
       </c>
       <c r="B335" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C335" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D335" s="3">
-        <v>1.7687000000000002</v>
+        <v>1.8411999999999999</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5082,13 +5082,13 @@
         <v>8</v>
       </c>
       <c r="B336" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C336" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D336" s="3">
-        <v>1.3537999999999999</v>
+        <v>1.8994</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5096,13 +5096,13 @@
         <v>8</v>
       </c>
       <c r="B337" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C337" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D337" s="3">
-        <v>1.1635</v>
+        <v>1.7765999999999997</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5113,10 +5113,10 @@
         <v>2021</v>
       </c>
       <c r="C338" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D338" s="3">
-        <v>1.9408000000000003</v>
+        <v>1.5302</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5127,10 +5127,10 @@
         <v>2021</v>
       </c>
       <c r="C339" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D339" s="3">
-        <v>1.2329000000000001</v>
+        <v>1.7687000000000002</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5141,10 +5141,10 @@
         <v>2021</v>
       </c>
       <c r="C340" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D340" s="3">
-        <v>1.3947000000000001</v>
+        <v>1.3537999999999999</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5155,10 +5155,10 @@
         <v>2021</v>
       </c>
       <c r="C341" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D341" s="3">
-        <v>1.323</v>
+        <v>1.1635</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5169,10 +5169,10 @@
         <v>2021</v>
       </c>
       <c r="C342" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D342" s="3">
-        <v>1.4914000000000001</v>
+        <v>1.9408000000000003</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5183,10 +5183,10 @@
         <v>2021</v>
       </c>
       <c r="C343" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D343" s="3">
-        <v>1.4085000000000001</v>
+        <v>1.2329000000000001</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5197,10 +5197,10 @@
         <v>2021</v>
       </c>
       <c r="C344" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D344" s="3">
-        <v>1.429</v>
+        <v>1.3947000000000001</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5211,10 +5211,10 @@
         <v>2021</v>
       </c>
       <c r="C345" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D345" s="3">
-        <v>1.3602000000000001</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5222,13 +5222,13 @@
         <v>8</v>
       </c>
       <c r="B346" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C346" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D346" s="3">
-        <v>1.4053</v>
+        <v>1.4914000000000001</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5236,13 +5236,13 @@
         <v>8</v>
       </c>
       <c r="B347" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C347" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D347" s="3">
-        <v>1.4612000000000001</v>
+        <v>1.4085000000000001</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5250,13 +5250,13 @@
         <v>8</v>
       </c>
       <c r="B348" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C348" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D348" s="3">
-        <v>1.4157999999999999</v>
+        <v>1.429</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5264,13 +5264,13 @@
         <v>8</v>
       </c>
       <c r="B349" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C349" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D349" s="3">
-        <v>1.4791999999999998</v>
+        <v>1.3602000000000001</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5281,10 +5281,10 @@
         <v>2022</v>
       </c>
       <c r="C350" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D350" s="3">
-        <v>1.4762999999999999</v>
+        <v>1.4053</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5295,10 +5295,10 @@
         <v>2022</v>
       </c>
       <c r="C351" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D351" s="3">
-        <v>1.4380999999999999</v>
+        <v>1.4612000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5309,10 +5309,10 @@
         <v>2022</v>
       </c>
       <c r="C352" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D352" s="3">
-        <v>1.6324000000000001</v>
+        <v>1.4157999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5323,10 +5323,10 @@
         <v>2022</v>
       </c>
       <c r="C353" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D353" s="3">
-        <v>1.5557000000000001</v>
+        <v>1.4791999999999998</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5337,10 +5337,10 @@
         <v>2022</v>
       </c>
       <c r="C354" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D354" s="3">
-        <v>1.599</v>
+        <v>1.4762999999999999</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5351,10 +5351,10 @@
         <v>2022</v>
       </c>
       <c r="C355" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D355" s="3">
-        <v>1.4990000000000001</v>
+        <v>1.4380999999999999</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5365,10 +5365,10 @@
         <v>2022</v>
       </c>
       <c r="C356" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D356" s="3">
-        <v>1.484</v>
+        <v>1.6324000000000001</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5379,10 +5379,10 @@
         <v>2022</v>
       </c>
       <c r="C357" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D357" s="3">
-        <v>1.5085999999999999</v>
+        <v>1.5557000000000001</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5390,13 +5390,13 @@
         <v>8</v>
       </c>
       <c r="B358" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C358" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D358" s="3">
-        <v>1.4896</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5404,13 +5404,13 @@
         <v>8</v>
       </c>
       <c r="B359" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C359" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D359" s="3">
-        <v>1.5462999999999998</v>
+        <v>1.4990000000000001</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5418,13 +5418,13 @@
         <v>8</v>
       </c>
       <c r="B360" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C360" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D360" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5432,13 +5432,13 @@
         <v>8</v>
       </c>
       <c r="B361" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C361" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D361" s="3">
-        <v>1.3847</v>
+        <v>1.5085999999999999</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5449,10 +5449,10 @@
         <v>2023</v>
       </c>
       <c r="C362" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D362" s="3">
-        <v>1.2858000000000001</v>
+        <v>1.4896</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5463,10 +5463,10 @@
         <v>2023</v>
       </c>
       <c r="C363" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D363" s="3">
-        <v>1.8708</v>
+        <v>1.5462999999999998</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5477,10 +5477,10 @@
         <v>2023</v>
       </c>
       <c r="C364" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D364" s="3">
-        <v>1.8864000000000001</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5491,10 +5491,10 @@
         <v>2023</v>
       </c>
       <c r="C365" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D365" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.3847</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5505,10 +5505,10 @@
         <v>2023</v>
       </c>
       <c r="C366" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D366" s="3">
-        <v>1.9263999999999999</v>
+        <v>1.2858000000000001</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5519,10 +5519,10 @@
         <v>2023</v>
       </c>
       <c r="C367" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D367" s="3">
-        <v>1.9342999999999999</v>
+        <v>1.8708</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5533,10 +5533,10 @@
         <v>2023</v>
       </c>
       <c r="C368" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D368" s="3">
-        <v>1.7403999999999999</v>
+        <v>1.8864000000000001</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5547,10 +5547,10 @@
         <v>2023</v>
       </c>
       <c r="C369" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D369" s="3">
-        <v>1.7998000000000001</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5558,13 +5558,13 @@
         <v>8</v>
       </c>
       <c r="B370" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C370" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D370" s="3">
-        <v>1.8641000000000001</v>
+        <v>1.9263999999999999</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5572,13 +5572,13 @@
         <v>8</v>
       </c>
       <c r="B371" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C371" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D371" s="3">
-        <v>2.0535999999999999</v>
+        <v>1.9342999999999999</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5586,13 +5586,13 @@
         <v>8</v>
       </c>
       <c r="B372" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C372" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D372" s="3">
-        <v>1.8251999999999999</v>
+        <v>1.7403999999999999</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5600,13 +5600,13 @@
         <v>8</v>
       </c>
       <c r="B373" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C373" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D373" s="3">
-        <v>1.8498000000000001</v>
+        <v>1.7998000000000001</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5617,10 +5617,10 @@
         <v>2024</v>
       </c>
       <c r="C374" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D374" s="3">
-        <v>1.8720000000000001</v>
+        <v>1.8641000000000001</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5631,10 +5631,10 @@
         <v>2024</v>
       </c>
       <c r="C375" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D375" s="3">
-        <v>1.8865000000000001</v>
+        <v>2.0535999999999999</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5645,10 +5645,10 @@
         <v>2024</v>
       </c>
       <c r="C376" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D376" s="3">
-        <v>1.6568000000000001</v>
+        <v>1.8251999999999999</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5659,10 +5659,10 @@
         <v>2024</v>
       </c>
       <c r="C377" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D377" s="3">
-        <v>1.8308</v>
+        <v>1.8498000000000001</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5673,10 +5673,10 @@
         <v>2024</v>
       </c>
       <c r="C378" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="3">
-        <v>1.8855</v>
+        <v>1.8720000000000001</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5687,10 +5687,10 @@
         <v>2024</v>
       </c>
       <c r="C379" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D379" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.8865000000000001</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5701,10 +5701,10 @@
         <v>2024</v>
       </c>
       <c r="C380" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D380" s="3">
-        <v>1.8120000000000001</v>
+        <v>1.6568000000000001</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5715,10 +5715,10 @@
         <v>2024</v>
       </c>
       <c r="C381" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D381" s="3">
-        <v>1.7609999999999999</v>
+        <v>1.8308</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5726,13 +5726,13 @@
         <v>8</v>
       </c>
       <c r="B382" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C382" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D382" s="3">
-        <v>1.7804</v>
+        <v>1.8855</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5740,13 +5740,13 @@
         <v>8</v>
       </c>
       <c r="B383" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C383" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D383" s="3">
-        <v>1.6732</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5754,13 +5754,13 @@
         <v>8</v>
       </c>
       <c r="B384" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C384" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D384" s="3">
-        <v>1.7315</v>
+        <v>1.8120000000000001</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5768,13 +5768,13 @@
         <v>8</v>
       </c>
       <c r="B385" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C385" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D385" s="3">
-        <v>1.4521999999999999</v>
+        <v>1.7609999999999999</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5785,10 +5785,10 @@
         <v>2025</v>
       </c>
       <c r="C386" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D386" s="3">
-        <v>1.4100999999999999</v>
+        <v>1.7804</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5799,10 +5799,10 @@
         <v>2025</v>
       </c>
       <c r="C387" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D387" s="3">
-        <v>1.5999000000000001</v>
+        <v>1.6728000000000001</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5813,10 +5813,10 @@
         <v>2025</v>
       </c>
       <c r="C388" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D388" s="3">
-        <v>1.5866</v>
+        <v>1.7315</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5827,10 +5827,10 @@
         <v>2025</v>
       </c>
       <c r="C389" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D389" s="3">
-        <v>1.5342</v>
+        <v>1.4521999999999999</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5841,10 +5841,10 @@
         <v>2025</v>
       </c>
       <c r="C390" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D390" s="3">
-        <v>1.5347999999999999</v>
+        <v>1.4100999999999999</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5855,10 +5855,10 @@
         <v>2025</v>
       </c>
       <c r="C391" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D391" s="3">
-        <v>1.5016</v>
+        <v>1.5999000000000001</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5869,10 +5869,10 @@
         <v>2025</v>
       </c>
       <c r="C392" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D392" s="3">
-        <v>1.7338</v>
+        <v>1.5866</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5883,10 +5883,10 @@
         <v>2025</v>
       </c>
       <c r="C393" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3">
-        <v>1.7231000000000003</v>
+        <v>1.5343</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5894,13 +5894,13 @@
         <v>8</v>
       </c>
       <c r="B394" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C394" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D394" s="3">
-        <v>1.4159999999999999</v>
+        <v>1.5347</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5908,13 +5908,13 @@
         <v>8</v>
       </c>
       <c r="B395" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C395" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D395" s="3">
-        <v>1.6003000000000001</v>
+        <v>1.5016</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5922,83 +5922,83 @@
         <v>8</v>
       </c>
       <c r="B396" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C396" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D396" s="3">
-        <v>1.4630000000000001</v>
+        <v>1.7339</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B397" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C397" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D397" s="3">
-        <v>1.1920999999999999</v>
+        <v>1.7327999999999999</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B398" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C398" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3">
-        <v>0.9788</v>
+        <v>1.4160999999999999</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B399" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C399" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D399" s="3">
-        <v>1.3588</v>
+        <v>1.5978000000000003</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B400" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C400" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D400" s="3">
-        <v>1.3531</v>
+        <v>1.4392</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B401" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C401" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D401" s="3">
-        <v>1.4061999999999999</v>
+        <v>1.3847</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6009,10 +6009,10 @@
         <v>2019</v>
       </c>
       <c r="C402" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D402" s="3">
-        <v>1.1672</v>
+        <v>1.1920999999999999</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6023,10 +6023,10 @@
         <v>2019</v>
       </c>
       <c r="C403" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D403" s="3">
-        <v>1.5024</v>
+        <v>0.9788</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6037,10 +6037,10 @@
         <v>2019</v>
       </c>
       <c r="C404" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D404" s="3">
-        <v>1.1561999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6048,13 +6048,13 @@
         <v>9</v>
       </c>
       <c r="B405" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C405" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D405" s="3">
-        <v>1.1536999999999999</v>
+        <v>1.3531</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6062,13 +6062,13 @@
         <v>9</v>
       </c>
       <c r="B406" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C406" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D406" s="3">
-        <v>1.0632999999999999</v>
+        <v>1.4061999999999999</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6076,13 +6076,13 @@
         <v>9</v>
       </c>
       <c r="B407" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C407" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D407" s="3">
-        <v>1.0150999999999999</v>
+        <v>1.1672</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6090,13 +6090,13 @@
         <v>9</v>
       </c>
       <c r="B408" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C408" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D408" s="3">
-        <v>1.1227</v>
+        <v>1.5024</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6104,13 +6104,13 @@
         <v>9</v>
       </c>
       <c r="B409" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C409" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D409" s="3">
-        <v>1.0437000000000001</v>
+        <v>1.1561999999999999</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6121,10 +6121,10 @@
         <v>2020</v>
       </c>
       <c r="C410" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D410" s="3">
-        <v>1.2843</v>
+        <v>1.1536999999999999</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6135,10 +6135,10 @@
         <v>2020</v>
       </c>
       <c r="C411" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D411" s="3">
-        <v>1.3385</v>
+        <v>1.0632999999999999</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6149,10 +6149,10 @@
         <v>2020</v>
       </c>
       <c r="C412" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D412" s="3">
-        <v>1.6960999999999999</v>
+        <v>1.0150999999999999</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6163,10 +6163,10 @@
         <v>2020</v>
       </c>
       <c r="C413" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D413" s="3">
-        <v>1.4695</v>
+        <v>1.1227</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6177,10 +6177,10 @@
         <v>2020</v>
       </c>
       <c r="C414" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D414" s="3">
-        <v>1.4509000000000001</v>
+        <v>1.0437000000000001</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6191,10 +6191,10 @@
         <v>2020</v>
       </c>
       <c r="C415" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D415" s="3">
-        <v>1.4291</v>
+        <v>1.2843</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6205,10 +6205,10 @@
         <v>2020</v>
       </c>
       <c r="C416" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D416" s="3">
-        <v>1.2766</v>
+        <v>1.3385</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6216,13 +6216,13 @@
         <v>9</v>
       </c>
       <c r="B417" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C417" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D417" s="3">
-        <v>1.2372000000000001</v>
+        <v>1.6960999999999999</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6230,13 +6230,13 @@
         <v>9</v>
       </c>
       <c r="B418" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C418" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D418" s="3">
-        <v>1.3984000000000001</v>
+        <v>1.4695</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6244,13 +6244,13 @@
         <v>9</v>
       </c>
       <c r="B419" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C419" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D419" s="3">
-        <v>1.2039</v>
+        <v>1.4509000000000001</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6258,13 +6258,13 @@
         <v>9</v>
       </c>
       <c r="B420" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C420" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D420" s="3">
-        <v>1.2987</v>
+        <v>1.4291</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6272,13 +6272,13 @@
         <v>9</v>
       </c>
       <c r="B421" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C421" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D421" s="3">
-        <v>1.2281</v>
+        <v>1.2766</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6289,10 +6289,10 @@
         <v>2021</v>
       </c>
       <c r="C422" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D422" s="3">
-        <v>1.3234999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6303,10 +6303,10 @@
         <v>2021</v>
       </c>
       <c r="C423" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D423" s="3">
-        <v>1.2829999999999999</v>
+        <v>1.3984000000000001</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6317,10 +6317,10 @@
         <v>2021</v>
       </c>
       <c r="C424" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D424" s="3">
-        <v>1.1142000000000001</v>
+        <v>1.2039</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6331,10 +6331,10 @@
         <v>2021</v>
       </c>
       <c r="C425" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D425" s="3">
-        <v>0.96379999999999988</v>
+        <v>1.2987</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6345,10 +6345,10 @@
         <v>2021</v>
       </c>
       <c r="C426" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D426" s="3">
-        <v>1.0775999999999999</v>
+        <v>1.2281</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6359,10 +6359,10 @@
         <v>2021</v>
       </c>
       <c r="C427" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D427" s="3">
-        <v>1.1780999999999999</v>
+        <v>1.3234999999999999</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6373,10 +6373,10 @@
         <v>2021</v>
       </c>
       <c r="C428" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D428" s="3">
-        <v>1.0859000000000001</v>
+        <v>1.2829999999999999</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6384,13 +6384,13 @@
         <v>9</v>
       </c>
       <c r="B429" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C429" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D429" s="3">
-        <v>1.1252</v>
+        <v>1.1142000000000001</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6398,13 +6398,13 @@
         <v>9</v>
       </c>
       <c r="B430" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C430" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D430" s="3">
-        <v>1.1546000000000001</v>
+        <v>0.96379999999999988</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6412,13 +6412,13 @@
         <v>9</v>
       </c>
       <c r="B431" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C431" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D431" s="3">
-        <v>1.0673999999999999</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6426,13 +6426,13 @@
         <v>9</v>
       </c>
       <c r="B432" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C432" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D432" s="3">
-        <v>1.1517999999999999</v>
+        <v>1.1780999999999999</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6440,13 +6440,13 @@
         <v>9</v>
       </c>
       <c r="B433" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C433" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D433" s="3">
-        <v>1.1574</v>
+        <v>1.0859000000000001</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6457,10 +6457,10 @@
         <v>2022</v>
       </c>
       <c r="C434" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D434" s="3">
-        <v>1.1416999999999999</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6471,10 +6471,10 @@
         <v>2022</v>
       </c>
       <c r="C435" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D435" s="3">
-        <v>1.2119</v>
+        <v>1.1546000000000001</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6485,10 +6485,10 @@
         <v>2022</v>
       </c>
       <c r="C436" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D436" s="3">
-        <v>1.1833</v>
+        <v>1.0673999999999999</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6499,10 +6499,10 @@
         <v>2022</v>
       </c>
       <c r="C437" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D437" s="3">
-        <v>1.2625</v>
+        <v>1.1517999999999999</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6513,10 +6513,10 @@
         <v>2022</v>
       </c>
       <c r="C438" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D438" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6527,10 +6527,10 @@
         <v>2022</v>
       </c>
       <c r="C439" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D439" s="3">
-        <v>1.2148000000000001</v>
+        <v>1.1416999999999999</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6541,10 +6541,10 @@
         <v>2022</v>
       </c>
       <c r="C440" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D440" s="3">
-        <v>1.1067</v>
+        <v>1.2119</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6552,13 +6552,13 @@
         <v>9</v>
       </c>
       <c r="B441" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C441" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D441" s="3">
-        <v>1.1968000000000001</v>
+        <v>1.1833</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6566,13 +6566,13 @@
         <v>9</v>
       </c>
       <c r="B442" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C442" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D442" s="3">
-        <v>1.032</v>
+        <v>1.2625</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6580,13 +6580,13 @@
         <v>9</v>
       </c>
       <c r="B443" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C443" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D443" s="3">
-        <v>1.0803</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6594,13 +6594,13 @@
         <v>9</v>
       </c>
       <c r="B444" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C444" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D444" s="3">
-        <v>1.1644000000000001</v>
+        <v>1.2148000000000001</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6608,13 +6608,13 @@
         <v>9</v>
       </c>
       <c r="B445" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C445" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D445" s="3">
-        <v>1.2673000000000001</v>
+        <v>1.1067</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6625,10 +6625,10 @@
         <v>2023</v>
       </c>
       <c r="C446" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D446" s="3">
-        <v>1.1983999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6639,10 +6639,10 @@
         <v>2023</v>
       </c>
       <c r="C447" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D447" s="3">
-        <v>1.3575999999999999</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6653,10 +6653,10 @@
         <v>2023</v>
       </c>
       <c r="C448" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D448" s="3">
-        <v>1.3444</v>
+        <v>1.0803</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6667,10 +6667,10 @@
         <v>2023</v>
       </c>
       <c r="C449" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D449" s="3">
-        <v>1.2949999999999999</v>
+        <v>1.1644000000000001</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6681,10 +6681,10 @@
         <v>2023</v>
       </c>
       <c r="C450" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D450" s="3">
-        <v>1.2145999999999999</v>
+        <v>1.2673000000000001</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6695,10 +6695,10 @@
         <v>2023</v>
       </c>
       <c r="C451" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D451" s="3">
-        <v>1.2192000000000001</v>
+        <v>1.1983999999999999</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6709,10 +6709,10 @@
         <v>2023</v>
       </c>
       <c r="C452" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D452" s="3">
-        <v>1.3759999999999999</v>
+        <v>1.3575999999999999</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6720,13 +6720,13 @@
         <v>9</v>
       </c>
       <c r="B453" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C453" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D453" s="3">
-        <v>1.3194999999999999</v>
+        <v>1.3444</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6734,13 +6734,13 @@
         <v>9</v>
       </c>
       <c r="B454" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C454" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D454" s="3">
-        <v>1.4132</v>
+        <v>1.2949999999999999</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6748,13 +6748,13 @@
         <v>9</v>
       </c>
       <c r="B455" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C455" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D455" s="3">
-        <v>1.6296000000000002</v>
+        <v>1.2145999999999999</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6762,13 +6762,13 @@
         <v>9</v>
       </c>
       <c r="B456" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C456" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D456" s="3">
-        <v>1.4339</v>
+        <v>1.2192000000000001</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6776,13 +6776,13 @@
         <v>9</v>
       </c>
       <c r="B457" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C457" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D457" s="3">
-        <v>1.2652000000000001</v>
+        <v>1.3759999999999999</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6793,10 +6793,10 @@
         <v>2024</v>
       </c>
       <c r="C458" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D458" s="3">
-        <v>1.4533</v>
+        <v>1.3194999999999999</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6807,10 +6807,10 @@
         <v>2024</v>
       </c>
       <c r="C459" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D459" s="3">
-        <v>1.3996999999999999</v>
+        <v>1.4132</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6821,10 +6821,10 @@
         <v>2024</v>
       </c>
       <c r="C460" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D460" s="3">
-        <v>1.2509999999999999</v>
+        <v>1.6296000000000002</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6835,10 +6835,10 @@
         <v>2024</v>
       </c>
       <c r="C461" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D461" s="3">
-        <v>1.2806999999999999</v>
+        <v>1.4339</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6849,10 +6849,10 @@
         <v>2024</v>
       </c>
       <c r="C462" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D462" s="3">
-        <v>1.2095</v>
+        <v>1.2652000000000001</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6863,10 +6863,10 @@
         <v>2024</v>
       </c>
       <c r="C463" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D463" s="3">
-        <v>1.2222999999999999</v>
+        <v>1.4533</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6877,10 +6877,10 @@
         <v>2024</v>
       </c>
       <c r="C464" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D464" s="3">
-        <v>1.2697000000000001</v>
+        <v>1.3996999999999999</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6888,13 +6888,13 @@
         <v>9</v>
       </c>
       <c r="B465" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C465" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D465" s="3">
-        <v>1.1957</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6902,13 +6902,13 @@
         <v>9</v>
       </c>
       <c r="B466" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C466" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D466" s="3">
-        <v>1.5154999999999998</v>
+        <v>1.2806999999999999</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6916,13 +6916,13 @@
         <v>9</v>
       </c>
       <c r="B467" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C467" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D467" s="3">
-        <v>1.2682</v>
+        <v>1.2095</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6930,13 +6930,13 @@
         <v>9</v>
       </c>
       <c r="B468" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C468" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D468" s="3">
-        <v>1.2907999999999999</v>
+        <v>1.2222999999999999</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6944,13 +6944,13 @@
         <v>9</v>
       </c>
       <c r="B469" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C469" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D469" s="3">
-        <v>1.2582</v>
+        <v>1.2697000000000001</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6961,10 +6961,10 @@
         <v>2025</v>
       </c>
       <c r="C470" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D470" s="3">
-        <v>1.3306</v>
+        <v>1.1957</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6975,10 +6975,10 @@
         <v>2025</v>
       </c>
       <c r="C471" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D471" s="3">
-        <v>1.4423999999999999</v>
+        <v>1.5154999999999998</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6989,10 +6989,10 @@
         <v>2025</v>
       </c>
       <c r="C472" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D472" s="3">
-        <v>1.3319000000000001</v>
+        <v>1.2682</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7003,10 +7003,10 @@
         <v>2025</v>
       </c>
       <c r="C473" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D473" s="3">
-        <v>1.3214999999999999</v>
+        <v>1.2907999999999999</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7017,10 +7017,10 @@
         <v>2025</v>
       </c>
       <c r="C474" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D474" s="3">
-        <v>1.4823</v>
+        <v>1.2582</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7031,10 +7031,10 @@
         <v>2025</v>
       </c>
       <c r="C475" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D475" s="3">
-        <v>1.3943000000000001</v>
+        <v>1.3306</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7045,10 +7045,10 @@
         <v>2025</v>
       </c>
       <c r="C476" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D476" s="3">
-        <v>1.4936999999999998</v>
+        <v>1.4423999999999999</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7056,13 +7056,13 @@
         <v>9</v>
       </c>
       <c r="B477" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C477" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D477" s="3">
-        <v>1.6764999999999999</v>
+        <v>1.3319000000000001</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7070,13 +7070,13 @@
         <v>9</v>
       </c>
       <c r="B478" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C478" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D478" s="3">
-        <v>1.5677000000000001</v>
+        <v>1.3214999999999999</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7084,97 +7084,97 @@
         <v>9</v>
       </c>
       <c r="B479" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C479" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D479" s="3">
-        <v>1.5886</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="480" spans="1:4">
       <c r="A480" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B480" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C480" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D480" s="3">
-        <v>1.8255999999999999</v>
+        <v>1.3943000000000001</v>
       </c>
     </row>
     <row r="481" spans="1:4">
       <c r="A481" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B481" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C481" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D481" s="3">
-        <v>2.1966999999999999</v>
+        <v>1.4936999999999998</v>
       </c>
     </row>
     <row r="482" spans="1:4">
       <c r="A482" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B482" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C482" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D482" s="3">
-        <v>0.69</v>
+        <v>1.6764999999999999</v>
       </c>
     </row>
     <row r="483" spans="1:4">
       <c r="A483" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B483" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C483" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D483" s="3">
-        <v>2.2656000000000001</v>
+        <v>1.5677000000000001</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B484" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C484" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D484" s="3">
-        <v>2.3290999999999999</v>
+        <v>1.5889</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B485" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C485" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D485" s="3">
-        <v>1.9074</v>
+        <v>1.6122000000000001</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7185,10 +7185,10 @@
         <v>2019</v>
       </c>
       <c r="C486" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D486" s="3">
-        <v>1.6099000000000001</v>
+        <v>1.8255999999999999</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7196,13 +7196,13 @@
         <v>10</v>
       </c>
       <c r="B487" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C487" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D487" s="3">
-        <v>1.2122999999999999</v>
+        <v>2.1966999999999999</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7210,13 +7210,13 @@
         <v>10</v>
       </c>
       <c r="B488" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C488" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D488" s="3">
-        <v>1.2574000000000001</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7224,13 +7224,13 @@
         <v>10</v>
       </c>
       <c r="B489" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C489" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D489" s="3">
-        <v>1.0529999999999999</v>
+        <v>2.2656000000000001</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7238,13 +7238,13 @@
         <v>10</v>
       </c>
       <c r="B490" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C490" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D490" s="3">
-        <v>1.3588</v>
+        <v>2.3290999999999999</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7252,13 +7252,13 @@
         <v>10</v>
       </c>
       <c r="B491" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C491" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D491" s="3">
-        <v>1.9334999999999998</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7266,13 +7266,13 @@
         <v>10</v>
       </c>
       <c r="B492" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C492" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D492" s="3">
-        <v>1.3191999999999997</v>
+        <v>1.6099000000000001</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7283,10 +7283,10 @@
         <v>2020</v>
       </c>
       <c r="C493" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D493" s="3">
-        <v>1.8477000000000001</v>
+        <v>1.2122999999999999</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7297,10 +7297,10 @@
         <v>2020</v>
       </c>
       <c r="C494" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D494" s="3">
-        <v>1.6778</v>
+        <v>1.2574000000000001</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7311,10 +7311,10 @@
         <v>2020</v>
       </c>
       <c r="C495" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D495" s="3">
-        <v>1.6319999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7325,10 +7325,10 @@
         <v>2020</v>
       </c>
       <c r="C496" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D496" s="3">
-        <v>2.4281999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7339,10 +7339,10 @@
         <v>2020</v>
       </c>
       <c r="C497" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D497" s="3">
-        <v>2.7423999999999999</v>
+        <v>1.9334999999999998</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7350,13 +7350,13 @@
         <v>10</v>
       </c>
       <c r="B498" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C498" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D498" s="3">
-        <v>1.9238999999999999</v>
+        <v>1.3191999999999997</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7364,13 +7364,13 @@
         <v>10</v>
       </c>
       <c r="B499" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C499" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D499" s="3">
-        <v>1.8746</v>
+        <v>1.8477000000000001</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7378,13 +7378,13 @@
         <v>10</v>
       </c>
       <c r="B500" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C500" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D500" s="3">
-        <v>2.1867999999999999</v>
+        <v>1.6778</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7392,13 +7392,13 @@
         <v>10</v>
       </c>
       <c r="B501" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C501" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D501" s="3">
-        <v>1.6684000000000003</v>
+        <v>1.6319999999999999</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7406,13 +7406,13 @@
         <v>10</v>
       </c>
       <c r="B502" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C502" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D502" s="3">
-        <v>1.8869</v>
+        <v>2.4281999999999999</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7420,13 +7420,13 @@
         <v>10</v>
       </c>
       <c r="B503" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C503" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D503" s="3">
-        <v>1.7607000000000002</v>
+        <v>2.7423999999999999</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7437,10 +7437,10 @@
         <v>2021</v>
       </c>
       <c r="C504" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D504" s="3">
-        <v>2.3298999999999999</v>
+        <v>1.9238999999999999</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7451,10 +7451,10 @@
         <v>2021</v>
       </c>
       <c r="C505" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D505" s="3">
-        <v>2.0569000000000002</v>
+        <v>1.8746</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7465,10 +7465,10 @@
         <v>2021</v>
       </c>
       <c r="C506" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D506" s="3">
-        <v>2.5038999999999998</v>
+        <v>2.1867999999999999</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7479,10 +7479,10 @@
         <v>2021</v>
       </c>
       <c r="C507" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D507" s="3">
-        <v>1.728</v>
+        <v>1.6684000000000003</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7493,10 +7493,10 @@
         <v>2021</v>
       </c>
       <c r="C508" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D508" s="3">
-        <v>1.7589999999999999</v>
+        <v>1.8869</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7507,10 +7507,10 @@
         <v>2021</v>
       </c>
       <c r="C509" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D509" s="3">
-        <v>1.9400000000000002</v>
+        <v>1.7607000000000002</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7518,13 +7518,13 @@
         <v>10</v>
       </c>
       <c r="B510" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C510" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D510" s="3">
-        <v>1.1923999999999999</v>
+        <v>2.3298999999999999</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7532,13 +7532,13 @@
         <v>10</v>
       </c>
       <c r="B511" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C511" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D511" s="3">
-        <v>1.5228999999999999</v>
+        <v>2.0569000000000002</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7546,13 +7546,13 @@
         <v>10</v>
       </c>
       <c r="B512" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C512" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D512" s="3">
-        <v>1.9296</v>
+        <v>2.5038999999999998</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7560,13 +7560,13 @@
         <v>10</v>
       </c>
       <c r="B513" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C513" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D513" s="3">
-        <v>1.5996999999999999</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -7574,13 +7574,13 @@
         <v>10</v>
       </c>
       <c r="B514" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C514" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D514" s="3">
-        <v>1.7376999999999998</v>
+        <v>1.7589999999999999</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7588,13 +7588,13 @@
         <v>10</v>
       </c>
       <c r="B515" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C515" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D515" s="3">
-        <v>1.6283000000000001</v>
+        <v>1.9400000000000002</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7605,10 +7605,10 @@
         <v>2022</v>
       </c>
       <c r="C516" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D516" s="3">
-        <v>1.6888000000000001</v>
+        <v>1.1923999999999999</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7619,10 +7619,10 @@
         <v>2022</v>
       </c>
       <c r="C517" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D517" s="3">
-        <v>1.7524</v>
+        <v>1.5228999999999999</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7633,10 +7633,10 @@
         <v>2022</v>
       </c>
       <c r="C518" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D518" s="3">
-        <v>1.8827</v>
+        <v>1.9296</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7647,10 +7647,10 @@
         <v>2022</v>
       </c>
       <c r="C519" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D519" s="3">
-        <v>1.52</v>
+        <v>1.5996999999999999</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7661,10 +7661,10 @@
         <v>2022</v>
       </c>
       <c r="C520" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D520" s="3">
-        <v>1.9222000000000001</v>
+        <v>1.7376999999999998</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7675,10 +7675,10 @@
         <v>2022</v>
       </c>
       <c r="C521" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D521" s="3">
-        <v>1.6540999999999999</v>
+        <v>1.6283000000000001</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7686,13 +7686,13 @@
         <v>10</v>
       </c>
       <c r="B522" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C522" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D522" s="3">
-        <v>1.6717000000000002</v>
+        <v>1.6888000000000001</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7700,13 +7700,13 @@
         <v>10</v>
       </c>
       <c r="B523" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C523" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D523" s="3">
-        <v>2.0114000000000001</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7714,13 +7714,13 @@
         <v>10</v>
       </c>
       <c r="B524" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C524" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D524" s="3">
-        <v>1.7808999999999999</v>
+        <v>1.8827</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7728,13 +7728,13 @@
         <v>10</v>
       </c>
       <c r="B525" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C525" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D525" s="3">
-        <v>1.6915</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7742,13 +7742,13 @@
         <v>10</v>
       </c>
       <c r="B526" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C526" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D526" s="3">
-        <v>1.8209</v>
+        <v>1.9222000000000001</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7756,13 +7756,13 @@
         <v>10</v>
       </c>
       <c r="B527" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C527" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D527" s="3">
-        <v>1.9435</v>
+        <v>1.6540999999999999</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7773,10 +7773,10 @@
         <v>2023</v>
       </c>
       <c r="C528" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D528" s="3">
-        <v>1.5912999999999999</v>
+        <v>1.6717000000000002</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7787,10 +7787,10 @@
         <v>2023</v>
       </c>
       <c r="C529" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D529" s="3">
-        <v>1.9621999999999999</v>
+        <v>2.0114000000000001</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7801,10 +7801,10 @@
         <v>2023</v>
       </c>
       <c r="C530" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D530" s="3">
-        <v>1.9907999999999999</v>
+        <v>1.7808999999999999</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7815,10 +7815,10 @@
         <v>2023</v>
       </c>
       <c r="C531" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D531" s="3">
-        <v>1.9017999999999999</v>
+        <v>1.6915</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7829,10 +7829,10 @@
         <v>2023</v>
       </c>
       <c r="C532" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D532" s="3">
-        <v>1.5719000000000001</v>
+        <v>1.8209</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7843,10 +7843,10 @@
         <v>2023</v>
       </c>
       <c r="C533" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D533" s="3">
-        <v>1.6617999999999999</v>
+        <v>1.9435</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7854,13 +7854,13 @@
         <v>10</v>
       </c>
       <c r="B534" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C534" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D534" s="3">
-        <v>1.9043000000000001</v>
+        <v>1.5912999999999999</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7868,13 +7868,13 @@
         <v>10</v>
       </c>
       <c r="B535" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C535" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D535" s="3">
-        <v>1.8562999999999998</v>
+        <v>1.9621999999999999</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7882,13 +7882,13 @@
         <v>10</v>
       </c>
       <c r="B536" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C536" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D536" s="3">
-        <v>1.6854</v>
+        <v>1.9907999999999999</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7896,13 +7896,13 @@
         <v>10</v>
       </c>
       <c r="B537" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C537" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D537" s="3">
-        <v>1.8065</v>
+        <v>1.9017999999999999</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7910,13 +7910,13 @@
         <v>10</v>
       </c>
       <c r="B538" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C538" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D538" s="3">
-        <v>1.7505999999999999</v>
+        <v>1.5719000000000001</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7924,13 +7924,13 @@
         <v>10</v>
       </c>
       <c r="B539" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C539" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D539" s="3">
-        <v>1.7563</v>
+        <v>1.6617999999999999</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7941,10 +7941,10 @@
         <v>2024</v>
       </c>
       <c r="C540" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D540" s="3">
-        <v>2.2259000000000002</v>
+        <v>1.9043000000000001</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7955,10 +7955,10 @@
         <v>2024</v>
       </c>
       <c r="C541" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D541" s="3">
-        <v>1.77</v>
+        <v>1.8562999999999998</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7969,10 +7969,10 @@
         <v>2024</v>
       </c>
       <c r="C542" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D542" s="3">
-        <v>1.8426999999999998</v>
+        <v>1.6854</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7983,10 +7983,10 @@
         <v>2024</v>
       </c>
       <c r="C543" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D543" s="3">
-        <v>1.8102</v>
+        <v>1.8065</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -7997,10 +7997,10 @@
         <v>2024</v>
       </c>
       <c r="C544" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D544" s="3">
-        <v>1.7421</v>
+        <v>1.7505999999999999</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8011,10 +8011,10 @@
         <v>2024</v>
       </c>
       <c r="C545" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D545" s="3">
-        <v>1.6943999999999999</v>
+        <v>1.7563</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8022,13 +8022,13 @@
         <v>10</v>
       </c>
       <c r="B546" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C546" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D546" s="3">
-        <v>1.6221000000000001</v>
+        <v>2.2259000000000002</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8036,13 +8036,13 @@
         <v>10</v>
       </c>
       <c r="B547" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C547" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D547" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8050,13 +8050,13 @@
         <v>10</v>
       </c>
       <c r="B548" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C548" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D548" s="3">
-        <v>1.7462</v>
+        <v>1.8426999999999998</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8064,13 +8064,13 @@
         <v>10</v>
       </c>
       <c r="B549" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C549" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D549" s="3">
-        <v>1.9338000000000002</v>
+        <v>1.8102</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8078,13 +8078,13 @@
         <v>10</v>
       </c>
       <c r="B550" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C550" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D550" s="3">
-        <v>1.9272</v>
+        <v>1.7421</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8092,13 +8092,13 @@
         <v>10</v>
       </c>
       <c r="B551" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C551" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D551" s="3">
-        <v>1.7902</v>
+        <v>1.6943999999999999</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8109,10 +8109,10 @@
         <v>2025</v>
       </c>
       <c r="C552" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D552" s="3">
-        <v>1.6865000000000001</v>
+        <v>1.6221000000000001</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8123,10 +8123,10 @@
         <v>2025</v>
       </c>
       <c r="C553" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D553" s="3">
-        <v>1.7938000000000001</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8137,10 +8137,10 @@
         <v>2025</v>
       </c>
       <c r="C554" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D554" s="3">
-        <v>1.732</v>
+        <v>1.7462</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8151,10 +8151,10 @@
         <v>2025</v>
       </c>
       <c r="C555" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D555" s="3">
-        <v>1.925</v>
+        <v>1.9338000000000002</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8165,10 +8165,10 @@
         <v>2025</v>
       </c>
       <c r="C556" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D556" s="3">
-        <v>1.9413</v>
+        <v>1.9272</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8179,10 +8179,10 @@
         <v>2025</v>
       </c>
       <c r="C557" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D557" s="3">
-        <v>1.7350000000000001</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8190,13 +8190,13 @@
         <v>10</v>
       </c>
       <c r="B558" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C558" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D558" s="3">
-        <v>1.6932</v>
+        <v>1.6865000000000001</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8204,13 +8204,13 @@
         <v>10</v>
       </c>
       <c r="B559" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C559" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D559" s="3">
-        <v>1.9579</v>
+        <v>1.7938000000000001</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8218,111 +8218,111 @@
         <v>10</v>
       </c>
       <c r="B560" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C560" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D560" s="3">
-        <v>1.7670999999999999</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B561" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C561" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D561" s="3">
-        <v>0.59160000000000001</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B562" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C562" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D562" s="3">
-        <v>0.71369999999999989</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B563" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C563" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D563" s="3">
-        <v>1.4662999999999999</v>
+        <v>1.7350000000000001</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B564" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C564" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D564" s="3">
-        <v>0.70140000000000002</v>
+        <v>1.6932</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B565" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C565" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D565" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.9579</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B566" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C566" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D566" s="3">
-        <v>1.2885</v>
+        <v>1.4839</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B567" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C567" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D567" s="3">
-        <v>0.97159999999999991</v>
+        <v>2.1160000000000001</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8333,10 +8333,10 @@
         <v>2019</v>
       </c>
       <c r="C568" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D568" s="3">
-        <v>0.59799999999999998</v>
+        <v>0.59160000000000001</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8344,13 +8344,13 @@
         <v>11</v>
       </c>
       <c r="B569" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C569" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D569" s="3">
-        <v>0.80840000000000001</v>
+        <v>0.71369999999999989</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8358,13 +8358,13 @@
         <v>11</v>
       </c>
       <c r="B570" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C570" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D570" s="3">
-        <v>0.57899999999999996</v>
+        <v>1.4662999999999999</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8372,13 +8372,13 @@
         <v>11</v>
       </c>
       <c r="B571" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C571" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D571" s="3">
-        <v>1.1052999999999999</v>
+        <v>0.70140000000000002</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8386,13 +8386,13 @@
         <v>11</v>
       </c>
       <c r="B572" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C572" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D572" s="3">
-        <v>0.77580000000000005</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8400,13 +8400,13 @@
         <v>11</v>
       </c>
       <c r="B573" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C573" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D573" s="3">
-        <v>1.0531999999999999</v>
+        <v>1.2885</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8414,13 +8414,13 @@
         <v>11</v>
       </c>
       <c r="B574" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C574" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D574" s="3">
-        <v>1.0923</v>
+        <v>0.97159999999999991</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8428,13 +8428,13 @@
         <v>11</v>
       </c>
       <c r="B575" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C575" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D575" s="3">
-        <v>1.2737000000000001</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8445,10 +8445,10 @@
         <v>2020</v>
       </c>
       <c r="C576" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D576" s="3">
-        <v>1.3653</v>
+        <v>0.80840000000000001</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8459,10 +8459,10 @@
         <v>2020</v>
       </c>
       <c r="C577" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D577" s="3">
-        <v>1.1208</v>
+        <v>0.57899999999999996</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8473,10 +8473,10 @@
         <v>2020</v>
       </c>
       <c r="C578" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D578" s="3">
-        <v>1.5089999999999999</v>
+        <v>1.1052999999999999</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8487,10 +8487,10 @@
         <v>2020</v>
       </c>
       <c r="C579" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D579" s="3">
-        <v>1.2372000000000001</v>
+        <v>0.77580000000000005</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8501,10 +8501,10 @@
         <v>2020</v>
       </c>
       <c r="C580" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D580" s="3">
-        <v>1.0697000000000001</v>
+        <v>1.0531999999999999</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8512,13 +8512,13 @@
         <v>11</v>
       </c>
       <c r="B581" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C581" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D581" s="3">
-        <v>1.2351000000000001</v>
+        <v>1.0923</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8526,13 +8526,13 @@
         <v>11</v>
       </c>
       <c r="B582" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C582" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D582" s="3">
-        <v>1.1274</v>
+        <v>1.2737000000000001</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8540,13 +8540,13 @@
         <v>11</v>
       </c>
       <c r="B583" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C583" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D583" s="3">
-        <v>1.3996</v>
+        <v>1.3653</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8554,13 +8554,13 @@
         <v>11</v>
       </c>
       <c r="B584" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C584" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D584" s="3">
-        <v>1.2915000000000001</v>
+        <v>1.1208</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8568,13 +8568,13 @@
         <v>11</v>
       </c>
       <c r="B585" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C585" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D585" s="3">
-        <v>1.218</v>
+        <v>1.5089999999999999</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -8582,13 +8582,13 @@
         <v>11</v>
       </c>
       <c r="B586" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C586" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D586" s="3">
-        <v>1.3958999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -8596,13 +8596,13 @@
         <v>11</v>
       </c>
       <c r="B587" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C587" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D587" s="3">
-        <v>1.5745000000000002</v>
+        <v>1.0697000000000001</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -8613,10 +8613,10 @@
         <v>2021</v>
       </c>
       <c r="C588" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D588" s="3">
-        <v>1.3656999999999999</v>
+        <v>1.2351000000000001</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8627,10 +8627,10 @@
         <v>2021</v>
       </c>
       <c r="C589" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D589" s="3">
-        <v>1.1288</v>
+        <v>1.1274</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -8641,10 +8641,10 @@
         <v>2021</v>
       </c>
       <c r="C590" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D590" s="3">
-        <v>0.96220000000000006</v>
+        <v>1.3996</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8655,10 +8655,10 @@
         <v>2021</v>
       </c>
       <c r="C591" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D591" s="3">
-        <v>0.94979999999999998</v>
+        <v>1.2915000000000001</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8669,10 +8669,10 @@
         <v>2021</v>
       </c>
       <c r="C592" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D592" s="3">
-        <v>1.1982999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8680,13 +8680,13 @@
         <v>11</v>
       </c>
       <c r="B593" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C593" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D593" s="3">
-        <v>1.0469999999999999</v>
+        <v>1.3958999999999999</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8694,13 +8694,13 @@
         <v>11</v>
       </c>
       <c r="B594" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C594" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D594" s="3">
-        <v>0.84160000000000001</v>
+        <v>1.5745000000000002</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8708,13 +8708,13 @@
         <v>11</v>
       </c>
       <c r="B595" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C595" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D595" s="3">
-        <v>0.85270000000000001</v>
+        <v>1.3656999999999999</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8722,13 +8722,13 @@
         <v>11</v>
       </c>
       <c r="B596" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C596" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D596" s="3">
-        <v>0.65920000000000001</v>
+        <v>1.1288</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8736,13 +8736,13 @@
         <v>11</v>
       </c>
       <c r="B597" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C597" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D597" s="3">
-        <v>0.91259999999999997</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="B598" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C598" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D598" s="3">
-        <v>0.68140000000000001</v>
+        <v>0.94979999999999998</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8764,13 +8764,13 @@
         <v>11</v>
       </c>
       <c r="B599" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C599" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D599" s="3">
-        <v>0.69020000000000004</v>
+        <v>1.1982999999999999</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8781,10 +8781,10 @@
         <v>2022</v>
       </c>
       <c r="C600" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D600" s="3">
-        <v>0.83509999999999995</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8795,10 +8795,10 @@
         <v>2022</v>
       </c>
       <c r="C601" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D601" s="3">
-        <v>0.8459000000000001</v>
+        <v>0.84160000000000001</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8809,10 +8809,10 @@
         <v>2022</v>
       </c>
       <c r="C602" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D602" s="3">
-        <v>1.0476000000000001</v>
+        <v>0.85270000000000001</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8823,10 +8823,10 @@
         <v>2022</v>
       </c>
       <c r="C603" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D603" s="3">
-        <v>0.93159999999999998</v>
+        <v>0.65920000000000001</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8837,10 +8837,10 @@
         <v>2022</v>
       </c>
       <c r="C604" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D604" s="3">
-        <v>0.60189999999999999</v>
+        <v>0.91259999999999997</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8848,13 +8848,13 @@
         <v>11</v>
       </c>
       <c r="B605" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C605" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D605" s="3">
-        <v>0.70330000000000004</v>
+        <v>0.68140000000000001</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8862,13 +8862,13 @@
         <v>11</v>
       </c>
       <c r="B606" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C606" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D606" s="3">
-        <v>0.68169999999999997</v>
+        <v>0.69020000000000004</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8876,13 +8876,13 @@
         <v>11</v>
       </c>
       <c r="B607" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C607" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D607" s="3">
-        <v>0.6391</v>
+        <v>0.83509999999999995</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8890,13 +8890,13 @@
         <v>11</v>
       </c>
       <c r="B608" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C608" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D608" s="3">
-        <v>0.72650000000000003</v>
+        <v>0.8459000000000001</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8904,13 +8904,13 @@
         <v>11</v>
       </c>
       <c r="B609" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C609" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D609" s="3">
-        <v>0.76770000000000005</v>
+        <v>1.0476000000000001</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8918,13 +8918,13 @@
         <v>11</v>
       </c>
       <c r="B610" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C610" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D610" s="3">
-        <v>0.64570000000000005</v>
+        <v>0.93159999999999998</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="B611" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C611" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D611" s="3">
-        <v>0.60250000000000004</v>
+        <v>0.60189999999999999</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8949,10 +8949,10 @@
         <v>2023</v>
       </c>
       <c r="C612" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D612" s="3">
-        <v>1.3164</v>
+        <v>0.70330000000000004</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8963,10 +8963,10 @@
         <v>2023</v>
       </c>
       <c r="C613" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D613" s="3">
-        <v>1.054</v>
+        <v>0.68169999999999997</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8977,10 +8977,10 @@
         <v>2023</v>
       </c>
       <c r="C614" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D614" s="3">
-        <v>1.1778</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8991,10 +8991,10 @@
         <v>2023</v>
       </c>
       <c r="C615" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D615" s="3">
-        <v>1.3501000000000001</v>
+        <v>0.72650000000000003</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9005,10 +9005,10 @@
         <v>2023</v>
       </c>
       <c r="C616" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D616" s="3">
-        <v>1.1941999999999999</v>
+        <v>0.76770000000000005</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9016,13 +9016,13 @@
         <v>11</v>
       </c>
       <c r="B617" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C617" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D617" s="3">
-        <v>1.1995</v>
+        <v>0.64570000000000005</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9030,13 +9030,13 @@
         <v>11</v>
       </c>
       <c r="B618" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C618" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D618" s="3">
-        <v>1.2528000000000001</v>
+        <v>0.60250000000000004</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9044,13 +9044,13 @@
         <v>11</v>
       </c>
       <c r="B619" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C619" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D619" s="3">
-        <v>1.2377</v>
+        <v>1.3164</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9058,13 +9058,13 @@
         <v>11</v>
       </c>
       <c r="B620" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C620" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D620" s="3">
-        <v>1.0448</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9072,13 +9072,13 @@
         <v>11</v>
       </c>
       <c r="B621" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C621" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D621" s="3">
-        <v>1.1088</v>
+        <v>1.1778</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9086,13 +9086,13 @@
         <v>11</v>
       </c>
       <c r="B622" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C622" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D622" s="3">
-        <v>1.1704000000000001</v>
+        <v>1.3501000000000001</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9100,13 +9100,13 @@
         <v>11</v>
       </c>
       <c r="B623" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C623" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D623" s="3">
-        <v>1.335</v>
+        <v>1.1941999999999999</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9117,10 +9117,10 @@
         <v>2024</v>
       </c>
       <c r="C624" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D624" s="3">
-        <v>1.2101999999999999</v>
+        <v>1.1995</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9131,10 +9131,10 @@
         <v>2024</v>
       </c>
       <c r="C625" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D625" s="3">
-        <v>1.2007000000000001</v>
+        <v>1.2528000000000001</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9145,10 +9145,10 @@
         <v>2024</v>
       </c>
       <c r="C626" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D626" s="3">
-        <v>1.2133</v>
+        <v>1.2377</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9159,10 +9159,10 @@
         <v>2024</v>
       </c>
       <c r="C627" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D627" s="3">
-        <v>0.85850000000000004</v>
+        <v>1.0448</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9173,10 +9173,10 @@
         <v>2024</v>
       </c>
       <c r="C628" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D628" s="3">
-        <v>1.1714</v>
+        <v>1.1088</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9184,13 +9184,13 @@
         <v>11</v>
       </c>
       <c r="B629" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C629" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D629" s="3">
-        <v>0.94820000000000004</v>
+        <v>1.1704000000000001</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9198,13 +9198,13 @@
         <v>11</v>
       </c>
       <c r="B630" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C630" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D630" s="3">
-        <v>0.94499999999999995</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9212,13 +9212,13 @@
         <v>11</v>
       </c>
       <c r="B631" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C631" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D631" s="3">
-        <v>1.0746</v>
+        <v>1.2101999999999999</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9226,13 +9226,13 @@
         <v>11</v>
       </c>
       <c r="B632" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C632" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D632" s="3">
-        <v>1.1345000000000001</v>
+        <v>1.2007000000000001</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9240,13 +9240,13 @@
         <v>11</v>
       </c>
       <c r="B633" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C633" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D633" s="3">
-        <v>0.96009999999999995</v>
+        <v>1.2133</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9254,13 +9254,13 @@
         <v>11</v>
       </c>
       <c r="B634" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C634" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D634" s="3">
-        <v>1.0189999999999999</v>
+        <v>0.85850000000000004</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9268,13 +9268,13 @@
         <v>11</v>
       </c>
       <c r="B635" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C635" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D635" s="3">
-        <v>1.0889</v>
+        <v>1.1714</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9285,10 +9285,10 @@
         <v>2025</v>
       </c>
       <c r="C636" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D636" s="3">
-        <v>1.0328999999999999</v>
+        <v>0.94820000000000004</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9299,10 +9299,10 @@
         <v>2025</v>
       </c>
       <c r="C637" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D637" s="3">
-        <v>1.0566</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9313,10 +9313,10 @@
         <v>2025</v>
       </c>
       <c r="C638" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D638" s="3">
-        <v>1.0752999999999999</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9327,10 +9327,10 @@
         <v>2025</v>
       </c>
       <c r="C639" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D639" s="3">
-        <v>0.91410000000000002</v>
+        <v>1.1345000000000001</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9341,10 +9341,10 @@
         <v>2025</v>
       </c>
       <c r="C640" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D640" s="3">
-        <v>1.0733999999999999</v>
+        <v>0.96009999999999995</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9352,13 +9352,13 @@
         <v>11</v>
       </c>
       <c r="B641" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C641" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D641" s="3">
-        <v>0.97189999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9366,13 +9366,13 @@
         <v>11</v>
       </c>
       <c r="B642" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C642" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D642" s="3">
-        <v>0.89129999999999987</v>
+        <v>1.0889</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9380,125 +9380,125 @@
         <v>11</v>
       </c>
       <c r="B643" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C643" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D643" s="3">
-        <v>0.87390000000000001</v>
+        <v>1.0328999999999999</v>
       </c>
     </row>
     <row r="644" spans="1:4">
       <c r="A644" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B644" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C644" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D644" s="3">
-        <v>0.62870000000000004</v>
+        <v>1.0566</v>
       </c>
     </row>
     <row r="645" spans="1:4">
       <c r="A645" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B645" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C645" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D645" s="3">
-        <v>0.97070000000000001</v>
+        <v>1.0752999999999999</v>
       </c>
     </row>
     <row r="646" spans="1:4">
       <c r="A646" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B646" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C646" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D646" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.91410000000000002</v>
       </c>
     </row>
     <row r="647" spans="1:4">
       <c r="A647" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B647" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C647" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D647" s="3">
-        <v>0.60429999999999995</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="648" spans="1:4">
       <c r="A648" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B648" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C648" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D648" s="3">
-        <v>0.87819999999999998</v>
+        <v>1.0165999999999999</v>
       </c>
     </row>
     <row r="649" spans="1:4">
       <c r="A649" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B649" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C649" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D649" s="3">
-        <v>0.97710000000000008</v>
+        <v>0.92769999999999997</v>
       </c>
     </row>
     <row r="650" spans="1:4">
       <c r="A650" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B650" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C650" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D650" s="3">
-        <v>0.78180000000000005</v>
+        <v>0.86799999999999999</v>
       </c>
     </row>
     <row r="651" spans="1:4">
       <c r="A651" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B651" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C651" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D651" s="3">
-        <v>0.88280000000000003</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9506,13 +9506,13 @@
         <v>12</v>
       </c>
       <c r="B652" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C652" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D652" s="3">
-        <v>0.84150000000000003</v>
+        <v>0.62870000000000004</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9520,13 +9520,13 @@
         <v>12</v>
       </c>
       <c r="B653" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C653" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D653" s="3">
-        <v>3.6991000000000001</v>
+        <v>0.97070000000000001</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9534,13 +9534,13 @@
         <v>12</v>
       </c>
       <c r="B654" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C654" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D654" s="3">
-        <v>0.63649999999999995</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9548,13 +9548,13 @@
         <v>12</v>
       </c>
       <c r="B655" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C655" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D655" s="3">
-        <v>0.63870000000000005</v>
+        <v>0.60429999999999995</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9562,13 +9562,13 @@
         <v>12</v>
       </c>
       <c r="B656" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C656" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D656" s="3">
-        <v>0.58840000000000003</v>
+        <v>0.87819999999999998</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -9576,13 +9576,13 @@
         <v>12</v>
       </c>
       <c r="B657" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C657" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D657" s="3">
-        <v>0.83720000000000006</v>
+        <v>0.97710000000000008</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -9590,13 +9590,13 @@
         <v>12</v>
       </c>
       <c r="B658" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C658" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D658" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.78180000000000005</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -9604,13 +9604,13 @@
         <v>12</v>
       </c>
       <c r="B659" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C659" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D659" s="3">
-        <v>0.75119999999999998</v>
+        <v>0.88280000000000003</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -9621,10 +9621,10 @@
         <v>2020</v>
       </c>
       <c r="C660" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D660" s="3">
-        <v>0.76349999999999996</v>
+        <v>0.84150000000000003</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -9635,10 +9635,10 @@
         <v>2020</v>
       </c>
       <c r="C661" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D661" s="3">
-        <v>0.80579999999999996</v>
+        <v>3.6991000000000001</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -9649,10 +9649,10 @@
         <v>2020</v>
       </c>
       <c r="C662" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D662" s="3">
-        <v>0.75339999999999996</v>
+        <v>0.63649999999999995</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -9660,13 +9660,13 @@
         <v>12</v>
       </c>
       <c r="B663" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C663" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D663" s="3">
-        <v>0.83040000000000003</v>
+        <v>0.63870000000000005</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -9674,13 +9674,13 @@
         <v>12</v>
       </c>
       <c r="B664" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C664" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D664" s="3">
-        <v>0.85129999999999995</v>
+        <v>0.58840000000000003</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -9688,13 +9688,13 @@
         <v>12</v>
       </c>
       <c r="B665" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C665" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D665" s="3">
-        <v>0.8536999999999999</v>
+        <v>0.83720000000000006</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -9702,13 +9702,13 @@
         <v>12</v>
       </c>
       <c r="B666" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C666" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D666" s="3">
-        <v>0.93080000000000007</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -9716,13 +9716,13 @@
         <v>12</v>
       </c>
       <c r="B667" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C667" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D667" s="3">
-        <v>0.8980999999999999</v>
+        <v>0.75119999999999998</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -9730,13 +9730,13 @@
         <v>12</v>
       </c>
       <c r="B668" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C668" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D668" s="3">
-        <v>0.88049999999999984</v>
+        <v>0.76349999999999996</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -9744,13 +9744,13 @@
         <v>12</v>
       </c>
       <c r="B669" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C669" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D669" s="3">
-        <v>0.89779999999999993</v>
+        <v>0.80579999999999996</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -9758,13 +9758,13 @@
         <v>12</v>
       </c>
       <c r="B670" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C670" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D670" s="3">
-        <v>0.94299999999999995</v>
+        <v>0.75339999999999996</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -9775,10 +9775,10 @@
         <v>2021</v>
       </c>
       <c r="C671" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D671" s="3">
-        <v>0.87270000000000014</v>
+        <v>0.83040000000000003</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -9789,10 +9789,10 @@
         <v>2021</v>
       </c>
       <c r="C672" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D672" s="3">
-        <v>0.89249999999999985</v>
+        <v>0.85129999999999995</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -9803,10 +9803,10 @@
         <v>2021</v>
       </c>
       <c r="C673" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D673" s="3">
-        <v>0.90710000000000002</v>
+        <v>0.8536999999999999</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -9817,10 +9817,10 @@
         <v>2021</v>
       </c>
       <c r="C674" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D674" s="3">
-        <v>0.80330000000000001</v>
+        <v>0.93080000000000007</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -9828,13 +9828,13 @@
         <v>12</v>
       </c>
       <c r="B675" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C675" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D675" s="3">
-        <v>0.7107</v>
+        <v>0.8980999999999999</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -9842,13 +9842,13 @@
         <v>12</v>
       </c>
       <c r="B676" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C676" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D676" s="3">
-        <v>0.78610000000000002</v>
+        <v>0.88049999999999984</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -9856,13 +9856,13 @@
         <v>12</v>
       </c>
       <c r="B677" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C677" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D677" s="3">
-        <v>0.83389999999999997</v>
+        <v>0.89779999999999993</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -9870,13 +9870,13 @@
         <v>12</v>
       </c>
       <c r="B678" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C678" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D678" s="3">
-        <v>0.88970000000000005</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -9884,13 +9884,13 @@
         <v>12</v>
       </c>
       <c r="B679" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C679" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D679" s="3">
-        <v>0.83260000000000001</v>
+        <v>0.87270000000000014</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -9898,13 +9898,13 @@
         <v>12</v>
       </c>
       <c r="B680" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C680" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D680" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.89249999999999985</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -9912,13 +9912,13 @@
         <v>12</v>
       </c>
       <c r="B681" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C681" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D681" s="3">
-        <v>0.90830000000000011</v>
+        <v>0.90710000000000002</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -9926,13 +9926,13 @@
         <v>12</v>
       </c>
       <c r="B682" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C682" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D682" s="3">
-        <v>0.80479999999999996</v>
+        <v>0.80330000000000001</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -9943,10 +9943,10 @@
         <v>2022</v>
       </c>
       <c r="C683" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D683" s="3">
-        <v>0.77749999999999997</v>
+        <v>0.7107</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -9957,10 +9957,10 @@
         <v>2022</v>
       </c>
       <c r="C684" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D684" s="3">
-        <v>0.81069999999999998</v>
+        <v>0.78610000000000002</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -9971,10 +9971,10 @@
         <v>2022</v>
       </c>
       <c r="C685" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D685" s="3">
-        <v>0.87409999999999999</v>
+        <v>0.83389999999999997</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -9985,10 +9985,10 @@
         <v>2022</v>
       </c>
       <c r="C686" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D686" s="3">
-        <v>0.86129999999999984</v>
+        <v>0.88970000000000005</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -9996,13 +9996,13 @@
         <v>12</v>
       </c>
       <c r="B687" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C687" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D687" s="3">
-        <v>0.78390000000000004</v>
+        <v>0.83260000000000001</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -10010,13 +10010,13 @@
         <v>12</v>
       </c>
       <c r="B688" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C688" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D688" s="3">
-        <v>0.84170000000000011</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -10024,13 +10024,13 @@
         <v>12</v>
       </c>
       <c r="B689" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C689" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D689" s="3">
-        <v>0.80769999999999986</v>
+        <v>0.90830000000000011</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -10038,13 +10038,13 @@
         <v>12</v>
       </c>
       <c r="B690" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C690" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D690" s="3">
-        <v>0.90670000000000006</v>
+        <v>0.80479999999999996</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -10052,13 +10052,13 @@
         <v>12</v>
       </c>
       <c r="B691" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C691" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D691" s="3">
-        <v>0.82020000000000004</v>
+        <v>0.77749999999999997</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -10066,13 +10066,13 @@
         <v>12</v>
       </c>
       <c r="B692" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C692" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D692" s="3">
-        <v>0.81120000000000014</v>
+        <v>0.81069999999999998</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -10080,13 +10080,13 @@
         <v>12</v>
       </c>
       <c r="B693" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C693" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D693" s="3">
-        <v>0.85009999999999997</v>
+        <v>0.87409999999999999</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -10094,13 +10094,13 @@
         <v>12</v>
       </c>
       <c r="B694" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C694" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D694" s="3">
-        <v>0.8327</v>
+        <v>0.86129999999999984</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -10111,10 +10111,10 @@
         <v>2023</v>
       </c>
       <c r="C695" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D695" s="3">
-        <v>0.90250000000000008</v>
+        <v>0.78390000000000004</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -10125,10 +10125,10 @@
         <v>2023</v>
       </c>
       <c r="C696" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D696" s="3">
-        <v>0.85660000000000003</v>
+        <v>0.84170000000000011</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -10139,10 +10139,10 @@
         <v>2023</v>
       </c>
       <c r="C697" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D697" s="3">
-        <v>0.92820000000000003</v>
+        <v>0.80769999999999986</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -10153,10 +10153,10 @@
         <v>2023</v>
       </c>
       <c r="C698" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D698" s="3">
-        <v>0.86169999999999991</v>
+        <v>0.90670000000000006</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -10164,13 +10164,13 @@
         <v>12</v>
       </c>
       <c r="B699" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C699" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D699" s="3">
-        <v>0.85750000000000004</v>
+        <v>0.82020000000000004</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -10178,13 +10178,13 @@
         <v>12</v>
       </c>
       <c r="B700" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C700" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D700" s="3">
-        <v>0.9355</v>
+        <v>0.81120000000000014</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -10192,13 +10192,13 @@
         <v>12</v>
       </c>
       <c r="B701" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C701" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D701" s="3">
-        <v>0.79620000000000002</v>
+        <v>0.85009999999999997</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -10206,13 +10206,13 @@
         <v>12</v>
       </c>
       <c r="B702" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C702" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D702" s="3">
-        <v>0.93479999999999996</v>
+        <v>0.8327</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -10220,13 +10220,13 @@
         <v>12</v>
       </c>
       <c r="B703" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C703" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D703" s="3">
-        <v>0.96489999999999998</v>
+        <v>0.90250000000000008</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -10234,13 +10234,13 @@
         <v>12</v>
       </c>
       <c r="B704" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C704" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D704" s="3">
-        <v>0.86809999999999998</v>
+        <v>0.85660000000000003</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -10248,13 +10248,13 @@
         <v>12</v>
       </c>
       <c r="B705" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C705" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D705" s="3">
-        <v>0.7752</v>
+        <v>0.92820000000000003</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -10262,13 +10262,13 @@
         <v>12</v>
       </c>
       <c r="B706" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C706" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D706" s="3">
-        <v>0.82489999999999997</v>
+        <v>0.86169999999999991</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -10279,10 +10279,10 @@
         <v>2024</v>
       </c>
       <c r="C707" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D707" s="3">
-        <v>0.91569999999999996</v>
+        <v>0.85750000000000004</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -10293,10 +10293,10 @@
         <v>2024</v>
       </c>
       <c r="C708" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D708" s="3">
-        <v>0.997</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -10307,10 +10307,10 @@
         <v>2024</v>
       </c>
       <c r="C709" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D709" s="3">
-        <v>1.0421</v>
+        <v>0.79620000000000002</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -10321,10 +10321,10 @@
         <v>2024</v>
       </c>
       <c r="C710" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D710" s="3">
-        <v>1.0548</v>
+        <v>0.93479999999999996</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -10332,13 +10332,13 @@
         <v>12</v>
       </c>
       <c r="B711" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C711" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D711" s="3">
-        <v>0.92949999999999999</v>
+        <v>0.96489999999999998</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -10346,13 +10346,13 @@
         <v>12</v>
       </c>
       <c r="B712" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C712" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D712" s="3">
-        <v>0.95120000000000016</v>
+        <v>0.86809999999999998</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -10360,13 +10360,13 @@
         <v>12</v>
       </c>
       <c r="B713" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C713" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D713" s="3">
-        <v>0.92459999999999998</v>
+        <v>0.7752</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -10374,13 +10374,13 @@
         <v>12</v>
       </c>
       <c r="B714" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C714" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D714" s="3">
-        <v>0.85740000000000005</v>
+        <v>0.82489999999999997</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -10388,13 +10388,13 @@
         <v>12</v>
       </c>
       <c r="B715" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C715" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D715" s="3">
-        <v>0.91100000000000003</v>
+        <v>0.91569999999999996</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -10402,13 +10402,13 @@
         <v>12</v>
       </c>
       <c r="B716" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C716" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D716" s="3">
-        <v>0.89139999999999986</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -10416,13 +10416,13 @@
         <v>12</v>
       </c>
       <c r="B717" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C717" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D717" s="3">
-        <v>0.92459999999999998</v>
+        <v>1.0421</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -10430,13 +10430,13 @@
         <v>12</v>
       </c>
       <c r="B718" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C718" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D718" s="3">
-        <v>0.97750000000000004</v>
+        <v>1.0548</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -10447,10 +10447,10 @@
         <v>2025</v>
       </c>
       <c r="C719" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D719" s="3">
-        <v>0.91020000000000001</v>
+        <v>0.92949999999999999</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -10461,10 +10461,10 @@
         <v>2025</v>
       </c>
       <c r="C720" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D720" s="3">
-        <v>0.89680000000000004</v>
+        <v>0.95120000000000016</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -10475,10 +10475,10 @@
         <v>2025</v>
       </c>
       <c r="C721" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D721" s="3">
-        <v>0.83699999999999997</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -10489,10 +10489,10 @@
         <v>2025</v>
       </c>
       <c r="C722" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D722" s="3">
-        <v>0.9587</v>
+        <v>0.85740000000000005</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -10500,13 +10500,13 @@
         <v>12</v>
       </c>
       <c r="B723" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C723" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D723" s="3">
-        <v>0.95770000000000011</v>
+        <v>0.91100000000000003</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -10514,13 +10514,13 @@
         <v>12</v>
       </c>
       <c r="B724" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C724" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D724" s="3">
-        <v>0.87290000000000001</v>
+        <v>0.89139999999999986</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -10528,13 +10528,139 @@
         <v>12</v>
       </c>
       <c r="B725" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C725" s="2">
+        <v>7</v>
+      </c>
+      <c r="D725" s="3">
+        <v>0.92459999999999998</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4">
+      <c r="A726" t="s">
+        <v>12</v>
+      </c>
+      <c r="B726" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C726" s="2">
+        <v>8</v>
+      </c>
+      <c r="D726" s="3">
+        <v>0.97750000000000004</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4">
+      <c r="A727" t="s">
+        <v>12</v>
+      </c>
+      <c r="B727" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C727" s="2">
+        <v>9</v>
+      </c>
+      <c r="D727" s="3">
+        <v>0.91020000000000001</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4">
+      <c r="A728" t="s">
+        <v>12</v>
+      </c>
+      <c r="B728" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C728" s="2">
+        <v>10</v>
+      </c>
+      <c r="D728" s="3">
+        <v>0.89680000000000004</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4">
+      <c r="A729" t="s">
+        <v>12</v>
+      </c>
+      <c r="B729" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C729" s="2">
+        <v>11</v>
+      </c>
+      <c r="D729" s="3">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4">
+      <c r="A730" t="s">
+        <v>12</v>
+      </c>
+      <c r="B730" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C730" s="2">
+        <v>12</v>
+      </c>
+      <c r="D730" s="3">
+        <v>0.97820000000000007</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4">
+      <c r="A731" t="s">
+        <v>12</v>
+      </c>
+      <c r="B731" s="2">
         <v>2026</v>
       </c>
-      <c r="C725" s="2">
+      <c r="C731" s="2">
+        <v>1</v>
+      </c>
+      <c r="D731" s="3">
+        <v>0.95220000000000005</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4">
+      <c r="A732" t="s">
+        <v>12</v>
+      </c>
+      <c r="B732" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C732" s="2">
+        <v>2</v>
+      </c>
+      <c r="D732" s="3">
+        <v>0.87929999999999986</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4">
+      <c r="A733" t="s">
+        <v>12</v>
+      </c>
+      <c r="B733" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C733" s="2">
         <v>3</v>
       </c>
-      <c r="D725" s="3">
-        <v>0.89890000000000003</v>
+      <c r="D733" s="3">
+        <v>0.89659999999999995</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4">
+      <c r="A734" t="s">
+        <v>12</v>
+      </c>
+      <c r="B734" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C734" s="2">
+        <v>4</v>
+      </c>
+      <c r="D734" s="3">
+        <v>0.87880000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/upload/case-mix-2025.xlsx
+++ b/upload/case-mix-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D734"/>
+  <dimension ref="A1:D743"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -636,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="3">
-        <v>1.5658000000000001</v>
+        <v>1.5555000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1392,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D72" s="3">
-        <v>1.6105</v>
+        <v>1.6205000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1406,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="D73" s="3">
-        <v>1.4464999999999999</v>
+        <v>1.4569000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1420,7 +1420,7 @@
         <v>5</v>
       </c>
       <c r="D74" s="3">
-        <v>1.6592</v>
+        <v>1.6585000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1434,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="D75" s="3">
-        <v>1.6178999999999999</v>
+        <v>1.6220000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1448,7 +1448,7 @@
         <v>7</v>
       </c>
       <c r="D76" s="3">
-        <v>1.458</v>
+        <v>1.4683999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1462,7 +1462,7 @@
         <v>8</v>
       </c>
       <c r="D77" s="3">
-        <v>1.5509999999999999</v>
+        <v>1.5622</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1476,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="3">
-        <v>1.4527000000000001</v>
+        <v>1.4641999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1579,16 +1579,16 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B86" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C86" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3">
-        <v>0.32269999999999999</v>
+        <v>1.2676000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1599,10 +1599,10 @@
         <v>2019</v>
       </c>
       <c r="C87" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D87" s="3">
-        <v>2.4020999999999999</v>
+        <v>0.32269999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1610,13 +1610,13 @@
         <v>5</v>
       </c>
       <c r="B88" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C88" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D88" s="3">
-        <v>2.0989</v>
+        <v>2.4020999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1627,10 +1627,10 @@
         <v>2020</v>
       </c>
       <c r="C89" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" s="3">
-        <v>1.9497</v>
+        <v>2.0989</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1641,10 +1641,10 @@
         <v>2020</v>
       </c>
       <c r="C90" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="3">
-        <v>2.1490999999999998</v>
+        <v>1.9497</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1655,10 +1655,10 @@
         <v>2020</v>
       </c>
       <c r="C91" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" s="3">
-        <v>1.6907000000000001</v>
+        <v>2.1490999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1669,10 +1669,10 @@
         <v>2020</v>
       </c>
       <c r="C92" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D92" s="3">
-        <v>2.1762999999999999</v>
+        <v>1.6907000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1683,10 +1683,10 @@
         <v>2020</v>
       </c>
       <c r="C93" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93" s="3">
-        <v>2.3714</v>
+        <v>2.1762999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1697,10 +1697,10 @@
         <v>2020</v>
       </c>
       <c r="C94" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D94" s="3">
-        <v>2.6513</v>
+        <v>2.3714</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1711,10 +1711,10 @@
         <v>2020</v>
       </c>
       <c r="C95" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="3">
-        <v>2.3975</v>
+        <v>2.6513</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1725,10 +1725,10 @@
         <v>2020</v>
       </c>
       <c r="C96" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D96" s="3">
-        <v>3.2244999999999999</v>
+        <v>2.3975</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1739,10 +1739,10 @@
         <v>2020</v>
       </c>
       <c r="C97" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D97" s="3">
-        <v>2.0931000000000002</v>
+        <v>3.2244999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1753,10 +1753,10 @@
         <v>2020</v>
       </c>
       <c r="C98" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D98" s="3">
-        <v>2.1968000000000001</v>
+        <v>2.0931000000000002</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1767,10 +1767,10 @@
         <v>2020</v>
       </c>
       <c r="C99" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D99" s="3">
-        <v>2.0958999999999999</v>
+        <v>2.1968000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1778,13 +1778,13 @@
         <v>5</v>
       </c>
       <c r="B100" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C100" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D100" s="3">
-        <v>2.4843000000000002</v>
+        <v>2.0958999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1795,10 +1795,10 @@
         <v>2021</v>
       </c>
       <c r="C101" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D101" s="3">
-        <v>2.3409</v>
+        <v>2.4843000000000002</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1809,10 +1809,10 @@
         <v>2021</v>
       </c>
       <c r="C102" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="3">
-        <v>2.7355999999999998</v>
+        <v>2.3409</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1823,10 +1823,10 @@
         <v>2021</v>
       </c>
       <c r="C103" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" s="3">
-        <v>2.8948</v>
+        <v>2.7355999999999998</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>2021</v>
       </c>
       <c r="C104" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104" s="3">
-        <v>2.7456</v>
+        <v>2.8948</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1851,10 +1851,10 @@
         <v>2021</v>
       </c>
       <c r="C105" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D105" s="3">
-        <v>2.5648</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1865,10 +1865,10 @@
         <v>2021</v>
       </c>
       <c r="C106" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D106" s="3">
-        <v>2.5844</v>
+        <v>2.5648</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1879,10 +1879,10 @@
         <v>2021</v>
       </c>
       <c r="C107" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D107" s="3">
-        <v>2.8304999999999998</v>
+        <v>2.5844</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1893,10 +1893,10 @@
         <v>2021</v>
       </c>
       <c r="C108" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D108" s="3">
-        <v>2.0144000000000002</v>
+        <v>2.8304999999999998</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1907,10 +1907,10 @@
         <v>2021</v>
       </c>
       <c r="C109" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D109" s="3">
-        <v>1.9097</v>
+        <v>2.0144000000000002</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1921,10 +1921,10 @@
         <v>2021</v>
       </c>
       <c r="C110" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D110" s="3">
-        <v>2.3733</v>
+        <v>1.9097</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1935,10 +1935,10 @@
         <v>2021</v>
       </c>
       <c r="C111" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D111" s="3">
-        <v>2.0158999999999998</v>
+        <v>2.3733</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1946,13 +1946,13 @@
         <v>5</v>
       </c>
       <c r="B112" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D112" s="3">
-        <v>2.0093999999999999</v>
+        <v>2.0158999999999998</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1963,10 +1963,10 @@
         <v>2022</v>
       </c>
       <c r="C113" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" s="3">
-        <v>3.6905000000000001</v>
+        <v>2.0093999999999999</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1977,10 +1977,10 @@
         <v>2022</v>
       </c>
       <c r="C114" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" s="3">
-        <v>2.6345000000000001</v>
+        <v>3.6905000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1991,10 +1991,10 @@
         <v>2022</v>
       </c>
       <c r="C115" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D115" s="3">
-        <v>2.0619999999999998</v>
+        <v>2.6345000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2005,10 +2005,10 @@
         <v>2022</v>
       </c>
       <c r="C116" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D116" s="3">
-        <v>1.9186000000000001</v>
+        <v>2.0619999999999998</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>2022</v>
       </c>
       <c r="C117" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D117" s="3">
-        <v>2.0594000000000001</v>
+        <v>1.9186000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2033,10 +2033,10 @@
         <v>2022</v>
       </c>
       <c r="C118" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D118" s="3">
-        <v>2.1585999999999999</v>
+        <v>2.0594000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2047,10 +2047,10 @@
         <v>2022</v>
       </c>
       <c r="C119" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D119" s="3">
-        <v>1.6135999999999999</v>
+        <v>2.1585999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2061,10 +2061,10 @@
         <v>2022</v>
       </c>
       <c r="C120" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D120" s="3">
-        <v>1.5652000000000001</v>
+        <v>1.6135999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2075,10 +2075,10 @@
         <v>2022</v>
       </c>
       <c r="C121" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D121" s="3">
-        <v>1.4952000000000001</v>
+        <v>1.5652000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2089,10 +2089,10 @@
         <v>2022</v>
       </c>
       <c r="C122" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D122" s="3">
-        <v>1.7753000000000001</v>
+        <v>1.4952000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2103,10 +2103,10 @@
         <v>2022</v>
       </c>
       <c r="C123" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D123" s="3">
-        <v>1.9029</v>
+        <v>1.7753000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2114,13 +2114,13 @@
         <v>5</v>
       </c>
       <c r="B124" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C124" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D124" s="3">
-        <v>1.5787</v>
+        <v>1.9029</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2131,10 +2131,10 @@
         <v>2023</v>
       </c>
       <c r="C125" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" s="3">
-        <v>1.8613999999999999</v>
+        <v>1.5787</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2145,10 +2145,10 @@
         <v>2023</v>
       </c>
       <c r="C126" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D126" s="3">
-        <v>1.6684000000000001</v>
+        <v>1.8613999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2159,10 +2159,10 @@
         <v>2023</v>
       </c>
       <c r="C127" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D127" s="3">
-        <v>1.5757000000000001</v>
+        <v>1.6684000000000001</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2173,10 +2173,10 @@
         <v>2023</v>
       </c>
       <c r="C128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D128" s="3">
-        <v>2.0183</v>
+        <v>1.5757000000000001</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2187,10 +2187,10 @@
         <v>2023</v>
       </c>
       <c r="C129" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D129" s="3">
-        <v>1.6662999999999997</v>
+        <v>2.0183</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2201,10 +2201,10 @@
         <v>2023</v>
       </c>
       <c r="C130" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" s="3">
-        <v>1.9484999999999999</v>
+        <v>1.6662999999999997</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2215,10 +2215,10 @@
         <v>2023</v>
       </c>
       <c r="C131" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" s="3">
-        <v>2.0987</v>
+        <v>1.9484999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2229,10 +2229,10 @@
         <v>2023</v>
       </c>
       <c r="C132" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D132" s="3">
-        <v>1.9556999999999998</v>
+        <v>2.0987</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2243,10 +2243,10 @@
         <v>2023</v>
       </c>
       <c r="C133" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D133" s="3">
-        <v>2.331</v>
+        <v>1.9556999999999998</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2257,10 +2257,10 @@
         <v>2023</v>
       </c>
       <c r="C134" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D134" s="3">
-        <v>1.7165999999999999</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2271,10 +2271,10 @@
         <v>2023</v>
       </c>
       <c r="C135" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D135" s="3">
-        <v>1.6557999999999999</v>
+        <v>1.7165999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2282,13 +2282,13 @@
         <v>5</v>
       </c>
       <c r="B136" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D136" s="3">
-        <v>0.99390000000000001</v>
+        <v>1.6557999999999999</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2299,10 +2299,10 @@
         <v>2024</v>
       </c>
       <c r="C137" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D137" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2313,10 +2313,10 @@
         <v>2024</v>
       </c>
       <c r="C138" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D138" s="3">
-        <v>0.88229999999999997</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2327,10 +2327,10 @@
         <v>2024</v>
       </c>
       <c r="C139" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D139" s="3">
-        <v>0.82889999999999997</v>
+        <v>0.88229999999999997</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2341,10 +2341,10 @@
         <v>2024</v>
       </c>
       <c r="C140" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D140" s="3">
-        <v>1.113</v>
+        <v>0.82889999999999997</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2355,10 +2355,10 @@
         <v>2024</v>
       </c>
       <c r="C141" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D141" s="3">
-        <v>1.7364999999999999</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2369,10 +2369,10 @@
         <v>2024</v>
       </c>
       <c r="C142" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D142" s="3">
-        <v>1.6022000000000001</v>
+        <v>1.7364999999999999</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2383,10 +2383,10 @@
         <v>2024</v>
       </c>
       <c r="C143" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="3">
-        <v>2.0381999999999998</v>
+        <v>1.6022000000000001</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2397,10 +2397,10 @@
         <v>2024</v>
       </c>
       <c r="C144" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D144" s="3">
-        <v>2.2471000000000001</v>
+        <v>2.0381999999999998</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2411,10 +2411,10 @@
         <v>2024</v>
       </c>
       <c r="C145" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D145" s="3">
-        <v>1.7967000000000002</v>
+        <v>2.2471000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2425,10 +2425,10 @@
         <v>2024</v>
       </c>
       <c r="C146" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D146" s="3">
-        <v>2.1593</v>
+        <v>1.7967000000000002</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2439,10 +2439,10 @@
         <v>2024</v>
       </c>
       <c r="C147" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D147" s="3">
-        <v>1.8868000000000003</v>
+        <v>2.1593</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2450,13 +2450,13 @@
         <v>5</v>
       </c>
       <c r="B148" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D148" s="3">
-        <v>1.7827999999999999</v>
+        <v>1.8868000000000003</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2467,10 +2467,10 @@
         <v>2025</v>
       </c>
       <c r="C149" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="3">
-        <v>2.1297999999999999</v>
+        <v>1.7827999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2481,10 +2481,10 @@
         <v>2025</v>
       </c>
       <c r="C150" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D150" s="3">
-        <v>2.4182999999999999</v>
+        <v>2.1297999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2495,10 +2495,10 @@
         <v>2025</v>
       </c>
       <c r="C151" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D151" s="3">
-        <v>1.9123000000000001</v>
+        <v>2.4182999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2509,10 +2509,10 @@
         <v>2025</v>
       </c>
       <c r="C152" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D152" s="3">
-        <v>1.6870000000000001</v>
+        <v>1.9123000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2523,10 +2523,10 @@
         <v>2025</v>
       </c>
       <c r="C153" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D153" s="3">
-        <v>2.0131000000000001</v>
+        <v>1.6870000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2537,10 +2537,10 @@
         <v>2025</v>
       </c>
       <c r="C154" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D154" s="3">
-        <v>1.8540000000000001</v>
+        <v>2.0131000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2551,10 +2551,10 @@
         <v>2025</v>
       </c>
       <c r="C155" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D155" s="3">
-        <v>2.1894999999999998</v>
+        <v>1.8540000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2565,10 +2565,10 @@
         <v>2025</v>
       </c>
       <c r="C156" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D156" s="3">
-        <v>2.0306999999999999</v>
+        <v>2.1894999999999998</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2579,10 +2579,10 @@
         <v>2025</v>
       </c>
       <c r="C157" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D157" s="3">
-        <v>2.2544</v>
+        <v>2.0306999999999999</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2593,10 +2593,10 @@
         <v>2025</v>
       </c>
       <c r="C158" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D158" s="3">
-        <v>2.1646000000000001</v>
+        <v>2.2544</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2607,10 +2607,10 @@
         <v>2025</v>
       </c>
       <c r="C159" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D159" s="3">
-        <v>1.7296</v>
+        <v>2.1646000000000001</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2618,13 +2618,13 @@
         <v>5</v>
       </c>
       <c r="B160" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C160" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D160" s="3">
-        <v>1.7944</v>
+        <v>1.7697000000000001</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2635,10 +2635,10 @@
         <v>2026</v>
       </c>
       <c r="C161" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" s="3">
-        <v>1.5825</v>
+        <v>1.8244</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2649,10 +2649,10 @@
         <v>2026</v>
       </c>
       <c r="C162" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162" s="3">
-        <v>1.5029000000000001</v>
+        <v>1.5788</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2663,38 +2663,38 @@
         <v>2026</v>
       </c>
       <c r="C163" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D163" s="3">
-        <v>1.5125</v>
+        <v>1.5091000000000001</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B164" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C164" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D164" s="3">
-        <v>0.76870000000000005</v>
+        <v>1.5005999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B165" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C165" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D165" s="3">
-        <v>0.73919999999999997</v>
+        <v>1.5471999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2705,10 +2705,10 @@
         <v>2019</v>
       </c>
       <c r="C166" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D166" s="3">
-        <v>0.40439999999999998</v>
+        <v>0.76870000000000005</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2719,10 +2719,10 @@
         <v>2019</v>
       </c>
       <c r="C167" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D167" s="3">
-        <v>0.91849999999999998</v>
+        <v>0.73919999999999997</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B168" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C168" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D168" s="3">
-        <v>0.91590000000000005</v>
+        <v>0.40439999999999998</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2744,13 +2744,13 @@
         <v>6</v>
       </c>
       <c r="B169" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C169" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D169" s="3">
-        <v>0.91639999999999999</v>
+        <v>0.91849999999999998</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2761,10 +2761,10 @@
         <v>2020</v>
       </c>
       <c r="C170" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D170" s="3">
-        <v>0.71460000000000001</v>
+        <v>0.91590000000000005</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2775,10 +2775,10 @@
         <v>2020</v>
       </c>
       <c r="C171" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D171" s="3">
-        <v>0.99629999999999985</v>
+        <v>0.91639999999999999</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2789,10 +2789,10 @@
         <v>2020</v>
       </c>
       <c r="C172" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D172" s="3">
-        <v>1.0396000000000001</v>
+        <v>0.71460000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2803,10 +2803,10 @@
         <v>2020</v>
       </c>
       <c r="C173" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D173" s="3">
-        <v>0.70820000000000005</v>
+        <v>0.99629999999999985</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2817,10 +2817,10 @@
         <v>2020</v>
       </c>
       <c r="C174" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D174" s="3">
-        <v>1.5511999999999999</v>
+        <v>1.0396000000000001</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2831,10 +2831,10 @@
         <v>2020</v>
       </c>
       <c r="C175" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D175" s="3">
-        <v>1.117</v>
+        <v>0.70820000000000005</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2845,10 +2845,10 @@
         <v>2020</v>
       </c>
       <c r="C176" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D176" s="3">
-        <v>1.1403000000000001</v>
+        <v>1.5511999999999999</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2859,10 +2859,10 @@
         <v>2020</v>
       </c>
       <c r="C177" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D177" s="3">
-        <v>1.431</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2873,10 +2873,10 @@
         <v>2020</v>
       </c>
       <c r="C178" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D178" s="3">
-        <v>1.3353999999999999</v>
+        <v>1.1403000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2887,10 +2887,10 @@
         <v>2020</v>
       </c>
       <c r="C179" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D179" s="3">
-        <v>1.8660000000000001</v>
+        <v>1.431</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2898,13 +2898,13 @@
         <v>6</v>
       </c>
       <c r="B180" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C180" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D180" s="3">
-        <v>1.4126000000000001</v>
+        <v>1.3353999999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2912,13 +2912,13 @@
         <v>6</v>
       </c>
       <c r="B181" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C181" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D181" s="3">
-        <v>1.2838000000000001</v>
+        <v>1.8660000000000001</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2929,10 +2929,10 @@
         <v>2021</v>
       </c>
       <c r="C182" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D182" s="3">
-        <v>1.0382</v>
+        <v>1.4126000000000001</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2943,10 +2943,10 @@
         <v>2021</v>
       </c>
       <c r="C183" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D183" s="3">
-        <v>1.4381999999999999</v>
+        <v>1.2838000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2957,10 +2957,10 @@
         <v>2021</v>
       </c>
       <c r="C184" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D184" s="3">
-        <v>1.1092</v>
+        <v>1.0382</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2971,10 +2971,10 @@
         <v>2021</v>
       </c>
       <c r="C185" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D185" s="3">
-        <v>0.93130000000000002</v>
+        <v>1.4381999999999999</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2985,10 +2985,10 @@
         <v>2021</v>
       </c>
       <c r="C186" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D186" s="3">
-        <v>1.4892000000000001</v>
+        <v>1.1092</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2999,10 +2999,10 @@
         <v>2021</v>
       </c>
       <c r="C187" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D187" s="3">
-        <v>1.1386000000000001</v>
+        <v>0.93130000000000002</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3013,10 +3013,10 @@
         <v>2021</v>
       </c>
       <c r="C188" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D188" s="3">
-        <v>1.1675</v>
+        <v>1.4892000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3027,10 +3027,10 @@
         <v>2021</v>
       </c>
       <c r="C189" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D189" s="3">
-        <v>1.2996000000000001</v>
+        <v>1.1386000000000001</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3041,10 +3041,10 @@
         <v>2021</v>
       </c>
       <c r="C190" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D190" s="3">
-        <v>1.0663</v>
+        <v>1.1675</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3052,13 +3052,13 @@
         <v>6</v>
       </c>
       <c r="B191" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C191" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D191" s="3">
-        <v>1.0550999999999999</v>
+        <v>1.2996000000000001</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3066,13 +3066,13 @@
         <v>6</v>
       </c>
       <c r="B192" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C192" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D192" s="3">
-        <v>1.0621</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3083,10 +3083,10 @@
         <v>2022</v>
       </c>
       <c r="C193" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D193" s="3">
-        <v>1.0516000000000001</v>
+        <v>1.0550999999999999</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3097,10 +3097,10 @@
         <v>2022</v>
       </c>
       <c r="C194" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D194" s="3">
-        <v>1.0001</v>
+        <v>1.0621</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3111,10 +3111,10 @@
         <v>2022</v>
       </c>
       <c r="C195" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D195" s="3">
-        <v>1.4765999999999999</v>
+        <v>1.0516000000000001</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3125,10 +3125,10 @@
         <v>2022</v>
       </c>
       <c r="C196" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D196" s="3">
-        <v>1.0939000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3139,10 +3139,10 @@
         <v>2022</v>
       </c>
       <c r="C197" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D197" s="3">
-        <v>1.2916000000000001</v>
+        <v>1.4765999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3153,10 +3153,10 @@
         <v>2022</v>
       </c>
       <c r="C198" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D198" s="3">
-        <v>1.2714000000000001</v>
+        <v>1.0939000000000001</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3167,10 +3167,10 @@
         <v>2022</v>
       </c>
       <c r="C199" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D199" s="3">
-        <v>1.2466999999999999</v>
+        <v>1.2916000000000001</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3181,10 +3181,10 @@
         <v>2022</v>
       </c>
       <c r="C200" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D200" s="3">
-        <v>1.0482</v>
+        <v>1.2714000000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3195,10 +3195,10 @@
         <v>2022</v>
       </c>
       <c r="C201" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D201" s="3">
-        <v>1.0491999999999999</v>
+        <v>1.2466999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3209,10 +3209,10 @@
         <v>2022</v>
       </c>
       <c r="C202" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D202" s="3">
-        <v>1.2296</v>
+        <v>1.0482</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3220,13 +3220,13 @@
         <v>6</v>
       </c>
       <c r="B203" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D203" s="3">
-        <v>1.2606999999999999</v>
+        <v>1.0491999999999999</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3234,13 +3234,13 @@
         <v>6</v>
       </c>
       <c r="B204" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C204" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D204" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.2296</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3251,10 +3251,10 @@
         <v>2023</v>
       </c>
       <c r="C205" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D205" s="3">
-        <v>1.5298</v>
+        <v>1.2606999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3265,10 +3265,10 @@
         <v>2023</v>
       </c>
       <c r="C206" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D206" s="3">
-        <v>1.1073</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3279,10 +3279,10 @@
         <v>2023</v>
       </c>
       <c r="C207" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D207" s="3">
-        <v>1.0602</v>
+        <v>1.5298</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3293,10 +3293,10 @@
         <v>2023</v>
       </c>
       <c r="C208" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D208" s="3">
-        <v>1.3539999999999999</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3307,10 +3307,10 @@
         <v>2023</v>
       </c>
       <c r="C209" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D209" s="3">
-        <v>1.3968</v>
+        <v>1.0602</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3321,10 +3321,10 @@
         <v>2023</v>
       </c>
       <c r="C210" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D210" s="3">
-        <v>1.2923</v>
+        <v>1.3539999999999999</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3335,10 +3335,10 @@
         <v>2023</v>
       </c>
       <c r="C211" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D211" s="3">
-        <v>1.0855999999999999</v>
+        <v>1.3968</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3349,10 +3349,10 @@
         <v>2023</v>
       </c>
       <c r="C212" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D212" s="3">
-        <v>1.2621</v>
+        <v>1.2923</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3363,10 +3363,10 @@
         <v>2023</v>
       </c>
       <c r="C213" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D213" s="3">
-        <v>1.1758</v>
+        <v>1.0855999999999999</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3377,10 +3377,10 @@
         <v>2023</v>
       </c>
       <c r="C214" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D214" s="3">
-        <v>1.3091999999999999</v>
+        <v>1.2621</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3388,13 +3388,13 @@
         <v>6</v>
       </c>
       <c r="B215" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C215" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D215" s="3">
-        <v>1.5447</v>
+        <v>1.1758</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3402,13 +3402,13 @@
         <v>6</v>
       </c>
       <c r="B216" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C216" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D216" s="3">
-        <v>1.087</v>
+        <v>1.3091999999999999</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3419,10 +3419,10 @@
         <v>2024</v>
       </c>
       <c r="C217" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D217" s="3">
-        <v>0.89500000000000002</v>
+        <v>1.5447</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3433,10 +3433,10 @@
         <v>2024</v>
       </c>
       <c r="C218" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D218" s="3">
-        <v>1.0757000000000001</v>
+        <v>1.087</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3447,10 +3447,10 @@
         <v>2024</v>
       </c>
       <c r="C219" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D219" s="3">
-        <v>1.2897000000000001</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3461,10 +3461,10 @@
         <v>2024</v>
       </c>
       <c r="C220" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D220" s="3">
-        <v>1.3664000000000001</v>
+        <v>1.0757000000000001</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3475,10 +3475,10 @@
         <v>2024</v>
       </c>
       <c r="C221" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D221" s="3">
-        <v>1.2185999999999999</v>
+        <v>1.2897000000000001</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>2024</v>
       </c>
       <c r="C222" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D222" s="3">
-        <v>1.2690999999999999</v>
+        <v>1.3664000000000001</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3503,10 +3503,10 @@
         <v>2024</v>
       </c>
       <c r="C223" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D223" s="3">
-        <v>1.0390999999999999</v>
+        <v>1.2185999999999999</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3517,10 +3517,10 @@
         <v>2024</v>
       </c>
       <c r="C224" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D224" s="3">
-        <v>1.1085</v>
+        <v>1.2690999999999999</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3531,10 +3531,10 @@
         <v>2024</v>
       </c>
       <c r="C225" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D225" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.0390999999999999</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3545,10 +3545,10 @@
         <v>2024</v>
       </c>
       <c r="C226" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D226" s="3">
-        <v>1.0940000000000001</v>
+        <v>1.1085</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3556,13 +3556,13 @@
         <v>6</v>
       </c>
       <c r="B227" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C227" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D227" s="3">
-        <v>0.94689999999999996</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3570,13 +3570,13 @@
         <v>6</v>
       </c>
       <c r="B228" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C228" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D228" s="3">
-        <v>0.95220000000000005</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3587,10 +3587,10 @@
         <v>2025</v>
       </c>
       <c r="C229" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229" s="3">
-        <v>0.95209999999999995</v>
+        <v>0.94689999999999996</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3601,10 +3601,10 @@
         <v>2025</v>
       </c>
       <c r="C230" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D230" s="3">
-        <v>1.0407999999999999</v>
+        <v>0.95220000000000005</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3615,10 +3615,10 @@
         <v>2025</v>
       </c>
       <c r="C231" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D231" s="3">
-        <v>1.1001000000000001</v>
+        <v>0.95209999999999995</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3629,10 +3629,10 @@
         <v>2025</v>
       </c>
       <c r="C232" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D232" s="3">
-        <v>1.0804</v>
+        <v>1.0407999999999999</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3643,10 +3643,10 @@
         <v>2025</v>
       </c>
       <c r="C233" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D233" s="3">
-        <v>1.1061000000000001</v>
+        <v>1.1001000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3657,10 +3657,10 @@
         <v>2025</v>
       </c>
       <c r="C234" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D234" s="3">
-        <v>0.98920000000000008</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3671,10 +3671,10 @@
         <v>2025</v>
       </c>
       <c r="C235" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D235" s="3">
-        <v>1.1734</v>
+        <v>1.1061000000000001</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3685,10 +3685,10 @@
         <v>2025</v>
       </c>
       <c r="C236" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D236" s="3">
-        <v>0.94899999999999995</v>
+        <v>0.98920000000000008</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3699,10 +3699,10 @@
         <v>2025</v>
       </c>
       <c r="C237" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D237" s="3">
-        <v>1.0885</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3713,10 +3713,10 @@
         <v>2025</v>
       </c>
       <c r="C238" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D238" s="3">
-        <v>1.0073000000000001</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3724,13 +3724,13 @@
         <v>6</v>
       </c>
       <c r="B239" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C239" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D239" s="3">
-        <v>0.98619999999999997</v>
+        <v>1.0072000000000001</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3738,13 +3738,13 @@
         <v>6</v>
       </c>
       <c r="B240" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C240" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D240" s="3">
-        <v>0.87270000000000003</v>
+        <v>1.0087999999999999</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3755,10 +3755,10 @@
         <v>2026</v>
       </c>
       <c r="C241" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D241" s="3">
-        <v>0.93330000000000013</v>
+        <v>0.98619999999999997</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3769,52 +3769,52 @@
         <v>2026</v>
       </c>
       <c r="C242" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D242" s="3">
-        <v>0.89370000000000016</v>
+        <v>0.87270000000000003</v>
       </c>
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B243" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C243" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D243" s="3">
-        <v>0.3634</v>
+        <v>0.93330000000000013</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B244" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C244" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D244" s="3">
-        <v>1.1855</v>
+        <v>0.89019999999999999</v>
       </c>
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B245" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C245" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D245" s="3">
-        <v>0.55079999999999996</v>
+        <v>0.89939999999999987</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3825,10 +3825,10 @@
         <v>2019</v>
       </c>
       <c r="C246" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D246" s="3">
-        <v>1.544</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3839,10 +3839,10 @@
         <v>2019</v>
       </c>
       <c r="C247" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D247" s="3">
-        <v>1.5068999999999997</v>
+        <v>1.1855</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3850,13 +3850,13 @@
         <v>7</v>
       </c>
       <c r="B248" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C248" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D248" s="3">
-        <v>0.94199999999999995</v>
+        <v>0.55089999999999995</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3864,13 +3864,13 @@
         <v>7</v>
       </c>
       <c r="B249" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C249" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D249" s="3">
-        <v>1.0011000000000001</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3878,13 +3878,13 @@
         <v>7</v>
       </c>
       <c r="B250" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C250" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D250" s="3">
-        <v>0.96850000000000003</v>
+        <v>1.5068999999999997</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3895,10 +3895,10 @@
         <v>2020</v>
       </c>
       <c r="C251" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D251" s="3">
-        <v>1.0559000000000001</v>
+        <v>0.94199999999999995</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3909,10 +3909,10 @@
         <v>2020</v>
       </c>
       <c r="C252" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D252" s="3">
-        <v>0.91450000000000009</v>
+        <v>1.0011000000000001</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3923,10 +3923,10 @@
         <v>2020</v>
       </c>
       <c r="C253" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D253" s="3">
-        <v>1.0116000000000001</v>
+        <v>0.96850000000000003</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3937,10 +3937,10 @@
         <v>2020</v>
       </c>
       <c r="C254" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D254" s="3">
-        <v>1.3797999999999999</v>
+        <v>1.0559000000000001</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3951,10 +3951,10 @@
         <v>2020</v>
       </c>
       <c r="C255" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D255" s="3">
-        <v>1.4618</v>
+        <v>0.91450000000000009</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3965,10 +3965,10 @@
         <v>2020</v>
       </c>
       <c r="C256" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D256" s="3">
-        <v>1.2636000000000001</v>
+        <v>1.0116000000000001</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3979,10 +3979,10 @@
         <v>2020</v>
       </c>
       <c r="C257" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D257" s="3">
-        <v>1.0907</v>
+        <v>1.3797999999999999</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3993,10 +3993,10 @@
         <v>2020</v>
       </c>
       <c r="C258" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D258" s="3">
-        <v>1.1226</v>
+        <v>1.4618</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4007,10 +4007,10 @@
         <v>2020</v>
       </c>
       <c r="C259" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D259" s="3">
-        <v>1.1798999999999999</v>
+        <v>1.2636000000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4018,13 +4018,13 @@
         <v>7</v>
       </c>
       <c r="B260" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C260" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D260" s="3">
-        <v>1.3149999999999999</v>
+        <v>1.0862000000000001</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4032,13 +4032,13 @@
         <v>7</v>
       </c>
       <c r="B261" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C261" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D261" s="3">
-        <v>1.2918000000000001</v>
+        <v>1.1226</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4046,13 +4046,13 @@
         <v>7</v>
       </c>
       <c r="B262" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C262" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D262" s="3">
-        <v>1.3935</v>
+        <v>1.1798999999999999</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4063,10 +4063,10 @@
         <v>2021</v>
       </c>
       <c r="C263" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D263" s="3">
-        <v>1.6409</v>
+        <v>1.3149999999999999</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4077,10 +4077,10 @@
         <v>2021</v>
       </c>
       <c r="C264" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D264" s="3">
-        <v>1.5944</v>
+        <v>1.2918000000000001</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4091,10 +4091,10 @@
         <v>2021</v>
       </c>
       <c r="C265" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D265" s="3">
-        <v>1.5669999999999999</v>
+        <v>1.3935</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4105,10 +4105,10 @@
         <v>2021</v>
       </c>
       <c r="C266" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D266" s="3">
-        <v>1.276</v>
+        <v>1.6409</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4119,10 +4119,10 @@
         <v>2021</v>
       </c>
       <c r="C267" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D267" s="3">
-        <v>1.1046</v>
+        <v>1.5944</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4133,10 +4133,10 @@
         <v>2021</v>
       </c>
       <c r="C268" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D268" s="3">
-        <v>1.0746</v>
+        <v>1.5669999999999999</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4147,10 +4147,10 @@
         <v>2021</v>
       </c>
       <c r="C269" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D269" s="3">
-        <v>0.95230000000000004</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4161,10 +4161,10 @@
         <v>2021</v>
       </c>
       <c r="C270" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D270" s="3">
-        <v>0.93070000000000008</v>
+        <v>1.1046</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4175,10 +4175,10 @@
         <v>2021</v>
       </c>
       <c r="C271" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D271" s="3">
-        <v>1.0242</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4186,13 +4186,13 @@
         <v>7</v>
       </c>
       <c r="B272" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C272" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D272" s="3">
-        <v>0.95179999999999998</v>
+        <v>0.95230000000000004</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4200,13 +4200,13 @@
         <v>7</v>
       </c>
       <c r="B273" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C273" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D273" s="3">
-        <v>1.1564000000000001</v>
+        <v>0.93070000000000008</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4214,13 +4214,13 @@
         <v>7</v>
       </c>
       <c r="B274" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C274" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D274" s="3">
-        <v>0.93640000000000001</v>
+        <v>1.0242</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4231,10 +4231,10 @@
         <v>2022</v>
       </c>
       <c r="C275" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D275" s="3">
-        <v>0.86789999999999989</v>
+        <v>0.95179999999999998</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4245,10 +4245,10 @@
         <v>2022</v>
       </c>
       <c r="C276" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D276" s="3">
-        <v>0.89589999999999992</v>
+        <v>1.1564000000000001</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4259,10 +4259,10 @@
         <v>2022</v>
       </c>
       <c r="C277" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D277" s="3">
-        <v>0.97230000000000005</v>
+        <v>0.93640000000000001</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4273,10 +4273,10 @@
         <v>2022</v>
       </c>
       <c r="C278" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D278" s="3">
-        <v>1.0585</v>
+        <v>0.86789999999999989</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4287,10 +4287,10 @@
         <v>2022</v>
       </c>
       <c r="C279" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D279" s="3">
-        <v>0.91169999999999995</v>
+        <v>0.89589999999999992</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4301,10 +4301,10 @@
         <v>2022</v>
       </c>
       <c r="C280" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D280" s="3">
-        <v>0.77860000000000007</v>
+        <v>0.97230000000000005</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4315,10 +4315,10 @@
         <v>2022</v>
       </c>
       <c r="C281" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D281" s="3">
-        <v>0.98480000000000001</v>
+        <v>1.0585</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4329,10 +4329,10 @@
         <v>2022</v>
       </c>
       <c r="C282" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D282" s="3">
-        <v>0.96220000000000006</v>
+        <v>0.91169999999999995</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4343,10 +4343,10 @@
         <v>2022</v>
       </c>
       <c r="C283" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D283" s="3">
-        <v>0.89329999999999998</v>
+        <v>0.77860000000000007</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4354,13 +4354,13 @@
         <v>7</v>
       </c>
       <c r="B284" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C284" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D284" s="3">
-        <v>0.99390000000000001</v>
+        <v>0.98480000000000001</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4368,13 +4368,13 @@
         <v>7</v>
       </c>
       <c r="B285" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C285" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D285" s="3">
-        <v>1.0999000000000001</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4382,13 +4382,13 @@
         <v>7</v>
       </c>
       <c r="B286" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C286" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D286" s="3">
-        <v>1.1256999999999999</v>
+        <v>0.89329999999999998</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4399,10 +4399,10 @@
         <v>2023</v>
       </c>
       <c r="C287" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D287" s="3">
-        <v>1.0003</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4413,10 +4413,10 @@
         <v>2023</v>
       </c>
       <c r="C288" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D288" s="3">
-        <v>1.1068</v>
+        <v>1.0999000000000001</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4427,10 +4427,10 @@
         <v>2023</v>
       </c>
       <c r="C289" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D289" s="3">
-        <v>1.0865</v>
+        <v>1.1256999999999999</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4441,10 +4441,10 @@
         <v>2023</v>
       </c>
       <c r="C290" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D290" s="3">
-        <v>0.97589999999999999</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4455,10 +4455,10 @@
         <v>2023</v>
       </c>
       <c r="C291" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D291" s="3">
-        <v>1.0511999999999999</v>
+        <v>1.1068</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4469,10 +4469,10 @@
         <v>2023</v>
       </c>
       <c r="C292" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D292" s="3">
-        <v>1.0577000000000001</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4483,10 +4483,10 @@
         <v>2023</v>
       </c>
       <c r="C293" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D293" s="3">
-        <v>0.97499999999999987</v>
+        <v>0.97589999999999999</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4497,10 +4497,10 @@
         <v>2023</v>
       </c>
       <c r="C294" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D294" s="3">
-        <v>1.0082</v>
+        <v>1.0511999999999999</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4511,10 +4511,10 @@
         <v>2023</v>
       </c>
       <c r="C295" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D295" s="3">
-        <v>1.0295000000000001</v>
+        <v>1.0577000000000001</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4522,13 +4522,13 @@
         <v>7</v>
       </c>
       <c r="B296" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C296" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D296" s="3">
-        <v>0.87479999999999991</v>
+        <v>0.97499999999999987</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4536,13 +4536,13 @@
         <v>7</v>
       </c>
       <c r="B297" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C297" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D297" s="3">
-        <v>0.8629</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4550,13 +4550,13 @@
         <v>7</v>
       </c>
       <c r="B298" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C298" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D298" s="3">
-        <v>0.87240000000000006</v>
+        <v>1.0295000000000001</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4567,10 +4567,10 @@
         <v>2024</v>
       </c>
       <c r="C299" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D299" s="3">
-        <v>1.1091</v>
+        <v>0.87479999999999991</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4581,10 +4581,10 @@
         <v>2024</v>
       </c>
       <c r="C300" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D300" s="3">
-        <v>1.0685</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4595,10 +4595,10 @@
         <v>2024</v>
       </c>
       <c r="C301" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D301" s="3">
-        <v>1.0423</v>
+        <v>0.87240000000000006</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4609,10 +4609,10 @@
         <v>2024</v>
       </c>
       <c r="C302" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D302" s="3">
-        <v>1.1042000000000001</v>
+        <v>1.1091</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4623,10 +4623,10 @@
         <v>2024</v>
       </c>
       <c r="C303" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D303" s="3">
-        <v>1.1225000000000001</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4637,10 +4637,10 @@
         <v>2024</v>
       </c>
       <c r="C304" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D304" s="3">
-        <v>1.2110000000000001</v>
+        <v>1.0423</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4651,10 +4651,10 @@
         <v>2024</v>
       </c>
       <c r="C305" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D305" s="3">
-        <v>1.2477</v>
+        <v>1.1042000000000001</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4665,10 +4665,10 @@
         <v>2024</v>
       </c>
       <c r="C306" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D306" s="3">
-        <v>1.1498999999999999</v>
+        <v>1.1225000000000001</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4679,10 +4679,10 @@
         <v>2024</v>
       </c>
       <c r="C307" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D307" s="3">
-        <v>1.2698</v>
+        <v>1.2110000000000001</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4690,13 +4690,13 @@
         <v>7</v>
       </c>
       <c r="B308" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C308" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D308" s="3">
-        <v>1.0690999999999999</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4704,13 +4704,13 @@
         <v>7</v>
       </c>
       <c r="B309" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C309" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D309" s="3">
-        <v>1.0788</v>
+        <v>1.1498999999999999</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4718,13 +4718,13 @@
         <v>7</v>
       </c>
       <c r="B310" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C310" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D310" s="3">
-        <v>1.206</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4735,10 +4735,10 @@
         <v>2025</v>
       </c>
       <c r="C311" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D311" s="3">
-        <v>1.1214999999999999</v>
+        <v>1.0773999999999999</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4749,10 +4749,10 @@
         <v>2025</v>
       </c>
       <c r="C312" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D312" s="3">
-        <v>1.1348</v>
+        <v>1.0772999999999999</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4763,10 +4763,10 @@
         <v>2025</v>
       </c>
       <c r="C313" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D313" s="3">
-        <v>1.2157000000000002</v>
+        <v>1.2062999999999999</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4777,10 +4777,10 @@
         <v>2025</v>
       </c>
       <c r="C314" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D314" s="3">
-        <v>1.3216000000000001</v>
+        <v>1.1231</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4791,10 +4791,10 @@
         <v>2025</v>
       </c>
       <c r="C315" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D315" s="3">
-        <v>1.1874</v>
+        <v>1.1679999999999999</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4805,10 +4805,10 @@
         <v>2025</v>
       </c>
       <c r="C316" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D316" s="3">
-        <v>1.1946000000000001</v>
+        <v>1.1792</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4819,10 +4819,10 @@
         <v>2025</v>
       </c>
       <c r="C317" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D317" s="3">
-        <v>1.355</v>
+        <v>1.3216000000000001</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4833,10 +4833,10 @@
         <v>2025</v>
       </c>
       <c r="C318" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D318" s="3">
-        <v>1.3223</v>
+        <v>1.1874</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4847,10 +4847,10 @@
         <v>2025</v>
       </c>
       <c r="C319" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D319" s="3">
-        <v>1.1866000000000001</v>
+        <v>1.1955</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4858,13 +4858,13 @@
         <v>7</v>
       </c>
       <c r="B320" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C320" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D320" s="3">
-        <v>1.1228</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4872,13 +4872,13 @@
         <v>7</v>
       </c>
       <c r="B321" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C321" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D321" s="3">
-        <v>1.2611000000000001</v>
+        <v>1.3223</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4886,13 +4886,13 @@
         <v>7</v>
       </c>
       <c r="B322" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C322" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D322" s="3">
-        <v>1.8692</v>
+        <v>1.1875</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4903,66 +4903,66 @@
         <v>2026</v>
       </c>
       <c r="C323" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D323" s="3">
-        <v>1.2091000000000001</v>
+        <v>1.1228</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B324" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C324" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D324" s="3">
-        <v>0.46260000000000001</v>
+        <v>1.2611000000000001</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B325" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C325" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D325" s="3">
-        <v>2.5009999999999999</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B326" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C326" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D326" s="3">
-        <v>0.60919999999999996</v>
+        <v>1.2192000000000001</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B327" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C327" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D327" s="3">
-        <v>0.43890000000000001</v>
+        <v>1.1336999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4970,13 +4970,13 @@
         <v>8</v>
       </c>
       <c r="B328" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C328" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D328" s="3">
-        <v>0.58919999999999995</v>
+        <v>0.46260000000000001</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4984,13 +4984,13 @@
         <v>8</v>
       </c>
       <c r="B329" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C329" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D329" s="3">
-        <v>1.8193999999999997</v>
+        <v>2.5009999999999999</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -4998,13 +4998,13 @@
         <v>8</v>
       </c>
       <c r="B330" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C330" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D330" s="3">
-        <v>1.2989999999999999</v>
+        <v>0.60919999999999996</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5015,10 +5015,10 @@
         <v>2020</v>
       </c>
       <c r="C331" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D331" s="3">
-        <v>1.3857999999999999</v>
+        <v>0.43890000000000001</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5029,10 +5029,10 @@
         <v>2020</v>
       </c>
       <c r="C332" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D332" s="3">
-        <v>1.9608000000000001</v>
+        <v>0.58919999999999995</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5043,10 +5043,10 @@
         <v>2020</v>
       </c>
       <c r="C333" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D333" s="3">
-        <v>1.8338000000000001</v>
+        <v>1.8193999999999997</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5057,10 +5057,10 @@
         <v>2020</v>
       </c>
       <c r="C334" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D334" s="3">
-        <v>1.7322999999999997</v>
+        <v>1.2989999999999999</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5071,10 +5071,10 @@
         <v>2020</v>
       </c>
       <c r="C335" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D335" s="3">
-        <v>1.8411999999999999</v>
+        <v>1.3857999999999999</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5085,10 +5085,10 @@
         <v>2020</v>
       </c>
       <c r="C336" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D336" s="3">
-        <v>1.8994</v>
+        <v>1.9608000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5099,10 +5099,10 @@
         <v>2020</v>
       </c>
       <c r="C337" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D337" s="3">
-        <v>1.7765999999999997</v>
+        <v>1.8338000000000001</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5110,13 +5110,13 @@
         <v>8</v>
       </c>
       <c r="B338" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C338" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D338" s="3">
-        <v>1.5302</v>
+        <v>1.7322999999999997</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5124,13 +5124,13 @@
         <v>8</v>
       </c>
       <c r="B339" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C339" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D339" s="3">
-        <v>1.7687000000000002</v>
+        <v>1.8366</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5138,13 +5138,13 @@
         <v>8</v>
       </c>
       <c r="B340" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C340" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D340" s="3">
-        <v>1.3537999999999999</v>
+        <v>1.8994</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5152,13 +5152,13 @@
         <v>8</v>
       </c>
       <c r="B341" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C341" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D341" s="3">
-        <v>1.1635</v>
+        <v>1.7765999999999997</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5169,10 +5169,10 @@
         <v>2021</v>
       </c>
       <c r="C342" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D342" s="3">
-        <v>1.9408000000000003</v>
+        <v>1.5302</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5183,10 +5183,10 @@
         <v>2021</v>
       </c>
       <c r="C343" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D343" s="3">
-        <v>1.2329000000000001</v>
+        <v>1.7687000000000002</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5197,10 +5197,10 @@
         <v>2021</v>
       </c>
       <c r="C344" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D344" s="3">
-        <v>1.3947000000000001</v>
+        <v>1.3537999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5211,10 +5211,10 @@
         <v>2021</v>
       </c>
       <c r="C345" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D345" s="3">
-        <v>1.323</v>
+        <v>1.1635</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5225,10 +5225,10 @@
         <v>2021</v>
       </c>
       <c r="C346" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D346" s="3">
-        <v>1.4914000000000001</v>
+        <v>1.9408000000000003</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5239,10 +5239,10 @@
         <v>2021</v>
       </c>
       <c r="C347" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D347" s="3">
-        <v>1.4085000000000001</v>
+        <v>1.2329000000000001</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5253,10 +5253,10 @@
         <v>2021</v>
       </c>
       <c r="C348" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D348" s="3">
-        <v>1.429</v>
+        <v>1.3917999999999999</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5267,10 +5267,10 @@
         <v>2021</v>
       </c>
       <c r="C349" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D349" s="3">
-        <v>1.3602000000000001</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5278,13 +5278,13 @@
         <v>8</v>
       </c>
       <c r="B350" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C350" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D350" s="3">
-        <v>1.4053</v>
+        <v>1.4914000000000001</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5292,13 +5292,13 @@
         <v>8</v>
       </c>
       <c r="B351" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C351" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D351" s="3">
-        <v>1.4612000000000001</v>
+        <v>1.4085000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5306,13 +5306,13 @@
         <v>8</v>
       </c>
       <c r="B352" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C352" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D352" s="3">
-        <v>1.4157999999999999</v>
+        <v>1.4259999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5320,13 +5320,13 @@
         <v>8</v>
       </c>
       <c r="B353" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C353" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D353" s="3">
-        <v>1.4791999999999998</v>
+        <v>1.3572</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5337,10 +5337,10 @@
         <v>2022</v>
       </c>
       <c r="C354" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D354" s="3">
-        <v>1.4762999999999999</v>
+        <v>1.4053</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5351,10 +5351,10 @@
         <v>2022</v>
       </c>
       <c r="C355" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D355" s="3">
-        <v>1.4380999999999999</v>
+        <v>1.4612000000000001</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5365,10 +5365,10 @@
         <v>2022</v>
       </c>
       <c r="C356" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D356" s="3">
-        <v>1.6324000000000001</v>
+        <v>1.4157999999999999</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5379,10 +5379,10 @@
         <v>2022</v>
       </c>
       <c r="C357" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D357" s="3">
-        <v>1.5557000000000001</v>
+        <v>1.4791999999999998</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5393,10 +5393,10 @@
         <v>2022</v>
       </c>
       <c r="C358" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D358" s="3">
-        <v>1.599</v>
+        <v>1.4762999999999999</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5407,10 +5407,10 @@
         <v>2022</v>
       </c>
       <c r="C359" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D359" s="3">
-        <v>1.4990000000000001</v>
+        <v>1.4380999999999999</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5421,10 +5421,10 @@
         <v>2022</v>
       </c>
       <c r="C360" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="3">
-        <v>1.484</v>
+        <v>1.6324000000000001</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5435,10 +5435,10 @@
         <v>2022</v>
       </c>
       <c r="C361" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D361" s="3">
-        <v>1.5085999999999999</v>
+        <v>1.5557000000000001</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5446,13 +5446,13 @@
         <v>8</v>
       </c>
       <c r="B362" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C362" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D362" s="3">
-        <v>1.4896</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5460,13 +5460,13 @@
         <v>8</v>
       </c>
       <c r="B363" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C363" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="3">
-        <v>1.5462999999999998</v>
+        <v>1.4990000000000001</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5474,13 +5474,13 @@
         <v>8</v>
       </c>
       <c r="B364" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C364" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D364" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5488,13 +5488,13 @@
         <v>8</v>
       </c>
       <c r="B365" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C365" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D365" s="3">
-        <v>1.3847</v>
+        <v>1.5085999999999999</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5505,10 +5505,10 @@
         <v>2023</v>
       </c>
       <c r="C366" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D366" s="3">
-        <v>1.2858000000000001</v>
+        <v>1.4896</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5519,10 +5519,10 @@
         <v>2023</v>
       </c>
       <c r="C367" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D367" s="3">
-        <v>1.8708</v>
+        <v>1.5462999999999998</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5533,10 +5533,10 @@
         <v>2023</v>
       </c>
       <c r="C368" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D368" s="3">
-        <v>1.8864000000000001</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5547,10 +5547,10 @@
         <v>2023</v>
       </c>
       <c r="C369" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D369" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.3847</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5561,10 +5561,10 @@
         <v>2023</v>
       </c>
       <c r="C370" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D370" s="3">
-        <v>1.9263999999999999</v>
+        <v>1.2858000000000001</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5575,10 +5575,10 @@
         <v>2023</v>
       </c>
       <c r="C371" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D371" s="3">
-        <v>1.9342999999999999</v>
+        <v>1.8708</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5589,10 +5589,10 @@
         <v>2023</v>
       </c>
       <c r="C372" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D372" s="3">
-        <v>1.7403999999999999</v>
+        <v>1.8864000000000001</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5603,10 +5603,10 @@
         <v>2023</v>
       </c>
       <c r="C373" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D373" s="3">
-        <v>1.7998000000000001</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5614,13 +5614,13 @@
         <v>8</v>
       </c>
       <c r="B374" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C374" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D374" s="3">
-        <v>1.8641000000000001</v>
+        <v>1.9263999999999999</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5628,13 +5628,13 @@
         <v>8</v>
       </c>
       <c r="B375" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C375" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D375" s="3">
-        <v>2.0535999999999999</v>
+        <v>1.9342999999999999</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5642,13 +5642,13 @@
         <v>8</v>
       </c>
       <c r="B376" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C376" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D376" s="3">
-        <v>1.8251999999999999</v>
+        <v>1.7403999999999999</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5656,13 +5656,13 @@
         <v>8</v>
       </c>
       <c r="B377" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C377" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D377" s="3">
-        <v>1.8498000000000001</v>
+        <v>1.7998000000000001</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5673,10 +5673,10 @@
         <v>2024</v>
       </c>
       <c r="C378" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D378" s="3">
-        <v>1.8720000000000001</v>
+        <v>1.8641000000000001</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5687,10 +5687,10 @@
         <v>2024</v>
       </c>
       <c r="C379" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D379" s="3">
-        <v>1.8865000000000001</v>
+        <v>2.0535999999999999</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5701,10 +5701,10 @@
         <v>2024</v>
       </c>
       <c r="C380" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D380" s="3">
-        <v>1.6568000000000001</v>
+        <v>1.8251999999999999</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5715,10 +5715,10 @@
         <v>2024</v>
       </c>
       <c r="C381" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D381" s="3">
-        <v>1.8308</v>
+        <v>1.8498000000000001</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5729,10 +5729,10 @@
         <v>2024</v>
       </c>
       <c r="C382" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D382" s="3">
-        <v>1.8855</v>
+        <v>1.8720000000000001</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5743,10 +5743,10 @@
         <v>2024</v>
       </c>
       <c r="C383" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D383" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.8865000000000001</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5757,10 +5757,10 @@
         <v>2024</v>
       </c>
       <c r="C384" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D384" s="3">
-        <v>1.8120000000000001</v>
+        <v>1.6568000000000001</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5771,10 +5771,10 @@
         <v>2024</v>
       </c>
       <c r="C385" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D385" s="3">
-        <v>1.7609999999999999</v>
+        <v>1.8308</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5782,13 +5782,13 @@
         <v>8</v>
       </c>
       <c r="B386" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C386" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D386" s="3">
-        <v>1.7804</v>
+        <v>1.8752</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5796,13 +5796,13 @@
         <v>8</v>
       </c>
       <c r="B387" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C387" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D387" s="3">
-        <v>1.6728000000000001</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5810,13 +5810,13 @@
         <v>8</v>
       </c>
       <c r="B388" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C388" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D388" s="3">
-        <v>1.7315</v>
+        <v>1.8120000000000001</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5824,13 +5824,13 @@
         <v>8</v>
       </c>
       <c r="B389" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C389" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D389" s="3">
-        <v>1.4521999999999999</v>
+        <v>1.7609999999999999</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5841,10 +5841,10 @@
         <v>2025</v>
       </c>
       <c r="C390" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D390" s="3">
-        <v>1.4100999999999999</v>
+        <v>1.7717000000000001</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5855,10 +5855,10 @@
         <v>2025</v>
       </c>
       <c r="C391" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D391" s="3">
-        <v>1.5999000000000001</v>
+        <v>1.6231</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5869,10 +5869,10 @@
         <v>2025</v>
       </c>
       <c r="C392" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D392" s="3">
-        <v>1.5866</v>
+        <v>1.706</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5883,10 +5883,10 @@
         <v>2025</v>
       </c>
       <c r="C393" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D393" s="3">
-        <v>1.5343</v>
+        <v>1.4521999999999999</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5897,10 +5897,10 @@
         <v>2025</v>
       </c>
       <c r="C394" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D394" s="3">
-        <v>1.5347</v>
+        <v>1.4100999999999999</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5911,10 +5911,10 @@
         <v>2025</v>
       </c>
       <c r="C395" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D395" s="3">
-        <v>1.5016</v>
+        <v>1.5933999999999999</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5925,10 +5925,10 @@
         <v>2025</v>
       </c>
       <c r="C396" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3">
-        <v>1.7339</v>
+        <v>1.5374000000000001</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5939,10 +5939,10 @@
         <v>2025</v>
       </c>
       <c r="C397" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D397" s="3">
-        <v>1.7327999999999999</v>
+        <v>1.5250999999999999</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5950,13 +5950,13 @@
         <v>8</v>
       </c>
       <c r="B398" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C398" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D398" s="3">
-        <v>1.4160999999999999</v>
+        <v>1.4985999999999999</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5964,13 +5964,13 @@
         <v>8</v>
       </c>
       <c r="B399" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C399" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3">
-        <v>1.5978000000000003</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -5978,13 +5978,13 @@
         <v>8</v>
       </c>
       <c r="B400" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C400" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D400" s="3">
-        <v>1.4392</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -5992,83 +5992,83 @@
         <v>8</v>
       </c>
       <c r="B401" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C401" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D401" s="3">
-        <v>1.3847</v>
+        <v>1.7341</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B402" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C402" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D402" s="3">
-        <v>1.1920999999999999</v>
+        <v>1.4160999999999999</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B403" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C403" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D403" s="3">
-        <v>0.9788</v>
+        <v>1.5978000000000003</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B404" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C404" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D404" s="3">
-        <v>1.3588</v>
+        <v>1.4392</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B405" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C405" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D405" s="3">
-        <v>1.3531</v>
+        <v>1.3837999999999997</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B406" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C406" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D406" s="3">
-        <v>1.4061999999999999</v>
+        <v>1.6129</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6079,10 +6079,10 @@
         <v>2019</v>
       </c>
       <c r="C407" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D407" s="3">
-        <v>1.1672</v>
+        <v>1.1920999999999999</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6093,10 +6093,10 @@
         <v>2019</v>
       </c>
       <c r="C408" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D408" s="3">
-        <v>1.5024</v>
+        <v>0.9788</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6107,10 +6107,10 @@
         <v>2019</v>
       </c>
       <c r="C409" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D409" s="3">
-        <v>1.1561999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6118,13 +6118,13 @@
         <v>9</v>
       </c>
       <c r="B410" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C410" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D410" s="3">
-        <v>1.1536999999999999</v>
+        <v>1.3531</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6132,13 +6132,13 @@
         <v>9</v>
       </c>
       <c r="B411" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C411" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D411" s="3">
-        <v>1.0632999999999999</v>
+        <v>1.4061999999999999</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6146,13 +6146,13 @@
         <v>9</v>
       </c>
       <c r="B412" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C412" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D412" s="3">
-        <v>1.0150999999999999</v>
+        <v>1.1672</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6160,13 +6160,13 @@
         <v>9</v>
       </c>
       <c r="B413" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C413" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D413" s="3">
-        <v>1.1227</v>
+        <v>1.5024</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6174,13 +6174,13 @@
         <v>9</v>
       </c>
       <c r="B414" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C414" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D414" s="3">
-        <v>1.0437000000000001</v>
+        <v>1.1561999999999999</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6191,10 +6191,10 @@
         <v>2020</v>
       </c>
       <c r="C415" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D415" s="3">
-        <v>1.2843</v>
+        <v>1.1488</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6205,10 +6205,10 @@
         <v>2020</v>
       </c>
       <c r="C416" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D416" s="3">
-        <v>1.3385</v>
+        <v>1.0632999999999999</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6219,10 +6219,10 @@
         <v>2020</v>
       </c>
       <c r="C417" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D417" s="3">
-        <v>1.6960999999999999</v>
+        <v>1.0150999999999999</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6233,10 +6233,10 @@
         <v>2020</v>
       </c>
       <c r="C418" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D418" s="3">
-        <v>1.4695</v>
+        <v>1.1227</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6247,10 +6247,10 @@
         <v>2020</v>
       </c>
       <c r="C419" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D419" s="3">
-        <v>1.4509000000000001</v>
+        <v>1.0437000000000001</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6261,10 +6261,10 @@
         <v>2020</v>
       </c>
       <c r="C420" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D420" s="3">
-        <v>1.4291</v>
+        <v>1.2843</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6275,10 +6275,10 @@
         <v>2020</v>
       </c>
       <c r="C421" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D421" s="3">
-        <v>1.2766</v>
+        <v>1.3385</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6286,13 +6286,13 @@
         <v>9</v>
       </c>
       <c r="B422" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C422" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D422" s="3">
-        <v>1.2372000000000001</v>
+        <v>1.6960999999999999</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6300,13 +6300,13 @@
         <v>9</v>
       </c>
       <c r="B423" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C423" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D423" s="3">
-        <v>1.3984000000000001</v>
+        <v>1.4695</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6314,13 +6314,13 @@
         <v>9</v>
       </c>
       <c r="B424" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C424" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D424" s="3">
-        <v>1.2039</v>
+        <v>1.4509000000000001</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6328,13 +6328,13 @@
         <v>9</v>
       </c>
       <c r="B425" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C425" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D425" s="3">
-        <v>1.2987</v>
+        <v>1.4291</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6342,13 +6342,13 @@
         <v>9</v>
       </c>
       <c r="B426" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C426" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D426" s="3">
-        <v>1.2281</v>
+        <v>1.2766</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6359,10 +6359,10 @@
         <v>2021</v>
       </c>
       <c r="C427" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D427" s="3">
-        <v>1.3234999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6373,10 +6373,10 @@
         <v>2021</v>
       </c>
       <c r="C428" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D428" s="3">
-        <v>1.2829999999999999</v>
+        <v>1.3984000000000001</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6387,10 +6387,10 @@
         <v>2021</v>
       </c>
       <c r="C429" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D429" s="3">
-        <v>1.1142000000000001</v>
+        <v>1.2039</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6401,10 +6401,10 @@
         <v>2021</v>
       </c>
       <c r="C430" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D430" s="3">
-        <v>0.96379999999999988</v>
+        <v>1.2943</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6415,10 +6415,10 @@
         <v>2021</v>
       </c>
       <c r="C431" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D431" s="3">
-        <v>1.0775999999999999</v>
+        <v>1.2281</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6429,10 +6429,10 @@
         <v>2021</v>
       </c>
       <c r="C432" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D432" s="3">
-        <v>1.1780999999999999</v>
+        <v>1.3234999999999999</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6443,10 +6443,10 @@
         <v>2021</v>
       </c>
       <c r="C433" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D433" s="3">
-        <v>1.0859000000000001</v>
+        <v>1.2829999999999999</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6454,13 +6454,13 @@
         <v>9</v>
       </c>
       <c r="B434" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C434" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D434" s="3">
-        <v>1.1252</v>
+        <v>1.1142000000000001</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6468,13 +6468,13 @@
         <v>9</v>
       </c>
       <c r="B435" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C435" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D435" s="3">
-        <v>1.1546000000000001</v>
+        <v>0.96379999999999988</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6482,13 +6482,13 @@
         <v>9</v>
       </c>
       <c r="B436" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C436" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D436" s="3">
-        <v>1.0673999999999999</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6496,13 +6496,13 @@
         <v>9</v>
       </c>
       <c r="B437" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C437" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D437" s="3">
-        <v>1.1517999999999999</v>
+        <v>1.1780999999999999</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6510,13 +6510,13 @@
         <v>9</v>
       </c>
       <c r="B438" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C438" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D438" s="3">
-        <v>1.1574</v>
+        <v>1.0859000000000001</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6527,10 +6527,10 @@
         <v>2022</v>
       </c>
       <c r="C439" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D439" s="3">
-        <v>1.1416999999999999</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6541,10 +6541,10 @@
         <v>2022</v>
       </c>
       <c r="C440" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D440" s="3">
-        <v>1.2119</v>
+        <v>1.1546000000000001</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6555,10 +6555,10 @@
         <v>2022</v>
       </c>
       <c r="C441" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D441" s="3">
-        <v>1.1833</v>
+        <v>1.0673999999999999</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6569,10 +6569,10 @@
         <v>2022</v>
       </c>
       <c r="C442" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D442" s="3">
-        <v>1.2625</v>
+        <v>1.1517999999999999</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6583,10 +6583,10 @@
         <v>2022</v>
       </c>
       <c r="C443" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D443" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6597,10 +6597,10 @@
         <v>2022</v>
       </c>
       <c r="C444" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D444" s="3">
-        <v>1.2148000000000001</v>
+        <v>1.1416999999999999</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6611,10 +6611,10 @@
         <v>2022</v>
       </c>
       <c r="C445" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D445" s="3">
-        <v>1.1067</v>
+        <v>1.2119</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6622,13 +6622,13 @@
         <v>9</v>
       </c>
       <c r="B446" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C446" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D446" s="3">
-        <v>1.1968000000000001</v>
+        <v>1.1833</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6636,13 +6636,13 @@
         <v>9</v>
       </c>
       <c r="B447" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C447" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D447" s="3">
-        <v>1.032</v>
+        <v>1.2625</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6650,13 +6650,13 @@
         <v>9</v>
       </c>
       <c r="B448" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C448" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D448" s="3">
-        <v>1.0803</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6664,13 +6664,13 @@
         <v>9</v>
       </c>
       <c r="B449" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C449" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D449" s="3">
-        <v>1.1644000000000001</v>
+        <v>1.2148000000000001</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6678,13 +6678,13 @@
         <v>9</v>
       </c>
       <c r="B450" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C450" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D450" s="3">
-        <v>1.2673000000000001</v>
+        <v>1.1067</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6695,10 +6695,10 @@
         <v>2023</v>
       </c>
       <c r="C451" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D451" s="3">
-        <v>1.1983999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6709,10 +6709,10 @@
         <v>2023</v>
       </c>
       <c r="C452" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D452" s="3">
-        <v>1.3575999999999999</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6723,10 +6723,10 @@
         <v>2023</v>
       </c>
       <c r="C453" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D453" s="3">
-        <v>1.3444</v>
+        <v>1.0803</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6737,10 +6737,10 @@
         <v>2023</v>
       </c>
       <c r="C454" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D454" s="3">
-        <v>1.2949999999999999</v>
+        <v>1.1644000000000001</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6751,10 +6751,10 @@
         <v>2023</v>
       </c>
       <c r="C455" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D455" s="3">
-        <v>1.2145999999999999</v>
+        <v>1.2673000000000001</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6765,10 +6765,10 @@
         <v>2023</v>
       </c>
       <c r="C456" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D456" s="3">
-        <v>1.2192000000000001</v>
+        <v>1.1983999999999999</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6779,10 +6779,10 @@
         <v>2023</v>
       </c>
       <c r="C457" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D457" s="3">
-        <v>1.3759999999999999</v>
+        <v>1.3575999999999999</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6790,13 +6790,13 @@
         <v>9</v>
       </c>
       <c r="B458" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C458" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D458" s="3">
-        <v>1.3194999999999999</v>
+        <v>1.3444</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6804,13 +6804,13 @@
         <v>9</v>
       </c>
       <c r="B459" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C459" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D459" s="3">
-        <v>1.4132</v>
+        <v>1.2949999999999999</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6818,13 +6818,13 @@
         <v>9</v>
       </c>
       <c r="B460" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C460" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D460" s="3">
-        <v>1.6296000000000002</v>
+        <v>1.2145999999999999</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6832,13 +6832,13 @@
         <v>9</v>
       </c>
       <c r="B461" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C461" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D461" s="3">
-        <v>1.4339</v>
+        <v>1.2192000000000001</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6846,13 +6846,13 @@
         <v>9</v>
       </c>
       <c r="B462" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C462" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D462" s="3">
-        <v>1.2652000000000001</v>
+        <v>1.3759999999999999</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6863,10 +6863,10 @@
         <v>2024</v>
       </c>
       <c r="C463" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D463" s="3">
-        <v>1.4533</v>
+        <v>1.3194999999999999</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6877,10 +6877,10 @@
         <v>2024</v>
       </c>
       <c r="C464" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D464" s="3">
-        <v>1.3996999999999999</v>
+        <v>1.4132</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6891,10 +6891,10 @@
         <v>2024</v>
       </c>
       <c r="C465" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D465" s="3">
-        <v>1.2509999999999999</v>
+        <v>1.6296000000000002</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6905,10 +6905,10 @@
         <v>2024</v>
       </c>
       <c r="C466" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D466" s="3">
-        <v>1.2806999999999999</v>
+        <v>1.4339</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6919,10 +6919,10 @@
         <v>2024</v>
       </c>
       <c r="C467" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D467" s="3">
-        <v>1.2095</v>
+        <v>1.2652000000000001</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6933,10 +6933,10 @@
         <v>2024</v>
       </c>
       <c r="C468" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D468" s="3">
-        <v>1.2222999999999999</v>
+        <v>1.4533</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6947,10 +6947,10 @@
         <v>2024</v>
       </c>
       <c r="C469" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D469" s="3">
-        <v>1.2697000000000001</v>
+        <v>1.3996999999999999</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6958,13 +6958,13 @@
         <v>9</v>
       </c>
       <c r="B470" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C470" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D470" s="3">
-        <v>1.1957</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6972,13 +6972,13 @@
         <v>9</v>
       </c>
       <c r="B471" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C471" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D471" s="3">
-        <v>1.5154999999999998</v>
+        <v>1.2806999999999999</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6986,13 +6986,13 @@
         <v>9</v>
       </c>
       <c r="B472" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C472" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D472" s="3">
-        <v>1.2682</v>
+        <v>1.2095</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7000,13 +7000,13 @@
         <v>9</v>
       </c>
       <c r="B473" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C473" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D473" s="3">
-        <v>1.2907999999999999</v>
+        <v>1.2222999999999999</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7014,13 +7014,13 @@
         <v>9</v>
       </c>
       <c r="B474" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C474" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D474" s="3">
-        <v>1.2582</v>
+        <v>1.2697000000000001</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7031,10 +7031,10 @@
         <v>2025</v>
       </c>
       <c r="C475" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D475" s="3">
-        <v>1.3306</v>
+        <v>1.1957</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7045,10 +7045,10 @@
         <v>2025</v>
       </c>
       <c r="C476" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D476" s="3">
-        <v>1.4423999999999999</v>
+        <v>1.5154999999999998</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7059,10 +7059,10 @@
         <v>2025</v>
       </c>
       <c r="C477" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D477" s="3">
-        <v>1.3319000000000001</v>
+        <v>1.2682</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7073,10 +7073,10 @@
         <v>2025</v>
       </c>
       <c r="C478" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D478" s="3">
-        <v>1.3214999999999999</v>
+        <v>1.2907999999999999</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7087,10 +7087,10 @@
         <v>2025</v>
       </c>
       <c r="C479" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D479" s="3">
-        <v>1.4823</v>
+        <v>1.2582</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7101,10 +7101,10 @@
         <v>2025</v>
       </c>
       <c r="C480" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D480" s="3">
-        <v>1.3943000000000001</v>
+        <v>1.3306</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7115,10 +7115,10 @@
         <v>2025</v>
       </c>
       <c r="C481" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D481" s="3">
-        <v>1.4936999999999998</v>
+        <v>1.4423999999999999</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7126,13 +7126,13 @@
         <v>9</v>
       </c>
       <c r="B482" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C482" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D482" s="3">
-        <v>1.6764999999999999</v>
+        <v>1.3319000000000001</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7140,13 +7140,13 @@
         <v>9</v>
       </c>
       <c r="B483" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C483" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D483" s="3">
-        <v>1.5677000000000001</v>
+        <v>1.3214999999999999</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7154,13 +7154,13 @@
         <v>9</v>
       </c>
       <c r="B484" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C484" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D484" s="3">
-        <v>1.5889</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7168,97 +7168,97 @@
         <v>9</v>
       </c>
       <c r="B485" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C485" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D485" s="3">
-        <v>1.6122000000000001</v>
+        <v>1.3943000000000001</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B486" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C486" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D486" s="3">
-        <v>1.8255999999999999</v>
+        <v>1.4936999999999998</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B487" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C487" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D487" s="3">
-        <v>2.1966999999999999</v>
+        <v>1.6764999999999999</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B488" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C488" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D488" s="3">
-        <v>0.69</v>
+        <v>1.5677000000000001</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B489" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C489" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D489" s="3">
-        <v>2.2656000000000001</v>
+        <v>1.5889</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B490" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C490" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D490" s="3">
-        <v>2.3290999999999999</v>
+        <v>1.6122000000000001</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B491" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C491" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D491" s="3">
-        <v>1.9074</v>
+        <v>1.5459000000000001</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7269,10 +7269,10 @@
         <v>2019</v>
       </c>
       <c r="C492" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D492" s="3">
-        <v>1.6099000000000001</v>
+        <v>1.8255999999999999</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7280,13 +7280,13 @@
         <v>10</v>
       </c>
       <c r="B493" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C493" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D493" s="3">
-        <v>1.2122999999999999</v>
+        <v>2.1966999999999999</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7294,13 +7294,13 @@
         <v>10</v>
       </c>
       <c r="B494" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C494" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D494" s="3">
-        <v>1.2574000000000001</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7308,13 +7308,13 @@
         <v>10</v>
       </c>
       <c r="B495" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C495" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D495" s="3">
-        <v>1.0529999999999999</v>
+        <v>2.2656000000000001</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7322,13 +7322,13 @@
         <v>10</v>
       </c>
       <c r="B496" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C496" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D496" s="3">
-        <v>1.3588</v>
+        <v>2.3290999999999999</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7336,13 +7336,13 @@
         <v>10</v>
       </c>
       <c r="B497" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C497" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D497" s="3">
-        <v>1.9334999999999998</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7350,13 +7350,13 @@
         <v>10</v>
       </c>
       <c r="B498" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C498" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D498" s="3">
-        <v>1.3191999999999997</v>
+        <v>1.6099000000000001</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7367,10 +7367,10 @@
         <v>2020</v>
       </c>
       <c r="C499" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D499" s="3">
-        <v>1.8477000000000001</v>
+        <v>1.2122999999999999</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7381,10 +7381,10 @@
         <v>2020</v>
       </c>
       <c r="C500" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D500" s="3">
-        <v>1.6778</v>
+        <v>1.2574000000000001</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7395,10 +7395,10 @@
         <v>2020</v>
       </c>
       <c r="C501" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D501" s="3">
-        <v>1.6319999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7409,10 +7409,10 @@
         <v>2020</v>
       </c>
       <c r="C502" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D502" s="3">
-        <v>2.4281999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7423,10 +7423,10 @@
         <v>2020</v>
       </c>
       <c r="C503" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D503" s="3">
-        <v>2.7423999999999999</v>
+        <v>1.9334999999999998</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7434,13 +7434,13 @@
         <v>10</v>
       </c>
       <c r="B504" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C504" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D504" s="3">
-        <v>1.9238999999999999</v>
+        <v>1.3191999999999997</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7448,13 +7448,13 @@
         <v>10</v>
       </c>
       <c r="B505" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C505" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D505" s="3">
-        <v>1.8746</v>
+        <v>1.8477000000000001</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7462,13 +7462,13 @@
         <v>10</v>
       </c>
       <c r="B506" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C506" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D506" s="3">
-        <v>2.1867999999999999</v>
+        <v>1.6778</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7476,13 +7476,13 @@
         <v>10</v>
       </c>
       <c r="B507" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C507" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D507" s="3">
-        <v>1.6684000000000003</v>
+        <v>1.6319999999999999</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7490,13 +7490,13 @@
         <v>10</v>
       </c>
       <c r="B508" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C508" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D508" s="3">
-        <v>1.8869</v>
+        <v>2.4281999999999999</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7504,13 +7504,13 @@
         <v>10</v>
       </c>
       <c r="B509" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C509" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D509" s="3">
-        <v>1.7607000000000002</v>
+        <v>2.7423999999999999</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7521,10 +7521,10 @@
         <v>2021</v>
       </c>
       <c r="C510" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D510" s="3">
-        <v>2.3298999999999999</v>
+        <v>1.9238999999999999</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7535,10 +7535,10 @@
         <v>2021</v>
       </c>
       <c r="C511" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D511" s="3">
-        <v>2.0569000000000002</v>
+        <v>1.8746</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7549,10 +7549,10 @@
         <v>2021</v>
       </c>
       <c r="C512" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D512" s="3">
-        <v>2.5038999999999998</v>
+        <v>2.1867999999999999</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7563,10 +7563,10 @@
         <v>2021</v>
       </c>
       <c r="C513" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D513" s="3">
-        <v>1.728</v>
+        <v>1.6684000000000003</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -7577,10 +7577,10 @@
         <v>2021</v>
       </c>
       <c r="C514" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D514" s="3">
-        <v>1.7589999999999999</v>
+        <v>1.8869</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7591,10 +7591,10 @@
         <v>2021</v>
       </c>
       <c r="C515" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D515" s="3">
-        <v>1.9400000000000002</v>
+        <v>1.7607000000000002</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7602,13 +7602,13 @@
         <v>10</v>
       </c>
       <c r="B516" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C516" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D516" s="3">
-        <v>1.1923999999999999</v>
+        <v>2.3298999999999999</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7616,13 +7616,13 @@
         <v>10</v>
       </c>
       <c r="B517" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C517" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D517" s="3">
-        <v>1.5228999999999999</v>
+        <v>2.0569000000000002</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7630,13 +7630,13 @@
         <v>10</v>
       </c>
       <c r="B518" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C518" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D518" s="3">
-        <v>1.9296</v>
+        <v>2.5038999999999998</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7644,13 +7644,13 @@
         <v>10</v>
       </c>
       <c r="B519" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C519" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D519" s="3">
-        <v>1.5996999999999999</v>
+        <v>1.7151000000000001</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7658,13 +7658,13 @@
         <v>10</v>
       </c>
       <c r="B520" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C520" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D520" s="3">
-        <v>1.7376999999999998</v>
+        <v>1.7589999999999999</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7672,13 +7672,13 @@
         <v>10</v>
       </c>
       <c r="B521" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C521" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D521" s="3">
-        <v>1.6283000000000001</v>
+        <v>1.9400000000000002</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7689,10 +7689,10 @@
         <v>2022</v>
       </c>
       <c r="C522" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D522" s="3">
-        <v>1.6888000000000001</v>
+        <v>1.1923999999999999</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7703,10 +7703,10 @@
         <v>2022</v>
       </c>
       <c r="C523" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D523" s="3">
-        <v>1.7524</v>
+        <v>1.5228999999999999</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7717,10 +7717,10 @@
         <v>2022</v>
       </c>
       <c r="C524" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D524" s="3">
-        <v>1.8827</v>
+        <v>1.9296</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7731,10 +7731,10 @@
         <v>2022</v>
       </c>
       <c r="C525" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D525" s="3">
-        <v>1.52</v>
+        <v>1.5996999999999999</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7745,10 +7745,10 @@
         <v>2022</v>
       </c>
       <c r="C526" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D526" s="3">
-        <v>1.9222000000000001</v>
+        <v>1.7376999999999998</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7759,10 +7759,10 @@
         <v>2022</v>
       </c>
       <c r="C527" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D527" s="3">
-        <v>1.6540999999999999</v>
+        <v>1.6283000000000001</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7770,13 +7770,13 @@
         <v>10</v>
       </c>
       <c r="B528" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C528" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D528" s="3">
-        <v>1.6717000000000002</v>
+        <v>1.6888000000000001</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7784,13 +7784,13 @@
         <v>10</v>
       </c>
       <c r="B529" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C529" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D529" s="3">
-        <v>2.0114000000000001</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7798,13 +7798,13 @@
         <v>10</v>
       </c>
       <c r="B530" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C530" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D530" s="3">
-        <v>1.7808999999999999</v>
+        <v>1.8827</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7812,13 +7812,13 @@
         <v>10</v>
       </c>
       <c r="B531" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C531" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D531" s="3">
-        <v>1.6915</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7826,13 +7826,13 @@
         <v>10</v>
       </c>
       <c r="B532" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C532" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D532" s="3">
-        <v>1.8209</v>
+        <v>1.9222000000000001</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7840,13 +7840,13 @@
         <v>10</v>
       </c>
       <c r="B533" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C533" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D533" s="3">
-        <v>1.9435</v>
+        <v>1.6540999999999999</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7857,10 +7857,10 @@
         <v>2023</v>
       </c>
       <c r="C534" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D534" s="3">
-        <v>1.5912999999999999</v>
+        <v>1.6717000000000002</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7871,10 +7871,10 @@
         <v>2023</v>
       </c>
       <c r="C535" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D535" s="3">
-        <v>1.9621999999999999</v>
+        <v>2.0114000000000001</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7885,10 +7885,10 @@
         <v>2023</v>
       </c>
       <c r="C536" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D536" s="3">
-        <v>1.9907999999999999</v>
+        <v>1.7808999999999999</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7899,10 +7899,10 @@
         <v>2023</v>
       </c>
       <c r="C537" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D537" s="3">
-        <v>1.9017999999999999</v>
+        <v>1.6915</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7913,10 +7913,10 @@
         <v>2023</v>
       </c>
       <c r="C538" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D538" s="3">
-        <v>1.5719000000000001</v>
+        <v>1.8209</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7927,10 +7927,10 @@
         <v>2023</v>
       </c>
       <c r="C539" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D539" s="3">
-        <v>1.6617999999999999</v>
+        <v>1.9435</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7938,13 +7938,13 @@
         <v>10</v>
       </c>
       <c r="B540" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C540" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D540" s="3">
-        <v>1.9043000000000001</v>
+        <v>1.5912999999999999</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7952,13 +7952,13 @@
         <v>10</v>
       </c>
       <c r="B541" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C541" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D541" s="3">
-        <v>1.8562999999999998</v>
+        <v>1.9621999999999999</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7966,13 +7966,13 @@
         <v>10</v>
       </c>
       <c r="B542" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C542" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D542" s="3">
-        <v>1.6854</v>
+        <v>1.9907999999999999</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7980,13 +7980,13 @@
         <v>10</v>
       </c>
       <c r="B543" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C543" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D543" s="3">
-        <v>1.8065</v>
+        <v>1.9017999999999999</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -7994,13 +7994,13 @@
         <v>10</v>
       </c>
       <c r="B544" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C544" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D544" s="3">
-        <v>1.7505999999999999</v>
+        <v>1.5719000000000001</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8008,13 +8008,13 @@
         <v>10</v>
       </c>
       <c r="B545" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C545" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D545" s="3">
-        <v>1.7563</v>
+        <v>1.6617999999999999</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8025,10 +8025,10 @@
         <v>2024</v>
       </c>
       <c r="C546" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D546" s="3">
-        <v>2.2259000000000002</v>
+        <v>1.9043000000000001</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8039,10 +8039,10 @@
         <v>2024</v>
       </c>
       <c r="C547" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D547" s="3">
-        <v>1.77</v>
+        <v>1.8562999999999998</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8053,10 +8053,10 @@
         <v>2024</v>
       </c>
       <c r="C548" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D548" s="3">
-        <v>1.8426999999999998</v>
+        <v>1.6854</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8067,10 +8067,10 @@
         <v>2024</v>
       </c>
       <c r="C549" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D549" s="3">
-        <v>1.8102</v>
+        <v>1.8065</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8081,10 +8081,10 @@
         <v>2024</v>
       </c>
       <c r="C550" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D550" s="3">
-        <v>1.7421</v>
+        <v>1.7505999999999999</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8095,10 +8095,10 @@
         <v>2024</v>
       </c>
       <c r="C551" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D551" s="3">
-        <v>1.6943999999999999</v>
+        <v>1.7563</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8106,13 +8106,13 @@
         <v>10</v>
       </c>
       <c r="B552" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C552" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D552" s="3">
-        <v>1.6221000000000001</v>
+        <v>2.2259000000000002</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8120,13 +8120,13 @@
         <v>10</v>
       </c>
       <c r="B553" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C553" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D553" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8134,13 +8134,13 @@
         <v>10</v>
       </c>
       <c r="B554" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C554" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D554" s="3">
-        <v>1.7462</v>
+        <v>1.8426999999999998</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8148,13 +8148,13 @@
         <v>10</v>
       </c>
       <c r="B555" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C555" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D555" s="3">
-        <v>1.9338000000000002</v>
+        <v>1.8102</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8162,13 +8162,13 @@
         <v>10</v>
       </c>
       <c r="B556" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C556" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D556" s="3">
-        <v>1.9272</v>
+        <v>1.7421</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8176,13 +8176,13 @@
         <v>10</v>
       </c>
       <c r="B557" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C557" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D557" s="3">
-        <v>1.7902</v>
+        <v>1.6943999999999999</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8193,10 +8193,10 @@
         <v>2025</v>
       </c>
       <c r="C558" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D558" s="3">
-        <v>1.6865000000000001</v>
+        <v>1.6221000000000001</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8207,10 +8207,10 @@
         <v>2025</v>
       </c>
       <c r="C559" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D559" s="3">
-        <v>1.7938000000000001</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8221,10 +8221,10 @@
         <v>2025</v>
       </c>
       <c r="C560" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D560" s="3">
-        <v>1.732</v>
+        <v>1.7462</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8235,10 +8235,10 @@
         <v>2025</v>
       </c>
       <c r="C561" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D561" s="3">
-        <v>1.925</v>
+        <v>1.9338000000000002</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8249,10 +8249,10 @@
         <v>2025</v>
       </c>
       <c r="C562" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D562" s="3">
-        <v>1.9413</v>
+        <v>1.9272</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8263,10 +8263,10 @@
         <v>2025</v>
       </c>
       <c r="C563" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D563" s="3">
-        <v>1.7350000000000001</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8274,13 +8274,13 @@
         <v>10</v>
       </c>
       <c r="B564" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C564" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D564" s="3">
-        <v>1.6932</v>
+        <v>1.6865000000000001</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8288,13 +8288,13 @@
         <v>10</v>
       </c>
       <c r="B565" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C565" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D565" s="3">
-        <v>1.9579</v>
+        <v>1.7938000000000001</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8302,13 +8302,13 @@
         <v>10</v>
       </c>
       <c r="B566" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C566" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D566" s="3">
-        <v>1.4839</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8316,111 +8316,111 @@
         <v>10</v>
       </c>
       <c r="B567" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C567" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D567" s="3">
-        <v>2.1160000000000001</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B568" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C568" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D568" s="3">
-        <v>0.59160000000000001</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B569" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C569" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D569" s="3">
-        <v>0.71369999999999989</v>
+        <v>1.7350000000000001</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B570" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C570" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D570" s="3">
-        <v>1.4662999999999999</v>
+        <v>1.6932</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B571" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C571" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D571" s="3">
-        <v>0.70140000000000002</v>
+        <v>1.9579</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B572" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C572" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D572" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.4839</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B573" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C573" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D573" s="3">
-        <v>1.2885</v>
+        <v>2.0834999999999999</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B574" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C574" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D574" s="3">
-        <v>0.97159999999999991</v>
+        <v>1.6456</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8431,10 +8431,10 @@
         <v>2019</v>
       </c>
       <c r="C575" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D575" s="3">
-        <v>0.59799999999999998</v>
+        <v>0.59160000000000001</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8442,13 +8442,13 @@
         <v>11</v>
       </c>
       <c r="B576" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C576" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D576" s="3">
-        <v>0.80840000000000001</v>
+        <v>0.71369999999999989</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8456,13 +8456,13 @@
         <v>11</v>
       </c>
       <c r="B577" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C577" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D577" s="3">
-        <v>0.57899999999999996</v>
+        <v>1.4662999999999999</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8470,13 +8470,13 @@
         <v>11</v>
       </c>
       <c r="B578" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C578" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D578" s="3">
-        <v>1.1052999999999999</v>
+        <v>0.70140000000000002</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8484,13 +8484,13 @@
         <v>11</v>
       </c>
       <c r="B579" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C579" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D579" s="3">
-        <v>0.77580000000000005</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8498,13 +8498,13 @@
         <v>11</v>
       </c>
       <c r="B580" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C580" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D580" s="3">
-        <v>1.0531999999999999</v>
+        <v>1.2885</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8512,13 +8512,13 @@
         <v>11</v>
       </c>
       <c r="B581" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C581" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D581" s="3">
-        <v>1.0923</v>
+        <v>0.97159999999999991</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8526,13 +8526,13 @@
         <v>11</v>
       </c>
       <c r="B582" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C582" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D582" s="3">
-        <v>1.2737000000000001</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8543,10 +8543,10 @@
         <v>2020</v>
       </c>
       <c r="C583" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D583" s="3">
-        <v>1.3653</v>
+        <v>0.80840000000000001</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8557,10 +8557,10 @@
         <v>2020</v>
       </c>
       <c r="C584" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D584" s="3">
-        <v>1.1208</v>
+        <v>0.57899999999999996</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8571,10 +8571,10 @@
         <v>2020</v>
       </c>
       <c r="C585" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D585" s="3">
-        <v>1.5089999999999999</v>
+        <v>1.1052999999999999</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -8585,10 +8585,10 @@
         <v>2020</v>
       </c>
       <c r="C586" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D586" s="3">
-        <v>1.2372000000000001</v>
+        <v>0.77580000000000005</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -8599,10 +8599,10 @@
         <v>2020</v>
       </c>
       <c r="C587" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D587" s="3">
-        <v>1.0697000000000001</v>
+        <v>1.0531999999999999</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -8610,13 +8610,13 @@
         <v>11</v>
       </c>
       <c r="B588" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C588" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D588" s="3">
-        <v>1.2351000000000001</v>
+        <v>1.0923</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8624,13 +8624,13 @@
         <v>11</v>
       </c>
       <c r="B589" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C589" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D589" s="3">
-        <v>1.1274</v>
+        <v>1.2737000000000001</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -8638,13 +8638,13 @@
         <v>11</v>
       </c>
       <c r="B590" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C590" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D590" s="3">
-        <v>1.3996</v>
+        <v>1.3653</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8652,13 +8652,13 @@
         <v>11</v>
       </c>
       <c r="B591" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C591" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D591" s="3">
-        <v>1.2915000000000001</v>
+        <v>1.1208</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8666,13 +8666,13 @@
         <v>11</v>
       </c>
       <c r="B592" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C592" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D592" s="3">
-        <v>1.218</v>
+        <v>1.5089999999999999</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8680,13 +8680,13 @@
         <v>11</v>
       </c>
       <c r="B593" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C593" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D593" s="3">
-        <v>1.3958999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8694,13 +8694,13 @@
         <v>11</v>
       </c>
       <c r="B594" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C594" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D594" s="3">
-        <v>1.5745000000000002</v>
+        <v>1.0697000000000001</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8711,10 +8711,10 @@
         <v>2021</v>
       </c>
       <c r="C595" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D595" s="3">
-        <v>1.3656999999999999</v>
+        <v>1.2351000000000001</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8725,10 +8725,10 @@
         <v>2021</v>
       </c>
       <c r="C596" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D596" s="3">
-        <v>1.1288</v>
+        <v>1.1274</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8739,10 +8739,10 @@
         <v>2021</v>
       </c>
       <c r="C597" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D597" s="3">
-        <v>0.96220000000000006</v>
+        <v>1.3996</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8753,10 +8753,10 @@
         <v>2021</v>
       </c>
       <c r="C598" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D598" s="3">
-        <v>0.94979999999999998</v>
+        <v>1.2915000000000001</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8767,10 +8767,10 @@
         <v>2021</v>
       </c>
       <c r="C599" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D599" s="3">
-        <v>1.1982999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8778,13 +8778,13 @@
         <v>11</v>
       </c>
       <c r="B600" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C600" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D600" s="3">
-        <v>1.0469999999999999</v>
+        <v>1.3958999999999999</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8792,13 +8792,13 @@
         <v>11</v>
       </c>
       <c r="B601" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C601" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D601" s="3">
-        <v>0.84160000000000001</v>
+        <v>1.5745000000000002</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8806,13 +8806,13 @@
         <v>11</v>
       </c>
       <c r="B602" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C602" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D602" s="3">
-        <v>0.85270000000000001</v>
+        <v>1.3656999999999999</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8820,13 +8820,13 @@
         <v>11</v>
       </c>
       <c r="B603" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C603" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D603" s="3">
-        <v>0.65920000000000001</v>
+        <v>1.1288</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8834,13 +8834,13 @@
         <v>11</v>
       </c>
       <c r="B604" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C604" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D604" s="3">
-        <v>0.91259999999999997</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8848,13 +8848,13 @@
         <v>11</v>
       </c>
       <c r="B605" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C605" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D605" s="3">
-        <v>0.68140000000000001</v>
+        <v>0.94979999999999998</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8862,13 +8862,13 @@
         <v>11</v>
       </c>
       <c r="B606" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C606" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D606" s="3">
-        <v>0.69020000000000004</v>
+        <v>1.1982999999999999</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8879,10 +8879,10 @@
         <v>2022</v>
       </c>
       <c r="C607" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D607" s="3">
-        <v>0.83509999999999995</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8893,10 +8893,10 @@
         <v>2022</v>
       </c>
       <c r="C608" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D608" s="3">
-        <v>0.8459000000000001</v>
+        <v>0.84160000000000001</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8907,10 +8907,10 @@
         <v>2022</v>
       </c>
       <c r="C609" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D609" s="3">
-        <v>1.0476000000000001</v>
+        <v>0.85270000000000001</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8921,10 +8921,10 @@
         <v>2022</v>
       </c>
       <c r="C610" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D610" s="3">
-        <v>0.93159999999999998</v>
+        <v>0.65920000000000001</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8935,10 +8935,10 @@
         <v>2022</v>
       </c>
       <c r="C611" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D611" s="3">
-        <v>0.60189999999999999</v>
+        <v>0.91259999999999997</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8946,13 +8946,13 @@
         <v>11</v>
       </c>
       <c r="B612" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C612" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D612" s="3">
-        <v>0.70330000000000004</v>
+        <v>0.68140000000000001</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8960,13 +8960,13 @@
         <v>11</v>
       </c>
       <c r="B613" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C613" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D613" s="3">
-        <v>0.68169999999999997</v>
+        <v>0.69020000000000004</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8974,13 +8974,13 @@
         <v>11</v>
       </c>
       <c r="B614" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C614" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D614" s="3">
-        <v>0.6391</v>
+        <v>0.83509999999999995</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8988,13 +8988,13 @@
         <v>11</v>
       </c>
       <c r="B615" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C615" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D615" s="3">
-        <v>0.72650000000000003</v>
+        <v>0.8459000000000001</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9002,13 +9002,13 @@
         <v>11</v>
       </c>
       <c r="B616" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C616" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D616" s="3">
-        <v>0.76770000000000005</v>
+        <v>1.0476000000000001</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9016,13 +9016,13 @@
         <v>11</v>
       </c>
       <c r="B617" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C617" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D617" s="3">
-        <v>0.64570000000000005</v>
+        <v>0.93159999999999998</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9030,13 +9030,13 @@
         <v>11</v>
       </c>
       <c r="B618" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C618" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D618" s="3">
-        <v>0.60250000000000004</v>
+        <v>0.60189999999999999</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9047,10 +9047,10 @@
         <v>2023</v>
       </c>
       <c r="C619" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D619" s="3">
-        <v>1.3164</v>
+        <v>0.70330000000000004</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9061,10 +9061,10 @@
         <v>2023</v>
       </c>
       <c r="C620" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D620" s="3">
-        <v>1.054</v>
+        <v>0.68169999999999997</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9075,10 +9075,10 @@
         <v>2023</v>
       </c>
       <c r="C621" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D621" s="3">
-        <v>1.1778</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9089,10 +9089,10 @@
         <v>2023</v>
       </c>
       <c r="C622" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D622" s="3">
-        <v>1.3501000000000001</v>
+        <v>0.72650000000000003</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9103,10 +9103,10 @@
         <v>2023</v>
       </c>
       <c r="C623" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D623" s="3">
-        <v>1.1941999999999999</v>
+        <v>0.76770000000000005</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="B624" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C624" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D624" s="3">
-        <v>1.1995</v>
+        <v>0.64570000000000005</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9128,13 +9128,13 @@
         <v>11</v>
       </c>
       <c r="B625" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C625" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D625" s="3">
-        <v>1.2528000000000001</v>
+        <v>0.60250000000000004</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9142,13 +9142,13 @@
         <v>11</v>
       </c>
       <c r="B626" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C626" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D626" s="3">
-        <v>1.2377</v>
+        <v>1.3164</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9156,13 +9156,13 @@
         <v>11</v>
       </c>
       <c r="B627" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C627" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D627" s="3">
-        <v>1.0448</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9170,13 +9170,13 @@
         <v>11</v>
       </c>
       <c r="B628" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C628" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D628" s="3">
-        <v>1.1088</v>
+        <v>1.1778</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9184,13 +9184,13 @@
         <v>11</v>
       </c>
       <c r="B629" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C629" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D629" s="3">
-        <v>1.1704000000000001</v>
+        <v>1.3501000000000001</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9198,13 +9198,13 @@
         <v>11</v>
       </c>
       <c r="B630" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C630" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D630" s="3">
-        <v>1.335</v>
+        <v>1.1941999999999999</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9215,10 +9215,10 @@
         <v>2024</v>
       </c>
       <c r="C631" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D631" s="3">
-        <v>1.2101999999999999</v>
+        <v>1.1995</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9229,10 +9229,10 @@
         <v>2024</v>
       </c>
       <c r="C632" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D632" s="3">
-        <v>1.2007000000000001</v>
+        <v>1.2528000000000001</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9243,10 +9243,10 @@
         <v>2024</v>
       </c>
       <c r="C633" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D633" s="3">
-        <v>1.2133</v>
+        <v>1.2377</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9257,10 +9257,10 @@
         <v>2024</v>
       </c>
       <c r="C634" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D634" s="3">
-        <v>0.85850000000000004</v>
+        <v>1.0448</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9271,10 +9271,10 @@
         <v>2024</v>
       </c>
       <c r="C635" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D635" s="3">
-        <v>1.1714</v>
+        <v>1.1088</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9282,13 +9282,13 @@
         <v>11</v>
       </c>
       <c r="B636" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C636" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D636" s="3">
-        <v>0.94820000000000004</v>
+        <v>1.1704000000000001</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="B637" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C637" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D637" s="3">
-        <v>0.94499999999999995</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9310,13 +9310,13 @@
         <v>11</v>
       </c>
       <c r="B638" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C638" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D638" s="3">
-        <v>1.0746</v>
+        <v>1.2101999999999999</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9324,13 +9324,13 @@
         <v>11</v>
       </c>
       <c r="B639" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C639" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D639" s="3">
-        <v>1.1345000000000001</v>
+        <v>1.2007000000000001</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9338,13 +9338,13 @@
         <v>11</v>
       </c>
       <c r="B640" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C640" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D640" s="3">
-        <v>0.96009999999999995</v>
+        <v>1.2133</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9352,13 +9352,13 @@
         <v>11</v>
       </c>
       <c r="B641" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C641" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D641" s="3">
-        <v>1.0189999999999999</v>
+        <v>0.85850000000000004</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9366,13 +9366,13 @@
         <v>11</v>
       </c>
       <c r="B642" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C642" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D642" s="3">
-        <v>1.0889</v>
+        <v>1.1714</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9383,10 +9383,10 @@
         <v>2025</v>
       </c>
       <c r="C643" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D643" s="3">
-        <v>1.0328999999999999</v>
+        <v>0.94820000000000004</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9397,10 +9397,10 @@
         <v>2025</v>
       </c>
       <c r="C644" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D644" s="3">
-        <v>1.0566</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9411,10 +9411,10 @@
         <v>2025</v>
       </c>
       <c r="C645" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D645" s="3">
-        <v>1.0752999999999999</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9425,10 +9425,10 @@
         <v>2025</v>
       </c>
       <c r="C646" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D646" s="3">
-        <v>0.91410000000000002</v>
+        <v>1.1345000000000001</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9439,10 +9439,10 @@
         <v>2025</v>
       </c>
       <c r="C647" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D647" s="3">
-        <v>1.083</v>
+        <v>0.96009999999999995</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9450,13 +9450,13 @@
         <v>11</v>
       </c>
       <c r="B648" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C648" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D648" s="3">
-        <v>1.0165999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9464,13 +9464,13 @@
         <v>11</v>
       </c>
       <c r="B649" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C649" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D649" s="3">
-        <v>0.92769999999999997</v>
+        <v>1.0889</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="B650" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C650" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D650" s="3">
-        <v>0.86799999999999999</v>
+        <v>1.0328999999999999</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9492,125 +9492,125 @@
         <v>11</v>
       </c>
       <c r="B651" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C651" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D651" s="3">
-        <v>0.84299999999999997</v>
+        <v>1.0566</v>
       </c>
     </row>
     <row r="652" spans="1:4">
       <c r="A652" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B652" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C652" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D652" s="3">
-        <v>0.62870000000000004</v>
+        <v>1.0752999999999999</v>
       </c>
     </row>
     <row r="653" spans="1:4">
       <c r="A653" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B653" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C653" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D653" s="3">
-        <v>0.97070000000000001</v>
+        <v>0.91410000000000002</v>
       </c>
     </row>
     <row r="654" spans="1:4">
       <c r="A654" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B654" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C654" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D654" s="3">
-        <v>0.71419999999999995</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="655" spans="1:4">
       <c r="A655" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B655" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C655" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D655" s="3">
-        <v>0.60429999999999995</v>
+        <v>1.0165999999999999</v>
       </c>
     </row>
     <row r="656" spans="1:4">
       <c r="A656" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B656" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C656" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D656" s="3">
-        <v>0.87819999999999998</v>
+        <v>0.92769999999999997</v>
       </c>
     </row>
     <row r="657" spans="1:4">
       <c r="A657" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B657" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C657" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D657" s="3">
-        <v>0.97710000000000008</v>
+        <v>0.86850000000000005</v>
       </c>
     </row>
     <row r="658" spans="1:4">
       <c r="A658" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B658" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C658" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D658" s="3">
-        <v>0.78180000000000005</v>
+        <v>0.84950000000000003</v>
       </c>
     </row>
     <row r="659" spans="1:4">
       <c r="A659" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B659" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C659" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D659" s="3">
-        <v>0.88280000000000003</v>
+        <v>0.86919999999999997</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -9618,13 +9618,13 @@
         <v>12</v>
       </c>
       <c r="B660" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C660" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D660" s="3">
-        <v>0.84150000000000003</v>
+        <v>0.62870000000000004</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -9632,13 +9632,13 @@
         <v>12</v>
       </c>
       <c r="B661" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C661" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D661" s="3">
-        <v>3.6991000000000001</v>
+        <v>0.97070000000000001</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -9646,13 +9646,13 @@
         <v>12</v>
       </c>
       <c r="B662" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C662" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D662" s="3">
-        <v>0.63649999999999995</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -9660,13 +9660,13 @@
         <v>12</v>
       </c>
       <c r="B663" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C663" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D663" s="3">
-        <v>0.63870000000000005</v>
+        <v>0.60429999999999995</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -9674,13 +9674,13 @@
         <v>12</v>
       </c>
       <c r="B664" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C664" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D664" s="3">
-        <v>0.58840000000000003</v>
+        <v>0.87819999999999998</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -9688,13 +9688,13 @@
         <v>12</v>
       </c>
       <c r="B665" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C665" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D665" s="3">
-        <v>0.83720000000000006</v>
+        <v>0.97710000000000008</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -9702,13 +9702,13 @@
         <v>12</v>
       </c>
       <c r="B666" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C666" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D666" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.78180000000000005</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -9716,13 +9716,13 @@
         <v>12</v>
       </c>
       <c r="B667" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C667" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D667" s="3">
-        <v>0.75119999999999998</v>
+        <v>0.88280000000000003</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -9733,10 +9733,10 @@
         <v>2020</v>
       </c>
       <c r="C668" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D668" s="3">
-        <v>0.76349999999999996</v>
+        <v>0.84150000000000003</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -9747,10 +9747,10 @@
         <v>2020</v>
       </c>
       <c r="C669" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D669" s="3">
-        <v>0.80579999999999996</v>
+        <v>3.6991000000000001</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -9761,10 +9761,10 @@
         <v>2020</v>
       </c>
       <c r="C670" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D670" s="3">
-        <v>0.75339999999999996</v>
+        <v>0.63649999999999995</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -9772,13 +9772,13 @@
         <v>12</v>
       </c>
       <c r="B671" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C671" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D671" s="3">
-        <v>0.83040000000000003</v>
+        <v>0.63870000000000005</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -9786,13 +9786,13 @@
         <v>12</v>
       </c>
       <c r="B672" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C672" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D672" s="3">
-        <v>0.85129999999999995</v>
+        <v>0.58840000000000003</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -9800,13 +9800,13 @@
         <v>12</v>
       </c>
       <c r="B673" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C673" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D673" s="3">
-        <v>0.8536999999999999</v>
+        <v>0.83720000000000006</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -9814,13 +9814,13 @@
         <v>12</v>
       </c>
       <c r="B674" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C674" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D674" s="3">
-        <v>0.93080000000000007</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -9828,13 +9828,13 @@
         <v>12</v>
       </c>
       <c r="B675" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C675" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D675" s="3">
-        <v>0.8980999999999999</v>
+        <v>0.75119999999999998</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -9842,13 +9842,13 @@
         <v>12</v>
       </c>
       <c r="B676" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C676" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D676" s="3">
-        <v>0.88049999999999984</v>
+        <v>0.76349999999999996</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -9856,13 +9856,13 @@
         <v>12</v>
       </c>
       <c r="B677" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C677" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D677" s="3">
-        <v>0.89779999999999993</v>
+        <v>0.80579999999999996</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -9870,13 +9870,13 @@
         <v>12</v>
       </c>
       <c r="B678" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C678" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D678" s="3">
-        <v>0.94299999999999995</v>
+        <v>0.75339999999999996</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -9887,10 +9887,10 @@
         <v>2021</v>
       </c>
       <c r="C679" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D679" s="3">
-        <v>0.87270000000000014</v>
+        <v>0.83040000000000003</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -9901,10 +9901,10 @@
         <v>2021</v>
       </c>
       <c r="C680" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D680" s="3">
-        <v>0.89249999999999985</v>
+        <v>0.85129999999999995</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -9915,10 +9915,10 @@
         <v>2021</v>
       </c>
       <c r="C681" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D681" s="3">
-        <v>0.90710000000000002</v>
+        <v>0.8536999999999999</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -9929,10 +9929,10 @@
         <v>2021</v>
       </c>
       <c r="C682" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D682" s="3">
-        <v>0.80330000000000001</v>
+        <v>0.93080000000000007</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -9940,13 +9940,13 @@
         <v>12</v>
       </c>
       <c r="B683" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C683" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D683" s="3">
-        <v>0.7107</v>
+        <v>0.8980999999999999</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -9954,13 +9954,13 @@
         <v>12</v>
       </c>
       <c r="B684" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C684" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D684" s="3">
-        <v>0.78610000000000002</v>
+        <v>0.88049999999999984</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -9968,13 +9968,13 @@
         <v>12</v>
       </c>
       <c r="B685" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C685" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D685" s="3">
-        <v>0.83389999999999997</v>
+        <v>0.89779999999999993</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -9982,13 +9982,13 @@
         <v>12</v>
       </c>
       <c r="B686" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C686" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D686" s="3">
-        <v>0.88970000000000005</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -9996,13 +9996,13 @@
         <v>12</v>
       </c>
       <c r="B687" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C687" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D687" s="3">
-        <v>0.83260000000000001</v>
+        <v>0.87270000000000014</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -10010,13 +10010,13 @@
         <v>12</v>
       </c>
       <c r="B688" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C688" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D688" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.89249999999999985</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -10024,13 +10024,13 @@
         <v>12</v>
       </c>
       <c r="B689" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C689" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D689" s="3">
-        <v>0.90830000000000011</v>
+        <v>0.90710000000000002</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -10038,13 +10038,13 @@
         <v>12</v>
       </c>
       <c r="B690" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C690" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D690" s="3">
-        <v>0.80479999999999996</v>
+        <v>0.80330000000000001</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -10055,10 +10055,10 @@
         <v>2022</v>
       </c>
       <c r="C691" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D691" s="3">
-        <v>0.77749999999999997</v>
+        <v>0.7107</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -10069,10 +10069,10 @@
         <v>2022</v>
       </c>
       <c r="C692" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D692" s="3">
-        <v>0.81069999999999998</v>
+        <v>0.78610000000000002</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -10083,10 +10083,10 @@
         <v>2022</v>
       </c>
       <c r="C693" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D693" s="3">
-        <v>0.87409999999999999</v>
+        <v>0.83389999999999997</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -10097,10 +10097,10 @@
         <v>2022</v>
       </c>
       <c r="C694" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D694" s="3">
-        <v>0.86129999999999984</v>
+        <v>0.88970000000000005</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -10108,13 +10108,13 @@
         <v>12</v>
       </c>
       <c r="B695" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C695" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D695" s="3">
-        <v>0.78390000000000004</v>
+        <v>0.83260000000000001</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -10122,13 +10122,13 @@
         <v>12</v>
       </c>
       <c r="B696" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C696" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D696" s="3">
-        <v>0.84170000000000011</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -10136,13 +10136,13 @@
         <v>12</v>
       </c>
       <c r="B697" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C697" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D697" s="3">
-        <v>0.80769999999999986</v>
+        <v>0.90830000000000011</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -10150,13 +10150,13 @@
         <v>12</v>
       </c>
       <c r="B698" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C698" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D698" s="3">
-        <v>0.90670000000000006</v>
+        <v>0.80479999999999996</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -10164,13 +10164,13 @@
         <v>12</v>
       </c>
       <c r="B699" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C699" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D699" s="3">
-        <v>0.82020000000000004</v>
+        <v>0.77749999999999997</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -10178,13 +10178,13 @@
         <v>12</v>
       </c>
       <c r="B700" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C700" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D700" s="3">
-        <v>0.81120000000000014</v>
+        <v>0.81069999999999998</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -10192,13 +10192,13 @@
         <v>12</v>
       </c>
       <c r="B701" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C701" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D701" s="3">
-        <v>0.85009999999999997</v>
+        <v>0.87409999999999999</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -10206,13 +10206,13 @@
         <v>12</v>
       </c>
       <c r="B702" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C702" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D702" s="3">
-        <v>0.8327</v>
+        <v>0.86129999999999984</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -10223,10 +10223,10 @@
         <v>2023</v>
       </c>
       <c r="C703" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D703" s="3">
-        <v>0.90250000000000008</v>
+        <v>0.78390000000000004</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -10237,10 +10237,10 @@
         <v>2023</v>
       </c>
       <c r="C704" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D704" s="3">
-        <v>0.85660000000000003</v>
+        <v>0.84170000000000011</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -10251,10 +10251,10 @@
         <v>2023</v>
       </c>
       <c r="C705" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D705" s="3">
-        <v>0.92820000000000003</v>
+        <v>0.80769999999999986</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -10265,10 +10265,10 @@
         <v>2023</v>
       </c>
       <c r="C706" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D706" s="3">
-        <v>0.86169999999999991</v>
+        <v>0.90670000000000006</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -10276,13 +10276,13 @@
         <v>12</v>
       </c>
       <c r="B707" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C707" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D707" s="3">
-        <v>0.85750000000000004</v>
+        <v>0.82020000000000004</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -10290,13 +10290,13 @@
         <v>12</v>
       </c>
       <c r="B708" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C708" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D708" s="3">
-        <v>0.9355</v>
+        <v>0.81120000000000014</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -10304,13 +10304,13 @@
         <v>12</v>
       </c>
       <c r="B709" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C709" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D709" s="3">
-        <v>0.79620000000000002</v>
+        <v>0.85009999999999997</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -10318,13 +10318,13 @@
         <v>12</v>
       </c>
       <c r="B710" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C710" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D710" s="3">
-        <v>0.93479999999999996</v>
+        <v>0.8327</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -10332,13 +10332,13 @@
         <v>12</v>
       </c>
       <c r="B711" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C711" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D711" s="3">
-        <v>0.96489999999999998</v>
+        <v>0.90250000000000008</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -10346,13 +10346,13 @@
         <v>12</v>
       </c>
       <c r="B712" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C712" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D712" s="3">
-        <v>0.86809999999999998</v>
+        <v>0.85660000000000003</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -10360,13 +10360,13 @@
         <v>12</v>
       </c>
       <c r="B713" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C713" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D713" s="3">
-        <v>0.7752</v>
+        <v>0.92820000000000003</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -10374,13 +10374,13 @@
         <v>12</v>
       </c>
       <c r="B714" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C714" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D714" s="3">
-        <v>0.82489999999999997</v>
+        <v>0.86169999999999991</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -10391,10 +10391,10 @@
         <v>2024</v>
       </c>
       <c r="C715" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D715" s="3">
-        <v>0.91569999999999996</v>
+        <v>0.85750000000000004</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -10405,10 +10405,10 @@
         <v>2024</v>
       </c>
       <c r="C716" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D716" s="3">
-        <v>0.997</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -10419,10 +10419,10 @@
         <v>2024</v>
       </c>
       <c r="C717" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D717" s="3">
-        <v>1.0421</v>
+        <v>0.79620000000000002</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -10433,10 +10433,10 @@
         <v>2024</v>
       </c>
       <c r="C718" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D718" s="3">
-        <v>1.0548</v>
+        <v>0.93479999999999996</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -10444,13 +10444,13 @@
         <v>12</v>
       </c>
       <c r="B719" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C719" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D719" s="3">
-        <v>0.92949999999999999</v>
+        <v>0.96489999999999998</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -10458,13 +10458,13 @@
         <v>12</v>
       </c>
       <c r="B720" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C720" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D720" s="3">
-        <v>0.95120000000000016</v>
+        <v>0.86809999999999998</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -10472,13 +10472,13 @@
         <v>12</v>
       </c>
       <c r="B721" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C721" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D721" s="3">
-        <v>0.92459999999999998</v>
+        <v>0.7752</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -10486,13 +10486,13 @@
         <v>12</v>
       </c>
       <c r="B722" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C722" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D722" s="3">
-        <v>0.85740000000000005</v>
+        <v>0.82489999999999997</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -10500,13 +10500,13 @@
         <v>12</v>
       </c>
       <c r="B723" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C723" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D723" s="3">
-        <v>0.91100000000000003</v>
+        <v>0.91569999999999996</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -10514,13 +10514,13 @@
         <v>12</v>
       </c>
       <c r="B724" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C724" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D724" s="3">
-        <v>0.89139999999999986</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -10528,13 +10528,13 @@
         <v>12</v>
       </c>
       <c r="B725" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C725" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D725" s="3">
-        <v>0.92459999999999998</v>
+        <v>1.0421</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -10542,13 +10542,13 @@
         <v>12</v>
       </c>
       <c r="B726" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C726" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D726" s="3">
-        <v>0.97750000000000004</v>
+        <v>1.0548</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -10559,10 +10559,10 @@
         <v>2025</v>
       </c>
       <c r="C727" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D727" s="3">
-        <v>0.91020000000000001</v>
+        <v>0.92949999999999999</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -10573,10 +10573,10 @@
         <v>2025</v>
       </c>
       <c r="C728" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D728" s="3">
-        <v>0.89680000000000004</v>
+        <v>0.95120000000000016</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -10587,10 +10587,10 @@
         <v>2025</v>
       </c>
       <c r="C729" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D729" s="3">
-        <v>0.83699999999999997</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -10601,10 +10601,10 @@
         <v>2025</v>
       </c>
       <c r="C730" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D730" s="3">
-        <v>0.97820000000000007</v>
+        <v>0.85740000000000005</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -10612,13 +10612,13 @@
         <v>12</v>
       </c>
       <c r="B731" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C731" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D731" s="3">
-        <v>0.95220000000000005</v>
+        <v>0.91100000000000003</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -10626,13 +10626,13 @@
         <v>12</v>
       </c>
       <c r="B732" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C732" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D732" s="3">
-        <v>0.87929999999999986</v>
+        <v>0.89139999999999986</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -10640,13 +10640,13 @@
         <v>12</v>
       </c>
       <c r="B733" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C733" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D733" s="3">
-        <v>0.89659999999999995</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -10654,13 +10654,139 @@
         <v>12</v>
       </c>
       <c r="B734" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C734" s="2">
+        <v>8</v>
+      </c>
+      <c r="D734" s="3">
+        <v>0.97750000000000004</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4">
+      <c r="A735" t="s">
+        <v>12</v>
+      </c>
+      <c r="B735" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C735" s="2">
+        <v>9</v>
+      </c>
+      <c r="D735" s="3">
+        <v>0.91020000000000001</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4">
+      <c r="A736" t="s">
+        <v>12</v>
+      </c>
+      <c r="B736" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C736" s="2">
+        <v>10</v>
+      </c>
+      <c r="D736" s="3">
+        <v>0.89680000000000004</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4">
+      <c r="A737" t="s">
+        <v>12</v>
+      </c>
+      <c r="B737" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C737" s="2">
+        <v>11</v>
+      </c>
+      <c r="D737" s="3">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4">
+      <c r="A738" t="s">
+        <v>12</v>
+      </c>
+      <c r="B738" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C738" s="2">
+        <v>12</v>
+      </c>
+      <c r="D738" s="3">
+        <v>0.97820000000000007</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4">
+      <c r="A739" t="s">
+        <v>12</v>
+      </c>
+      <c r="B739" s="2">
         <v>2026</v>
       </c>
-      <c r="C734" s="2">
-        <v>4</v>
-      </c>
-      <c r="D734" s="3">
-        <v>0.87880000000000003</v>
+      <c r="C739" s="2">
+        <v>1</v>
+      </c>
+      <c r="D739" s="3">
+        <v>0.98870000000000002</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4">
+      <c r="A740" t="s">
+        <v>12</v>
+      </c>
+      <c r="B740" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C740" s="2">
+        <v>2</v>
+      </c>
+      <c r="D740" s="3">
+        <v>0.90090000000000015</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4">
+      <c r="A741" t="s">
+        <v>12</v>
+      </c>
+      <c r="B741" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C741" s="2">
+        <v>3</v>
+      </c>
+      <c r="D741" s="3">
+        <v>0.91339999999999999</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4">
+      <c r="A742" t="s">
+        <v>12</v>
+      </c>
+      <c r="B742" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C742" s="2">
+        <v>4</v>
+      </c>
+      <c r="D742" s="3">
+        <v>0.93269999999999997</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4">
+      <c r="A743" t="s">
+        <v>12</v>
+      </c>
+      <c r="B743" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C743" s="2">
+        <v>5</v>
+      </c>
+      <c r="D743" s="3">
+        <v>0.89729999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/upload/case-mix-2025.xlsx
+++ b/upload/case-mix-2025.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D743"/>
+  <dimension ref="A1:D752"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -720,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="3">
-        <v>1.4815</v>
+        <v>1.4846999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1546,7 +1546,7 @@
         <v>2</v>
       </c>
       <c r="D83" s="3">
-        <v>1.6696</v>
+        <v>1.6687000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1560,7 +1560,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="3">
-        <v>1.5893999999999999</v>
+        <v>1.6366000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="3">
-        <v>1.5334000000000001</v>
+        <v>1.4151</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1588,21 +1588,21 @@
         <v>5</v>
       </c>
       <c r="D86" s="3">
-        <v>1.2676000000000001</v>
+        <v>1.2664</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B87" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C87" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D87" s="3">
-        <v>0.32269999999999999</v>
+        <v>1.3947000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1613,10 +1613,10 @@
         <v>2019</v>
       </c>
       <c r="C88" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D88" s="3">
-        <v>2.4020999999999999</v>
+        <v>0.32269999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1624,13 +1624,13 @@
         <v>5</v>
       </c>
       <c r="B89" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C89" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D89" s="3">
-        <v>2.0989</v>
+        <v>2.4020999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1641,10 +1641,10 @@
         <v>2020</v>
       </c>
       <c r="C90" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" s="3">
-        <v>1.9497</v>
+        <v>2.0989</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1655,10 +1655,10 @@
         <v>2020</v>
       </c>
       <c r="C91" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="3">
-        <v>2.1490999999999998</v>
+        <v>1.9497</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1669,10 +1669,10 @@
         <v>2020</v>
       </c>
       <c r="C92" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" s="3">
-        <v>1.6907000000000001</v>
+        <v>2.1490999999999998</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1683,10 +1683,10 @@
         <v>2020</v>
       </c>
       <c r="C93" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D93" s="3">
-        <v>2.1762999999999999</v>
+        <v>1.6907000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1697,10 +1697,10 @@
         <v>2020</v>
       </c>
       <c r="C94" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D94" s="3">
-        <v>2.3714</v>
+        <v>2.1762999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1711,10 +1711,10 @@
         <v>2020</v>
       </c>
       <c r="C95" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" s="3">
-        <v>2.6513</v>
+        <v>2.3714</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1725,10 +1725,10 @@
         <v>2020</v>
       </c>
       <c r="C96" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96" s="3">
-        <v>2.3975</v>
+        <v>2.6513</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1739,10 +1739,10 @@
         <v>2020</v>
       </c>
       <c r="C97" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D97" s="3">
-        <v>3.2244999999999999</v>
+        <v>2.3975</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1753,10 +1753,10 @@
         <v>2020</v>
       </c>
       <c r="C98" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D98" s="3">
-        <v>2.0931000000000002</v>
+        <v>3.2244999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1767,10 +1767,10 @@
         <v>2020</v>
       </c>
       <c r="C99" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D99" s="3">
-        <v>2.1968000000000001</v>
+        <v>2.0931000000000002</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1781,10 +1781,10 @@
         <v>2020</v>
       </c>
       <c r="C100" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D100" s="3">
-        <v>2.0958999999999999</v>
+        <v>2.1968000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1792,13 +1792,13 @@
         <v>5</v>
       </c>
       <c r="B101" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C101" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D101" s="3">
-        <v>2.4843000000000002</v>
+        <v>2.0958999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1809,10 +1809,10 @@
         <v>2021</v>
       </c>
       <c r="C102" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D102" s="3">
-        <v>2.3409</v>
+        <v>2.4843000000000002</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1823,10 +1823,10 @@
         <v>2021</v>
       </c>
       <c r="C103" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="3">
-        <v>2.7355999999999998</v>
+        <v>2.3409</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>2021</v>
       </c>
       <c r="C104" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" s="3">
-        <v>2.8948</v>
+        <v>2.7355999999999998</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1851,10 +1851,10 @@
         <v>2021</v>
       </c>
       <c r="C105" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D105" s="3">
-        <v>2.7456</v>
+        <v>2.8948</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1865,10 +1865,10 @@
         <v>2021</v>
       </c>
       <c r="C106" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D106" s="3">
-        <v>2.5648</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1879,10 +1879,10 @@
         <v>2021</v>
       </c>
       <c r="C107" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D107" s="3">
-        <v>2.5844</v>
+        <v>2.5648</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1893,10 +1893,10 @@
         <v>2021</v>
       </c>
       <c r="C108" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D108" s="3">
-        <v>2.8304999999999998</v>
+        <v>2.5844</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1907,10 +1907,10 @@
         <v>2021</v>
       </c>
       <c r="C109" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D109" s="3">
-        <v>2.0144000000000002</v>
+        <v>2.8304999999999998</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1921,10 +1921,10 @@
         <v>2021</v>
       </c>
       <c r="C110" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D110" s="3">
-        <v>1.9097</v>
+        <v>2.0144000000000002</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1935,10 +1935,10 @@
         <v>2021</v>
       </c>
       <c r="C111" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D111" s="3">
-        <v>2.3733</v>
+        <v>1.9097</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1949,10 +1949,10 @@
         <v>2021</v>
       </c>
       <c r="C112" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D112" s="3">
-        <v>2.0158999999999998</v>
+        <v>2.3733</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1960,13 +1960,13 @@
         <v>5</v>
       </c>
       <c r="B113" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D113" s="3">
-        <v>2.0093999999999999</v>
+        <v>2.0158999999999998</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1977,10 +1977,10 @@
         <v>2022</v>
       </c>
       <c r="C114" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" s="3">
-        <v>3.6905000000000001</v>
+        <v>2.0093999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1991,10 +1991,10 @@
         <v>2022</v>
       </c>
       <c r="C115" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3">
-        <v>2.6345000000000001</v>
+        <v>3.6905000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2005,10 +2005,10 @@
         <v>2022</v>
       </c>
       <c r="C116" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D116" s="3">
-        <v>2.0619999999999998</v>
+        <v>2.6345000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>2022</v>
       </c>
       <c r="C117" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117" s="3">
-        <v>1.9186000000000001</v>
+        <v>2.0619999999999998</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2033,10 +2033,10 @@
         <v>2022</v>
       </c>
       <c r="C118" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" s="3">
-        <v>2.0594000000000001</v>
+        <v>1.9186000000000001</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2047,10 +2047,10 @@
         <v>2022</v>
       </c>
       <c r="C119" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D119" s="3">
-        <v>2.1585999999999999</v>
+        <v>2.0594000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2061,10 +2061,10 @@
         <v>2022</v>
       </c>
       <c r="C120" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D120" s="3">
-        <v>1.6135999999999999</v>
+        <v>2.1585999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2075,10 +2075,10 @@
         <v>2022</v>
       </c>
       <c r="C121" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D121" s="3">
-        <v>1.5652000000000001</v>
+        <v>1.6135999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2089,10 +2089,10 @@
         <v>2022</v>
       </c>
       <c r="C122" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D122" s="3">
-        <v>1.4952000000000001</v>
+        <v>1.5652000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2103,10 +2103,10 @@
         <v>2022</v>
       </c>
       <c r="C123" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D123" s="3">
-        <v>1.7753000000000001</v>
+        <v>1.4952000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2117,10 +2117,10 @@
         <v>2022</v>
       </c>
       <c r="C124" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D124" s="3">
-        <v>1.9029</v>
+        <v>1.7753000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2128,13 +2128,13 @@
         <v>5</v>
       </c>
       <c r="B125" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D125" s="3">
-        <v>1.5787</v>
+        <v>1.9029</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2145,10 +2145,10 @@
         <v>2023</v>
       </c>
       <c r="C126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="3">
-        <v>1.8613999999999999</v>
+        <v>1.5787</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2159,10 +2159,10 @@
         <v>2023</v>
       </c>
       <c r="C127" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" s="3">
-        <v>1.6684000000000001</v>
+        <v>1.8613999999999999</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2173,10 +2173,10 @@
         <v>2023</v>
       </c>
       <c r="C128" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D128" s="3">
-        <v>1.5757000000000001</v>
+        <v>1.6684000000000001</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2187,10 +2187,10 @@
         <v>2023</v>
       </c>
       <c r="C129" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D129" s="3">
-        <v>2.0183</v>
+        <v>1.5757000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2201,10 +2201,10 @@
         <v>2023</v>
       </c>
       <c r="C130" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D130" s="3">
-        <v>1.6662999999999997</v>
+        <v>2.0183</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2215,10 +2215,10 @@
         <v>2023</v>
       </c>
       <c r="C131" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D131" s="3">
-        <v>1.9484999999999999</v>
+        <v>1.6662999999999997</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2229,10 +2229,10 @@
         <v>2023</v>
       </c>
       <c r="C132" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D132" s="3">
-        <v>2.0987</v>
+        <v>1.9484999999999999</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2243,10 +2243,10 @@
         <v>2023</v>
       </c>
       <c r="C133" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D133" s="3">
-        <v>1.9556999999999998</v>
+        <v>2.0987</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2257,10 +2257,10 @@
         <v>2023</v>
       </c>
       <c r="C134" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D134" s="3">
-        <v>2.331</v>
+        <v>1.9556999999999998</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2271,10 +2271,10 @@
         <v>2023</v>
       </c>
       <c r="C135" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D135" s="3">
-        <v>1.7165999999999999</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2285,10 +2285,10 @@
         <v>2023</v>
       </c>
       <c r="C136" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D136" s="3">
-        <v>1.6557999999999999</v>
+        <v>1.7165999999999999</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2296,13 +2296,13 @@
         <v>5</v>
       </c>
       <c r="B137" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D137" s="3">
-        <v>0.99390000000000001</v>
+        <v>1.6557999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2313,10 +2313,10 @@
         <v>2024</v>
       </c>
       <c r="C138" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2327,10 +2327,10 @@
         <v>2024</v>
       </c>
       <c r="C139" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" s="3">
-        <v>0.88229999999999997</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2341,10 +2341,10 @@
         <v>2024</v>
       </c>
       <c r="C140" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" s="3">
-        <v>0.82889999999999997</v>
+        <v>0.88229999999999997</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2355,10 +2355,10 @@
         <v>2024</v>
       </c>
       <c r="C141" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D141" s="3">
-        <v>1.113</v>
+        <v>0.82889999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2369,10 +2369,10 @@
         <v>2024</v>
       </c>
       <c r="C142" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D142" s="3">
-        <v>1.7364999999999999</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2383,10 +2383,10 @@
         <v>2024</v>
       </c>
       <c r="C143" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" s="3">
-        <v>1.6022000000000001</v>
+        <v>1.7364999999999999</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2397,10 +2397,10 @@
         <v>2024</v>
       </c>
       <c r="C144" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D144" s="3">
-        <v>2.0381999999999998</v>
+        <v>1.6022000000000001</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2411,10 +2411,10 @@
         <v>2024</v>
       </c>
       <c r="C145" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D145" s="3">
-        <v>2.2471000000000001</v>
+        <v>2.0381999999999998</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2425,10 +2425,10 @@
         <v>2024</v>
       </c>
       <c r="C146" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D146" s="3">
-        <v>1.7967000000000002</v>
+        <v>2.2471000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2439,10 +2439,10 @@
         <v>2024</v>
       </c>
       <c r="C147" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D147" s="3">
-        <v>2.1593</v>
+        <v>1.7967000000000002</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2453,10 +2453,10 @@
         <v>2024</v>
       </c>
       <c r="C148" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D148" s="3">
-        <v>1.8868000000000003</v>
+        <v>2.1593</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2464,13 +2464,13 @@
         <v>5</v>
       </c>
       <c r="B149" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C149" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D149" s="3">
-        <v>1.7827999999999999</v>
+        <v>1.8868000000000003</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2481,10 +2481,10 @@
         <v>2025</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" s="3">
-        <v>2.1297999999999999</v>
+        <v>1.7712000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2495,10 +2495,10 @@
         <v>2025</v>
       </c>
       <c r="C151" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D151" s="3">
-        <v>2.4182999999999999</v>
+        <v>2.1036999999999999</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2509,10 +2509,10 @@
         <v>2025</v>
       </c>
       <c r="C152" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D152" s="3">
-        <v>1.9123000000000001</v>
+        <v>2.3969</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2523,10 +2523,10 @@
         <v>2025</v>
       </c>
       <c r="C153" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D153" s="3">
-        <v>1.6870000000000001</v>
+        <v>1.9019999999999997</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2537,10 +2537,10 @@
         <v>2025</v>
       </c>
       <c r="C154" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D154" s="3">
-        <v>2.0131000000000001</v>
+        <v>1.6771</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2551,10 +2551,10 @@
         <v>2025</v>
       </c>
       <c r="C155" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D155" s="3">
-        <v>1.8540000000000001</v>
+        <v>2.0131000000000001</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2565,10 +2565,10 @@
         <v>2025</v>
       </c>
       <c r="C156" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D156" s="3">
-        <v>2.1894999999999998</v>
+        <v>1.8540000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2579,10 +2579,10 @@
         <v>2025</v>
       </c>
       <c r="C157" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D157" s="3">
-        <v>2.0306999999999999</v>
+        <v>2.1505999999999998</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2593,10 +2593,10 @@
         <v>2025</v>
       </c>
       <c r="C158" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D158" s="3">
-        <v>2.2544</v>
+        <v>2.0398999999999998</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2607,10 +2607,10 @@
         <v>2025</v>
       </c>
       <c r="C159" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D159" s="3">
-        <v>2.1646000000000001</v>
+        <v>2.2544</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2621,10 +2621,10 @@
         <v>2025</v>
       </c>
       <c r="C160" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D160" s="3">
-        <v>1.7697000000000001</v>
+        <v>2.1743999999999999</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2632,13 +2632,13 @@
         <v>5</v>
       </c>
       <c r="B161" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C161" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D161" s="3">
-        <v>1.8244</v>
+        <v>1.7697000000000001</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2649,10 +2649,10 @@
         <v>2026</v>
       </c>
       <c r="C162" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" s="3">
-        <v>1.5788</v>
+        <v>1.8560000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2663,10 +2663,10 @@
         <v>2026</v>
       </c>
       <c r="C163" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D163" s="3">
-        <v>1.5091000000000001</v>
+        <v>1.5873999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2677,10 +2677,10 @@
         <v>2026</v>
       </c>
       <c r="C164" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D164" s="3">
-        <v>1.5005999999999999</v>
+        <v>1.5267999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2691,38 +2691,38 @@
         <v>2026</v>
       </c>
       <c r="C165" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D165" s="3">
-        <v>1.5471999999999999</v>
+        <v>1.5854999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B166" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C166" s="2">
         <v>5</v>
       </c>
       <c r="D166" s="3">
-        <v>0.76870000000000005</v>
+        <v>1.7642</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B167" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C167" s="2">
         <v>6</v>
       </c>
       <c r="D167" s="3">
-        <v>0.73919999999999997</v>
+        <v>1.6396999999999999</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -2733,10 +2733,10 @@
         <v>2019</v>
       </c>
       <c r="C168" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D168" s="3">
-        <v>0.40439999999999998</v>
+        <v>0.76870000000000005</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -2747,10 +2747,10 @@
         <v>2019</v>
       </c>
       <c r="C169" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D169" s="3">
-        <v>0.91849999999999998</v>
+        <v>0.73919999999999997</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2758,13 +2758,13 @@
         <v>6</v>
       </c>
       <c r="B170" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D170" s="3">
-        <v>0.91590000000000005</v>
+        <v>0.40439999999999998</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2772,13 +2772,13 @@
         <v>6</v>
       </c>
       <c r="B171" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C171" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D171" s="3">
-        <v>0.91639999999999999</v>
+        <v>0.91849999999999998</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2789,10 +2789,10 @@
         <v>2020</v>
       </c>
       <c r="C172" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D172" s="3">
-        <v>0.71460000000000001</v>
+        <v>0.91590000000000005</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2803,10 +2803,10 @@
         <v>2020</v>
       </c>
       <c r="C173" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D173" s="3">
-        <v>0.99629999999999985</v>
+        <v>0.91639999999999999</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2817,10 +2817,10 @@
         <v>2020</v>
       </c>
       <c r="C174" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D174" s="3">
-        <v>1.0396000000000001</v>
+        <v>0.71460000000000001</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2831,10 +2831,10 @@
         <v>2020</v>
       </c>
       <c r="C175" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D175" s="3">
-        <v>0.70820000000000005</v>
+        <v>1.002</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2845,10 +2845,10 @@
         <v>2020</v>
       </c>
       <c r="C176" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D176" s="3">
-        <v>1.5511999999999999</v>
+        <v>1.0396000000000001</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2859,10 +2859,10 @@
         <v>2020</v>
       </c>
       <c r="C177" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D177" s="3">
-        <v>1.117</v>
+        <v>0.70820000000000005</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2873,10 +2873,10 @@
         <v>2020</v>
       </c>
       <c r="C178" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D178" s="3">
-        <v>1.1403000000000001</v>
+        <v>1.5511999999999999</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2887,10 +2887,10 @@
         <v>2020</v>
       </c>
       <c r="C179" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D179" s="3">
-        <v>1.431</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2901,10 +2901,10 @@
         <v>2020</v>
       </c>
       <c r="C180" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D180" s="3">
-        <v>1.3353999999999999</v>
+        <v>1.1403000000000001</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2915,10 +2915,10 @@
         <v>2020</v>
       </c>
       <c r="C181" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D181" s="3">
-        <v>1.8660000000000001</v>
+        <v>1.4339</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2926,13 +2926,13 @@
         <v>6</v>
       </c>
       <c r="B182" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C182" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D182" s="3">
-        <v>1.4126000000000001</v>
+        <v>1.3353999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2940,13 +2940,13 @@
         <v>6</v>
       </c>
       <c r="B183" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C183" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D183" s="3">
-        <v>1.2838000000000001</v>
+        <v>1.8660000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2957,10 +2957,10 @@
         <v>2021</v>
       </c>
       <c r="C184" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D184" s="3">
-        <v>1.0382</v>
+        <v>1.4126000000000001</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2971,10 +2971,10 @@
         <v>2021</v>
       </c>
       <c r="C185" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D185" s="3">
-        <v>1.4381999999999999</v>
+        <v>1.2838000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2985,10 +2985,10 @@
         <v>2021</v>
       </c>
       <c r="C186" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D186" s="3">
-        <v>1.1092</v>
+        <v>1.0397000000000001</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2999,10 +2999,10 @@
         <v>2021</v>
       </c>
       <c r="C187" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D187" s="3">
-        <v>0.93130000000000002</v>
+        <v>1.4381999999999999</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3013,10 +3013,10 @@
         <v>2021</v>
       </c>
       <c r="C188" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D188" s="3">
-        <v>1.4892000000000001</v>
+        <v>1.1092</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3027,10 +3027,10 @@
         <v>2021</v>
       </c>
       <c r="C189" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D189" s="3">
-        <v>1.1386000000000001</v>
+        <v>0.93130000000000002</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3041,10 +3041,10 @@
         <v>2021</v>
       </c>
       <c r="C190" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D190" s="3">
-        <v>1.1675</v>
+        <v>1.4892000000000001</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3055,10 +3055,10 @@
         <v>2021</v>
       </c>
       <c r="C191" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D191" s="3">
-        <v>1.2996000000000001</v>
+        <v>1.1386000000000001</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3069,10 +3069,10 @@
         <v>2021</v>
       </c>
       <c r="C192" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D192" s="3">
-        <v>1.0663</v>
+        <v>1.1675</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3080,13 +3080,13 @@
         <v>6</v>
       </c>
       <c r="B193" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C193" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D193" s="3">
-        <v>1.0550999999999999</v>
+        <v>1.2996000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3094,13 +3094,13 @@
         <v>6</v>
       </c>
       <c r="B194" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C194" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D194" s="3">
-        <v>1.0621</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3111,10 +3111,10 @@
         <v>2022</v>
       </c>
       <c r="C195" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D195" s="3">
-        <v>1.0516000000000001</v>
+        <v>1.0550999999999999</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3125,10 +3125,10 @@
         <v>2022</v>
       </c>
       <c r="C196" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D196" s="3">
-        <v>1.0001</v>
+        <v>1.0621</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3139,10 +3139,10 @@
         <v>2022</v>
       </c>
       <c r="C197" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D197" s="3">
-        <v>1.4765999999999999</v>
+        <v>1.0516000000000001</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3153,10 +3153,10 @@
         <v>2022</v>
       </c>
       <c r="C198" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D198" s="3">
-        <v>1.0939000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3167,10 +3167,10 @@
         <v>2022</v>
       </c>
       <c r="C199" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D199" s="3">
-        <v>1.2916000000000001</v>
+        <v>1.4765999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3181,10 +3181,10 @@
         <v>2022</v>
       </c>
       <c r="C200" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D200" s="3">
-        <v>1.2714000000000001</v>
+        <v>1.0939000000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3195,10 +3195,10 @@
         <v>2022</v>
       </c>
       <c r="C201" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D201" s="3">
-        <v>1.2466999999999999</v>
+        <v>1.2916000000000001</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3209,10 +3209,10 @@
         <v>2022</v>
       </c>
       <c r="C202" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D202" s="3">
-        <v>1.0482</v>
+        <v>1.2714000000000001</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3223,10 +3223,10 @@
         <v>2022</v>
       </c>
       <c r="C203" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D203" s="3">
-        <v>1.0491999999999999</v>
+        <v>1.2466999999999999</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3237,10 +3237,10 @@
         <v>2022</v>
       </c>
       <c r="C204" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D204" s="3">
-        <v>1.2296</v>
+        <v>1.0482</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3248,13 +3248,13 @@
         <v>6</v>
       </c>
       <c r="B205" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D205" s="3">
-        <v>1.2606999999999999</v>
+        <v>1.0491999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3262,13 +3262,13 @@
         <v>6</v>
       </c>
       <c r="B206" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C206" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D206" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.2296</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3279,10 +3279,10 @@
         <v>2023</v>
       </c>
       <c r="C207" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D207" s="3">
-        <v>1.5298</v>
+        <v>1.2606999999999999</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3293,10 +3293,10 @@
         <v>2023</v>
       </c>
       <c r="C208" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D208" s="3">
-        <v>1.1073</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3307,10 +3307,10 @@
         <v>2023</v>
       </c>
       <c r="C209" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D209" s="3">
-        <v>1.0602</v>
+        <v>1.5298</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3321,10 +3321,10 @@
         <v>2023</v>
       </c>
       <c r="C210" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D210" s="3">
-        <v>1.3539999999999999</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3335,10 +3335,10 @@
         <v>2023</v>
       </c>
       <c r="C211" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D211" s="3">
-        <v>1.3968</v>
+        <v>1.0602</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3349,10 +3349,10 @@
         <v>2023</v>
       </c>
       <c r="C212" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D212" s="3">
-        <v>1.2923</v>
+        <v>1.3539999999999999</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3363,10 +3363,10 @@
         <v>2023</v>
       </c>
       <c r="C213" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D213" s="3">
-        <v>1.0855999999999999</v>
+        <v>1.3968</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3377,10 +3377,10 @@
         <v>2023</v>
       </c>
       <c r="C214" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D214" s="3">
-        <v>1.2621</v>
+        <v>1.2923</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3391,10 +3391,10 @@
         <v>2023</v>
       </c>
       <c r="C215" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D215" s="3">
-        <v>1.1758</v>
+        <v>1.0855999999999999</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3405,10 +3405,10 @@
         <v>2023</v>
       </c>
       <c r="C216" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D216" s="3">
-        <v>1.3091999999999999</v>
+        <v>1.2621</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3416,13 +3416,13 @@
         <v>6</v>
       </c>
       <c r="B217" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C217" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D217" s="3">
-        <v>1.5447</v>
+        <v>1.1758</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3430,13 +3430,13 @@
         <v>6</v>
       </c>
       <c r="B218" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C218" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D218" s="3">
-        <v>1.087</v>
+        <v>1.3091999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3447,10 +3447,10 @@
         <v>2024</v>
       </c>
       <c r="C219" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D219" s="3">
-        <v>0.89500000000000002</v>
+        <v>1.5447</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3461,10 +3461,10 @@
         <v>2024</v>
       </c>
       <c r="C220" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D220" s="3">
-        <v>1.0757000000000001</v>
+        <v>1.087</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3475,10 +3475,10 @@
         <v>2024</v>
       </c>
       <c r="C221" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D221" s="3">
-        <v>1.2897000000000001</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>2024</v>
       </c>
       <c r="C222" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D222" s="3">
-        <v>1.3664000000000001</v>
+        <v>1.0757000000000001</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3503,10 +3503,10 @@
         <v>2024</v>
       </c>
       <c r="C223" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D223" s="3">
-        <v>1.2185999999999999</v>
+        <v>1.2897000000000001</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3517,10 +3517,10 @@
         <v>2024</v>
       </c>
       <c r="C224" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D224" s="3">
-        <v>1.2690999999999999</v>
+        <v>1.3664000000000001</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3531,10 +3531,10 @@
         <v>2024</v>
       </c>
       <c r="C225" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D225" s="3">
-        <v>1.0390999999999999</v>
+        <v>1.2185999999999999</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3545,10 +3545,10 @@
         <v>2024</v>
       </c>
       <c r="C226" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D226" s="3">
-        <v>1.1085</v>
+        <v>1.2690999999999999</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3559,10 +3559,10 @@
         <v>2024</v>
       </c>
       <c r="C227" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D227" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.0390999999999999</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3573,10 +3573,10 @@
         <v>2024</v>
       </c>
       <c r="C228" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D228" s="3">
-        <v>1.0940000000000001</v>
+        <v>1.1085</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3584,13 +3584,13 @@
         <v>6</v>
       </c>
       <c r="B229" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C229" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D229" s="3">
-        <v>0.94689999999999996</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3598,13 +3598,13 @@
         <v>6</v>
       </c>
       <c r="B230" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C230" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D230" s="3">
-        <v>0.95220000000000005</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3615,10 +3615,10 @@
         <v>2025</v>
       </c>
       <c r="C231" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" s="3">
-        <v>0.95209999999999995</v>
+        <v>0.94689999999999996</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3629,10 +3629,10 @@
         <v>2025</v>
       </c>
       <c r="C232" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D232" s="3">
-        <v>1.0407999999999999</v>
+        <v>0.95220000000000005</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3643,10 +3643,10 @@
         <v>2025</v>
       </c>
       <c r="C233" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D233" s="3">
-        <v>1.1001000000000001</v>
+        <v>0.95209999999999995</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3657,10 +3657,10 @@
         <v>2025</v>
       </c>
       <c r="C234" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D234" s="3">
-        <v>1.0804</v>
+        <v>1.0407999999999999</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3671,10 +3671,10 @@
         <v>2025</v>
       </c>
       <c r="C235" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D235" s="3">
-        <v>1.1061000000000001</v>
+        <v>1.1001000000000001</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3685,10 +3685,10 @@
         <v>2025</v>
       </c>
       <c r="C236" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D236" s="3">
-        <v>0.98920000000000008</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3699,10 +3699,10 @@
         <v>2025</v>
       </c>
       <c r="C237" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D237" s="3">
-        <v>1.0139</v>
+        <v>1.1061000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3713,10 +3713,10 @@
         <v>2025</v>
       </c>
       <c r="C238" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D238" s="3">
-        <v>0.94899999999999995</v>
+        <v>0.98920000000000008</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3727,10 +3727,10 @@
         <v>2025</v>
       </c>
       <c r="C239" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D239" s="3">
-        <v>1.0072000000000001</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3741,10 +3741,10 @@
         <v>2025</v>
       </c>
       <c r="C240" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D240" s="3">
-        <v>1.0087999999999999</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3752,13 +3752,13 @@
         <v>6</v>
       </c>
       <c r="B241" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C241" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D241" s="3">
-        <v>0.98619999999999997</v>
+        <v>1.0072000000000001</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3766,13 +3766,13 @@
         <v>6</v>
       </c>
       <c r="B242" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C242" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D242" s="3">
-        <v>0.87270000000000003</v>
+        <v>1.0069999999999999</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3783,10 +3783,10 @@
         <v>2026</v>
       </c>
       <c r="C243" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D243" s="3">
-        <v>0.93330000000000013</v>
+        <v>0.94920000000000015</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3797,10 +3797,10 @@
         <v>2026</v>
       </c>
       <c r="C244" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D244" s="3">
-        <v>0.89019999999999999</v>
+        <v>0.87809999999999999</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3811,52 +3811,52 @@
         <v>2026</v>
       </c>
       <c r="C245" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D245" s="3">
-        <v>0.89939999999999987</v>
+        <v>0.97489999999999988</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B246" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C246" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D246" s="3">
-        <v>0.3634</v>
+        <v>0.94169999999999987</v>
       </c>
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B247" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C247" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D247" s="3">
-        <v>1.1855</v>
+        <v>1.0869</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B248" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C248" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D248" s="3">
-        <v>0.55089999999999995</v>
+        <v>1.1671</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3867,10 +3867,10 @@
         <v>2019</v>
       </c>
       <c r="C249" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D249" s="3">
-        <v>1.544</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3881,10 +3881,10 @@
         <v>2019</v>
       </c>
       <c r="C250" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D250" s="3">
-        <v>1.5068999999999997</v>
+        <v>1.1855</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3892,13 +3892,13 @@
         <v>7</v>
       </c>
       <c r="B251" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C251" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D251" s="3">
-        <v>0.94199999999999995</v>
+        <v>0.55079999999999996</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3906,13 +3906,13 @@
         <v>7</v>
       </c>
       <c r="B252" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C252" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D252" s="3">
-        <v>1.0011000000000001</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3920,13 +3920,13 @@
         <v>7</v>
       </c>
       <c r="B253" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C253" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D253" s="3">
-        <v>0.96850000000000003</v>
+        <v>1.5068999999999997</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3937,10 +3937,10 @@
         <v>2020</v>
       </c>
       <c r="C254" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D254" s="3">
-        <v>1.0559000000000001</v>
+        <v>0.94240000000000002</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3951,10 +3951,10 @@
         <v>2020</v>
       </c>
       <c r="C255" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D255" s="3">
-        <v>0.91450000000000009</v>
+        <v>1.0011000000000001</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3965,10 +3965,10 @@
         <v>2020</v>
       </c>
       <c r="C256" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D256" s="3">
-        <v>1.0116000000000001</v>
+        <v>0.96850000000000003</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3979,10 +3979,10 @@
         <v>2020</v>
       </c>
       <c r="C257" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D257" s="3">
-        <v>1.3797999999999999</v>
+        <v>1.0559000000000001</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3993,10 +3993,10 @@
         <v>2020</v>
       </c>
       <c r="C258" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D258" s="3">
-        <v>1.4618</v>
+        <v>0.91450000000000009</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4007,10 +4007,10 @@
         <v>2020</v>
       </c>
       <c r="C259" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D259" s="3">
-        <v>1.2636000000000001</v>
+        <v>1.0116000000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4021,10 +4021,10 @@
         <v>2020</v>
       </c>
       <c r="C260" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D260" s="3">
-        <v>1.0862000000000001</v>
+        <v>1.3797999999999999</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4035,10 +4035,10 @@
         <v>2020</v>
       </c>
       <c r="C261" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D261" s="3">
-        <v>1.1226</v>
+        <v>1.4618</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4049,10 +4049,10 @@
         <v>2020</v>
       </c>
       <c r="C262" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D262" s="3">
-        <v>1.1798999999999999</v>
+        <v>1.2636000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4060,13 +4060,13 @@
         <v>7</v>
       </c>
       <c r="B263" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C263" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D263" s="3">
-        <v>1.3149999999999999</v>
+        <v>1.0862000000000001</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4074,13 +4074,13 @@
         <v>7</v>
       </c>
       <c r="B264" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C264" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D264" s="3">
-        <v>1.2918000000000001</v>
+        <v>1.1226</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4088,13 +4088,13 @@
         <v>7</v>
       </c>
       <c r="B265" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C265" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D265" s="3">
-        <v>1.3935</v>
+        <v>1.1798999999999999</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4105,10 +4105,10 @@
         <v>2021</v>
       </c>
       <c r="C266" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D266" s="3">
-        <v>1.6409</v>
+        <v>1.3149999999999999</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4119,10 +4119,10 @@
         <v>2021</v>
       </c>
       <c r="C267" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D267" s="3">
-        <v>1.5944</v>
+        <v>1.2918000000000001</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4133,10 +4133,10 @@
         <v>2021</v>
       </c>
       <c r="C268" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3">
-        <v>1.5669999999999999</v>
+        <v>1.3935</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4147,10 +4147,10 @@
         <v>2021</v>
       </c>
       <c r="C269" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D269" s="3">
-        <v>1.276</v>
+        <v>1.6409</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4161,10 +4161,10 @@
         <v>2021</v>
       </c>
       <c r="C270" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D270" s="3">
-        <v>1.1046</v>
+        <v>1.5944</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4175,10 +4175,10 @@
         <v>2021</v>
       </c>
       <c r="C271" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D271" s="3">
-        <v>1.0746</v>
+        <v>1.5669999999999999</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4189,10 +4189,10 @@
         <v>2021</v>
       </c>
       <c r="C272" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D272" s="3">
-        <v>0.95230000000000004</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4203,10 +4203,10 @@
         <v>2021</v>
       </c>
       <c r="C273" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D273" s="3">
-        <v>0.93070000000000008</v>
+        <v>1.1046</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4217,10 +4217,10 @@
         <v>2021</v>
       </c>
       <c r="C274" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D274" s="3">
-        <v>1.0242</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4228,13 +4228,13 @@
         <v>7</v>
       </c>
       <c r="B275" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C275" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D275" s="3">
-        <v>0.95179999999999998</v>
+        <v>0.95230000000000004</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4242,13 +4242,13 @@
         <v>7</v>
       </c>
       <c r="B276" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C276" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D276" s="3">
-        <v>1.1564000000000001</v>
+        <v>0.93070000000000008</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4256,13 +4256,13 @@
         <v>7</v>
       </c>
       <c r="B277" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C277" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D277" s="3">
-        <v>0.93640000000000001</v>
+        <v>1.0242</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4273,10 +4273,10 @@
         <v>2022</v>
       </c>
       <c r="C278" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D278" s="3">
-        <v>0.86789999999999989</v>
+        <v>0.95179999999999998</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4287,10 +4287,10 @@
         <v>2022</v>
       </c>
       <c r="C279" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D279" s="3">
-        <v>0.89589999999999992</v>
+        <v>1.1564000000000001</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4301,10 +4301,10 @@
         <v>2022</v>
       </c>
       <c r="C280" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D280" s="3">
-        <v>0.97230000000000005</v>
+        <v>0.93640000000000001</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4315,10 +4315,10 @@
         <v>2022</v>
       </c>
       <c r="C281" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D281" s="3">
-        <v>1.0585</v>
+        <v>0.86789999999999989</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4329,10 +4329,10 @@
         <v>2022</v>
       </c>
       <c r="C282" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D282" s="3">
-        <v>0.91169999999999995</v>
+        <v>0.89589999999999992</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4343,10 +4343,10 @@
         <v>2022</v>
       </c>
       <c r="C283" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D283" s="3">
-        <v>0.77860000000000007</v>
+        <v>0.97230000000000005</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4357,10 +4357,10 @@
         <v>2022</v>
       </c>
       <c r="C284" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D284" s="3">
-        <v>0.98480000000000001</v>
+        <v>1.0585</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4371,10 +4371,10 @@
         <v>2022</v>
       </c>
       <c r="C285" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D285" s="3">
-        <v>0.96220000000000006</v>
+        <v>0.91169999999999995</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4385,10 +4385,10 @@
         <v>2022</v>
       </c>
       <c r="C286" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D286" s="3">
-        <v>0.89329999999999998</v>
+        <v>0.77860000000000007</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4396,13 +4396,13 @@
         <v>7</v>
       </c>
       <c r="B287" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C287" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D287" s="3">
-        <v>0.99390000000000001</v>
+        <v>0.98480000000000001</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4410,13 +4410,13 @@
         <v>7</v>
       </c>
       <c r="B288" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C288" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D288" s="3">
-        <v>1.0999000000000001</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4424,13 +4424,13 @@
         <v>7</v>
       </c>
       <c r="B289" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C289" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D289" s="3">
-        <v>1.1256999999999999</v>
+        <v>0.89329999999999998</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4441,10 +4441,10 @@
         <v>2023</v>
       </c>
       <c r="C290" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D290" s="3">
-        <v>1.0003</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4455,10 +4455,10 @@
         <v>2023</v>
       </c>
       <c r="C291" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D291" s="3">
-        <v>1.1068</v>
+        <v>1.0999000000000001</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4469,10 +4469,10 @@
         <v>2023</v>
       </c>
       <c r="C292" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D292" s="3">
-        <v>1.0865</v>
+        <v>1.1256999999999999</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4483,10 +4483,10 @@
         <v>2023</v>
       </c>
       <c r="C293" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D293" s="3">
-        <v>0.97589999999999999</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4497,10 +4497,10 @@
         <v>2023</v>
       </c>
       <c r="C294" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D294" s="3">
-        <v>1.0511999999999999</v>
+        <v>1.1068</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4511,10 +4511,10 @@
         <v>2023</v>
       </c>
       <c r="C295" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D295" s="3">
-        <v>1.0577000000000001</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4525,10 +4525,10 @@
         <v>2023</v>
       </c>
       <c r="C296" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D296" s="3">
-        <v>0.97499999999999987</v>
+        <v>0.97589999999999999</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4539,10 +4539,10 @@
         <v>2023</v>
       </c>
       <c r="C297" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D297" s="3">
-        <v>1.0082</v>
+        <v>1.0511999999999999</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4553,10 +4553,10 @@
         <v>2023</v>
       </c>
       <c r="C298" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D298" s="3">
-        <v>1.0295000000000001</v>
+        <v>1.0577000000000001</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4564,13 +4564,13 @@
         <v>7</v>
       </c>
       <c r="B299" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C299" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D299" s="3">
-        <v>0.87479999999999991</v>
+        <v>0.97499999999999987</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4578,13 +4578,13 @@
         <v>7</v>
       </c>
       <c r="B300" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C300" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D300" s="3">
-        <v>0.8629</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4592,13 +4592,13 @@
         <v>7</v>
       </c>
       <c r="B301" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C301" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D301" s="3">
-        <v>0.87240000000000006</v>
+        <v>1.0295000000000001</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4609,10 +4609,10 @@
         <v>2024</v>
       </c>
       <c r="C302" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D302" s="3">
-        <v>1.1091</v>
+        <v>0.87479999999999991</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4623,10 +4623,10 @@
         <v>2024</v>
       </c>
       <c r="C303" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D303" s="3">
-        <v>1.0685</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4637,10 +4637,10 @@
         <v>2024</v>
       </c>
       <c r="C304" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D304" s="3">
-        <v>1.0423</v>
+        <v>0.87240000000000006</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4651,10 +4651,10 @@
         <v>2024</v>
       </c>
       <c r="C305" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D305" s="3">
-        <v>1.1042000000000001</v>
+        <v>1.1091</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4665,10 +4665,10 @@
         <v>2024</v>
       </c>
       <c r="C306" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D306" s="3">
-        <v>1.1225000000000001</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4679,10 +4679,10 @@
         <v>2024</v>
       </c>
       <c r="C307" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D307" s="3">
-        <v>1.2110000000000001</v>
+        <v>1.0423</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4693,10 +4693,10 @@
         <v>2024</v>
       </c>
       <c r="C308" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D308" s="3">
-        <v>1.2477</v>
+        <v>1.1042000000000001</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4707,10 +4707,10 @@
         <v>2024</v>
       </c>
       <c r="C309" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D309" s="3">
-        <v>1.1498999999999999</v>
+        <v>1.1225000000000001</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4721,10 +4721,10 @@
         <v>2024</v>
       </c>
       <c r="C310" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D310" s="3">
-        <v>1.2698</v>
+        <v>1.2110000000000001</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4732,13 +4732,13 @@
         <v>7</v>
       </c>
       <c r="B311" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C311" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D311" s="3">
-        <v>1.0773999999999999</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4746,13 +4746,13 @@
         <v>7</v>
       </c>
       <c r="B312" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C312" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D312" s="3">
-        <v>1.0772999999999999</v>
+        <v>1.1498999999999999</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4760,13 +4760,13 @@
         <v>7</v>
       </c>
       <c r="B313" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C313" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D313" s="3">
-        <v>1.2062999999999999</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4777,10 +4777,10 @@
         <v>2025</v>
       </c>
       <c r="C314" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D314" s="3">
-        <v>1.1231</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4791,10 +4791,10 @@
         <v>2025</v>
       </c>
       <c r="C315" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D315" s="3">
-        <v>1.1679999999999999</v>
+        <v>1.0754999999999999</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4805,10 +4805,10 @@
         <v>2025</v>
       </c>
       <c r="C316" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D316" s="3">
-        <v>1.1792</v>
+        <v>1.2067000000000001</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4819,10 +4819,10 @@
         <v>2025</v>
       </c>
       <c r="C317" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D317" s="3">
-        <v>1.3216000000000001</v>
+        <v>1.1234999999999999</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4833,10 +4833,10 @@
         <v>2025</v>
       </c>
       <c r="C318" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D318" s="3">
-        <v>1.1874</v>
+        <v>1.2224999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4847,10 +4847,10 @@
         <v>2025</v>
       </c>
       <c r="C319" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D319" s="3">
-        <v>1.1955</v>
+        <v>1.1957</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4861,10 +4861,10 @@
         <v>2025</v>
       </c>
       <c r="C320" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D320" s="3">
-        <v>1.355</v>
+        <v>1.3280000000000001</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4875,10 +4875,10 @@
         <v>2025</v>
       </c>
       <c r="C321" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D321" s="3">
-        <v>1.3223</v>
+        <v>1.1873</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4889,10 +4889,10 @@
         <v>2025</v>
       </c>
       <c r="C322" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D322" s="3">
-        <v>1.1875</v>
+        <v>1.1939</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4900,13 +4900,13 @@
         <v>7</v>
       </c>
       <c r="B323" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C323" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D323" s="3">
-        <v>1.1228</v>
+        <v>1.3411</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4914,13 +4914,13 @@
         <v>7</v>
       </c>
       <c r="B324" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C324" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D324" s="3">
-        <v>1.2611000000000001</v>
+        <v>1.3031999999999999</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4928,13 +4928,13 @@
         <v>7</v>
       </c>
       <c r="B325" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C325" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D325" s="3">
-        <v>1.7902</v>
+        <v>1.1761999999999999</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4945,10 +4945,10 @@
         <v>2026</v>
       </c>
       <c r="C326" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D326" s="3">
-        <v>1.2192000000000001</v>
+        <v>1.1228</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4959,66 +4959,66 @@
         <v>2026</v>
       </c>
       <c r="C327" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D327" s="3">
-        <v>1.1336999999999999</v>
+        <v>1.2719</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B328" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C328" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D328" s="3">
-        <v>0.46260000000000001</v>
+        <v>1.3737999999999999</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B329" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C329" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D329" s="3">
-        <v>2.5009999999999999</v>
+        <v>1.2373000000000001</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B330" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C330" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D330" s="3">
-        <v>0.60919999999999996</v>
+        <v>1.1888000000000001</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B331" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C331" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D331" s="3">
-        <v>0.43890000000000001</v>
+        <v>1.2088000000000001</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5026,13 +5026,13 @@
         <v>8</v>
       </c>
       <c r="B332" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C332" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D332" s="3">
-        <v>0.58919999999999995</v>
+        <v>0.46260000000000001</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5040,13 +5040,13 @@
         <v>8</v>
       </c>
       <c r="B333" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C333" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D333" s="3">
-        <v>1.8193999999999997</v>
+        <v>2.5009999999999999</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5054,13 +5054,13 @@
         <v>8</v>
       </c>
       <c r="B334" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C334" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D334" s="3">
-        <v>1.2989999999999999</v>
+        <v>0.60919999999999996</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5071,10 +5071,10 @@
         <v>2020</v>
       </c>
       <c r="C335" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D335" s="3">
-        <v>1.3857999999999999</v>
+        <v>0.43890000000000001</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5085,10 +5085,10 @@
         <v>2020</v>
       </c>
       <c r="C336" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D336" s="3">
-        <v>1.9608000000000001</v>
+        <v>0.58919999999999995</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5099,10 +5099,10 @@
         <v>2020</v>
       </c>
       <c r="C337" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D337" s="3">
-        <v>1.8338000000000001</v>
+        <v>1.8193999999999997</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5113,10 +5113,10 @@
         <v>2020</v>
       </c>
       <c r="C338" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D338" s="3">
-        <v>1.7322999999999997</v>
+        <v>1.2989999999999999</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5127,10 +5127,10 @@
         <v>2020</v>
       </c>
       <c r="C339" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D339" s="3">
-        <v>1.8366</v>
+        <v>1.3857999999999999</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5141,10 +5141,10 @@
         <v>2020</v>
       </c>
       <c r="C340" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D340" s="3">
-        <v>1.8994</v>
+        <v>1.9608000000000001</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5155,10 +5155,10 @@
         <v>2020</v>
       </c>
       <c r="C341" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D341" s="3">
-        <v>1.7765999999999997</v>
+        <v>1.8338000000000001</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5166,13 +5166,13 @@
         <v>8</v>
       </c>
       <c r="B342" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C342" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D342" s="3">
-        <v>1.5302</v>
+        <v>1.7322999999999997</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5180,13 +5180,13 @@
         <v>8</v>
       </c>
       <c r="B343" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C343" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D343" s="3">
-        <v>1.7687000000000002</v>
+        <v>1.8378000000000001</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5194,13 +5194,13 @@
         <v>8</v>
       </c>
       <c r="B344" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C344" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D344" s="3">
-        <v>1.3537999999999999</v>
+        <v>1.8994</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5208,13 +5208,13 @@
         <v>8</v>
       </c>
       <c r="B345" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C345" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D345" s="3">
-        <v>1.1635</v>
+        <v>1.7765999999999997</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5225,10 +5225,10 @@
         <v>2021</v>
       </c>
       <c r="C346" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D346" s="3">
-        <v>1.9408000000000003</v>
+        <v>1.5302</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5239,10 +5239,10 @@
         <v>2021</v>
       </c>
       <c r="C347" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D347" s="3">
-        <v>1.2329000000000001</v>
+        <v>1.7687000000000002</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5253,10 +5253,10 @@
         <v>2021</v>
       </c>
       <c r="C348" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D348" s="3">
-        <v>1.3917999999999999</v>
+        <v>1.3537999999999999</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5267,10 +5267,10 @@
         <v>2021</v>
       </c>
       <c r="C349" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D349" s="3">
-        <v>1.323</v>
+        <v>1.1635</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5281,10 +5281,10 @@
         <v>2021</v>
       </c>
       <c r="C350" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D350" s="3">
-        <v>1.4914000000000001</v>
+        <v>1.9408000000000003</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5295,10 +5295,10 @@
         <v>2021</v>
       </c>
       <c r="C351" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D351" s="3">
-        <v>1.4085000000000001</v>
+        <v>1.2329000000000001</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5309,10 +5309,10 @@
         <v>2021</v>
       </c>
       <c r="C352" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D352" s="3">
-        <v>1.4259999999999999</v>
+        <v>1.3917999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5323,10 +5323,10 @@
         <v>2021</v>
       </c>
       <c r="C353" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D353" s="3">
-        <v>1.3572</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5334,13 +5334,13 @@
         <v>8</v>
       </c>
       <c r="B354" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C354" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D354" s="3">
-        <v>1.4053</v>
+        <v>1.4923999999999999</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5348,13 +5348,13 @@
         <v>8</v>
       </c>
       <c r="B355" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C355" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D355" s="3">
-        <v>1.4612000000000001</v>
+        <v>1.4085000000000001</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5362,13 +5362,13 @@
         <v>8</v>
       </c>
       <c r="B356" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C356" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D356" s="3">
-        <v>1.4157999999999999</v>
+        <v>1.4259999999999999</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5376,13 +5376,13 @@
         <v>8</v>
       </c>
       <c r="B357" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C357" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D357" s="3">
-        <v>1.4791999999999998</v>
+        <v>1.3572</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5393,10 +5393,10 @@
         <v>2022</v>
       </c>
       <c r="C358" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D358" s="3">
-        <v>1.4762999999999999</v>
+        <v>1.4053</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5407,10 +5407,10 @@
         <v>2022</v>
       </c>
       <c r="C359" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D359" s="3">
-        <v>1.4380999999999999</v>
+        <v>1.4612000000000001</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5421,10 +5421,10 @@
         <v>2022</v>
       </c>
       <c r="C360" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D360" s="3">
-        <v>1.6324000000000001</v>
+        <v>1.4157999999999999</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5435,10 +5435,10 @@
         <v>2022</v>
       </c>
       <c r="C361" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D361" s="3">
-        <v>1.5557000000000001</v>
+        <v>1.4791999999999998</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5449,10 +5449,10 @@
         <v>2022</v>
       </c>
       <c r="C362" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D362" s="3">
-        <v>1.599</v>
+        <v>1.4770000000000001</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5463,10 +5463,10 @@
         <v>2022</v>
       </c>
       <c r="C363" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D363" s="3">
-        <v>1.4990000000000001</v>
+        <v>1.4380999999999999</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5477,10 +5477,10 @@
         <v>2022</v>
       </c>
       <c r="C364" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D364" s="3">
-        <v>1.484</v>
+        <v>1.6324000000000001</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5491,10 +5491,10 @@
         <v>2022</v>
       </c>
       <c r="C365" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D365" s="3">
-        <v>1.5085999999999999</v>
+        <v>1.5557000000000001</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5502,13 +5502,13 @@
         <v>8</v>
       </c>
       <c r="B366" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C366" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D366" s="3">
-        <v>1.4896</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5516,13 +5516,13 @@
         <v>8</v>
       </c>
       <c r="B367" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C367" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D367" s="3">
-        <v>1.5462999999999998</v>
+        <v>1.4990000000000001</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5530,13 +5530,13 @@
         <v>8</v>
       </c>
       <c r="B368" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C368" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D368" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5544,13 +5544,13 @@
         <v>8</v>
       </c>
       <c r="B369" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C369" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D369" s="3">
-        <v>1.3847</v>
+        <v>1.5085999999999999</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5561,10 +5561,10 @@
         <v>2023</v>
       </c>
       <c r="C370" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D370" s="3">
-        <v>1.2858000000000001</v>
+        <v>1.4896</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5575,10 +5575,10 @@
         <v>2023</v>
       </c>
       <c r="C371" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D371" s="3">
-        <v>1.8708</v>
+        <v>1.5462999999999998</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5589,10 +5589,10 @@
         <v>2023</v>
       </c>
       <c r="C372" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D372" s="3">
-        <v>1.8864000000000001</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5603,10 +5603,10 @@
         <v>2023</v>
       </c>
       <c r="C373" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D373" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.3847</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5617,10 +5617,10 @@
         <v>2023</v>
       </c>
       <c r="C374" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D374" s="3">
-        <v>1.9263999999999999</v>
+        <v>1.2858000000000001</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5631,10 +5631,10 @@
         <v>2023</v>
       </c>
       <c r="C375" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D375" s="3">
-        <v>1.9342999999999999</v>
+        <v>1.8708</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5645,10 +5645,10 @@
         <v>2023</v>
       </c>
       <c r="C376" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D376" s="3">
-        <v>1.7403999999999999</v>
+        <v>1.8864000000000001</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5659,10 +5659,10 @@
         <v>2023</v>
       </c>
       <c r="C377" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D377" s="3">
-        <v>1.7998000000000001</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5670,13 +5670,13 @@
         <v>8</v>
       </c>
       <c r="B378" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C378" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D378" s="3">
-        <v>1.8641000000000001</v>
+        <v>1.9263999999999999</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5684,13 +5684,13 @@
         <v>8</v>
       </c>
       <c r="B379" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C379" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D379" s="3">
-        <v>2.0535999999999999</v>
+        <v>1.9342999999999999</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5698,13 +5698,13 @@
         <v>8</v>
       </c>
       <c r="B380" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C380" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D380" s="3">
-        <v>1.8251999999999999</v>
+        <v>1.7403999999999999</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5712,13 +5712,13 @@
         <v>8</v>
       </c>
       <c r="B381" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C381" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D381" s="3">
-        <v>1.8498000000000001</v>
+        <v>1.7998000000000001</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5729,10 +5729,10 @@
         <v>2024</v>
       </c>
       <c r="C382" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D382" s="3">
-        <v>1.8720000000000001</v>
+        <v>1.8641000000000001</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5743,10 +5743,10 @@
         <v>2024</v>
       </c>
       <c r="C383" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D383" s="3">
-        <v>1.8865000000000001</v>
+        <v>2.0535999999999999</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5757,10 +5757,10 @@
         <v>2024</v>
       </c>
       <c r="C384" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D384" s="3">
-        <v>1.6568000000000001</v>
+        <v>1.8251999999999999</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5771,10 +5771,10 @@
         <v>2024</v>
       </c>
       <c r="C385" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D385" s="3">
-        <v>1.8308</v>
+        <v>1.8498000000000001</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5785,10 +5785,10 @@
         <v>2024</v>
       </c>
       <c r="C386" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D386" s="3">
-        <v>1.8752</v>
+        <v>1.8720000000000001</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5799,10 +5799,10 @@
         <v>2024</v>
       </c>
       <c r="C387" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D387" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.8865000000000001</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5813,10 +5813,10 @@
         <v>2024</v>
       </c>
       <c r="C388" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D388" s="3">
-        <v>1.8120000000000001</v>
+        <v>1.6568000000000001</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5827,10 +5827,10 @@
         <v>2024</v>
       </c>
       <c r="C389" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D389" s="3">
-        <v>1.7609999999999999</v>
+        <v>1.8308</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5838,13 +5838,13 @@
         <v>8</v>
       </c>
       <c r="B390" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C390" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D390" s="3">
-        <v>1.7717000000000001</v>
+        <v>1.8752</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5852,13 +5852,13 @@
         <v>8</v>
       </c>
       <c r="B391" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C391" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D391" s="3">
-        <v>1.6231</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5866,13 +5866,13 @@
         <v>8</v>
       </c>
       <c r="B392" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C392" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D392" s="3">
-        <v>1.706</v>
+        <v>1.8120000000000001</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5880,13 +5880,13 @@
         <v>8</v>
       </c>
       <c r="B393" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C393" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D393" s="3">
-        <v>1.4521999999999999</v>
+        <v>1.7609999999999999</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5897,10 +5897,10 @@
         <v>2025</v>
       </c>
       <c r="C394" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D394" s="3">
-        <v>1.4100999999999999</v>
+        <v>1.7717000000000001</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5911,10 +5911,10 @@
         <v>2025</v>
       </c>
       <c r="C395" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3">
-        <v>1.5933999999999999</v>
+        <v>1.6231</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5925,10 +5925,10 @@
         <v>2025</v>
       </c>
       <c r="C396" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D396" s="3">
-        <v>1.5374000000000001</v>
+        <v>1.7063999999999999</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5939,10 +5939,10 @@
         <v>2025</v>
       </c>
       <c r="C397" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D397" s="3">
-        <v>1.5250999999999999</v>
+        <v>1.4521999999999999</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5953,10 +5953,10 @@
         <v>2025</v>
       </c>
       <c r="C398" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D398" s="3">
-        <v>1.4985999999999999</v>
+        <v>1.4105000000000001</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5967,10 +5967,10 @@
         <v>2025</v>
       </c>
       <c r="C399" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D399" s="3">
-        <v>1.462</v>
+        <v>1.5933999999999999</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -5981,10 +5981,10 @@
         <v>2025</v>
       </c>
       <c r="C400" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D400" s="3">
-        <v>1.635</v>
+        <v>1.5374000000000001</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -5995,10 +5995,10 @@
         <v>2025</v>
       </c>
       <c r="C401" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D401" s="3">
-        <v>1.7341</v>
+        <v>1.5250999999999999</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6006,13 +6006,13 @@
         <v>8</v>
       </c>
       <c r="B402" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C402" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D402" s="3">
-        <v>1.4160999999999999</v>
+        <v>1.4985999999999999</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6020,13 +6020,13 @@
         <v>8</v>
       </c>
       <c r="B403" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C403" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D403" s="3">
-        <v>1.5978000000000003</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6034,13 +6034,13 @@
         <v>8</v>
       </c>
       <c r="B404" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C404" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D404" s="3">
-        <v>1.4392</v>
+        <v>1.6359999999999999</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6048,13 +6048,13 @@
         <v>8</v>
       </c>
       <c r="B405" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C405" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D405" s="3">
-        <v>1.3837999999999997</v>
+        <v>1.7412000000000001</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6065,80 +6065,80 @@
         <v>2026</v>
       </c>
       <c r="C406" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D406" s="3">
-        <v>1.6129</v>
+        <v>1.4174</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B407" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C407" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D407" s="3">
-        <v>1.1920999999999999</v>
+        <v>1.5972</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B408" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C408" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D408" s="3">
-        <v>0.9788</v>
+        <v>1.4419999999999999</v>
       </c>
     </row>
     <row r="409" spans="1:4">
       <c r="A409" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B409" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C409" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D409" s="3">
-        <v>1.3588</v>
+        <v>1.4006000000000001</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B410" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C410" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D410" s="3">
-        <v>1.3531</v>
+        <v>1.6073999999999999</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B411" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C411" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D411" s="3">
-        <v>1.4061999999999999</v>
+        <v>1.6576</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6149,10 +6149,10 @@
         <v>2019</v>
       </c>
       <c r="C412" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D412" s="3">
-        <v>1.1672</v>
+        <v>1.1920999999999999</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6163,10 +6163,10 @@
         <v>2019</v>
       </c>
       <c r="C413" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D413" s="3">
-        <v>1.5024</v>
+        <v>0.9788</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6177,10 +6177,10 @@
         <v>2019</v>
       </c>
       <c r="C414" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D414" s="3">
-        <v>1.1561999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6188,13 +6188,13 @@
         <v>9</v>
       </c>
       <c r="B415" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C415" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D415" s="3">
-        <v>1.1488</v>
+        <v>1.3531</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6202,13 +6202,13 @@
         <v>9</v>
       </c>
       <c r="B416" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C416" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D416" s="3">
-        <v>1.0632999999999999</v>
+        <v>1.4077999999999999</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6216,13 +6216,13 @@
         <v>9</v>
       </c>
       <c r="B417" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C417" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D417" s="3">
-        <v>1.0150999999999999</v>
+        <v>1.1672</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6230,13 +6230,13 @@
         <v>9</v>
       </c>
       <c r="B418" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C418" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D418" s="3">
-        <v>1.1227</v>
+        <v>1.5024</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6244,13 +6244,13 @@
         <v>9</v>
       </c>
       <c r="B419" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C419" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D419" s="3">
-        <v>1.0437000000000001</v>
+        <v>1.1561999999999999</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6261,10 +6261,10 @@
         <v>2020</v>
       </c>
       <c r="C420" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D420" s="3">
-        <v>1.2843</v>
+        <v>1.1488</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6275,10 +6275,10 @@
         <v>2020</v>
       </c>
       <c r="C421" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D421" s="3">
-        <v>1.3385</v>
+        <v>1.0632999999999999</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6289,10 +6289,10 @@
         <v>2020</v>
       </c>
       <c r="C422" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D422" s="3">
-        <v>1.6960999999999999</v>
+        <v>1.0150999999999999</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6303,10 +6303,10 @@
         <v>2020</v>
       </c>
       <c r="C423" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D423" s="3">
-        <v>1.4695</v>
+        <v>1.1227</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6317,10 +6317,10 @@
         <v>2020</v>
       </c>
       <c r="C424" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D424" s="3">
-        <v>1.4509000000000001</v>
+        <v>1.0437000000000001</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6331,10 +6331,10 @@
         <v>2020</v>
       </c>
       <c r="C425" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D425" s="3">
-        <v>1.4291</v>
+        <v>1.2843</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6345,10 +6345,10 @@
         <v>2020</v>
       </c>
       <c r="C426" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D426" s="3">
-        <v>1.2766</v>
+        <v>1.3385</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6356,13 +6356,13 @@
         <v>9</v>
       </c>
       <c r="B427" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C427" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D427" s="3">
-        <v>1.2372000000000001</v>
+        <v>1.6960999999999999</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6370,13 +6370,13 @@
         <v>9</v>
       </c>
       <c r="B428" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C428" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D428" s="3">
-        <v>1.3984000000000001</v>
+        <v>1.4695</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6384,13 +6384,13 @@
         <v>9</v>
       </c>
       <c r="B429" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C429" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D429" s="3">
-        <v>1.2039</v>
+        <v>1.4509000000000001</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6398,13 +6398,13 @@
         <v>9</v>
       </c>
       <c r="B430" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C430" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D430" s="3">
-        <v>1.2943</v>
+        <v>1.4291</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6412,13 +6412,13 @@
         <v>9</v>
       </c>
       <c r="B431" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C431" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D431" s="3">
-        <v>1.2281</v>
+        <v>1.2766</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6429,10 +6429,10 @@
         <v>2021</v>
       </c>
       <c r="C432" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D432" s="3">
-        <v>1.3234999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6443,10 +6443,10 @@
         <v>2021</v>
       </c>
       <c r="C433" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D433" s="3">
-        <v>1.2829999999999999</v>
+        <v>1.3984000000000001</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6457,10 +6457,10 @@
         <v>2021</v>
       </c>
       <c r="C434" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D434" s="3">
-        <v>1.1142000000000001</v>
+        <v>1.2039</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6471,10 +6471,10 @@
         <v>2021</v>
       </c>
       <c r="C435" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D435" s="3">
-        <v>0.96379999999999988</v>
+        <v>1.2943</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6485,10 +6485,10 @@
         <v>2021</v>
       </c>
       <c r="C436" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D436" s="3">
-        <v>1.0775999999999999</v>
+        <v>1.2292000000000001</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6499,10 +6499,10 @@
         <v>2021</v>
       </c>
       <c r="C437" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D437" s="3">
-        <v>1.1780999999999999</v>
+        <v>1.3234999999999999</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6513,10 +6513,10 @@
         <v>2021</v>
       </c>
       <c r="C438" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D438" s="3">
-        <v>1.0859000000000001</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6524,13 +6524,13 @@
         <v>9</v>
       </c>
       <c r="B439" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C439" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D439" s="3">
-        <v>1.1252</v>
+        <v>1.1142000000000001</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6538,13 +6538,13 @@
         <v>9</v>
       </c>
       <c r="B440" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C440" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D440" s="3">
-        <v>1.1546000000000001</v>
+        <v>0.96379999999999988</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6552,13 +6552,13 @@
         <v>9</v>
       </c>
       <c r="B441" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C441" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D441" s="3">
-        <v>1.0673999999999999</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6566,13 +6566,13 @@
         <v>9</v>
       </c>
       <c r="B442" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C442" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D442" s="3">
-        <v>1.1517999999999999</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6580,13 +6580,13 @@
         <v>9</v>
       </c>
       <c r="B443" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C443" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D443" s="3">
-        <v>1.1574</v>
+        <v>1.0859000000000001</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6597,10 +6597,10 @@
         <v>2022</v>
       </c>
       <c r="C444" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D444" s="3">
-        <v>1.1416999999999999</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6611,10 +6611,10 @@
         <v>2022</v>
       </c>
       <c r="C445" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D445" s="3">
-        <v>1.2119</v>
+        <v>1.1546000000000001</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6625,10 +6625,10 @@
         <v>2022</v>
       </c>
       <c r="C446" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D446" s="3">
-        <v>1.1833</v>
+        <v>1.0673999999999999</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6639,10 +6639,10 @@
         <v>2022</v>
       </c>
       <c r="C447" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D447" s="3">
-        <v>1.2625</v>
+        <v>1.1517999999999999</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6653,10 +6653,10 @@
         <v>2022</v>
       </c>
       <c r="C448" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D448" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6667,10 +6667,10 @@
         <v>2022</v>
       </c>
       <c r="C449" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D449" s="3">
-        <v>1.2148000000000001</v>
+        <v>1.1416999999999999</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6681,10 +6681,10 @@
         <v>2022</v>
       </c>
       <c r="C450" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D450" s="3">
-        <v>1.1067</v>
+        <v>1.2119</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6692,13 +6692,13 @@
         <v>9</v>
       </c>
       <c r="B451" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C451" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D451" s="3">
-        <v>1.1968000000000001</v>
+        <v>1.1833</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6706,13 +6706,13 @@
         <v>9</v>
       </c>
       <c r="B452" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C452" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D452" s="3">
-        <v>1.032</v>
+        <v>1.2625</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6720,13 +6720,13 @@
         <v>9</v>
       </c>
       <c r="B453" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C453" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D453" s="3">
-        <v>1.0803</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6734,13 +6734,13 @@
         <v>9</v>
       </c>
       <c r="B454" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C454" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D454" s="3">
-        <v>1.1644000000000001</v>
+        <v>1.2148000000000001</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6748,13 +6748,13 @@
         <v>9</v>
       </c>
       <c r="B455" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C455" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D455" s="3">
-        <v>1.2673000000000001</v>
+        <v>1.1067</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6765,10 +6765,10 @@
         <v>2023</v>
       </c>
       <c r="C456" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D456" s="3">
-        <v>1.1983999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6779,10 +6779,10 @@
         <v>2023</v>
       </c>
       <c r="C457" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D457" s="3">
-        <v>1.3575999999999999</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6793,10 +6793,10 @@
         <v>2023</v>
       </c>
       <c r="C458" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D458" s="3">
-        <v>1.3444</v>
+        <v>1.0803</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6807,10 +6807,10 @@
         <v>2023</v>
       </c>
       <c r="C459" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D459" s="3">
-        <v>1.2949999999999999</v>
+        <v>1.1644000000000001</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6821,10 +6821,10 @@
         <v>2023</v>
       </c>
       <c r="C460" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D460" s="3">
-        <v>1.2145999999999999</v>
+        <v>1.2673000000000001</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6835,10 +6835,10 @@
         <v>2023</v>
       </c>
       <c r="C461" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D461" s="3">
-        <v>1.2192000000000001</v>
+        <v>1.1983999999999999</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6849,10 +6849,10 @@
         <v>2023</v>
       </c>
       <c r="C462" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D462" s="3">
-        <v>1.3759999999999999</v>
+        <v>1.3575999999999999</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6860,13 +6860,13 @@
         <v>9</v>
       </c>
       <c r="B463" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C463" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D463" s="3">
-        <v>1.3194999999999999</v>
+        <v>1.3444</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6874,13 +6874,13 @@
         <v>9</v>
       </c>
       <c r="B464" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C464" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D464" s="3">
-        <v>1.4132</v>
+        <v>1.2949999999999999</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6888,13 +6888,13 @@
         <v>9</v>
       </c>
       <c r="B465" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C465" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D465" s="3">
-        <v>1.6296000000000002</v>
+        <v>1.2145999999999999</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6902,13 +6902,13 @@
         <v>9</v>
       </c>
       <c r="B466" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C466" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D466" s="3">
-        <v>1.4339</v>
+        <v>1.2192000000000001</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6916,13 +6916,13 @@
         <v>9</v>
       </c>
       <c r="B467" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C467" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D467" s="3">
-        <v>1.2652000000000001</v>
+        <v>1.3759999999999999</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6933,10 +6933,10 @@
         <v>2024</v>
       </c>
       <c r="C468" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D468" s="3">
-        <v>1.4533</v>
+        <v>1.3194999999999999</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6947,10 +6947,10 @@
         <v>2024</v>
       </c>
       <c r="C469" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D469" s="3">
-        <v>1.3996999999999999</v>
+        <v>1.4132</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6961,10 +6961,10 @@
         <v>2024</v>
       </c>
       <c r="C470" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D470" s="3">
-        <v>1.2509999999999999</v>
+        <v>1.6296000000000002</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6975,10 +6975,10 @@
         <v>2024</v>
       </c>
       <c r="C471" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D471" s="3">
-        <v>1.2806999999999999</v>
+        <v>1.4339</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6989,10 +6989,10 @@
         <v>2024</v>
       </c>
       <c r="C472" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D472" s="3">
-        <v>1.2095</v>
+        <v>1.2652000000000001</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7003,10 +7003,10 @@
         <v>2024</v>
       </c>
       <c r="C473" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D473" s="3">
-        <v>1.2222999999999999</v>
+        <v>1.4533</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7017,10 +7017,10 @@
         <v>2024</v>
       </c>
       <c r="C474" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D474" s="3">
-        <v>1.2697000000000001</v>
+        <v>1.3996999999999999</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7028,13 +7028,13 @@
         <v>9</v>
       </c>
       <c r="B475" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C475" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D475" s="3">
-        <v>1.1957</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7042,13 +7042,13 @@
         <v>9</v>
       </c>
       <c r="B476" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C476" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D476" s="3">
-        <v>1.5154999999999998</v>
+        <v>1.2806999999999999</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7056,13 +7056,13 @@
         <v>9</v>
       </c>
       <c r="B477" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C477" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D477" s="3">
-        <v>1.2682</v>
+        <v>1.2095</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7070,13 +7070,13 @@
         <v>9</v>
       </c>
       <c r="B478" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C478" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D478" s="3">
-        <v>1.2907999999999999</v>
+        <v>1.2222999999999999</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7084,13 +7084,13 @@
         <v>9</v>
       </c>
       <c r="B479" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C479" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D479" s="3">
-        <v>1.2582</v>
+        <v>1.2697000000000001</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7101,10 +7101,10 @@
         <v>2025</v>
       </c>
       <c r="C480" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D480" s="3">
-        <v>1.3306</v>
+        <v>1.1957</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7115,10 +7115,10 @@
         <v>2025</v>
       </c>
       <c r="C481" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D481" s="3">
-        <v>1.4423999999999999</v>
+        <v>1.5154999999999998</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7129,10 +7129,10 @@
         <v>2025</v>
       </c>
       <c r="C482" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D482" s="3">
-        <v>1.3319000000000001</v>
+        <v>1.2657</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7143,10 +7143,10 @@
         <v>2025</v>
       </c>
       <c r="C483" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D483" s="3">
-        <v>1.3214999999999999</v>
+        <v>1.2907999999999999</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7157,10 +7157,10 @@
         <v>2025</v>
       </c>
       <c r="C484" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D484" s="3">
-        <v>1.4823</v>
+        <v>1.2582</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7171,10 +7171,10 @@
         <v>2025</v>
       </c>
       <c r="C485" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D485" s="3">
-        <v>1.3943000000000001</v>
+        <v>1.3306</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7185,10 +7185,10 @@
         <v>2025</v>
       </c>
       <c r="C486" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D486" s="3">
-        <v>1.4936999999999998</v>
+        <v>1.4423999999999999</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7196,13 +7196,13 @@
         <v>9</v>
       </c>
       <c r="B487" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C487" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D487" s="3">
-        <v>1.6764999999999999</v>
+        <v>1.3319000000000001</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7210,13 +7210,13 @@
         <v>9</v>
       </c>
       <c r="B488" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C488" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D488" s="3">
-        <v>1.5677000000000001</v>
+        <v>1.3214999999999999</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7224,13 +7224,13 @@
         <v>9</v>
       </c>
       <c r="B489" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C489" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D489" s="3">
-        <v>1.5889</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7238,13 +7238,13 @@
         <v>9</v>
       </c>
       <c r="B490" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C490" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D490" s="3">
-        <v>1.6122000000000001</v>
+        <v>1.3943000000000001</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7252,97 +7252,97 @@
         <v>9</v>
       </c>
       <c r="B491" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C491" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D491" s="3">
-        <v>1.5459000000000001</v>
+        <v>1.4936999999999998</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B492" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C492" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D492" s="3">
-        <v>1.8255999999999999</v>
+        <v>1.6705000000000001</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B493" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C493" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D493" s="3">
-        <v>2.1966999999999999</v>
+        <v>1.5677000000000001</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B494" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C494" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D494" s="3">
-        <v>0.69</v>
+        <v>1.5706999999999998</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B495" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C495" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D495" s="3">
-        <v>2.2656000000000001</v>
+        <v>1.6088</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B496" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C496" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D496" s="3">
-        <v>2.3290999999999999</v>
+        <v>1.5682</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B497" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C497" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D497" s="3">
-        <v>1.9074</v>
+        <v>1.7074</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7353,10 +7353,10 @@
         <v>2019</v>
       </c>
       <c r="C498" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D498" s="3">
-        <v>1.6099000000000001</v>
+        <v>1.8255999999999999</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7364,13 +7364,13 @@
         <v>10</v>
       </c>
       <c r="B499" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C499" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D499" s="3">
-        <v>1.2122999999999999</v>
+        <v>2.1966999999999999</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7378,13 +7378,13 @@
         <v>10</v>
       </c>
       <c r="B500" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C500" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D500" s="3">
-        <v>1.2574000000000001</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7392,13 +7392,13 @@
         <v>10</v>
       </c>
       <c r="B501" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C501" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D501" s="3">
-        <v>1.0529999999999999</v>
+        <v>2.2656000000000001</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7406,13 +7406,13 @@
         <v>10</v>
       </c>
       <c r="B502" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C502" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D502" s="3">
-        <v>1.3588</v>
+        <v>2.3290999999999999</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7420,13 +7420,13 @@
         <v>10</v>
       </c>
       <c r="B503" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C503" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D503" s="3">
-        <v>1.9334999999999998</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7434,13 +7434,13 @@
         <v>10</v>
       </c>
       <c r="B504" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C504" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D504" s="3">
-        <v>1.3191999999999997</v>
+        <v>1.6099000000000001</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7451,10 +7451,10 @@
         <v>2020</v>
       </c>
       <c r="C505" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D505" s="3">
-        <v>1.8477000000000001</v>
+        <v>1.2122999999999999</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7465,10 +7465,10 @@
         <v>2020</v>
       </c>
       <c r="C506" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D506" s="3">
-        <v>1.6778</v>
+        <v>1.2574000000000001</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7479,10 +7479,10 @@
         <v>2020</v>
       </c>
       <c r="C507" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D507" s="3">
-        <v>1.6319999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7493,10 +7493,10 @@
         <v>2020</v>
       </c>
       <c r="C508" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D508" s="3">
-        <v>2.4281999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7507,10 +7507,10 @@
         <v>2020</v>
       </c>
       <c r="C509" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D509" s="3">
-        <v>2.7423999999999999</v>
+        <v>1.9334999999999998</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7518,13 +7518,13 @@
         <v>10</v>
       </c>
       <c r="B510" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C510" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D510" s="3">
-        <v>1.9238999999999999</v>
+        <v>1.3191999999999997</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7532,13 +7532,13 @@
         <v>10</v>
       </c>
       <c r="B511" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C511" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D511" s="3">
-        <v>1.8746</v>
+        <v>1.8477000000000001</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7546,13 +7546,13 @@
         <v>10</v>
       </c>
       <c r="B512" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C512" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D512" s="3">
-        <v>2.1867999999999999</v>
+        <v>1.6833</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7560,13 +7560,13 @@
         <v>10</v>
       </c>
       <c r="B513" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C513" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D513" s="3">
-        <v>1.6684000000000003</v>
+        <v>1.6319999999999999</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -7574,13 +7574,13 @@
         <v>10</v>
       </c>
       <c r="B514" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C514" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D514" s="3">
-        <v>1.8869</v>
+        <v>2.4281999999999999</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7588,13 +7588,13 @@
         <v>10</v>
       </c>
       <c r="B515" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C515" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D515" s="3">
-        <v>1.7607000000000002</v>
+        <v>2.7423999999999999</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7605,10 +7605,10 @@
         <v>2021</v>
       </c>
       <c r="C516" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D516" s="3">
-        <v>2.3298999999999999</v>
+        <v>1.9238999999999999</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7619,10 +7619,10 @@
         <v>2021</v>
       </c>
       <c r="C517" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D517" s="3">
-        <v>2.0569000000000002</v>
+        <v>1.8746</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7633,10 +7633,10 @@
         <v>2021</v>
       </c>
       <c r="C518" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D518" s="3">
-        <v>2.5038999999999998</v>
+        <v>2.1867999999999999</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7647,10 +7647,10 @@
         <v>2021</v>
       </c>
       <c r="C519" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D519" s="3">
-        <v>1.7151000000000001</v>
+        <v>1.6684000000000003</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7661,10 +7661,10 @@
         <v>2021</v>
       </c>
       <c r="C520" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D520" s="3">
-        <v>1.7589999999999999</v>
+        <v>1.8869</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7675,10 +7675,10 @@
         <v>2021</v>
       </c>
       <c r="C521" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D521" s="3">
-        <v>1.9400000000000002</v>
+        <v>1.7607000000000002</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7686,13 +7686,13 @@
         <v>10</v>
       </c>
       <c r="B522" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C522" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D522" s="3">
-        <v>1.1923999999999999</v>
+        <v>2.3298999999999999</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7700,13 +7700,13 @@
         <v>10</v>
       </c>
       <c r="B523" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C523" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D523" s="3">
-        <v>1.5228999999999999</v>
+        <v>2.0569000000000002</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7714,13 +7714,13 @@
         <v>10</v>
       </c>
       <c r="B524" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C524" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D524" s="3">
-        <v>1.9296</v>
+        <v>2.5038999999999998</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7728,13 +7728,13 @@
         <v>10</v>
       </c>
       <c r="B525" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C525" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D525" s="3">
-        <v>1.5996999999999999</v>
+        <v>1.7151000000000001</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7742,13 +7742,13 @@
         <v>10</v>
       </c>
       <c r="B526" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C526" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D526" s="3">
-        <v>1.7376999999999998</v>
+        <v>1.7589999999999999</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7756,13 +7756,13 @@
         <v>10</v>
       </c>
       <c r="B527" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C527" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D527" s="3">
-        <v>1.6283000000000001</v>
+        <v>1.9400000000000002</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7773,10 +7773,10 @@
         <v>2022</v>
       </c>
       <c r="C528" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D528" s="3">
-        <v>1.6888000000000001</v>
+        <v>1.1923999999999999</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7787,10 +7787,10 @@
         <v>2022</v>
       </c>
       <c r="C529" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D529" s="3">
-        <v>1.7524</v>
+        <v>1.5228999999999999</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7801,10 +7801,10 @@
         <v>2022</v>
       </c>
       <c r="C530" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D530" s="3">
-        <v>1.8827</v>
+        <v>1.9296</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7815,10 +7815,10 @@
         <v>2022</v>
       </c>
       <c r="C531" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D531" s="3">
-        <v>1.52</v>
+        <v>1.5996999999999999</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7829,10 +7829,10 @@
         <v>2022</v>
       </c>
       <c r="C532" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D532" s="3">
-        <v>1.9222000000000001</v>
+        <v>1.7376999999999998</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7843,10 +7843,10 @@
         <v>2022</v>
       </c>
       <c r="C533" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D533" s="3">
-        <v>1.6540999999999999</v>
+        <v>1.6283000000000001</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7854,13 +7854,13 @@
         <v>10</v>
       </c>
       <c r="B534" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C534" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D534" s="3">
-        <v>1.6717000000000002</v>
+        <v>1.6888000000000001</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7868,13 +7868,13 @@
         <v>10</v>
       </c>
       <c r="B535" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C535" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D535" s="3">
-        <v>2.0114000000000001</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7882,13 +7882,13 @@
         <v>10</v>
       </c>
       <c r="B536" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C536" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D536" s="3">
-        <v>1.7808999999999999</v>
+        <v>1.8827</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7896,13 +7896,13 @@
         <v>10</v>
       </c>
       <c r="B537" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C537" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D537" s="3">
-        <v>1.6915</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7910,13 +7910,13 @@
         <v>10</v>
       </c>
       <c r="B538" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C538" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D538" s="3">
-        <v>1.8209</v>
+        <v>1.9222000000000001</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7924,13 +7924,13 @@
         <v>10</v>
       </c>
       <c r="B539" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C539" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D539" s="3">
-        <v>1.9435</v>
+        <v>1.6540999999999999</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7941,10 +7941,10 @@
         <v>2023</v>
       </c>
       <c r="C540" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D540" s="3">
-        <v>1.5912999999999999</v>
+        <v>1.6717000000000002</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7955,10 +7955,10 @@
         <v>2023</v>
       </c>
       <c r="C541" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D541" s="3">
-        <v>1.9621999999999999</v>
+        <v>2.0114000000000001</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7969,10 +7969,10 @@
         <v>2023</v>
       </c>
       <c r="C542" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D542" s="3">
-        <v>1.9907999999999999</v>
+        <v>1.7808999999999999</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7983,10 +7983,10 @@
         <v>2023</v>
       </c>
       <c r="C543" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D543" s="3">
-        <v>1.9017999999999999</v>
+        <v>1.6915</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -7997,10 +7997,10 @@
         <v>2023</v>
       </c>
       <c r="C544" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D544" s="3">
-        <v>1.5719000000000001</v>
+        <v>1.8209</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8011,10 +8011,10 @@
         <v>2023</v>
       </c>
       <c r="C545" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D545" s="3">
-        <v>1.6617999999999999</v>
+        <v>1.9435</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8022,13 +8022,13 @@
         <v>10</v>
       </c>
       <c r="B546" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C546" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D546" s="3">
-        <v>1.9043000000000001</v>
+        <v>1.5912999999999999</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8036,13 +8036,13 @@
         <v>10</v>
       </c>
       <c r="B547" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C547" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D547" s="3">
-        <v>1.8562999999999998</v>
+        <v>1.9621999999999999</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8050,13 +8050,13 @@
         <v>10</v>
       </c>
       <c r="B548" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C548" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D548" s="3">
-        <v>1.6854</v>
+        <v>1.9907999999999999</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8064,13 +8064,13 @@
         <v>10</v>
       </c>
       <c r="B549" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C549" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D549" s="3">
-        <v>1.8065</v>
+        <v>1.9017999999999999</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8078,13 +8078,13 @@
         <v>10</v>
       </c>
       <c r="B550" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C550" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D550" s="3">
-        <v>1.7505999999999999</v>
+        <v>1.5719000000000001</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8092,13 +8092,13 @@
         <v>10</v>
       </c>
       <c r="B551" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C551" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D551" s="3">
-        <v>1.7563</v>
+        <v>1.6617999999999999</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8109,10 +8109,10 @@
         <v>2024</v>
       </c>
       <c r="C552" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D552" s="3">
-        <v>2.2259000000000002</v>
+        <v>1.9043000000000001</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8123,10 +8123,10 @@
         <v>2024</v>
       </c>
       <c r="C553" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D553" s="3">
-        <v>1.77</v>
+        <v>1.8562999999999998</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8137,10 +8137,10 @@
         <v>2024</v>
       </c>
       <c r="C554" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D554" s="3">
-        <v>1.8426999999999998</v>
+        <v>1.6854</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8151,10 +8151,10 @@
         <v>2024</v>
       </c>
       <c r="C555" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D555" s="3">
-        <v>1.8102</v>
+        <v>1.8065</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8165,10 +8165,10 @@
         <v>2024</v>
       </c>
       <c r="C556" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D556" s="3">
-        <v>1.7421</v>
+        <v>1.7505999999999999</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8179,10 +8179,10 @@
         <v>2024</v>
       </c>
       <c r="C557" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D557" s="3">
-        <v>1.6943999999999999</v>
+        <v>1.7563</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8190,13 +8190,13 @@
         <v>10</v>
       </c>
       <c r="B558" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C558" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D558" s="3">
-        <v>1.6221000000000001</v>
+        <v>2.2259000000000002</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8204,13 +8204,13 @@
         <v>10</v>
       </c>
       <c r="B559" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C559" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D559" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8218,13 +8218,13 @@
         <v>10</v>
       </c>
       <c r="B560" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C560" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D560" s="3">
-        <v>1.7462</v>
+        <v>1.8426999999999998</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8232,13 +8232,13 @@
         <v>10</v>
       </c>
       <c r="B561" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C561" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D561" s="3">
-        <v>1.9338000000000002</v>
+        <v>1.8102</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8246,13 +8246,13 @@
         <v>10</v>
       </c>
       <c r="B562" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C562" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D562" s="3">
-        <v>1.9272</v>
+        <v>1.7421</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8260,13 +8260,13 @@
         <v>10</v>
       </c>
       <c r="B563" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C563" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D563" s="3">
-        <v>1.7902</v>
+        <v>1.6943999999999999</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8277,10 +8277,10 @@
         <v>2025</v>
       </c>
       <c r="C564" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D564" s="3">
-        <v>1.6865000000000001</v>
+        <v>1.6221000000000001</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8291,10 +8291,10 @@
         <v>2025</v>
       </c>
       <c r="C565" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D565" s="3">
-        <v>1.7938000000000001</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8305,10 +8305,10 @@
         <v>2025</v>
       </c>
       <c r="C566" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D566" s="3">
-        <v>1.732</v>
+        <v>1.7462</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8319,10 +8319,10 @@
         <v>2025</v>
       </c>
       <c r="C567" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D567" s="3">
-        <v>1.925</v>
+        <v>1.9338000000000002</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8333,10 +8333,10 @@
         <v>2025</v>
       </c>
       <c r="C568" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D568" s="3">
-        <v>1.9413</v>
+        <v>1.9272</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8347,10 +8347,10 @@
         <v>2025</v>
       </c>
       <c r="C569" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D569" s="3">
-        <v>1.7350000000000001</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8358,13 +8358,13 @@
         <v>10</v>
       </c>
       <c r="B570" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C570" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D570" s="3">
-        <v>1.6932</v>
+        <v>1.6876</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8372,13 +8372,13 @@
         <v>10</v>
       </c>
       <c r="B571" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C571" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D571" s="3">
-        <v>1.9579</v>
+        <v>1.7938000000000001</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8386,13 +8386,13 @@
         <v>10</v>
       </c>
       <c r="B572" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C572" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D572" s="3">
-        <v>1.4839</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8400,13 +8400,13 @@
         <v>10</v>
       </c>
       <c r="B573" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C573" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D573" s="3">
-        <v>2.0834999999999999</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8414,111 +8414,111 @@
         <v>10</v>
       </c>
       <c r="B574" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C574" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D574" s="3">
-        <v>1.6456</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B575" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C575" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D575" s="3">
-        <v>0.59160000000000001</v>
+        <v>1.7350000000000001</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B576" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C576" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D576" s="3">
-        <v>0.71369999999999989</v>
+        <v>1.6893</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B577" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C577" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D577" s="3">
-        <v>1.4662999999999999</v>
+        <v>1.9579</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B578" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C578" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D578" s="3">
-        <v>0.70140000000000002</v>
+        <v>1.5611999999999999</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B579" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C579" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D579" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.6298000000000001</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B580" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C580" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D580" s="3">
-        <v>1.2885</v>
+        <v>1.7371000000000001</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B581" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C581" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D581" s="3">
-        <v>0.97159999999999991</v>
+        <v>2.0629</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8529,10 +8529,10 @@
         <v>2019</v>
       </c>
       <c r="C582" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D582" s="3">
-        <v>0.59799999999999998</v>
+        <v>0.59160000000000001</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8540,13 +8540,13 @@
         <v>11</v>
       </c>
       <c r="B583" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C583" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D583" s="3">
-        <v>0.80840000000000001</v>
+        <v>0.71369999999999989</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8554,13 +8554,13 @@
         <v>11</v>
       </c>
       <c r="B584" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C584" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D584" s="3">
-        <v>0.57899999999999996</v>
+        <v>1.4662999999999999</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8568,13 +8568,13 @@
         <v>11</v>
       </c>
       <c r="B585" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C585" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D585" s="3">
-        <v>1.1052999999999999</v>
+        <v>0.70140000000000002</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -8582,13 +8582,13 @@
         <v>11</v>
       </c>
       <c r="B586" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C586" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D586" s="3">
-        <v>0.77580000000000005</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -8596,13 +8596,13 @@
         <v>11</v>
       </c>
       <c r="B587" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C587" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D587" s="3">
-        <v>1.0531999999999999</v>
+        <v>1.2885</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -8610,13 +8610,13 @@
         <v>11</v>
       </c>
       <c r="B588" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C588" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D588" s="3">
-        <v>1.0923</v>
+        <v>0.97159999999999991</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8624,13 +8624,13 @@
         <v>11</v>
       </c>
       <c r="B589" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C589" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D589" s="3">
-        <v>1.2737000000000001</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -8641,10 +8641,10 @@
         <v>2020</v>
       </c>
       <c r="C590" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D590" s="3">
-        <v>1.3653</v>
+        <v>0.80840000000000001</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8655,10 +8655,10 @@
         <v>2020</v>
       </c>
       <c r="C591" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D591" s="3">
-        <v>1.1208</v>
+        <v>0.57899999999999996</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8669,10 +8669,10 @@
         <v>2020</v>
       </c>
       <c r="C592" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D592" s="3">
-        <v>1.5089999999999999</v>
+        <v>1.1052999999999999</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8683,10 +8683,10 @@
         <v>2020</v>
       </c>
       <c r="C593" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D593" s="3">
-        <v>1.2372000000000001</v>
+        <v>0.77580000000000005</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8697,10 +8697,10 @@
         <v>2020</v>
       </c>
       <c r="C594" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D594" s="3">
-        <v>1.0697000000000001</v>
+        <v>1.0531999999999999</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8708,13 +8708,13 @@
         <v>11</v>
       </c>
       <c r="B595" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C595" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D595" s="3">
-        <v>1.2351000000000001</v>
+        <v>1.0923</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8722,13 +8722,13 @@
         <v>11</v>
       </c>
       <c r="B596" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C596" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D596" s="3">
-        <v>1.1274</v>
+        <v>1.2737000000000001</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8736,13 +8736,13 @@
         <v>11</v>
       </c>
       <c r="B597" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C597" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D597" s="3">
-        <v>1.3996</v>
+        <v>1.3653</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8750,13 +8750,13 @@
         <v>11</v>
       </c>
       <c r="B598" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C598" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D598" s="3">
-        <v>1.2915000000000001</v>
+        <v>1.1208</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8764,13 +8764,13 @@
         <v>11</v>
       </c>
       <c r="B599" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C599" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D599" s="3">
-        <v>1.218</v>
+        <v>1.5089999999999999</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8778,13 +8778,13 @@
         <v>11</v>
       </c>
       <c r="B600" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C600" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D600" s="3">
-        <v>1.3958999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8792,13 +8792,13 @@
         <v>11</v>
       </c>
       <c r="B601" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C601" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D601" s="3">
-        <v>1.5745000000000002</v>
+        <v>1.0697000000000001</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8809,10 +8809,10 @@
         <v>2021</v>
       </c>
       <c r="C602" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D602" s="3">
-        <v>1.3656999999999999</v>
+        <v>1.2366999999999999</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8823,10 +8823,10 @@
         <v>2021</v>
       </c>
       <c r="C603" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D603" s="3">
-        <v>1.1288</v>
+        <v>1.1274</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8837,10 +8837,10 @@
         <v>2021</v>
       </c>
       <c r="C604" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D604" s="3">
-        <v>0.96220000000000006</v>
+        <v>1.3996</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8851,10 +8851,10 @@
         <v>2021</v>
       </c>
       <c r="C605" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D605" s="3">
-        <v>0.94979999999999998</v>
+        <v>1.2915000000000001</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8865,10 +8865,10 @@
         <v>2021</v>
       </c>
       <c r="C606" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D606" s="3">
-        <v>1.1982999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8876,13 +8876,13 @@
         <v>11</v>
       </c>
       <c r="B607" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C607" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D607" s="3">
-        <v>1.0469999999999999</v>
+        <v>1.3958999999999999</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8890,13 +8890,13 @@
         <v>11</v>
       </c>
       <c r="B608" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C608" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D608" s="3">
-        <v>0.84160000000000001</v>
+        <v>1.5745000000000002</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8904,13 +8904,13 @@
         <v>11</v>
       </c>
       <c r="B609" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C609" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D609" s="3">
-        <v>0.85270000000000001</v>
+        <v>1.3656999999999999</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8918,13 +8918,13 @@
         <v>11</v>
       </c>
       <c r="B610" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C610" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D610" s="3">
-        <v>0.65920000000000001</v>
+        <v>1.1288</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8932,13 +8932,13 @@
         <v>11</v>
       </c>
       <c r="B611" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C611" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D611" s="3">
-        <v>0.91259999999999997</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8946,13 +8946,13 @@
         <v>11</v>
       </c>
       <c r="B612" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C612" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D612" s="3">
-        <v>0.68140000000000001</v>
+        <v>0.94979999999999998</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8960,13 +8960,13 @@
         <v>11</v>
       </c>
       <c r="B613" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C613" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D613" s="3">
-        <v>0.69020000000000004</v>
+        <v>1.1982999999999999</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8977,10 +8977,10 @@
         <v>2022</v>
       </c>
       <c r="C614" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D614" s="3">
-        <v>0.83509999999999995</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8991,10 +8991,10 @@
         <v>2022</v>
       </c>
       <c r="C615" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D615" s="3">
-        <v>0.8459000000000001</v>
+        <v>0.84160000000000001</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9005,10 +9005,10 @@
         <v>2022</v>
       </c>
       <c r="C616" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D616" s="3">
-        <v>1.0476000000000001</v>
+        <v>0.85270000000000001</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9019,10 +9019,10 @@
         <v>2022</v>
       </c>
       <c r="C617" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D617" s="3">
-        <v>0.93159999999999998</v>
+        <v>0.65920000000000001</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9033,10 +9033,10 @@
         <v>2022</v>
       </c>
       <c r="C618" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D618" s="3">
-        <v>0.60189999999999999</v>
+        <v>0.91259999999999997</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9044,13 +9044,13 @@
         <v>11</v>
       </c>
       <c r="B619" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C619" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D619" s="3">
-        <v>0.70330000000000004</v>
+        <v>0.68140000000000001</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9058,13 +9058,13 @@
         <v>11</v>
       </c>
       <c r="B620" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C620" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D620" s="3">
-        <v>0.68169999999999997</v>
+        <v>0.69020000000000004</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9072,13 +9072,13 @@
         <v>11</v>
       </c>
       <c r="B621" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C621" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D621" s="3">
-        <v>0.6391</v>
+        <v>0.83509999999999995</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9086,13 +9086,13 @@
         <v>11</v>
       </c>
       <c r="B622" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C622" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D622" s="3">
-        <v>0.72650000000000003</v>
+        <v>0.8459000000000001</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9100,13 +9100,13 @@
         <v>11</v>
       </c>
       <c r="B623" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C623" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D623" s="3">
-        <v>0.76770000000000005</v>
+        <v>1.0476000000000001</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9114,13 +9114,13 @@
         <v>11</v>
       </c>
       <c r="B624" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C624" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D624" s="3">
-        <v>0.64570000000000005</v>
+        <v>0.93159999999999998</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9128,13 +9128,13 @@
         <v>11</v>
       </c>
       <c r="B625" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C625" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D625" s="3">
-        <v>0.60250000000000004</v>
+        <v>0.60189999999999999</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9145,10 +9145,10 @@
         <v>2023</v>
       </c>
       <c r="C626" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D626" s="3">
-        <v>1.3164</v>
+        <v>0.70330000000000004</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9159,10 +9159,10 @@
         <v>2023</v>
       </c>
       <c r="C627" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D627" s="3">
-        <v>1.054</v>
+        <v>0.68169999999999997</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9173,10 +9173,10 @@
         <v>2023</v>
       </c>
       <c r="C628" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D628" s="3">
-        <v>1.1778</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9187,10 +9187,10 @@
         <v>2023</v>
       </c>
       <c r="C629" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D629" s="3">
-        <v>1.3501000000000001</v>
+        <v>0.72650000000000003</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9201,10 +9201,10 @@
         <v>2023</v>
       </c>
       <c r="C630" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D630" s="3">
-        <v>1.1941999999999999</v>
+        <v>0.76770000000000005</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9212,13 +9212,13 @@
         <v>11</v>
       </c>
       <c r="B631" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C631" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D631" s="3">
-        <v>1.1995</v>
+        <v>0.64570000000000005</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9226,13 +9226,13 @@
         <v>11</v>
       </c>
       <c r="B632" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C632" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D632" s="3">
-        <v>1.2528000000000001</v>
+        <v>0.60250000000000004</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9240,13 +9240,13 @@
         <v>11</v>
       </c>
       <c r="B633" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C633" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D633" s="3">
-        <v>1.2377</v>
+        <v>1.3164</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9254,13 +9254,13 @@
         <v>11</v>
       </c>
       <c r="B634" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C634" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D634" s="3">
-        <v>1.0448</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9268,13 +9268,13 @@
         <v>11</v>
       </c>
       <c r="B635" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C635" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D635" s="3">
-        <v>1.1088</v>
+        <v>1.1778</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9282,13 +9282,13 @@
         <v>11</v>
       </c>
       <c r="B636" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C636" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D636" s="3">
-        <v>1.1704000000000001</v>
+        <v>1.3501000000000001</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9296,13 +9296,13 @@
         <v>11</v>
       </c>
       <c r="B637" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C637" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D637" s="3">
-        <v>1.335</v>
+        <v>1.1941999999999999</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9313,10 +9313,10 @@
         <v>2024</v>
       </c>
       <c r="C638" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D638" s="3">
-        <v>1.2101999999999999</v>
+        <v>1.1995</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9327,10 +9327,10 @@
         <v>2024</v>
       </c>
       <c r="C639" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D639" s="3">
-        <v>1.2007000000000001</v>
+        <v>1.2528000000000001</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9341,10 +9341,10 @@
         <v>2024</v>
       </c>
       <c r="C640" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D640" s="3">
-        <v>1.2133</v>
+        <v>1.2377</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9355,10 +9355,10 @@
         <v>2024</v>
       </c>
       <c r="C641" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D641" s="3">
-        <v>0.85850000000000004</v>
+        <v>1.0448</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9369,10 +9369,10 @@
         <v>2024</v>
       </c>
       <c r="C642" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D642" s="3">
-        <v>1.1714</v>
+        <v>1.1088</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9380,13 +9380,13 @@
         <v>11</v>
       </c>
       <c r="B643" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C643" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D643" s="3">
-        <v>0.94820000000000004</v>
+        <v>1.1704000000000001</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9394,13 +9394,13 @@
         <v>11</v>
       </c>
       <c r="B644" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C644" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D644" s="3">
-        <v>0.94499999999999995</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9408,13 +9408,13 @@
         <v>11</v>
       </c>
       <c r="B645" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C645" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D645" s="3">
-        <v>1.0746</v>
+        <v>1.2101999999999999</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9422,13 +9422,13 @@
         <v>11</v>
       </c>
       <c r="B646" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C646" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D646" s="3">
-        <v>1.1345000000000001</v>
+        <v>1.2007000000000001</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9436,13 +9436,13 @@
         <v>11</v>
       </c>
       <c r="B647" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C647" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D647" s="3">
-        <v>0.96009999999999995</v>
+        <v>1.2133</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9450,13 +9450,13 @@
         <v>11</v>
       </c>
       <c r="B648" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C648" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D648" s="3">
-        <v>1.0189999999999999</v>
+        <v>0.85850000000000004</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9464,13 +9464,13 @@
         <v>11</v>
       </c>
       <c r="B649" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C649" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D649" s="3">
-        <v>1.0889</v>
+        <v>1.1714</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9481,10 +9481,10 @@
         <v>2025</v>
       </c>
       <c r="C650" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D650" s="3">
-        <v>1.0328999999999999</v>
+        <v>0.94820000000000004</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9495,10 +9495,10 @@
         <v>2025</v>
       </c>
       <c r="C651" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D651" s="3">
-        <v>1.0566</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9509,10 +9509,10 @@
         <v>2025</v>
       </c>
       <c r="C652" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D652" s="3">
-        <v>1.0752999999999999</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9523,10 +9523,10 @@
         <v>2025</v>
       </c>
       <c r="C653" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D653" s="3">
-        <v>0.91410000000000002</v>
+        <v>1.1345000000000001</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9537,10 +9537,10 @@
         <v>2025</v>
       </c>
       <c r="C654" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D654" s="3">
-        <v>1.083</v>
+        <v>0.96009999999999995</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9548,13 +9548,13 @@
         <v>11</v>
       </c>
       <c r="B655" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C655" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D655" s="3">
-        <v>1.0165999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9562,13 +9562,13 @@
         <v>11</v>
       </c>
       <c r="B656" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C656" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D656" s="3">
-        <v>0.92769999999999997</v>
+        <v>1.0889</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -9576,13 +9576,13 @@
         <v>11</v>
       </c>
       <c r="B657" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C657" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D657" s="3">
-        <v>0.86850000000000005</v>
+        <v>1.0328999999999999</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -9590,13 +9590,13 @@
         <v>11</v>
       </c>
       <c r="B658" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C658" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D658" s="3">
-        <v>0.84950000000000003</v>
+        <v>1.0566</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -9604,125 +9604,125 @@
         <v>11</v>
       </c>
       <c r="B659" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C659" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D659" s="3">
-        <v>0.86919999999999997</v>
+        <v>1.0752999999999999</v>
       </c>
     </row>
     <row r="660" spans="1:4">
       <c r="A660" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B660" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C660" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D660" s="3">
-        <v>0.62870000000000004</v>
+        <v>0.91410000000000002</v>
       </c>
     </row>
     <row r="661" spans="1:4">
       <c r="A661" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B661" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C661" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D661" s="3">
-        <v>0.97070000000000001</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="662" spans="1:4">
       <c r="A662" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B662" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C662" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D662" s="3">
-        <v>0.71419999999999995</v>
+        <v>1.0168999999999999</v>
       </c>
     </row>
     <row r="663" spans="1:4">
       <c r="A663" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B663" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C663" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D663" s="3">
-        <v>0.60429999999999995</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="664" spans="1:4">
       <c r="A664" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B664" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C664" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D664" s="3">
-        <v>0.87819999999999998</v>
+        <v>0.96539999999999992</v>
       </c>
     </row>
     <row r="665" spans="1:4">
       <c r="A665" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B665" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C665" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D665" s="3">
-        <v>0.97710000000000008</v>
+        <v>0.9587</v>
       </c>
     </row>
     <row r="666" spans="1:4">
       <c r="A666" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B666" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C666" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D666" s="3">
-        <v>0.78180000000000005</v>
+        <v>1.1483000000000001</v>
       </c>
     </row>
     <row r="667" spans="1:4">
       <c r="A667" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B667" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C667" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D667" s="3">
-        <v>0.88280000000000003</v>
+        <v>1.2275</v>
       </c>
     </row>
     <row r="668" spans="1:4">
@@ -9730,13 +9730,13 @@
         <v>12</v>
       </c>
       <c r="B668" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C668" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D668" s="3">
-        <v>0.84150000000000003</v>
+        <v>0.62870000000000004</v>
       </c>
     </row>
     <row r="669" spans="1:4">
@@ -9744,13 +9744,13 @@
         <v>12</v>
       </c>
       <c r="B669" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C669" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D669" s="3">
-        <v>3.6991000000000001</v>
+        <v>0.97070000000000001</v>
       </c>
     </row>
     <row r="670" spans="1:4">
@@ -9758,13 +9758,13 @@
         <v>12</v>
       </c>
       <c r="B670" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C670" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D670" s="3">
-        <v>0.63649999999999995</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="671" spans="1:4">
@@ -9772,13 +9772,13 @@
         <v>12</v>
       </c>
       <c r="B671" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C671" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D671" s="3">
-        <v>0.63870000000000005</v>
+        <v>0.60429999999999995</v>
       </c>
     </row>
     <row r="672" spans="1:4">
@@ -9786,13 +9786,13 @@
         <v>12</v>
       </c>
       <c r="B672" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C672" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D672" s="3">
-        <v>0.58840000000000003</v>
+        <v>0.87819999999999998</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -9800,13 +9800,13 @@
         <v>12</v>
       </c>
       <c r="B673" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C673" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D673" s="3">
-        <v>0.83720000000000006</v>
+        <v>0.97710000000000008</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -9814,13 +9814,13 @@
         <v>12</v>
       </c>
       <c r="B674" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C674" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D674" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.78180000000000005</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -9828,13 +9828,13 @@
         <v>12</v>
       </c>
       <c r="B675" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C675" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D675" s="3">
-        <v>0.75119999999999998</v>
+        <v>0.88280000000000003</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -9845,10 +9845,10 @@
         <v>2020</v>
       </c>
       <c r="C676" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D676" s="3">
-        <v>0.76349999999999996</v>
+        <v>0.84150000000000003</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -9859,10 +9859,10 @@
         <v>2020</v>
       </c>
       <c r="C677" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D677" s="3">
-        <v>0.80579999999999996</v>
+        <v>3.6991000000000001</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -9873,10 +9873,10 @@
         <v>2020</v>
       </c>
       <c r="C678" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D678" s="3">
-        <v>0.75339999999999996</v>
+        <v>0.63649999999999995</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -9884,13 +9884,13 @@
         <v>12</v>
       </c>
       <c r="B679" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C679" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D679" s="3">
-        <v>0.83040000000000003</v>
+        <v>0.63870000000000005</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -9898,13 +9898,13 @@
         <v>12</v>
       </c>
       <c r="B680" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C680" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D680" s="3">
-        <v>0.85129999999999995</v>
+        <v>0.58840000000000003</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -9912,13 +9912,13 @@
         <v>12</v>
       </c>
       <c r="B681" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C681" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D681" s="3">
-        <v>0.8536999999999999</v>
+        <v>0.83720000000000006</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -9926,13 +9926,13 @@
         <v>12</v>
       </c>
       <c r="B682" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C682" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D682" s="3">
-        <v>0.93080000000000007</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -9940,13 +9940,13 @@
         <v>12</v>
       </c>
       <c r="B683" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C683" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D683" s="3">
-        <v>0.8980999999999999</v>
+        <v>0.75119999999999998</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -9954,13 +9954,13 @@
         <v>12</v>
       </c>
       <c r="B684" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C684" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D684" s="3">
-        <v>0.88049999999999984</v>
+        <v>0.76349999999999996</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -9968,13 +9968,13 @@
         <v>12</v>
       </c>
       <c r="B685" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C685" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D685" s="3">
-        <v>0.89779999999999993</v>
+        <v>0.80579999999999996</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -9982,13 +9982,13 @@
         <v>12</v>
       </c>
       <c r="B686" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C686" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D686" s="3">
-        <v>0.94299999999999995</v>
+        <v>0.75339999999999996</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -9999,10 +9999,10 @@
         <v>2021</v>
       </c>
       <c r="C687" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D687" s="3">
-        <v>0.87270000000000014</v>
+        <v>0.83040000000000003</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -10013,10 +10013,10 @@
         <v>2021</v>
       </c>
       <c r="C688" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D688" s="3">
-        <v>0.89249999999999985</v>
+        <v>0.85129999999999995</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -10027,10 +10027,10 @@
         <v>2021</v>
       </c>
       <c r="C689" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D689" s="3">
-        <v>0.90710000000000002</v>
+        <v>0.8536999999999999</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -10041,10 +10041,10 @@
         <v>2021</v>
       </c>
       <c r="C690" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D690" s="3">
-        <v>0.80330000000000001</v>
+        <v>0.93080000000000007</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -10052,13 +10052,13 @@
         <v>12</v>
       </c>
       <c r="B691" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C691" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D691" s="3">
-        <v>0.7107</v>
+        <v>0.8980999999999999</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -10066,13 +10066,13 @@
         <v>12</v>
       </c>
       <c r="B692" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C692" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D692" s="3">
-        <v>0.78610000000000002</v>
+        <v>0.88049999999999984</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -10080,13 +10080,13 @@
         <v>12</v>
       </c>
       <c r="B693" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C693" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D693" s="3">
-        <v>0.83389999999999997</v>
+        <v>0.89779999999999993</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -10094,13 +10094,13 @@
         <v>12</v>
       </c>
       <c r="B694" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C694" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D694" s="3">
-        <v>0.88970000000000005</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -10108,13 +10108,13 @@
         <v>12</v>
       </c>
       <c r="B695" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C695" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D695" s="3">
-        <v>0.83260000000000001</v>
+        <v>0.87270000000000014</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -10122,13 +10122,13 @@
         <v>12</v>
       </c>
       <c r="B696" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C696" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D696" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.89249999999999985</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -10136,13 +10136,13 @@
         <v>12</v>
       </c>
       <c r="B697" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C697" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D697" s="3">
-        <v>0.90830000000000011</v>
+        <v>0.90710000000000002</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -10150,13 +10150,13 @@
         <v>12</v>
       </c>
       <c r="B698" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C698" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D698" s="3">
-        <v>0.80479999999999996</v>
+        <v>0.80330000000000001</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -10167,10 +10167,10 @@
         <v>2022</v>
       </c>
       <c r="C699" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D699" s="3">
-        <v>0.77749999999999997</v>
+        <v>0.7107</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -10181,10 +10181,10 @@
         <v>2022</v>
       </c>
       <c r="C700" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D700" s="3">
-        <v>0.81069999999999998</v>
+        <v>0.78610000000000002</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -10195,10 +10195,10 @@
         <v>2022</v>
       </c>
       <c r="C701" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D701" s="3">
-        <v>0.87409999999999999</v>
+        <v>0.83389999999999997</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -10209,10 +10209,10 @@
         <v>2022</v>
       </c>
       <c r="C702" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D702" s="3">
-        <v>0.86129999999999984</v>
+        <v>0.88970000000000005</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -10220,13 +10220,13 @@
         <v>12</v>
       </c>
       <c r="B703" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C703" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D703" s="3">
-        <v>0.78390000000000004</v>
+        <v>0.83260000000000001</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -10234,13 +10234,13 @@
         <v>12</v>
       </c>
       <c r="B704" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C704" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D704" s="3">
-        <v>0.84170000000000011</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -10248,13 +10248,13 @@
         <v>12</v>
       </c>
       <c r="B705" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C705" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D705" s="3">
-        <v>0.80769999999999986</v>
+        <v>0.90830000000000011</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -10262,13 +10262,13 @@
         <v>12</v>
       </c>
       <c r="B706" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C706" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D706" s="3">
-        <v>0.90670000000000006</v>
+        <v>0.80479999999999996</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -10276,13 +10276,13 @@
         <v>12</v>
       </c>
       <c r="B707" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C707" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D707" s="3">
-        <v>0.82020000000000004</v>
+        <v>0.77749999999999997</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -10290,13 +10290,13 @@
         <v>12</v>
       </c>
       <c r="B708" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C708" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D708" s="3">
-        <v>0.81120000000000014</v>
+        <v>0.81069999999999998</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -10304,13 +10304,13 @@
         <v>12</v>
       </c>
       <c r="B709" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C709" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D709" s="3">
-        <v>0.85009999999999997</v>
+        <v>0.87409999999999999</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -10318,13 +10318,13 @@
         <v>12</v>
       </c>
       <c r="B710" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C710" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D710" s="3">
-        <v>0.8327</v>
+        <v>0.86129999999999984</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -10335,10 +10335,10 @@
         <v>2023</v>
       </c>
       <c r="C711" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D711" s="3">
-        <v>0.90250000000000008</v>
+        <v>0.78390000000000004</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -10349,10 +10349,10 @@
         <v>2023</v>
       </c>
       <c r="C712" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D712" s="3">
-        <v>0.85660000000000003</v>
+        <v>0.84170000000000011</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -10363,10 +10363,10 @@
         <v>2023</v>
       </c>
       <c r="C713" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D713" s="3">
-        <v>0.92820000000000003</v>
+        <v>0.80769999999999986</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -10377,10 +10377,10 @@
         <v>2023</v>
       </c>
       <c r="C714" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D714" s="3">
-        <v>0.86169999999999991</v>
+        <v>0.90670000000000006</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -10388,13 +10388,13 @@
         <v>12</v>
       </c>
       <c r="B715" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C715" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D715" s="3">
-        <v>0.85750000000000004</v>
+        <v>0.82020000000000004</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -10402,13 +10402,13 @@
         <v>12</v>
       </c>
       <c r="B716" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C716" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D716" s="3">
-        <v>0.9355</v>
+        <v>0.81120000000000014</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -10416,13 +10416,13 @@
         <v>12</v>
       </c>
       <c r="B717" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C717" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D717" s="3">
-        <v>0.79620000000000002</v>
+        <v>0.85009999999999997</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -10430,13 +10430,13 @@
         <v>12</v>
       </c>
       <c r="B718" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C718" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D718" s="3">
-        <v>0.93479999999999996</v>
+        <v>0.8327</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -10444,13 +10444,13 @@
         <v>12</v>
       </c>
       <c r="B719" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C719" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D719" s="3">
-        <v>0.96489999999999998</v>
+        <v>0.90250000000000008</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -10458,13 +10458,13 @@
         <v>12</v>
       </c>
       <c r="B720" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C720" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D720" s="3">
-        <v>0.86809999999999998</v>
+        <v>0.85660000000000003</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -10472,13 +10472,13 @@
         <v>12</v>
       </c>
       <c r="B721" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C721" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D721" s="3">
-        <v>0.7752</v>
+        <v>0.92820000000000003</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -10486,13 +10486,13 @@
         <v>12</v>
       </c>
       <c r="B722" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C722" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D722" s="3">
-        <v>0.82489999999999997</v>
+        <v>0.86169999999999991</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -10503,10 +10503,10 @@
         <v>2024</v>
       </c>
       <c r="C723" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D723" s="3">
-        <v>0.91569999999999996</v>
+        <v>0.85750000000000004</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -10517,10 +10517,10 @@
         <v>2024</v>
       </c>
       <c r="C724" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D724" s="3">
-        <v>0.997</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -10531,10 +10531,10 @@
         <v>2024</v>
       </c>
       <c r="C725" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D725" s="3">
-        <v>1.0421</v>
+        <v>0.79620000000000002</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -10545,10 +10545,10 @@
         <v>2024</v>
       </c>
       <c r="C726" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D726" s="3">
-        <v>1.0548</v>
+        <v>0.93479999999999996</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -10556,13 +10556,13 @@
         <v>12</v>
       </c>
       <c r="B727" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C727" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D727" s="3">
-        <v>0.92949999999999999</v>
+        <v>0.96489999999999998</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -10570,13 +10570,13 @@
         <v>12</v>
       </c>
       <c r="B728" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C728" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D728" s="3">
-        <v>0.95120000000000016</v>
+        <v>0.86809999999999998</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -10584,13 +10584,13 @@
         <v>12</v>
       </c>
       <c r="B729" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C729" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D729" s="3">
-        <v>0.92459999999999998</v>
+        <v>0.7752</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -10598,13 +10598,13 @@
         <v>12</v>
       </c>
       <c r="B730" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C730" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D730" s="3">
-        <v>0.85740000000000005</v>
+        <v>0.82489999999999997</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -10612,13 +10612,13 @@
         <v>12</v>
       </c>
       <c r="B731" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C731" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D731" s="3">
-        <v>0.91100000000000003</v>
+        <v>0.91530000000000011</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -10626,13 +10626,13 @@
         <v>12</v>
       </c>
       <c r="B732" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C732" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D732" s="3">
-        <v>0.89139999999999986</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -10640,13 +10640,13 @@
         <v>12</v>
       </c>
       <c r="B733" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C733" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D733" s="3">
-        <v>0.92459999999999998</v>
+        <v>1.0399</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -10654,13 +10654,13 @@
         <v>12</v>
       </c>
       <c r="B734" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C734" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D734" s="3">
-        <v>0.97750000000000004</v>
+        <v>1.0548</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -10671,10 +10671,10 @@
         <v>2025</v>
       </c>
       <c r="C735" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D735" s="3">
-        <v>0.91020000000000001</v>
+        <v>0.92949999999999999</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -10685,10 +10685,10 @@
         <v>2025</v>
       </c>
       <c r="C736" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D736" s="3">
-        <v>0.89680000000000004</v>
+        <v>0.95120000000000016</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -10699,10 +10699,10 @@
         <v>2025</v>
       </c>
       <c r="C737" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D737" s="3">
-        <v>0.83699999999999997</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -10713,10 +10713,10 @@
         <v>2025</v>
       </c>
       <c r="C738" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D738" s="3">
-        <v>0.97820000000000007</v>
+        <v>0.85740000000000005</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -10724,13 +10724,13 @@
         <v>12</v>
       </c>
       <c r="B739" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C739" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D739" s="3">
-        <v>0.98870000000000002</v>
+        <v>0.91100000000000003</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -10738,13 +10738,13 @@
         <v>12</v>
       </c>
       <c r="B740" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C740" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D740" s="3">
-        <v>0.90090000000000015</v>
+        <v>0.89139999999999986</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -10752,13 +10752,13 @@
         <v>12</v>
       </c>
       <c r="B741" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C741" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D741" s="3">
-        <v>0.91339999999999999</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -10766,13 +10766,13 @@
         <v>12</v>
       </c>
       <c r="B742" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C742" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D742" s="3">
-        <v>0.93269999999999997</v>
+        <v>0.98109999999999997</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -10780,13 +10780,139 @@
         <v>12</v>
       </c>
       <c r="B743" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C743" s="2">
+        <v>9</v>
+      </c>
+      <c r="D743" s="3">
+        <v>0.91020000000000001</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4">
+      <c r="A744" t="s">
+        <v>12</v>
+      </c>
+      <c r="B744" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C744" s="2">
+        <v>10</v>
+      </c>
+      <c r="D744" s="3">
+        <v>0.89680000000000004</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4">
+      <c r="A745" t="s">
+        <v>12</v>
+      </c>
+      <c r="B745" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C745" s="2">
+        <v>11</v>
+      </c>
+      <c r="D745" s="3">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4">
+      <c r="A746" t="s">
+        <v>12</v>
+      </c>
+      <c r="B746" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C746" s="2">
+        <v>12</v>
+      </c>
+      <c r="D746" s="3">
+        <v>0.97820000000000007</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4">
+      <c r="A747" t="s">
+        <v>12</v>
+      </c>
+      <c r="B747" s="2">
         <v>2026</v>
       </c>
-      <c r="C743" s="2">
-        <v>5</v>
-      </c>
-      <c r="D743" s="3">
-        <v>0.89729999999999999</v>
+      <c r="C747" s="2">
+        <v>1</v>
+      </c>
+      <c r="D747" s="3">
+        <v>0.98019999999999996</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4">
+      <c r="A748" t="s">
+        <v>12</v>
+      </c>
+      <c r="B748" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C748" s="2">
+        <v>2</v>
+      </c>
+      <c r="D748" s="3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4">
+      <c r="A749" t="s">
+        <v>12</v>
+      </c>
+      <c r="B749" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C749" s="2">
+        <v>3</v>
+      </c>
+      <c r="D749" s="3">
+        <v>1.0012000000000001</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4">
+      <c r="A750" t="s">
+        <v>12</v>
+      </c>
+      <c r="B750" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C750" s="2">
+        <v>4</v>
+      </c>
+      <c r="D750" s="3">
+        <v>0.93299999999999994</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4">
+      <c r="A751" t="s">
+        <v>12</v>
+      </c>
+      <c r="B751" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C751" s="2">
+        <v>5</v>
+      </c>
+      <c r="D751" s="3">
+        <v>0.8708999999999999</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4">
+      <c r="A752" t="s">
+        <v>12</v>
+      </c>
+      <c r="B752" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C752" s="2">
+        <v>6</v>
+      </c>
+      <c r="D752" s="3">
+        <v>0.89470000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/upload/case-mix-2025.xlsx
+++ b/upload/case-mix-2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="13">
   <si>
     <t>unidade</t>
   </si>
@@ -384,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D752"/>
+  <dimension ref="A1:D761"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1560,7 +1560,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="3">
-        <v>1.6366000000000001</v>
+        <v>1.5205</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1574,7 +1574,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="3">
-        <v>1.4151</v>
+        <v>1.2578</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,16 +1607,16 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B88" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C88" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="3">
-        <v>0.32269999999999999</v>
+        <v>1.2541</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -1627,10 +1627,10 @@
         <v>2019</v>
       </c>
       <c r="C89" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D89" s="3">
-        <v>2.4020999999999999</v>
+        <v>0.32269999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1638,13 +1638,13 @@
         <v>5</v>
       </c>
       <c r="B90" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D90" s="3">
-        <v>2.0989</v>
+        <v>2.4020999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1655,10 +1655,10 @@
         <v>2020</v>
       </c>
       <c r="C91" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="3">
-        <v>1.9497</v>
+        <v>2.0989</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1669,10 +1669,10 @@
         <v>2020</v>
       </c>
       <c r="C92" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" s="3">
-        <v>2.1490999999999998</v>
+        <v>1.9497</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1683,10 +1683,10 @@
         <v>2020</v>
       </c>
       <c r="C93" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D93" s="3">
-        <v>1.6907000000000001</v>
+        <v>2.1490999999999998</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -1697,10 +1697,10 @@
         <v>2020</v>
       </c>
       <c r="C94" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94" s="3">
-        <v>2.1762999999999999</v>
+        <v>1.6907000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1711,10 +1711,10 @@
         <v>2020</v>
       </c>
       <c r="C95" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D95" s="3">
-        <v>2.3714</v>
+        <v>2.1762999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -1725,10 +1725,10 @@
         <v>2020</v>
       </c>
       <c r="C96" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D96" s="3">
-        <v>2.6513</v>
+        <v>2.3714</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1739,10 +1739,10 @@
         <v>2020</v>
       </c>
       <c r="C97" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="3">
-        <v>2.3975</v>
+        <v>2.6513</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1753,10 +1753,10 @@
         <v>2020</v>
       </c>
       <c r="C98" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98" s="3">
-        <v>3.2244999999999999</v>
+        <v>2.3975</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1767,10 +1767,10 @@
         <v>2020</v>
       </c>
       <c r="C99" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" s="3">
-        <v>2.0931000000000002</v>
+        <v>3.2244999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -1781,10 +1781,10 @@
         <v>2020</v>
       </c>
       <c r="C100" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D100" s="3">
-        <v>2.1968000000000001</v>
+        <v>2.0931000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -1795,10 +1795,10 @@
         <v>2020</v>
       </c>
       <c r="C101" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D101" s="3">
-        <v>2.0958999999999999</v>
+        <v>2.1968000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1806,13 +1806,13 @@
         <v>5</v>
       </c>
       <c r="B102" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C102" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D102" s="3">
-        <v>2.4843000000000002</v>
+        <v>2.0958999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1823,10 +1823,10 @@
         <v>2021</v>
       </c>
       <c r="C103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" s="3">
-        <v>2.3409</v>
+        <v>2.4843000000000002</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -1837,10 +1837,10 @@
         <v>2021</v>
       </c>
       <c r="C104" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D104" s="3">
-        <v>2.7355999999999998</v>
+        <v>2.3409</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -1851,10 +1851,10 @@
         <v>2021</v>
       </c>
       <c r="C105" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" s="3">
-        <v>2.8948</v>
+        <v>2.7355999999999998</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1865,10 +1865,10 @@
         <v>2021</v>
       </c>
       <c r="C106" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D106" s="3">
-        <v>2.7456</v>
+        <v>2.8948</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1879,10 +1879,10 @@
         <v>2021</v>
       </c>
       <c r="C107" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" s="3">
-        <v>2.5648</v>
+        <v>2.7456</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1893,10 +1893,10 @@
         <v>2021</v>
       </c>
       <c r="C108" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" s="3">
-        <v>2.5844</v>
+        <v>2.5648</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1907,10 +1907,10 @@
         <v>2021</v>
       </c>
       <c r="C109" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109" s="3">
-        <v>2.8304999999999998</v>
+        <v>2.5844</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1921,10 +1921,10 @@
         <v>2021</v>
       </c>
       <c r="C110" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110" s="3">
-        <v>2.0144000000000002</v>
+        <v>2.8304999999999998</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -1935,10 +1935,10 @@
         <v>2021</v>
       </c>
       <c r="C111" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111" s="3">
-        <v>1.9097</v>
+        <v>2.0144000000000002</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1949,10 +1949,10 @@
         <v>2021</v>
       </c>
       <c r="C112" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112" s="3">
-        <v>2.3733</v>
+        <v>1.9097</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1963,10 +1963,10 @@
         <v>2021</v>
       </c>
       <c r="C113" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D113" s="3">
-        <v>2.0158999999999998</v>
+        <v>2.3733</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -1974,13 +1974,13 @@
         <v>5</v>
       </c>
       <c r="B114" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C114" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D114" s="3">
-        <v>2.0093999999999999</v>
+        <v>2.0158999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -1991,10 +1991,10 @@
         <v>2022</v>
       </c>
       <c r="C115" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" s="3">
-        <v>3.6905000000000001</v>
+        <v>2.0093999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2005,10 +2005,10 @@
         <v>2022</v>
       </c>
       <c r="C116" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D116" s="3">
-        <v>2.6345000000000001</v>
+        <v>3.6905000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2019,10 +2019,10 @@
         <v>2022</v>
       </c>
       <c r="C117" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D117" s="3">
-        <v>2.0619999999999998</v>
+        <v>2.6345000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2033,10 +2033,10 @@
         <v>2022</v>
       </c>
       <c r="C118" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D118" s="3">
-        <v>1.9186000000000001</v>
+        <v>2.0619999999999998</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2047,10 +2047,10 @@
         <v>2022</v>
       </c>
       <c r="C119" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D119" s="3">
-        <v>2.0594000000000001</v>
+        <v>1.9186000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2061,10 +2061,10 @@
         <v>2022</v>
       </c>
       <c r="C120" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D120" s="3">
-        <v>2.1585999999999999</v>
+        <v>2.0594000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2075,10 +2075,10 @@
         <v>2022</v>
       </c>
       <c r="C121" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D121" s="3">
-        <v>1.6135999999999999</v>
+        <v>2.1585999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2089,10 +2089,10 @@
         <v>2022</v>
       </c>
       <c r="C122" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D122" s="3">
-        <v>1.5652000000000001</v>
+        <v>1.6135999999999999</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2103,10 +2103,10 @@
         <v>2022</v>
       </c>
       <c r="C123" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D123" s="3">
-        <v>1.4952000000000001</v>
+        <v>1.5652000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2117,10 +2117,10 @@
         <v>2022</v>
       </c>
       <c r="C124" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D124" s="3">
-        <v>1.7753000000000001</v>
+        <v>1.4952000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2131,10 +2131,10 @@
         <v>2022</v>
       </c>
       <c r="C125" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D125" s="3">
-        <v>1.9029</v>
+        <v>1.7753000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2142,13 +2142,13 @@
         <v>5</v>
       </c>
       <c r="B126" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C126" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D126" s="3">
-        <v>1.5787</v>
+        <v>1.9029</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2159,10 +2159,10 @@
         <v>2023</v>
       </c>
       <c r="C127" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" s="3">
-        <v>1.8613999999999999</v>
+        <v>1.5787</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2173,10 +2173,10 @@
         <v>2023</v>
       </c>
       <c r="C128" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D128" s="3">
-        <v>1.6684000000000001</v>
+        <v>1.8613999999999999</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2187,10 +2187,10 @@
         <v>2023</v>
       </c>
       <c r="C129" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D129" s="3">
-        <v>1.5757000000000001</v>
+        <v>1.6684000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2201,10 +2201,10 @@
         <v>2023</v>
       </c>
       <c r="C130" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D130" s="3">
-        <v>2.0183</v>
+        <v>1.5757000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2215,10 +2215,10 @@
         <v>2023</v>
       </c>
       <c r="C131" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D131" s="3">
-        <v>1.6662999999999997</v>
+        <v>2.0183</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2229,10 +2229,10 @@
         <v>2023</v>
       </c>
       <c r="C132" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D132" s="3">
-        <v>1.9484999999999999</v>
+        <v>1.6662999999999997</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2243,10 +2243,10 @@
         <v>2023</v>
       </c>
       <c r="C133" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D133" s="3">
-        <v>2.0987</v>
+        <v>1.9484999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2257,10 +2257,10 @@
         <v>2023</v>
       </c>
       <c r="C134" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D134" s="3">
-        <v>1.9556999999999998</v>
+        <v>2.0987</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2271,10 +2271,10 @@
         <v>2023</v>
       </c>
       <c r="C135" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D135" s="3">
-        <v>2.331</v>
+        <v>1.9556999999999998</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2285,10 +2285,10 @@
         <v>2023</v>
       </c>
       <c r="C136" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D136" s="3">
-        <v>1.7165999999999999</v>
+        <v>2.331</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2299,10 +2299,10 @@
         <v>2023</v>
       </c>
       <c r="C137" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D137" s="3">
-        <v>1.6557999999999999</v>
+        <v>1.7165999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2310,13 +2310,13 @@
         <v>5</v>
       </c>
       <c r="B138" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D138" s="3">
-        <v>0.99390000000000001</v>
+        <v>1.6557999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2327,10 +2327,10 @@
         <v>2024</v>
       </c>
       <c r="C139" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2341,10 +2341,10 @@
         <v>2024</v>
       </c>
       <c r="C140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" s="3">
-        <v>0.88229999999999997</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2355,10 +2355,10 @@
         <v>2024</v>
       </c>
       <c r="C141" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D141" s="3">
-        <v>0.82889999999999997</v>
+        <v>0.88229999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2369,10 +2369,10 @@
         <v>2024</v>
       </c>
       <c r="C142" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D142" s="3">
-        <v>1.113</v>
+        <v>0.82889999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2383,10 +2383,10 @@
         <v>2024</v>
       </c>
       <c r="C143" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D143" s="3">
-        <v>1.7364999999999999</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2397,10 +2397,10 @@
         <v>2024</v>
       </c>
       <c r="C144" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D144" s="3">
-        <v>1.6022000000000001</v>
+        <v>1.7364999999999999</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2411,10 +2411,10 @@
         <v>2024</v>
       </c>
       <c r="C145" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D145" s="3">
-        <v>2.0381999999999998</v>
+        <v>1.6022000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2425,10 +2425,10 @@
         <v>2024</v>
       </c>
       <c r="C146" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D146" s="3">
-        <v>2.2471000000000001</v>
+        <v>2.0381999999999998</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2439,10 +2439,10 @@
         <v>2024</v>
       </c>
       <c r="C147" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D147" s="3">
-        <v>1.7967000000000002</v>
+        <v>2.2471000000000001</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2453,10 +2453,10 @@
         <v>2024</v>
       </c>
       <c r="C148" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D148" s="3">
-        <v>2.1593</v>
+        <v>1.7967000000000002</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2467,10 +2467,10 @@
         <v>2024</v>
       </c>
       <c r="C149" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D149" s="3">
-        <v>1.8868000000000003</v>
+        <v>2.1593</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2478,13 +2478,13 @@
         <v>5</v>
       </c>
       <c r="B150" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C150" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D150" s="3">
-        <v>1.7712000000000001</v>
+        <v>1.8868000000000003</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -2495,10 +2495,10 @@
         <v>2025</v>
       </c>
       <c r="C151" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" s="3">
-        <v>2.1036999999999999</v>
+        <v>1.7712000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2509,10 +2509,10 @@
         <v>2025</v>
       </c>
       <c r="C152" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D152" s="3">
-        <v>2.3969</v>
+        <v>2.1036999999999999</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2523,10 +2523,10 @@
         <v>2025</v>
       </c>
       <c r="C153" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D153" s="3">
-        <v>1.9019999999999997</v>
+        <v>2.3969</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2537,10 +2537,10 @@
         <v>2025</v>
       </c>
       <c r="C154" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D154" s="3">
-        <v>1.6771</v>
+        <v>1.9019999999999997</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2551,10 +2551,10 @@
         <v>2025</v>
       </c>
       <c r="C155" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D155" s="3">
-        <v>2.0131000000000001</v>
+        <v>1.6771</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2565,10 +2565,10 @@
         <v>2025</v>
       </c>
       <c r="C156" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D156" s="3">
-        <v>1.8540000000000001</v>
+        <v>2.0131000000000001</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -2579,10 +2579,10 @@
         <v>2025</v>
       </c>
       <c r="C157" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D157" s="3">
-        <v>2.1505999999999998</v>
+        <v>1.8540000000000001</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -2593,10 +2593,10 @@
         <v>2025</v>
       </c>
       <c r="C158" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D158" s="3">
-        <v>2.0398999999999998</v>
+        <v>2.1505999999999998</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2607,10 +2607,10 @@
         <v>2025</v>
       </c>
       <c r="C159" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D159" s="3">
-        <v>2.2544</v>
+        <v>2.0398999999999998</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -2621,10 +2621,10 @@
         <v>2025</v>
       </c>
       <c r="C160" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D160" s="3">
-        <v>2.1743999999999999</v>
+        <v>2.2544</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2635,10 +2635,10 @@
         <v>2025</v>
       </c>
       <c r="C161" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D161" s="3">
-        <v>1.7697000000000001</v>
+        <v>2.1743999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -2646,13 +2646,13 @@
         <v>5</v>
       </c>
       <c r="B162" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C162" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D162" s="3">
-        <v>1.8560000000000001</v>
+        <v>1.7697000000000001</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2663,10 +2663,10 @@
         <v>2026</v>
       </c>
       <c r="C163" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3">
-        <v>1.5873999999999999</v>
+        <v>1.9179000000000002</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -2677,10 +2677,10 @@
         <v>2026</v>
       </c>
       <c r="C164" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D164" s="3">
-        <v>1.5267999999999999</v>
+        <v>1.5873999999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2691,10 +2691,10 @@
         <v>2026</v>
       </c>
       <c r="C165" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" s="3">
-        <v>1.5854999999999999</v>
+        <v>1.5267999999999999</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2705,10 +2705,10 @@
         <v>2026</v>
       </c>
       <c r="C166" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D166" s="3">
-        <v>1.7642</v>
+        <v>1.5863</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -2719,38 +2719,38 @@
         <v>2026</v>
       </c>
       <c r="C167" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167" s="3">
-        <v>1.6396999999999999</v>
+        <v>1.7642</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B168" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C168" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D168" s="3">
-        <v>0.76870000000000005</v>
+        <v>1.6396999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B169" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C169" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D169" s="3">
-        <v>0.73919999999999997</v>
+        <v>1.6228</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2761,10 +2761,10 @@
         <v>2019</v>
       </c>
       <c r="C170" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D170" s="3">
-        <v>0.40439999999999998</v>
+        <v>0.76870000000000005</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2775,10 +2775,10 @@
         <v>2019</v>
       </c>
       <c r="C171" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D171" s="3">
-        <v>0.91849999999999998</v>
+        <v>0.73919999999999997</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2786,13 +2786,13 @@
         <v>6</v>
       </c>
       <c r="B172" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C172" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D172" s="3">
-        <v>0.91590000000000005</v>
+        <v>0.40439999999999998</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -2800,13 +2800,13 @@
         <v>6</v>
       </c>
       <c r="B173" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C173" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D173" s="3">
-        <v>0.91639999999999999</v>
+        <v>0.91849999999999998</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2817,10 +2817,10 @@
         <v>2020</v>
       </c>
       <c r="C174" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174" s="3">
-        <v>0.71460000000000001</v>
+        <v>0.91590000000000005</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2831,10 +2831,10 @@
         <v>2020</v>
       </c>
       <c r="C175" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D175" s="3">
-        <v>1.002</v>
+        <v>0.91639999999999999</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -2845,10 +2845,10 @@
         <v>2020</v>
       </c>
       <c r="C176" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D176" s="3">
-        <v>1.0396000000000001</v>
+        <v>0.71460000000000001</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -2859,10 +2859,10 @@
         <v>2020</v>
       </c>
       <c r="C177" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D177" s="3">
-        <v>0.70820000000000005</v>
+        <v>0.99880000000000002</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2873,10 +2873,10 @@
         <v>2020</v>
       </c>
       <c r="C178" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D178" s="3">
-        <v>1.5511999999999999</v>
+        <v>1.0396000000000001</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2887,10 +2887,10 @@
         <v>2020</v>
       </c>
       <c r="C179" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D179" s="3">
-        <v>1.117</v>
+        <v>0.70820000000000005</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2901,10 +2901,10 @@
         <v>2020</v>
       </c>
       <c r="C180" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D180" s="3">
-        <v>1.1403000000000001</v>
+        <v>1.5511999999999999</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -2915,10 +2915,10 @@
         <v>2020</v>
       </c>
       <c r="C181" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D181" s="3">
-        <v>1.4339</v>
+        <v>1.117</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2929,10 +2929,10 @@
         <v>2020</v>
       </c>
       <c r="C182" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D182" s="3">
-        <v>1.3353999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2943,10 +2943,10 @@
         <v>2020</v>
       </c>
       <c r="C183" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D183" s="3">
-        <v>1.8660000000000001</v>
+        <v>1.4347000000000001</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -2954,13 +2954,13 @@
         <v>6</v>
       </c>
       <c r="B184" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C184" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D184" s="3">
-        <v>1.4126000000000001</v>
+        <v>1.3353999999999999</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2968,13 +2968,13 @@
         <v>6</v>
       </c>
       <c r="B185" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C185" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D185" s="3">
-        <v>1.2838000000000001</v>
+        <v>1.8660000000000001</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -2985,10 +2985,10 @@
         <v>2021</v>
       </c>
       <c r="C186" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D186" s="3">
-        <v>1.0397000000000001</v>
+        <v>1.4126000000000001</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -2999,10 +2999,10 @@
         <v>2021</v>
       </c>
       <c r="C187" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D187" s="3">
-        <v>1.4381999999999999</v>
+        <v>1.2838000000000001</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3013,10 +3013,10 @@
         <v>2021</v>
       </c>
       <c r="C188" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D188" s="3">
-        <v>1.1092</v>
+        <v>1.0397000000000001</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3027,10 +3027,10 @@
         <v>2021</v>
       </c>
       <c r="C189" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D189" s="3">
-        <v>0.93130000000000002</v>
+        <v>1.4381999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3041,10 +3041,10 @@
         <v>2021</v>
       </c>
       <c r="C190" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D190" s="3">
-        <v>1.4892000000000001</v>
+        <v>1.1092</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3055,10 +3055,10 @@
         <v>2021</v>
       </c>
       <c r="C191" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D191" s="3">
-        <v>1.1386000000000001</v>
+        <v>0.93130000000000002</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3069,10 +3069,10 @@
         <v>2021</v>
       </c>
       <c r="C192" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D192" s="3">
-        <v>1.1675</v>
+        <v>1.4892000000000001</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3083,10 +3083,10 @@
         <v>2021</v>
       </c>
       <c r="C193" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D193" s="3">
-        <v>1.2996000000000001</v>
+        <v>1.1383000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3097,10 +3097,10 @@
         <v>2021</v>
       </c>
       <c r="C194" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D194" s="3">
-        <v>1.0663</v>
+        <v>1.1675</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3108,13 +3108,13 @@
         <v>6</v>
       </c>
       <c r="B195" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C195" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D195" s="3">
-        <v>1.0550999999999999</v>
+        <v>1.2996000000000001</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3122,13 +3122,13 @@
         <v>6</v>
       </c>
       <c r="B196" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C196" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D196" s="3">
-        <v>1.0621</v>
+        <v>1.0663</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3139,10 +3139,10 @@
         <v>2022</v>
       </c>
       <c r="C197" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D197" s="3">
-        <v>1.0516000000000001</v>
+        <v>1.0550999999999999</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3153,10 +3153,10 @@
         <v>2022</v>
       </c>
       <c r="C198" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D198" s="3">
-        <v>1.0001</v>
+        <v>1.0621</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3167,10 +3167,10 @@
         <v>2022</v>
       </c>
       <c r="C199" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D199" s="3">
-        <v>1.4765999999999999</v>
+        <v>1.0516000000000001</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3181,10 +3181,10 @@
         <v>2022</v>
       </c>
       <c r="C200" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D200" s="3">
-        <v>1.0939000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3195,10 +3195,10 @@
         <v>2022</v>
       </c>
       <c r="C201" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D201" s="3">
-        <v>1.2916000000000001</v>
+        <v>1.4765999999999999</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3209,10 +3209,10 @@
         <v>2022</v>
       </c>
       <c r="C202" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D202" s="3">
-        <v>1.2714000000000001</v>
+        <v>1.0939000000000001</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3223,10 +3223,10 @@
         <v>2022</v>
       </c>
       <c r="C203" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D203" s="3">
-        <v>1.2466999999999999</v>
+        <v>1.2916000000000001</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3237,10 +3237,10 @@
         <v>2022</v>
       </c>
       <c r="C204" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D204" s="3">
-        <v>1.0482</v>
+        <v>1.2714000000000001</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3251,10 +3251,10 @@
         <v>2022</v>
       </c>
       <c r="C205" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D205" s="3">
-        <v>1.0491999999999999</v>
+        <v>1.2466999999999999</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3265,10 +3265,10 @@
         <v>2022</v>
       </c>
       <c r="C206" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D206" s="3">
-        <v>1.2296</v>
+        <v>1.0482</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3276,13 +3276,13 @@
         <v>6</v>
       </c>
       <c r="B207" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C207" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D207" s="3">
-        <v>1.2606999999999999</v>
+        <v>1.0491999999999999</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3290,13 +3290,13 @@
         <v>6</v>
       </c>
       <c r="B208" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C208" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D208" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.2296</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3307,10 +3307,10 @@
         <v>2023</v>
       </c>
       <c r="C209" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D209" s="3">
-        <v>1.5298</v>
+        <v>1.2606999999999999</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3321,10 +3321,10 @@
         <v>2023</v>
       </c>
       <c r="C210" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D210" s="3">
-        <v>1.1073</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3335,10 +3335,10 @@
         <v>2023</v>
       </c>
       <c r="C211" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D211" s="3">
-        <v>1.0602</v>
+        <v>1.5298</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3349,10 +3349,10 @@
         <v>2023</v>
       </c>
       <c r="C212" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D212" s="3">
-        <v>1.3539999999999999</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3363,10 +3363,10 @@
         <v>2023</v>
       </c>
       <c r="C213" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D213" s="3">
-        <v>1.3968</v>
+        <v>1.0602</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3377,10 +3377,10 @@
         <v>2023</v>
       </c>
       <c r="C214" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D214" s="3">
-        <v>1.2923</v>
+        <v>1.3539999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3391,10 +3391,10 @@
         <v>2023</v>
       </c>
       <c r="C215" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D215" s="3">
-        <v>1.0855999999999999</v>
+        <v>1.3968</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3405,10 +3405,10 @@
         <v>2023</v>
       </c>
       <c r="C216" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D216" s="3">
-        <v>1.2621</v>
+        <v>1.2923</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3419,10 +3419,10 @@
         <v>2023</v>
       </c>
       <c r="C217" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D217" s="3">
-        <v>1.1758</v>
+        <v>1.0855999999999999</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3433,10 +3433,10 @@
         <v>2023</v>
       </c>
       <c r="C218" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D218" s="3">
-        <v>1.3091999999999999</v>
+        <v>1.2621</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3444,13 +3444,13 @@
         <v>6</v>
       </c>
       <c r="B219" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C219" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D219" s="3">
-        <v>1.5447</v>
+        <v>1.1758</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3458,13 +3458,13 @@
         <v>6</v>
       </c>
       <c r="B220" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C220" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D220" s="3">
-        <v>1.087</v>
+        <v>1.3091999999999999</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3475,10 +3475,10 @@
         <v>2024</v>
       </c>
       <c r="C221" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D221" s="3">
-        <v>0.89500000000000002</v>
+        <v>1.5447</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3489,10 +3489,10 @@
         <v>2024</v>
       </c>
       <c r="C222" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D222" s="3">
-        <v>1.0757000000000001</v>
+        <v>1.087</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3503,10 +3503,10 @@
         <v>2024</v>
       </c>
       <c r="C223" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D223" s="3">
-        <v>1.2897000000000001</v>
+        <v>0.89500000000000002</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -3517,10 +3517,10 @@
         <v>2024</v>
       </c>
       <c r="C224" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D224" s="3">
-        <v>1.3664000000000001</v>
+        <v>1.0757000000000001</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3531,10 +3531,10 @@
         <v>2024</v>
       </c>
       <c r="C225" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D225" s="3">
-        <v>1.2185999999999999</v>
+        <v>1.2897000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3545,10 +3545,10 @@
         <v>2024</v>
       </c>
       <c r="C226" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D226" s="3">
-        <v>1.2690999999999999</v>
+        <v>1.3664000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3559,10 +3559,10 @@
         <v>2024</v>
       </c>
       <c r="C227" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D227" s="3">
-        <v>1.0390999999999999</v>
+        <v>1.2185999999999999</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3573,10 +3573,10 @@
         <v>2024</v>
       </c>
       <c r="C228" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D228" s="3">
-        <v>1.1085</v>
+        <v>1.2690999999999999</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3587,10 +3587,10 @@
         <v>2024</v>
       </c>
       <c r="C229" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D229" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.0390999999999999</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3601,10 +3601,10 @@
         <v>2024</v>
       </c>
       <c r="C230" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D230" s="3">
-        <v>1.0940000000000001</v>
+        <v>1.1085</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3612,13 +3612,13 @@
         <v>6</v>
       </c>
       <c r="B231" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D231" s="3">
-        <v>0.94689999999999996</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3626,13 +3626,13 @@
         <v>6</v>
       </c>
       <c r="B232" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C232" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D232" s="3">
-        <v>0.95220000000000005</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3643,10 +3643,10 @@
         <v>2025</v>
       </c>
       <c r="C233" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D233" s="3">
-        <v>0.95209999999999995</v>
+        <v>0.94689999999999996</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3657,10 +3657,10 @@
         <v>2025</v>
       </c>
       <c r="C234" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D234" s="3">
-        <v>1.0407999999999999</v>
+        <v>0.95220000000000005</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3671,10 +3671,10 @@
         <v>2025</v>
       </c>
       <c r="C235" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D235" s="3">
-        <v>1.1001000000000001</v>
+        <v>0.95209999999999995</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3685,10 +3685,10 @@
         <v>2025</v>
       </c>
       <c r="C236" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D236" s="3">
-        <v>1.0804</v>
+        <v>1.0407999999999999</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3699,10 +3699,10 @@
         <v>2025</v>
       </c>
       <c r="C237" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D237" s="3">
-        <v>1.1061000000000001</v>
+        <v>1.1001000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3713,10 +3713,10 @@
         <v>2025</v>
       </c>
       <c r="C238" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D238" s="3">
-        <v>0.98920000000000008</v>
+        <v>1.0804</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3727,10 +3727,10 @@
         <v>2025</v>
       </c>
       <c r="C239" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D239" s="3">
-        <v>1.0139</v>
+        <v>1.1061000000000001</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3741,10 +3741,10 @@
         <v>2025</v>
       </c>
       <c r="C240" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D240" s="3">
-        <v>0.94899999999999995</v>
+        <v>0.98920000000000008</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3755,10 +3755,10 @@
         <v>2025</v>
       </c>
       <c r="C241" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D241" s="3">
-        <v>1.0072000000000001</v>
+        <v>1.0139</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3769,10 +3769,10 @@
         <v>2025</v>
       </c>
       <c r="C242" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D242" s="3">
-        <v>1.0069999999999999</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3780,13 +3780,13 @@
         <v>6</v>
       </c>
       <c r="B243" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C243" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D243" s="3">
-        <v>0.94920000000000015</v>
+        <v>1.0072000000000001</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3794,13 +3794,13 @@
         <v>6</v>
       </c>
       <c r="B244" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C244" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D244" s="3">
-        <v>0.87809999999999999</v>
+        <v>1.0069999999999999</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3811,10 +3811,10 @@
         <v>2026</v>
       </c>
       <c r="C245" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D245" s="3">
-        <v>0.97489999999999988</v>
+        <v>0.94920000000000015</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3825,10 +3825,10 @@
         <v>2026</v>
       </c>
       <c r="C246" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D246" s="3">
-        <v>0.94169999999999987</v>
+        <v>0.87809999999999999</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3839,10 +3839,10 @@
         <v>2026</v>
       </c>
       <c r="C247" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D247" s="3">
-        <v>1.0869</v>
+        <v>0.88470000000000004</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3853,52 +3853,52 @@
         <v>2026</v>
       </c>
       <c r="C248" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D248" s="3">
-        <v>1.1671</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B249" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C249" s="2">
         <v>5</v>
       </c>
       <c r="D249" s="3">
-        <v>0.3634</v>
+        <v>1.0716000000000001</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B250" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C250" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D250" s="3">
-        <v>1.1855</v>
+        <v>1.1191</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B251" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C251" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D251" s="3">
-        <v>0.55079999999999996</v>
+        <v>1.0051000000000001</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3909,10 +3909,10 @@
         <v>2019</v>
       </c>
       <c r="C252" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3">
-        <v>1.544</v>
+        <v>0.3634</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3923,10 +3923,10 @@
         <v>2019</v>
       </c>
       <c r="C253" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D253" s="3">
-        <v>1.5068999999999997</v>
+        <v>1.1855</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3934,13 +3934,13 @@
         <v>7</v>
       </c>
       <c r="B254" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C254" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D254" s="3">
-        <v>0.94240000000000002</v>
+        <v>0.55079999999999996</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -3948,13 +3948,13 @@
         <v>7</v>
       </c>
       <c r="B255" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C255" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D255" s="3">
-        <v>1.0011000000000001</v>
+        <v>1.544</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3962,13 +3962,13 @@
         <v>7</v>
       </c>
       <c r="B256" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C256" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D256" s="3">
-        <v>0.96850000000000003</v>
+        <v>1.5068999999999997</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -3979,10 +3979,10 @@
         <v>2020</v>
       </c>
       <c r="C257" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D257" s="3">
-        <v>1.0559000000000001</v>
+        <v>0.94240000000000002</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -3993,10 +3993,10 @@
         <v>2020</v>
       </c>
       <c r="C258" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D258" s="3">
-        <v>0.91450000000000009</v>
+        <v>1.0011000000000001</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4007,10 +4007,10 @@
         <v>2020</v>
       </c>
       <c r="C259" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D259" s="3">
-        <v>1.0116000000000001</v>
+        <v>0.96850000000000003</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4021,10 +4021,10 @@
         <v>2020</v>
       </c>
       <c r="C260" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D260" s="3">
-        <v>1.3797999999999999</v>
+        <v>1.0559000000000001</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4035,10 +4035,10 @@
         <v>2020</v>
       </c>
       <c r="C261" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D261" s="3">
-        <v>1.4618</v>
+        <v>0.91450000000000009</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4049,10 +4049,10 @@
         <v>2020</v>
       </c>
       <c r="C262" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D262" s="3">
-        <v>1.2636000000000001</v>
+        <v>1.0116000000000001</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4063,10 +4063,10 @@
         <v>2020</v>
       </c>
       <c r="C263" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D263" s="3">
-        <v>1.0862000000000001</v>
+        <v>1.3797999999999999</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4077,10 +4077,10 @@
         <v>2020</v>
       </c>
       <c r="C264" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D264" s="3">
-        <v>1.1226</v>
+        <v>1.4618</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4091,10 +4091,10 @@
         <v>2020</v>
       </c>
       <c r="C265" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D265" s="3">
-        <v>1.1798999999999999</v>
+        <v>1.2636000000000001</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4102,13 +4102,13 @@
         <v>7</v>
       </c>
       <c r="B266" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C266" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D266" s="3">
-        <v>1.3149999999999999</v>
+        <v>1.0862000000000001</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4116,13 +4116,13 @@
         <v>7</v>
       </c>
       <c r="B267" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C267" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D267" s="3">
-        <v>1.2918000000000001</v>
+        <v>1.1226</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4130,13 +4130,13 @@
         <v>7</v>
       </c>
       <c r="B268" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C268" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D268" s="3">
-        <v>1.3935</v>
+        <v>1.1798999999999999</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4147,10 +4147,10 @@
         <v>2021</v>
       </c>
       <c r="C269" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D269" s="3">
-        <v>1.6409</v>
+        <v>1.3149999999999999</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4161,10 +4161,10 @@
         <v>2021</v>
       </c>
       <c r="C270" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D270" s="3">
-        <v>1.5944</v>
+        <v>1.2918000000000001</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4175,10 +4175,10 @@
         <v>2021</v>
       </c>
       <c r="C271" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D271" s="3">
-        <v>1.5669999999999999</v>
+        <v>1.3935</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4189,10 +4189,10 @@
         <v>2021</v>
       </c>
       <c r="C272" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D272" s="3">
-        <v>1.276</v>
+        <v>1.6409</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4203,10 +4203,10 @@
         <v>2021</v>
       </c>
       <c r="C273" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D273" s="3">
-        <v>1.1046</v>
+        <v>1.5944</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4217,10 +4217,10 @@
         <v>2021</v>
       </c>
       <c r="C274" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D274" s="3">
-        <v>1.0746</v>
+        <v>1.5669999999999999</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4231,10 +4231,10 @@
         <v>2021</v>
       </c>
       <c r="C275" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D275" s="3">
-        <v>0.95230000000000004</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4245,10 +4245,10 @@
         <v>2021</v>
       </c>
       <c r="C276" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D276" s="3">
-        <v>0.93070000000000008</v>
+        <v>1.1046</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4259,10 +4259,10 @@
         <v>2021</v>
       </c>
       <c r="C277" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D277" s="3">
-        <v>1.0242</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4270,13 +4270,13 @@
         <v>7</v>
       </c>
       <c r="B278" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C278" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D278" s="3">
-        <v>0.95179999999999998</v>
+        <v>0.95230000000000004</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4284,13 +4284,13 @@
         <v>7</v>
       </c>
       <c r="B279" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C279" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D279" s="3">
-        <v>1.1564000000000001</v>
+        <v>0.93070000000000008</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4298,13 +4298,13 @@
         <v>7</v>
       </c>
       <c r="B280" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C280" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D280" s="3">
-        <v>0.93640000000000001</v>
+        <v>1.0242</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4315,10 +4315,10 @@
         <v>2022</v>
       </c>
       <c r="C281" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D281" s="3">
-        <v>0.86789999999999989</v>
+        <v>0.95179999999999998</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4329,10 +4329,10 @@
         <v>2022</v>
       </c>
       <c r="C282" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D282" s="3">
-        <v>0.89589999999999992</v>
+        <v>1.1564000000000001</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4343,10 +4343,10 @@
         <v>2022</v>
       </c>
       <c r="C283" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D283" s="3">
-        <v>0.97230000000000005</v>
+        <v>0.93640000000000001</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4357,10 +4357,10 @@
         <v>2022</v>
       </c>
       <c r="C284" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D284" s="3">
-        <v>1.0585</v>
+        <v>0.86789999999999989</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4371,10 +4371,10 @@
         <v>2022</v>
       </c>
       <c r="C285" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D285" s="3">
-        <v>0.91169999999999995</v>
+        <v>0.89589999999999992</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4385,10 +4385,10 @@
         <v>2022</v>
       </c>
       <c r="C286" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D286" s="3">
-        <v>0.77860000000000007</v>
+        <v>0.97230000000000005</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4399,10 +4399,10 @@
         <v>2022</v>
       </c>
       <c r="C287" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D287" s="3">
-        <v>0.98480000000000001</v>
+        <v>1.0585</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4413,10 +4413,10 @@
         <v>2022</v>
       </c>
       <c r="C288" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D288" s="3">
-        <v>0.96220000000000006</v>
+        <v>0.91169999999999995</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4427,10 +4427,10 @@
         <v>2022</v>
       </c>
       <c r="C289" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D289" s="3">
-        <v>0.89329999999999998</v>
+        <v>0.77860000000000007</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4438,13 +4438,13 @@
         <v>7</v>
       </c>
       <c r="B290" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C290" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D290" s="3">
-        <v>0.99390000000000001</v>
+        <v>0.98480000000000001</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4452,13 +4452,13 @@
         <v>7</v>
       </c>
       <c r="B291" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C291" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D291" s="3">
-        <v>1.0999000000000001</v>
+        <v>0.96220000000000006</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4466,13 +4466,13 @@
         <v>7</v>
       </c>
       <c r="B292" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C292" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D292" s="3">
-        <v>1.1256999999999999</v>
+        <v>0.89329999999999998</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4483,10 +4483,10 @@
         <v>2023</v>
       </c>
       <c r="C293" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D293" s="3">
-        <v>1.0003</v>
+        <v>0.99390000000000001</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4497,10 +4497,10 @@
         <v>2023</v>
       </c>
       <c r="C294" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D294" s="3">
-        <v>1.1068</v>
+        <v>1.0999000000000001</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4511,10 +4511,10 @@
         <v>2023</v>
       </c>
       <c r="C295" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D295" s="3">
-        <v>1.0865</v>
+        <v>1.1256999999999999</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4525,10 +4525,10 @@
         <v>2023</v>
       </c>
       <c r="C296" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D296" s="3">
-        <v>0.97589999999999999</v>
+        <v>1.0003</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4539,10 +4539,10 @@
         <v>2023</v>
       </c>
       <c r="C297" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D297" s="3">
-        <v>1.0511999999999999</v>
+        <v>1.1068</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4553,10 +4553,10 @@
         <v>2023</v>
       </c>
       <c r="C298" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D298" s="3">
-        <v>1.0577000000000001</v>
+        <v>1.0865</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4567,10 +4567,10 @@
         <v>2023</v>
       </c>
       <c r="C299" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D299" s="3">
-        <v>0.97499999999999987</v>
+        <v>0.97589999999999999</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4581,10 +4581,10 @@
         <v>2023</v>
       </c>
       <c r="C300" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D300" s="3">
-        <v>1.0082</v>
+        <v>1.0511999999999999</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4595,10 +4595,10 @@
         <v>2023</v>
       </c>
       <c r="C301" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D301" s="3">
-        <v>1.0295000000000001</v>
+        <v>1.0577000000000001</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4606,13 +4606,13 @@
         <v>7</v>
       </c>
       <c r="B302" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C302" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D302" s="3">
-        <v>0.87479999999999991</v>
+        <v>0.97499999999999987</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4620,13 +4620,13 @@
         <v>7</v>
       </c>
       <c r="B303" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C303" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D303" s="3">
-        <v>0.8629</v>
+        <v>1.0082</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4634,13 +4634,13 @@
         <v>7</v>
       </c>
       <c r="B304" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C304" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D304" s="3">
-        <v>0.87240000000000006</v>
+        <v>1.0295000000000001</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4651,10 +4651,10 @@
         <v>2024</v>
       </c>
       <c r="C305" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D305" s="3">
-        <v>1.1091</v>
+        <v>0.87479999999999991</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4665,10 +4665,10 @@
         <v>2024</v>
       </c>
       <c r="C306" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D306" s="3">
-        <v>1.0685</v>
+        <v>0.8629</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -4679,10 +4679,10 @@
         <v>2024</v>
       </c>
       <c r="C307" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D307" s="3">
-        <v>1.0423</v>
+        <v>0.87240000000000006</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -4693,10 +4693,10 @@
         <v>2024</v>
       </c>
       <c r="C308" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D308" s="3">
-        <v>1.1042000000000001</v>
+        <v>1.1091</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4707,10 +4707,10 @@
         <v>2024</v>
       </c>
       <c r="C309" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D309" s="3">
-        <v>1.1225000000000001</v>
+        <v>1.0685</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4721,10 +4721,10 @@
         <v>2024</v>
       </c>
       <c r="C310" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D310" s="3">
-        <v>1.2110000000000001</v>
+        <v>1.0423</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4735,10 +4735,10 @@
         <v>2024</v>
       </c>
       <c r="C311" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D311" s="3">
-        <v>1.2477</v>
+        <v>1.1042000000000001</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4749,10 +4749,10 @@
         <v>2024</v>
       </c>
       <c r="C312" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D312" s="3">
-        <v>1.1498999999999999</v>
+        <v>1.1225000000000001</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4763,10 +4763,10 @@
         <v>2024</v>
       </c>
       <c r="C313" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D313" s="3">
-        <v>1.2698</v>
+        <v>1.2110000000000001</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -4774,13 +4774,13 @@
         <v>7</v>
       </c>
       <c r="B314" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C314" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D314" s="3">
-        <v>1.0775999999999999</v>
+        <v>1.2477</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4788,13 +4788,13 @@
         <v>7</v>
       </c>
       <c r="B315" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C315" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D315" s="3">
-        <v>1.0754999999999999</v>
+        <v>1.1498999999999999</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4802,13 +4802,13 @@
         <v>7</v>
       </c>
       <c r="B316" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C316" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D316" s="3">
-        <v>1.2067000000000001</v>
+        <v>1.2698</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4819,10 +4819,10 @@
         <v>2025</v>
       </c>
       <c r="C317" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D317" s="3">
-        <v>1.1234999999999999</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4833,10 +4833,10 @@
         <v>2025</v>
       </c>
       <c r="C318" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D318" s="3">
-        <v>1.2224999999999999</v>
+        <v>1.0754999999999999</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4847,10 +4847,10 @@
         <v>2025</v>
       </c>
       <c r="C319" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D319" s="3">
-        <v>1.1957</v>
+        <v>1.2067000000000001</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4861,10 +4861,10 @@
         <v>2025</v>
       </c>
       <c r="C320" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D320" s="3">
-        <v>1.3280000000000001</v>
+        <v>1.1234999999999999</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4875,10 +4875,10 @@
         <v>2025</v>
       </c>
       <c r="C321" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D321" s="3">
-        <v>1.1873</v>
+        <v>1.2224999999999999</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4889,10 +4889,10 @@
         <v>2025</v>
       </c>
       <c r="C322" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D322" s="3">
-        <v>1.1939</v>
+        <v>1.1960999999999999</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4903,10 +4903,10 @@
         <v>2025</v>
       </c>
       <c r="C323" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D323" s="3">
-        <v>1.3411</v>
+        <v>1.3280000000000001</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4917,10 +4917,10 @@
         <v>2025</v>
       </c>
       <c r="C324" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D324" s="3">
-        <v>1.3031999999999999</v>
+        <v>1.1873</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4931,10 +4931,10 @@
         <v>2025</v>
       </c>
       <c r="C325" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D325" s="3">
-        <v>1.1761999999999999</v>
+        <v>1.1939</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4942,13 +4942,13 @@
         <v>7</v>
       </c>
       <c r="B326" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C326" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D326" s="3">
-        <v>1.1228</v>
+        <v>1.3411</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4956,13 +4956,13 @@
         <v>7</v>
       </c>
       <c r="B327" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C327" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D327" s="3">
-        <v>1.2719</v>
+        <v>1.3031999999999999</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4970,13 +4970,13 @@
         <v>7</v>
       </c>
       <c r="B328" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C328" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D328" s="3">
-        <v>1.3737999999999999</v>
+        <v>1.1752</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -4987,10 +4987,10 @@
         <v>2026</v>
       </c>
       <c r="C329" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D329" s="3">
-        <v>1.2373000000000001</v>
+        <v>1.1258999999999999</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5001,10 +5001,10 @@
         <v>2026</v>
       </c>
       <c r="C330" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D330" s="3">
-        <v>1.1888000000000001</v>
+        <v>1.2725</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5015,66 +5015,66 @@
         <v>2026</v>
       </c>
       <c r="C331" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D331" s="3">
-        <v>1.2088000000000001</v>
+        <v>1.2396</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B332" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C332" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D332" s="3">
-        <v>0.46260000000000001</v>
+        <v>1.2282999999999999</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B333" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C333" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D333" s="3">
-        <v>2.5009999999999999</v>
+        <v>1.1887000000000001</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B334" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C334" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D334" s="3">
-        <v>0.60919999999999996</v>
+        <v>1.1737</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B335" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C335" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D335" s="3">
-        <v>0.43890000000000001</v>
+        <v>1.1597999999999999</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5082,13 +5082,13 @@
         <v>8</v>
       </c>
       <c r="B336" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C336" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D336" s="3">
-        <v>0.58919999999999995</v>
+        <v>0.46260000000000001</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5096,13 +5096,13 @@
         <v>8</v>
       </c>
       <c r="B337" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C337" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D337" s="3">
-        <v>1.8193999999999997</v>
+        <v>2.5009999999999999</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5110,13 +5110,13 @@
         <v>8</v>
       </c>
       <c r="B338" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C338" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D338" s="3">
-        <v>1.2989999999999999</v>
+        <v>0.60919999999999996</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5127,10 +5127,10 @@
         <v>2020</v>
       </c>
       <c r="C339" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D339" s="3">
-        <v>1.3857999999999999</v>
+        <v>0.43890000000000001</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5141,10 +5141,10 @@
         <v>2020</v>
       </c>
       <c r="C340" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D340" s="3">
-        <v>1.9608000000000001</v>
+        <v>0.58919999999999995</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5155,10 +5155,10 @@
         <v>2020</v>
       </c>
       <c r="C341" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D341" s="3">
-        <v>1.8338000000000001</v>
+        <v>1.8193999999999997</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5169,10 +5169,10 @@
         <v>2020</v>
       </c>
       <c r="C342" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D342" s="3">
-        <v>1.7322999999999997</v>
+        <v>1.2971999999999999</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5183,10 +5183,10 @@
         <v>2020</v>
       </c>
       <c r="C343" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D343" s="3">
-        <v>1.8378000000000001</v>
+        <v>1.3857999999999999</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5197,10 +5197,10 @@
         <v>2020</v>
       </c>
       <c r="C344" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D344" s="3">
-        <v>1.8994</v>
+        <v>1.9622999999999999</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5211,10 +5211,10 @@
         <v>2020</v>
       </c>
       <c r="C345" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D345" s="3">
-        <v>1.7765999999999997</v>
+        <v>1.8338000000000001</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5222,13 +5222,13 @@
         <v>8</v>
       </c>
       <c r="B346" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C346" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D346" s="3">
-        <v>1.5302</v>
+        <v>1.7322999999999997</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5236,13 +5236,13 @@
         <v>8</v>
       </c>
       <c r="B347" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C347" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D347" s="3">
-        <v>1.7687000000000002</v>
+        <v>1.8385</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5250,13 +5250,13 @@
         <v>8</v>
       </c>
       <c r="B348" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C348" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D348" s="3">
-        <v>1.3537999999999999</v>
+        <v>1.8994</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5264,13 +5264,13 @@
         <v>8</v>
       </c>
       <c r="B349" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C349" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D349" s="3">
-        <v>1.1635</v>
+        <v>1.7783</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5281,10 +5281,10 @@
         <v>2021</v>
       </c>
       <c r="C350" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D350" s="3">
-        <v>1.9408000000000003</v>
+        <v>1.5302</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5295,10 +5295,10 @@
         <v>2021</v>
       </c>
       <c r="C351" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D351" s="3">
-        <v>1.2329000000000001</v>
+        <v>1.7687000000000002</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5309,10 +5309,10 @@
         <v>2021</v>
       </c>
       <c r="C352" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D352" s="3">
-        <v>1.3917999999999999</v>
+        <v>1.3537999999999999</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -5323,10 +5323,10 @@
         <v>2021</v>
       </c>
       <c r="C353" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D353" s="3">
-        <v>1.323</v>
+        <v>1.1635</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5337,10 +5337,10 @@
         <v>2021</v>
       </c>
       <c r="C354" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D354" s="3">
-        <v>1.4923999999999999</v>
+        <v>1.9408000000000003</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5351,10 +5351,10 @@
         <v>2021</v>
       </c>
       <c r="C355" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D355" s="3">
-        <v>1.4085000000000001</v>
+        <v>1.2329000000000001</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -5365,10 +5365,10 @@
         <v>2021</v>
       </c>
       <c r="C356" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D356" s="3">
-        <v>1.4259999999999999</v>
+        <v>1.3917999999999999</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5379,10 +5379,10 @@
         <v>2021</v>
       </c>
       <c r="C357" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D357" s="3">
-        <v>1.3572</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -5390,13 +5390,13 @@
         <v>8</v>
       </c>
       <c r="B358" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C358" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D358" s="3">
-        <v>1.4053</v>
+        <v>1.4923999999999999</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5404,13 +5404,13 @@
         <v>8</v>
       </c>
       <c r="B359" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C359" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D359" s="3">
-        <v>1.4612000000000001</v>
+        <v>1.4086000000000001</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -5418,13 +5418,13 @@
         <v>8</v>
       </c>
       <c r="B360" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C360" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D360" s="3">
-        <v>1.4157999999999999</v>
+        <v>1.4259999999999999</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -5432,13 +5432,13 @@
         <v>8</v>
       </c>
       <c r="B361" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C361" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D361" s="3">
-        <v>1.4791999999999998</v>
+        <v>1.3573</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5449,10 +5449,10 @@
         <v>2022</v>
       </c>
       <c r="C362" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D362" s="3">
-        <v>1.4770000000000001</v>
+        <v>1.4053</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5463,10 +5463,10 @@
         <v>2022</v>
       </c>
       <c r="C363" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D363" s="3">
-        <v>1.4380999999999999</v>
+        <v>1.4612000000000001</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5477,10 +5477,10 @@
         <v>2022</v>
       </c>
       <c r="C364" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D364" s="3">
-        <v>1.6324000000000001</v>
+        <v>1.4157999999999999</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5491,10 +5491,10 @@
         <v>2022</v>
       </c>
       <c r="C365" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D365" s="3">
-        <v>1.5557000000000001</v>
+        <v>1.4791999999999998</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5505,10 +5505,10 @@
         <v>2022</v>
       </c>
       <c r="C366" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D366" s="3">
-        <v>1.599</v>
+        <v>1.4770000000000001</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -5519,10 +5519,10 @@
         <v>2022</v>
       </c>
       <c r="C367" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D367" s="3">
-        <v>1.4990000000000001</v>
+        <v>1.4380999999999999</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5533,10 +5533,10 @@
         <v>2022</v>
       </c>
       <c r="C368" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D368" s="3">
-        <v>1.484</v>
+        <v>1.6324000000000001</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5547,10 +5547,10 @@
         <v>2022</v>
       </c>
       <c r="C369" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D369" s="3">
-        <v>1.5085999999999999</v>
+        <v>1.5557000000000001</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5558,13 +5558,13 @@
         <v>8</v>
       </c>
       <c r="B370" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C370" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D370" s="3">
-        <v>1.4896</v>
+        <v>1.599</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5572,13 +5572,13 @@
         <v>8</v>
       </c>
       <c r="B371" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C371" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D371" s="3">
-        <v>1.5462999999999998</v>
+        <v>1.4990000000000001</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -5586,13 +5586,13 @@
         <v>8</v>
       </c>
       <c r="B372" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C372" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D372" s="3">
-        <v>1.3642000000000001</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -5600,13 +5600,13 @@
         <v>8</v>
       </c>
       <c r="B373" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C373" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D373" s="3">
-        <v>1.3847</v>
+        <v>1.5085999999999999</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5617,10 +5617,10 @@
         <v>2023</v>
       </c>
       <c r="C374" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D374" s="3">
-        <v>1.2858000000000001</v>
+        <v>1.4896</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5631,10 +5631,10 @@
         <v>2023</v>
       </c>
       <c r="C375" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D375" s="3">
-        <v>1.8708</v>
+        <v>1.5462999999999998</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -5645,10 +5645,10 @@
         <v>2023</v>
       </c>
       <c r="C376" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D376" s="3">
-        <v>1.8864000000000001</v>
+        <v>1.3642000000000001</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -5659,10 +5659,10 @@
         <v>2023</v>
       </c>
       <c r="C377" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D377" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.3847</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5673,10 +5673,10 @@
         <v>2023</v>
       </c>
       <c r="C378" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="3">
-        <v>1.9263999999999999</v>
+        <v>1.2858000000000001</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5687,10 +5687,10 @@
         <v>2023</v>
       </c>
       <c r="C379" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D379" s="3">
-        <v>1.9342999999999999</v>
+        <v>1.8708</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5701,10 +5701,10 @@
         <v>2023</v>
       </c>
       <c r="C380" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D380" s="3">
-        <v>1.7403999999999999</v>
+        <v>1.8864000000000001</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5715,10 +5715,10 @@
         <v>2023</v>
       </c>
       <c r="C381" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D381" s="3">
-        <v>1.7998000000000001</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5726,13 +5726,13 @@
         <v>8</v>
       </c>
       <c r="B382" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C382" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D382" s="3">
-        <v>1.8641000000000001</v>
+        <v>1.9263999999999999</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -5740,13 +5740,13 @@
         <v>8</v>
       </c>
       <c r="B383" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C383" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D383" s="3">
-        <v>2.0535999999999999</v>
+        <v>1.9342999999999999</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -5754,13 +5754,13 @@
         <v>8</v>
       </c>
       <c r="B384" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C384" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D384" s="3">
-        <v>1.8251999999999999</v>
+        <v>1.7403999999999999</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5768,13 +5768,13 @@
         <v>8</v>
       </c>
       <c r="B385" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C385" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D385" s="3">
-        <v>1.8498000000000001</v>
+        <v>1.7998000000000001</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5785,10 +5785,10 @@
         <v>2024</v>
       </c>
       <c r="C386" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D386" s="3">
-        <v>1.8720000000000001</v>
+        <v>1.8641000000000001</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5799,10 +5799,10 @@
         <v>2024</v>
       </c>
       <c r="C387" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D387" s="3">
-        <v>1.8865000000000001</v>
+        <v>2.0535999999999999</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5813,10 +5813,10 @@
         <v>2024</v>
       </c>
       <c r="C388" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D388" s="3">
-        <v>1.6568000000000001</v>
+        <v>1.8251999999999999</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5827,10 +5827,10 @@
         <v>2024</v>
       </c>
       <c r="C389" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D389" s="3">
-        <v>1.8308</v>
+        <v>1.8498000000000001</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5841,10 +5841,10 @@
         <v>2024</v>
       </c>
       <c r="C390" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D390" s="3">
-        <v>1.8752</v>
+        <v>1.8717999999999999</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5855,10 +5855,10 @@
         <v>2024</v>
       </c>
       <c r="C391" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D391" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.8865000000000001</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5869,10 +5869,10 @@
         <v>2024</v>
       </c>
       <c r="C392" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D392" s="3">
-        <v>1.8120000000000001</v>
+        <v>1.6568000000000001</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5883,10 +5883,10 @@
         <v>2024</v>
       </c>
       <c r="C393" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3">
-        <v>1.7609999999999999</v>
+        <v>1.8308</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5894,13 +5894,13 @@
         <v>8</v>
       </c>
       <c r="B394" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C394" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D394" s="3">
-        <v>1.7717000000000001</v>
+        <v>1.8752</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5908,13 +5908,13 @@
         <v>8</v>
       </c>
       <c r="B395" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C395" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D395" s="3">
-        <v>1.6231</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5922,13 +5922,13 @@
         <v>8</v>
       </c>
       <c r="B396" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C396" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D396" s="3">
-        <v>1.7063999999999999</v>
+        <v>1.8120000000000001</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5936,13 +5936,13 @@
         <v>8</v>
       </c>
       <c r="B397" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C397" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D397" s="3">
-        <v>1.4521999999999999</v>
+        <v>1.7609999999999999</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5953,10 +5953,10 @@
         <v>2025</v>
       </c>
       <c r="C398" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3">
-        <v>1.4105000000000001</v>
+        <v>1.7717000000000001</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -5967,10 +5967,10 @@
         <v>2025</v>
       </c>
       <c r="C399" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D399" s="3">
-        <v>1.5933999999999999</v>
+        <v>1.6231</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -5981,10 +5981,10 @@
         <v>2025</v>
       </c>
       <c r="C400" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D400" s="3">
-        <v>1.5374000000000001</v>
+        <v>1.7063999999999999</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -5995,10 +5995,10 @@
         <v>2025</v>
       </c>
       <c r="C401" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D401" s="3">
-        <v>1.5250999999999999</v>
+        <v>1.4521999999999999</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6009,10 +6009,10 @@
         <v>2025</v>
       </c>
       <c r="C402" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D402" s="3">
-        <v>1.4985999999999999</v>
+        <v>1.4105000000000001</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6023,10 +6023,10 @@
         <v>2025</v>
       </c>
       <c r="C403" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D403" s="3">
-        <v>1.462</v>
+        <v>1.5945</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6037,10 +6037,10 @@
         <v>2025</v>
       </c>
       <c r="C404" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D404" s="3">
-        <v>1.6359999999999999</v>
+        <v>1.5374000000000001</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6051,10 +6051,10 @@
         <v>2025</v>
       </c>
       <c r="C405" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D405" s="3">
-        <v>1.7412000000000001</v>
+        <v>1.5250999999999999</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6062,13 +6062,13 @@
         <v>8</v>
       </c>
       <c r="B406" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C406" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D406" s="3">
-        <v>1.4174</v>
+        <v>1.4985999999999999</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6076,13 +6076,13 @@
         <v>8</v>
       </c>
       <c r="B407" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C407" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D407" s="3">
-        <v>1.5972</v>
+        <v>1.462</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6090,13 +6090,13 @@
         <v>8</v>
       </c>
       <c r="B408" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C408" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D408" s="3">
-        <v>1.4419999999999999</v>
+        <v>1.6359999999999999</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6104,13 +6104,13 @@
         <v>8</v>
       </c>
       <c r="B409" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C409" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D409" s="3">
-        <v>1.4006000000000001</v>
+        <v>1.7412000000000001</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6121,10 +6121,10 @@
         <v>2026</v>
       </c>
       <c r="C410" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D410" s="3">
-        <v>1.6073999999999999</v>
+        <v>1.4895</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6135,80 +6135,80 @@
         <v>2026</v>
       </c>
       <c r="C411" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D411" s="3">
-        <v>1.6576</v>
+        <v>1.5972</v>
       </c>
     </row>
     <row r="412" spans="1:4">
       <c r="A412" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B412" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C412" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D412" s="3">
-        <v>1.1920999999999999</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="413" spans="1:4">
       <c r="A413" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B413" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C413" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D413" s="3">
-        <v>0.9788</v>
+        <v>1.4261999999999997</v>
       </c>
     </row>
     <row r="414" spans="1:4">
       <c r="A414" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B414" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C414" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D414" s="3">
-        <v>1.3588</v>
+        <v>1.6074999999999999</v>
       </c>
     </row>
     <row r="415" spans="1:4">
       <c r="A415" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B415" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C415" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D415" s="3">
-        <v>1.3531</v>
+        <v>1.5484</v>
       </c>
     </row>
     <row r="416" spans="1:4">
       <c r="A416" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B416" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C416" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D416" s="3">
-        <v>1.4077999999999999</v>
+        <v>1.6223000000000001</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6219,10 +6219,10 @@
         <v>2019</v>
       </c>
       <c r="C417" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D417" s="3">
-        <v>1.1672</v>
+        <v>1.1920999999999999</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6233,10 +6233,10 @@
         <v>2019</v>
       </c>
       <c r="C418" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D418" s="3">
-        <v>1.5024</v>
+        <v>0.9788</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6247,10 +6247,10 @@
         <v>2019</v>
       </c>
       <c r="C419" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D419" s="3">
-        <v>1.1561999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6258,13 +6258,13 @@
         <v>9</v>
       </c>
       <c r="B420" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C420" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D420" s="3">
-        <v>1.1488</v>
+        <v>1.3531</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6272,13 +6272,13 @@
         <v>9</v>
       </c>
       <c r="B421" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C421" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D421" s="3">
-        <v>1.0632999999999999</v>
+        <v>1.4077999999999999</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6286,13 +6286,13 @@
         <v>9</v>
       </c>
       <c r="B422" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C422" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D422" s="3">
-        <v>1.0150999999999999</v>
+        <v>1.1672</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6300,13 +6300,13 @@
         <v>9</v>
       </c>
       <c r="B423" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C423" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D423" s="3">
-        <v>1.1227</v>
+        <v>1.5024</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6314,13 +6314,13 @@
         <v>9</v>
       </c>
       <c r="B424" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C424" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D424" s="3">
-        <v>1.0437000000000001</v>
+        <v>1.1561999999999999</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6331,10 +6331,10 @@
         <v>2020</v>
       </c>
       <c r="C425" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D425" s="3">
-        <v>1.2843</v>
+        <v>1.1488</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6345,10 +6345,10 @@
         <v>2020</v>
       </c>
       <c r="C426" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D426" s="3">
-        <v>1.3385</v>
+        <v>1.0632999999999999</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6359,10 +6359,10 @@
         <v>2020</v>
       </c>
       <c r="C427" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D427" s="3">
-        <v>1.6960999999999999</v>
+        <v>1.0150999999999999</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6373,10 +6373,10 @@
         <v>2020</v>
       </c>
       <c r="C428" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D428" s="3">
-        <v>1.4695</v>
+        <v>1.1227</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6387,10 +6387,10 @@
         <v>2020</v>
       </c>
       <c r="C429" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D429" s="3">
-        <v>1.4509000000000001</v>
+        <v>1.0437000000000001</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6401,10 +6401,10 @@
         <v>2020</v>
       </c>
       <c r="C430" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D430" s="3">
-        <v>1.4291</v>
+        <v>1.2843</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6415,10 +6415,10 @@
         <v>2020</v>
       </c>
       <c r="C431" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D431" s="3">
-        <v>1.2766</v>
+        <v>1.3385</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6426,13 +6426,13 @@
         <v>9</v>
       </c>
       <c r="B432" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C432" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D432" s="3">
-        <v>1.2372000000000001</v>
+        <v>1.6960999999999999</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6440,13 +6440,13 @@
         <v>9</v>
       </c>
       <c r="B433" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C433" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D433" s="3">
-        <v>1.3984000000000001</v>
+        <v>1.4695</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6454,13 +6454,13 @@
         <v>9</v>
       </c>
       <c r="B434" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C434" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D434" s="3">
-        <v>1.2039</v>
+        <v>1.4509000000000001</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6468,13 +6468,13 @@
         <v>9</v>
       </c>
       <c r="B435" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C435" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D435" s="3">
-        <v>1.2943</v>
+        <v>1.4296</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6482,13 +6482,13 @@
         <v>9</v>
       </c>
       <c r="B436" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C436" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D436" s="3">
-        <v>1.2292000000000001</v>
+        <v>1.2766999999999999</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6499,10 +6499,10 @@
         <v>2021</v>
       </c>
       <c r="C437" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D437" s="3">
-        <v>1.3234999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6513,10 +6513,10 @@
         <v>2021</v>
       </c>
       <c r="C438" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D438" s="3">
-        <v>1.284</v>
+        <v>1.3984000000000001</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6527,10 +6527,10 @@
         <v>2021</v>
       </c>
       <c r="C439" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D439" s="3">
-        <v>1.1142000000000001</v>
+        <v>1.2039</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6541,10 +6541,10 @@
         <v>2021</v>
       </c>
       <c r="C440" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D440" s="3">
-        <v>0.96379999999999988</v>
+        <v>1.2944</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6555,10 +6555,10 @@
         <v>2021</v>
       </c>
       <c r="C441" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D441" s="3">
-        <v>1.0775999999999999</v>
+        <v>1.2292000000000001</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6569,10 +6569,10 @@
         <v>2021</v>
       </c>
       <c r="C442" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D442" s="3">
-        <v>1.179</v>
+        <v>1.3234999999999999</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6583,10 +6583,10 @@
         <v>2021</v>
       </c>
       <c r="C443" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D443" s="3">
-        <v>1.0859000000000001</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6594,13 +6594,13 @@
         <v>9</v>
       </c>
       <c r="B444" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C444" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D444" s="3">
-        <v>1.1252</v>
+        <v>1.1142000000000001</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6608,13 +6608,13 @@
         <v>9</v>
       </c>
       <c r="B445" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C445" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D445" s="3">
-        <v>1.1546000000000001</v>
+        <v>0.96379999999999988</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6622,13 +6622,13 @@
         <v>9</v>
       </c>
       <c r="B446" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C446" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D446" s="3">
-        <v>1.0673999999999999</v>
+        <v>1.0775999999999999</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6636,13 +6636,13 @@
         <v>9</v>
       </c>
       <c r="B447" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C447" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D447" s="3">
-        <v>1.1517999999999999</v>
+        <v>1.179</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6650,13 +6650,13 @@
         <v>9</v>
       </c>
       <c r="B448" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C448" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D448" s="3">
-        <v>1.1574</v>
+        <v>1.0859000000000001</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6667,10 +6667,10 @@
         <v>2022</v>
       </c>
       <c r="C449" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D449" s="3">
-        <v>1.1416999999999999</v>
+        <v>1.1252</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6681,10 +6681,10 @@
         <v>2022</v>
       </c>
       <c r="C450" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D450" s="3">
-        <v>1.2119</v>
+        <v>1.1546000000000001</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6695,10 +6695,10 @@
         <v>2022</v>
       </c>
       <c r="C451" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D451" s="3">
-        <v>1.1833</v>
+        <v>1.0673999999999999</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6709,10 +6709,10 @@
         <v>2022</v>
       </c>
       <c r="C452" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D452" s="3">
-        <v>1.2625</v>
+        <v>1.1517999999999999</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6723,10 +6723,10 @@
         <v>2022</v>
       </c>
       <c r="C453" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D453" s="3">
-        <v>1.0780000000000001</v>
+        <v>1.1574</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6737,10 +6737,10 @@
         <v>2022</v>
       </c>
       <c r="C454" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D454" s="3">
-        <v>1.2148000000000001</v>
+        <v>1.1416999999999999</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6751,10 +6751,10 @@
         <v>2022</v>
       </c>
       <c r="C455" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D455" s="3">
-        <v>1.1067</v>
+        <v>1.2119</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6762,13 +6762,13 @@
         <v>9</v>
       </c>
       <c r="B456" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C456" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D456" s="3">
-        <v>1.1968000000000001</v>
+        <v>1.1833</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6776,13 +6776,13 @@
         <v>9</v>
       </c>
       <c r="B457" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C457" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D457" s="3">
-        <v>1.032</v>
+        <v>1.2625</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6790,13 +6790,13 @@
         <v>9</v>
       </c>
       <c r="B458" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C458" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D458" s="3">
-        <v>1.0803</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6804,13 +6804,13 @@
         <v>9</v>
       </c>
       <c r="B459" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C459" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D459" s="3">
-        <v>1.1644000000000001</v>
+        <v>1.2148000000000001</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6818,13 +6818,13 @@
         <v>9</v>
       </c>
       <c r="B460" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C460" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D460" s="3">
-        <v>1.2673000000000001</v>
+        <v>1.1067</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6835,10 +6835,10 @@
         <v>2023</v>
       </c>
       <c r="C461" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D461" s="3">
-        <v>1.1983999999999999</v>
+        <v>1.1968000000000001</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6849,10 +6849,10 @@
         <v>2023</v>
       </c>
       <c r="C462" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D462" s="3">
-        <v>1.3575999999999999</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6863,10 +6863,10 @@
         <v>2023</v>
       </c>
       <c r="C463" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D463" s="3">
-        <v>1.3444</v>
+        <v>1.0803</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6877,10 +6877,10 @@
         <v>2023</v>
       </c>
       <c r="C464" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D464" s="3">
-        <v>1.2949999999999999</v>
+        <v>1.1644000000000001</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6891,10 +6891,10 @@
         <v>2023</v>
       </c>
       <c r="C465" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D465" s="3">
-        <v>1.2145999999999999</v>
+        <v>1.2673000000000001</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6905,10 +6905,10 @@
         <v>2023</v>
       </c>
       <c r="C466" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D466" s="3">
-        <v>1.2192000000000001</v>
+        <v>1.1983999999999999</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6919,10 +6919,10 @@
         <v>2023</v>
       </c>
       <c r="C467" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D467" s="3">
-        <v>1.3759999999999999</v>
+        <v>1.3575999999999999</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6930,13 +6930,13 @@
         <v>9</v>
       </c>
       <c r="B468" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C468" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D468" s="3">
-        <v>1.3194999999999999</v>
+        <v>1.3444</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6944,13 +6944,13 @@
         <v>9</v>
       </c>
       <c r="B469" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C469" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D469" s="3">
-        <v>1.4132</v>
+        <v>1.2949999999999999</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -6958,13 +6958,13 @@
         <v>9</v>
       </c>
       <c r="B470" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C470" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D470" s="3">
-        <v>1.6296000000000002</v>
+        <v>1.2145999999999999</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -6972,13 +6972,13 @@
         <v>9</v>
       </c>
       <c r="B471" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C471" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D471" s="3">
-        <v>1.4339</v>
+        <v>1.2192000000000001</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -6986,13 +6986,13 @@
         <v>9</v>
       </c>
       <c r="B472" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C472" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D472" s="3">
-        <v>1.2652000000000001</v>
+        <v>1.3759999999999999</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7003,10 +7003,10 @@
         <v>2024</v>
       </c>
       <c r="C473" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D473" s="3">
-        <v>1.4533</v>
+        <v>1.3194999999999999</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7017,10 +7017,10 @@
         <v>2024</v>
       </c>
       <c r="C474" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D474" s="3">
-        <v>1.3996999999999999</v>
+        <v>1.4132</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -7031,10 +7031,10 @@
         <v>2024</v>
       </c>
       <c r="C475" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D475" s="3">
-        <v>1.2509999999999999</v>
+        <v>1.6296000000000002</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7045,10 +7045,10 @@
         <v>2024</v>
       </c>
       <c r="C476" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D476" s="3">
-        <v>1.2806999999999999</v>
+        <v>1.4339</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7059,10 +7059,10 @@
         <v>2024</v>
       </c>
       <c r="C477" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D477" s="3">
-        <v>1.2095</v>
+        <v>1.2652000000000001</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7073,10 +7073,10 @@
         <v>2024</v>
       </c>
       <c r="C478" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D478" s="3">
-        <v>1.2222999999999999</v>
+        <v>1.4533</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7087,10 +7087,10 @@
         <v>2024</v>
       </c>
       <c r="C479" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D479" s="3">
-        <v>1.2697000000000001</v>
+        <v>1.3996999999999999</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7098,13 +7098,13 @@
         <v>9</v>
       </c>
       <c r="B480" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C480" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D480" s="3">
-        <v>1.1957</v>
+        <v>1.2509999999999999</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7112,13 +7112,13 @@
         <v>9</v>
       </c>
       <c r="B481" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C481" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D481" s="3">
-        <v>1.5154999999999998</v>
+        <v>1.2806999999999999</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7126,13 +7126,13 @@
         <v>9</v>
       </c>
       <c r="B482" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C482" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D482" s="3">
-        <v>1.2657</v>
+        <v>1.2095</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7140,13 +7140,13 @@
         <v>9</v>
       </c>
       <c r="B483" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C483" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D483" s="3">
-        <v>1.2907999999999999</v>
+        <v>1.2222999999999999</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7154,13 +7154,13 @@
         <v>9</v>
       </c>
       <c r="B484" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C484" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D484" s="3">
-        <v>1.2582</v>
+        <v>1.2697000000000001</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7171,10 +7171,10 @@
         <v>2025</v>
       </c>
       <c r="C485" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D485" s="3">
-        <v>1.3306</v>
+        <v>1.1957</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7185,10 +7185,10 @@
         <v>2025</v>
       </c>
       <c r="C486" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D486" s="3">
-        <v>1.4423999999999999</v>
+        <v>1.5154999999999998</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7199,10 +7199,10 @@
         <v>2025</v>
       </c>
       <c r="C487" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D487" s="3">
-        <v>1.3319000000000001</v>
+        <v>1.2657</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7213,10 +7213,10 @@
         <v>2025</v>
       </c>
       <c r="C488" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D488" s="3">
-        <v>1.3214999999999999</v>
+        <v>1.2907999999999999</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7227,10 +7227,10 @@
         <v>2025</v>
       </c>
       <c r="C489" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D489" s="3">
-        <v>1.4823</v>
+        <v>1.2582</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7241,10 +7241,10 @@
         <v>2025</v>
       </c>
       <c r="C490" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D490" s="3">
-        <v>1.3943000000000001</v>
+        <v>1.3306</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7255,10 +7255,10 @@
         <v>2025</v>
       </c>
       <c r="C491" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D491" s="3">
-        <v>1.4936999999999998</v>
+        <v>1.4423999999999999</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7266,13 +7266,13 @@
         <v>9</v>
       </c>
       <c r="B492" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C492" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D492" s="3">
-        <v>1.6705000000000001</v>
+        <v>1.3319000000000001</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7280,13 +7280,13 @@
         <v>9</v>
       </c>
       <c r="B493" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C493" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D493" s="3">
-        <v>1.5677000000000001</v>
+        <v>1.3214999999999999</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7294,13 +7294,13 @@
         <v>9</v>
       </c>
       <c r="B494" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C494" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D494" s="3">
-        <v>1.5706999999999998</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7308,13 +7308,13 @@
         <v>9</v>
       </c>
       <c r="B495" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C495" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D495" s="3">
-        <v>1.6088</v>
+        <v>1.3943000000000001</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7322,13 +7322,13 @@
         <v>9</v>
       </c>
       <c r="B496" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C496" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D496" s="3">
-        <v>1.5682</v>
+        <v>1.4936999999999998</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7339,94 +7339,94 @@
         <v>2026</v>
       </c>
       <c r="C497" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D497" s="3">
-        <v>1.7074</v>
+        <v>1.6705000000000001</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B498" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C498" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D498" s="3">
-        <v>1.8255999999999999</v>
+        <v>1.5677000000000001</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B499" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C499" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D499" s="3">
-        <v>2.1966999999999999</v>
+        <v>1.5706999999999998</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B500" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C500" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D500" s="3">
-        <v>0.69</v>
+        <v>1.6088</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B501" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C501" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D501" s="3">
-        <v>2.2656000000000001</v>
+        <v>1.5774000000000001</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B502" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C502" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D502" s="3">
-        <v>2.3290999999999999</v>
+        <v>1.7053</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B503" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C503" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D503" s="3">
-        <v>1.9074</v>
+        <v>1.6214999999999999</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7437,10 +7437,10 @@
         <v>2019</v>
       </c>
       <c r="C504" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D504" s="3">
-        <v>1.6099000000000001</v>
+        <v>1.8255999999999999</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7448,13 +7448,13 @@
         <v>10</v>
       </c>
       <c r="B505" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C505" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D505" s="3">
-        <v>1.2122999999999999</v>
+        <v>2.1966999999999999</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7462,13 +7462,13 @@
         <v>10</v>
       </c>
       <c r="B506" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C506" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D506" s="3">
-        <v>1.2574000000000001</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7476,13 +7476,13 @@
         <v>10</v>
       </c>
       <c r="B507" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C507" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D507" s="3">
-        <v>1.0529999999999999</v>
+        <v>2.2656000000000001</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7490,13 +7490,13 @@
         <v>10</v>
       </c>
       <c r="B508" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C508" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D508" s="3">
-        <v>1.3588</v>
+        <v>2.3290999999999999</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7504,13 +7504,13 @@
         <v>10</v>
       </c>
       <c r="B509" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C509" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D509" s="3">
-        <v>1.9334999999999998</v>
+        <v>1.9074</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7518,13 +7518,13 @@
         <v>10</v>
       </c>
       <c r="B510" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C510" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D510" s="3">
-        <v>1.3191999999999997</v>
+        <v>1.6099000000000001</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7535,10 +7535,10 @@
         <v>2020</v>
       </c>
       <c r="C511" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D511" s="3">
-        <v>1.8477000000000001</v>
+        <v>1.2122999999999999</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7549,10 +7549,10 @@
         <v>2020</v>
       </c>
       <c r="C512" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D512" s="3">
-        <v>1.6833</v>
+        <v>1.2574000000000001</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7563,10 +7563,10 @@
         <v>2020</v>
       </c>
       <c r="C513" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D513" s="3">
-        <v>1.6319999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -7577,10 +7577,10 @@
         <v>2020</v>
       </c>
       <c r="C514" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D514" s="3">
-        <v>2.4281999999999999</v>
+        <v>1.3588</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7591,10 +7591,10 @@
         <v>2020</v>
       </c>
       <c r="C515" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D515" s="3">
-        <v>2.7423999999999999</v>
+        <v>1.9374</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7602,13 +7602,13 @@
         <v>10</v>
       </c>
       <c r="B516" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C516" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D516" s="3">
-        <v>1.9238999999999999</v>
+        <v>1.3191999999999997</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7616,13 +7616,13 @@
         <v>10</v>
       </c>
       <c r="B517" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C517" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D517" s="3">
-        <v>1.8746</v>
+        <v>1.8477000000000001</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7630,13 +7630,13 @@
         <v>10</v>
       </c>
       <c r="B518" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C518" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D518" s="3">
-        <v>2.1867999999999999</v>
+        <v>1.6833</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7644,13 +7644,13 @@
         <v>10</v>
       </c>
       <c r="B519" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C519" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D519" s="3">
-        <v>1.6684000000000003</v>
+        <v>1.6343000000000001</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7658,13 +7658,13 @@
         <v>10</v>
       </c>
       <c r="B520" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C520" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D520" s="3">
-        <v>1.8869</v>
+        <v>2.4281999999999999</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7672,13 +7672,13 @@
         <v>10</v>
       </c>
       <c r="B521" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C521" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D521" s="3">
-        <v>1.7607000000000002</v>
+        <v>2.7423999999999999</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7689,10 +7689,10 @@
         <v>2021</v>
       </c>
       <c r="C522" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D522" s="3">
-        <v>2.3298999999999999</v>
+        <v>1.9238999999999999</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7703,10 +7703,10 @@
         <v>2021</v>
       </c>
       <c r="C523" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D523" s="3">
-        <v>2.0569000000000002</v>
+        <v>1.8746</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7717,10 +7717,10 @@
         <v>2021</v>
       </c>
       <c r="C524" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D524" s="3">
-        <v>2.5038999999999998</v>
+        <v>2.1867999999999999</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7731,10 +7731,10 @@
         <v>2021</v>
       </c>
       <c r="C525" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D525" s="3">
-        <v>1.7151000000000001</v>
+        <v>1.6684000000000003</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7745,10 +7745,10 @@
         <v>2021</v>
       </c>
       <c r="C526" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D526" s="3">
-        <v>1.7589999999999999</v>
+        <v>1.8903000000000001</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7759,10 +7759,10 @@
         <v>2021</v>
       </c>
       <c r="C527" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D527" s="3">
-        <v>1.9400000000000002</v>
+        <v>1.7607000000000002</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -7770,13 +7770,13 @@
         <v>10</v>
       </c>
       <c r="B528" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C528" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D528" s="3">
-        <v>1.1923999999999999</v>
+        <v>2.3298999999999999</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7784,13 +7784,13 @@
         <v>10</v>
       </c>
       <c r="B529" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C529" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D529" s="3">
-        <v>1.5228999999999999</v>
+        <v>2.0569000000000002</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7798,13 +7798,13 @@
         <v>10</v>
       </c>
       <c r="B530" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C530" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D530" s="3">
-        <v>1.9296</v>
+        <v>2.5112000000000001</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7812,13 +7812,13 @@
         <v>10</v>
       </c>
       <c r="B531" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C531" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D531" s="3">
-        <v>1.5996999999999999</v>
+        <v>1.7177</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7826,13 +7826,13 @@
         <v>10</v>
       </c>
       <c r="B532" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C532" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D532" s="3">
-        <v>1.7376999999999998</v>
+        <v>1.7589999999999999</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7840,13 +7840,13 @@
         <v>10</v>
       </c>
       <c r="B533" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C533" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D533" s="3">
-        <v>1.6283000000000001</v>
+        <v>1.9400000000000002</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7857,10 +7857,10 @@
         <v>2022</v>
       </c>
       <c r="C534" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D534" s="3">
-        <v>1.6888000000000001</v>
+        <v>1.1923999999999999</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7871,10 +7871,10 @@
         <v>2022</v>
       </c>
       <c r="C535" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D535" s="3">
-        <v>1.7524</v>
+        <v>1.5228999999999999</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7885,10 +7885,10 @@
         <v>2022</v>
       </c>
       <c r="C536" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D536" s="3">
-        <v>1.8827</v>
+        <v>1.9296</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7899,10 +7899,10 @@
         <v>2022</v>
       </c>
       <c r="C537" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D537" s="3">
-        <v>1.52</v>
+        <v>1.5996999999999999</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7913,10 +7913,10 @@
         <v>2022</v>
       </c>
       <c r="C538" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D538" s="3">
-        <v>1.9222000000000001</v>
+        <v>1.7376999999999998</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7927,10 +7927,10 @@
         <v>2022</v>
       </c>
       <c r="C539" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D539" s="3">
-        <v>1.6540999999999999</v>
+        <v>1.6283000000000001</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -7938,13 +7938,13 @@
         <v>10</v>
       </c>
       <c r="B540" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C540" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D540" s="3">
-        <v>1.6717000000000002</v>
+        <v>1.6888000000000001</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -7952,13 +7952,13 @@
         <v>10</v>
       </c>
       <c r="B541" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C541" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D541" s="3">
-        <v>2.0114000000000001</v>
+        <v>1.7524</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -7966,13 +7966,13 @@
         <v>10</v>
       </c>
       <c r="B542" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C542" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D542" s="3">
-        <v>1.7808999999999999</v>
+        <v>1.8827</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -7980,13 +7980,13 @@
         <v>10</v>
       </c>
       <c r="B543" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C543" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D543" s="3">
-        <v>1.6915</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -7994,13 +7994,13 @@
         <v>10</v>
       </c>
       <c r="B544" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C544" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D544" s="3">
-        <v>1.8209</v>
+        <v>1.9222000000000001</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8008,13 +8008,13 @@
         <v>10</v>
       </c>
       <c r="B545" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C545" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D545" s="3">
-        <v>1.9435</v>
+        <v>1.6540999999999999</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8025,10 +8025,10 @@
         <v>2023</v>
       </c>
       <c r="C546" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D546" s="3">
-        <v>1.5912999999999999</v>
+        <v>1.6717000000000002</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8039,10 +8039,10 @@
         <v>2023</v>
       </c>
       <c r="C547" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D547" s="3">
-        <v>1.9621999999999999</v>
+        <v>2.0114000000000001</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8053,10 +8053,10 @@
         <v>2023</v>
       </c>
       <c r="C548" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D548" s="3">
-        <v>1.9907999999999999</v>
+        <v>1.7808999999999999</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8067,10 +8067,10 @@
         <v>2023</v>
       </c>
       <c r="C549" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D549" s="3">
-        <v>1.9017999999999999</v>
+        <v>1.6915</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8081,10 +8081,10 @@
         <v>2023</v>
       </c>
       <c r="C550" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D550" s="3">
-        <v>1.5719000000000001</v>
+        <v>1.8209</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8095,10 +8095,10 @@
         <v>2023</v>
       </c>
       <c r="C551" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D551" s="3">
-        <v>1.6617999999999999</v>
+        <v>1.9435</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8106,13 +8106,13 @@
         <v>10</v>
       </c>
       <c r="B552" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C552" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D552" s="3">
-        <v>1.9043000000000001</v>
+        <v>1.5912999999999999</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8120,13 +8120,13 @@
         <v>10</v>
       </c>
       <c r="B553" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C553" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D553" s="3">
-        <v>1.8562999999999998</v>
+        <v>1.9621999999999999</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8134,13 +8134,13 @@
         <v>10</v>
       </c>
       <c r="B554" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C554" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D554" s="3">
-        <v>1.6854</v>
+        <v>1.9907999999999999</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8148,13 +8148,13 @@
         <v>10</v>
       </c>
       <c r="B555" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C555" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D555" s="3">
-        <v>1.8065</v>
+        <v>1.9017999999999999</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8162,13 +8162,13 @@
         <v>10</v>
       </c>
       <c r="B556" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C556" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D556" s="3">
-        <v>1.7505999999999999</v>
+        <v>1.5719000000000001</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8176,13 +8176,13 @@
         <v>10</v>
       </c>
       <c r="B557" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C557" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D557" s="3">
-        <v>1.7563</v>
+        <v>1.6617999999999999</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8193,10 +8193,10 @@
         <v>2024</v>
       </c>
       <c r="C558" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D558" s="3">
-        <v>2.2259000000000002</v>
+        <v>1.9043000000000001</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8207,10 +8207,10 @@
         <v>2024</v>
       </c>
       <c r="C559" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D559" s="3">
-        <v>1.77</v>
+        <v>1.8562999999999998</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8221,10 +8221,10 @@
         <v>2024</v>
       </c>
       <c r="C560" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D560" s="3">
-        <v>1.8426999999999998</v>
+        <v>1.6854</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8235,10 +8235,10 @@
         <v>2024</v>
       </c>
       <c r="C561" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D561" s="3">
-        <v>1.8102</v>
+        <v>1.8065</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8249,10 +8249,10 @@
         <v>2024</v>
       </c>
       <c r="C562" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D562" s="3">
-        <v>1.7421</v>
+        <v>1.7505999999999999</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8263,10 +8263,10 @@
         <v>2024</v>
       </c>
       <c r="C563" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D563" s="3">
-        <v>1.6943999999999999</v>
+        <v>1.7563</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8274,13 +8274,13 @@
         <v>10</v>
       </c>
       <c r="B564" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C564" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D564" s="3">
-        <v>1.6221000000000001</v>
+        <v>2.2259000000000002</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8288,13 +8288,13 @@
         <v>10</v>
       </c>
       <c r="B565" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C565" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D565" s="3">
-        <v>1.7716000000000001</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8302,13 +8302,13 @@
         <v>10</v>
       </c>
       <c r="B566" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C566" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D566" s="3">
-        <v>1.7462</v>
+        <v>1.8426999999999998</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8316,13 +8316,13 @@
         <v>10</v>
       </c>
       <c r="B567" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C567" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D567" s="3">
-        <v>1.9338000000000002</v>
+        <v>1.8102</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8330,13 +8330,13 @@
         <v>10</v>
       </c>
       <c r="B568" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C568" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D568" s="3">
-        <v>1.9272</v>
+        <v>1.7421</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8344,13 +8344,13 @@
         <v>10</v>
       </c>
       <c r="B569" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C569" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D569" s="3">
-        <v>1.7902</v>
+        <v>1.6943999999999999</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8361,10 +8361,10 @@
         <v>2025</v>
       </c>
       <c r="C570" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D570" s="3">
-        <v>1.6876</v>
+        <v>1.6221000000000001</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8375,10 +8375,10 @@
         <v>2025</v>
       </c>
       <c r="C571" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D571" s="3">
-        <v>1.7938000000000001</v>
+        <v>1.7716000000000001</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8389,10 +8389,10 @@
         <v>2025</v>
       </c>
       <c r="C572" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D572" s="3">
-        <v>1.732</v>
+        <v>1.7462</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8403,10 +8403,10 @@
         <v>2025</v>
       </c>
       <c r="C573" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D573" s="3">
-        <v>1.925</v>
+        <v>1.9338000000000002</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8417,10 +8417,10 @@
         <v>2025</v>
       </c>
       <c r="C574" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D574" s="3">
-        <v>1.9413</v>
+        <v>1.9272</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8431,10 +8431,10 @@
         <v>2025</v>
       </c>
       <c r="C575" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D575" s="3">
-        <v>1.7350000000000001</v>
+        <v>1.7902</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8442,13 +8442,13 @@
         <v>10</v>
       </c>
       <c r="B576" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C576" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D576" s="3">
-        <v>1.6893</v>
+        <v>1.6876</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8456,13 +8456,13 @@
         <v>10</v>
       </c>
       <c r="B577" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C577" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D577" s="3">
-        <v>1.9579</v>
+        <v>1.7938000000000001</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8470,13 +8470,13 @@
         <v>10</v>
       </c>
       <c r="B578" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C578" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D578" s="3">
-        <v>1.5611999999999999</v>
+        <v>1.732</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8484,13 +8484,13 @@
         <v>10</v>
       </c>
       <c r="B579" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C579" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D579" s="3">
-        <v>1.6298000000000001</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8498,13 +8498,13 @@
         <v>10</v>
       </c>
       <c r="B580" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C580" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D580" s="3">
-        <v>1.7371000000000001</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8512,111 +8512,111 @@
         <v>10</v>
       </c>
       <c r="B581" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C581" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D581" s="3">
-        <v>2.0629</v>
+        <v>1.7350000000000001</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B582" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C582" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D582" s="3">
-        <v>0.59160000000000001</v>
+        <v>1.6893</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B583" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C583" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D583" s="3">
-        <v>0.71369999999999989</v>
+        <v>1.9579</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B584" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C584" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D584" s="3">
-        <v>1.4662999999999999</v>
+        <v>1.3545</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B585" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C585" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D585" s="3">
-        <v>0.70140000000000002</v>
+        <v>1.6024</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B586" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C586" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D586" s="3">
-        <v>1.8838999999999999</v>
+        <v>1.7356</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B587" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C587" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D587" s="3">
-        <v>1.2885</v>
+        <v>2.0179</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B588" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C588" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D588" s="3">
-        <v>0.97159999999999991</v>
+        <v>1.7312000000000003</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8627,10 +8627,10 @@
         <v>2019</v>
       </c>
       <c r="C589" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D589" s="3">
-        <v>0.59799999999999998</v>
+        <v>0.59160000000000001</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -8638,13 +8638,13 @@
         <v>11</v>
       </c>
       <c r="B590" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C590" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D590" s="3">
-        <v>0.80840000000000001</v>
+        <v>0.71369999999999989</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8652,13 +8652,13 @@
         <v>11</v>
       </c>
       <c r="B591" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C591" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D591" s="3">
-        <v>0.57899999999999996</v>
+        <v>1.4662999999999999</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8666,13 +8666,13 @@
         <v>11</v>
       </c>
       <c r="B592" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C592" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D592" s="3">
-        <v>1.1052999999999999</v>
+        <v>0.70140000000000002</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8680,13 +8680,13 @@
         <v>11</v>
       </c>
       <c r="B593" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C593" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D593" s="3">
-        <v>0.77580000000000005</v>
+        <v>1.8838999999999999</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8694,13 +8694,13 @@
         <v>11</v>
       </c>
       <c r="B594" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C594" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D594" s="3">
-        <v>1.0531999999999999</v>
+        <v>1.2885</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8708,13 +8708,13 @@
         <v>11</v>
       </c>
       <c r="B595" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C595" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D595" s="3">
-        <v>1.0923</v>
+        <v>0.97159999999999991</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8722,13 +8722,13 @@
         <v>11</v>
       </c>
       <c r="B596" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C596" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D596" s="3">
-        <v>1.2737000000000001</v>
+        <v>0.59799999999999998</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8739,10 +8739,10 @@
         <v>2020</v>
       </c>
       <c r="C597" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D597" s="3">
-        <v>1.3653</v>
+        <v>0.80840000000000001</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8753,10 +8753,10 @@
         <v>2020</v>
       </c>
       <c r="C598" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D598" s="3">
-        <v>1.1208</v>
+        <v>0.57899999999999996</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8767,10 +8767,10 @@
         <v>2020</v>
       </c>
       <c r="C599" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D599" s="3">
-        <v>1.5089999999999999</v>
+        <v>1.1052999999999999</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8781,10 +8781,10 @@
         <v>2020</v>
       </c>
       <c r="C600" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D600" s="3">
-        <v>1.2372000000000001</v>
+        <v>0.77580000000000005</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8795,10 +8795,10 @@
         <v>2020</v>
       </c>
       <c r="C601" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D601" s="3">
-        <v>1.0697000000000001</v>
+        <v>1.0531999999999999</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8806,13 +8806,13 @@
         <v>11</v>
       </c>
       <c r="B602" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C602" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D602" s="3">
-        <v>1.2366999999999999</v>
+        <v>1.0923</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8820,13 +8820,13 @@
         <v>11</v>
       </c>
       <c r="B603" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C603" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D603" s="3">
-        <v>1.1274</v>
+        <v>1.2737000000000001</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8834,13 +8834,13 @@
         <v>11</v>
       </c>
       <c r="B604" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C604" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D604" s="3">
-        <v>1.3996</v>
+        <v>1.3653</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8848,13 +8848,13 @@
         <v>11</v>
       </c>
       <c r="B605" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C605" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D605" s="3">
-        <v>1.2915000000000001</v>
+        <v>1.1208</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8862,13 +8862,13 @@
         <v>11</v>
       </c>
       <c r="B606" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C606" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D606" s="3">
-        <v>1.218</v>
+        <v>1.5089999999999999</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8876,13 +8876,13 @@
         <v>11</v>
       </c>
       <c r="B607" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C607" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D607" s="3">
-        <v>1.3958999999999999</v>
+        <v>1.2372000000000001</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8890,13 +8890,13 @@
         <v>11</v>
       </c>
       <c r="B608" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C608" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D608" s="3">
-        <v>1.5745000000000002</v>
+        <v>1.0697000000000001</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8907,10 +8907,10 @@
         <v>2021</v>
       </c>
       <c r="C609" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D609" s="3">
-        <v>1.3656999999999999</v>
+        <v>1.2366999999999999</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8921,10 +8921,10 @@
         <v>2021</v>
       </c>
       <c r="C610" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D610" s="3">
-        <v>1.1288</v>
+        <v>1.1274</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -8935,10 +8935,10 @@
         <v>2021</v>
       </c>
       <c r="C611" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D611" s="3">
-        <v>0.96220000000000006</v>
+        <v>1.3996</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -8949,10 +8949,10 @@
         <v>2021</v>
       </c>
       <c r="C612" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D612" s="3">
-        <v>0.94979999999999998</v>
+        <v>1.2915000000000001</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -8963,10 +8963,10 @@
         <v>2021</v>
       </c>
       <c r="C613" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D613" s="3">
-        <v>1.1982999999999999</v>
+        <v>1.218</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -8974,13 +8974,13 @@
         <v>11</v>
       </c>
       <c r="B614" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C614" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D614" s="3">
-        <v>1.0469999999999999</v>
+        <v>1.3958999999999999</v>
       </c>
     </row>
     <row r="615" spans="1:4">
@@ -8988,13 +8988,13 @@
         <v>11</v>
       </c>
       <c r="B615" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C615" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D615" s="3">
-        <v>0.84160000000000001</v>
+        <v>1.5745000000000002</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9002,13 +9002,13 @@
         <v>11</v>
       </c>
       <c r="B616" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C616" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D616" s="3">
-        <v>0.85270000000000001</v>
+        <v>1.3656999999999999</v>
       </c>
     </row>
     <row r="617" spans="1:4">
@@ -9016,13 +9016,13 @@
         <v>11</v>
       </c>
       <c r="B617" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C617" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D617" s="3">
-        <v>0.65920000000000001</v>
+        <v>1.1288</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9030,13 +9030,13 @@
         <v>11</v>
       </c>
       <c r="B618" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C618" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D618" s="3">
-        <v>0.91259999999999997</v>
+        <v>0.96130000000000015</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9044,13 +9044,13 @@
         <v>11</v>
       </c>
       <c r="B619" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C619" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D619" s="3">
-        <v>0.68140000000000001</v>
+        <v>0.94979999999999998</v>
       </c>
     </row>
     <row r="620" spans="1:4">
@@ -9058,13 +9058,13 @@
         <v>11</v>
       </c>
       <c r="B620" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C620" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D620" s="3">
-        <v>0.69020000000000004</v>
+        <v>1.1982999999999999</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9075,10 +9075,10 @@
         <v>2022</v>
       </c>
       <c r="C621" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D621" s="3">
-        <v>0.83509999999999995</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9089,10 +9089,10 @@
         <v>2022</v>
       </c>
       <c r="C622" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D622" s="3">
-        <v>0.8459000000000001</v>
+        <v>0.84160000000000001</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9103,10 +9103,10 @@
         <v>2022</v>
       </c>
       <c r="C623" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D623" s="3">
-        <v>1.0476000000000001</v>
+        <v>0.85270000000000001</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9117,10 +9117,10 @@
         <v>2022</v>
       </c>
       <c r="C624" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D624" s="3">
-        <v>0.93159999999999998</v>
+        <v>0.65920000000000001</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -9131,10 +9131,10 @@
         <v>2022</v>
       </c>
       <c r="C625" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D625" s="3">
-        <v>0.60189999999999999</v>
+        <v>0.91259999999999997</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -9142,13 +9142,13 @@
         <v>11</v>
       </c>
       <c r="B626" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C626" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D626" s="3">
-        <v>0.70330000000000004</v>
+        <v>0.68140000000000001</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -9156,13 +9156,13 @@
         <v>11</v>
       </c>
       <c r="B627" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C627" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D627" s="3">
-        <v>0.68169999999999997</v>
+        <v>0.69020000000000004</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -9170,13 +9170,13 @@
         <v>11</v>
       </c>
       <c r="B628" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C628" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D628" s="3">
-        <v>0.6391</v>
+        <v>0.83509999999999995</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -9184,13 +9184,13 @@
         <v>11</v>
       </c>
       <c r="B629" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C629" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D629" s="3">
-        <v>0.72650000000000003</v>
+        <v>0.8459000000000001</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -9198,13 +9198,13 @@
         <v>11</v>
       </c>
       <c r="B630" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C630" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D630" s="3">
-        <v>0.76770000000000005</v>
+        <v>1.0476000000000001</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -9212,13 +9212,13 @@
         <v>11</v>
       </c>
       <c r="B631" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C631" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D631" s="3">
-        <v>0.64570000000000005</v>
+        <v>0.93159999999999998</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -9226,13 +9226,13 @@
         <v>11</v>
       </c>
       <c r="B632" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C632" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D632" s="3">
-        <v>0.60250000000000004</v>
+        <v>0.60189999999999999</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -9243,10 +9243,10 @@
         <v>2023</v>
       </c>
       <c r="C633" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D633" s="3">
-        <v>1.3164</v>
+        <v>0.70330000000000004</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -9257,10 +9257,10 @@
         <v>2023</v>
       </c>
       <c r="C634" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D634" s="3">
-        <v>1.054</v>
+        <v>0.68169999999999997</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -9271,10 +9271,10 @@
         <v>2023</v>
       </c>
       <c r="C635" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D635" s="3">
-        <v>1.1778</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="636" spans="1:4">
@@ -9285,10 +9285,10 @@
         <v>2023</v>
       </c>
       <c r="C636" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D636" s="3">
-        <v>1.3501000000000001</v>
+        <v>0.72650000000000003</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -9299,10 +9299,10 @@
         <v>2023</v>
       </c>
       <c r="C637" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D637" s="3">
-        <v>1.1941999999999999</v>
+        <v>0.76770000000000005</v>
       </c>
     </row>
     <row r="638" spans="1:4">
@@ -9310,13 +9310,13 @@
         <v>11</v>
       </c>
       <c r="B638" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C638" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D638" s="3">
-        <v>1.1995</v>
+        <v>0.64570000000000005</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -9324,13 +9324,13 @@
         <v>11</v>
       </c>
       <c r="B639" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C639" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D639" s="3">
-        <v>1.2528000000000001</v>
+        <v>0.60250000000000004</v>
       </c>
     </row>
     <row r="640" spans="1:4">
@@ -9338,13 +9338,13 @@
         <v>11</v>
       </c>
       <c r="B640" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C640" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D640" s="3">
-        <v>1.2377</v>
+        <v>1.3164</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9352,13 +9352,13 @@
         <v>11</v>
       </c>
       <c r="B641" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C641" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D641" s="3">
-        <v>1.0448</v>
+        <v>1.054</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9366,13 +9366,13 @@
         <v>11</v>
       </c>
       <c r="B642" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C642" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D642" s="3">
-        <v>1.1088</v>
+        <v>1.1778</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9380,13 +9380,13 @@
         <v>11</v>
       </c>
       <c r="B643" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C643" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D643" s="3">
-        <v>1.1704000000000001</v>
+        <v>1.3501000000000001</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9394,13 +9394,13 @@
         <v>11</v>
       </c>
       <c r="B644" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C644" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D644" s="3">
-        <v>1.335</v>
+        <v>1.1941999999999999</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9411,10 +9411,10 @@
         <v>2024</v>
       </c>
       <c r="C645" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D645" s="3">
-        <v>1.2101999999999999</v>
+        <v>1.1995</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9425,10 +9425,10 @@
         <v>2024</v>
       </c>
       <c r="C646" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D646" s="3">
-        <v>1.2007000000000001</v>
+        <v>1.2528000000000001</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9439,10 +9439,10 @@
         <v>2024</v>
       </c>
       <c r="C647" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D647" s="3">
-        <v>1.2133</v>
+        <v>1.2377</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9453,10 +9453,10 @@
         <v>2024</v>
       </c>
       <c r="C648" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D648" s="3">
-        <v>0.85850000000000004</v>
+        <v>1.0448</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9467,10 +9467,10 @@
         <v>2024</v>
       </c>
       <c r="C649" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D649" s="3">
-        <v>1.1714</v>
+        <v>1.1088</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9478,13 +9478,13 @@
         <v>11</v>
       </c>
       <c r="B650" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C650" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D650" s="3">
-        <v>0.94820000000000004</v>
+        <v>1.1704000000000001</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9492,13 +9492,13 @@
         <v>11</v>
       </c>
       <c r="B651" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C651" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D651" s="3">
-        <v>0.94499999999999995</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9506,13 +9506,13 @@
         <v>11</v>
       </c>
       <c r="B652" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C652" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D652" s="3">
-        <v>1.0746</v>
+        <v>1.2101999999999999</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9520,13 +9520,13 @@
         <v>11</v>
       </c>
       <c r="B653" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C653" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D653" s="3">
-        <v>1.1345000000000001</v>
+        <v>1.2007000000000001</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9534,13 +9534,13 @@
         <v>11</v>
       </c>
       <c r="B654" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C654" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D654" s="3">
-        <v>0.96009999999999995</v>
+        <v>1.2133</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9548,13 +9548,13 @@
         <v>11</v>
       </c>
       <c r="B655" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C655" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D655" s="3">
-        <v>1.0189999999999999</v>
+        <v>0.85850000000000004</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9562,13 +9562,13 @@
         <v>11</v>
       </c>
       <c r="B656" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C656" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D656" s="3">
-        <v>1.0889</v>
+        <v>1.1714</v>
       </c>
     </row>
     <row r="657" spans="1:4">
@@ -9579,10 +9579,10 @@
         <v>2025</v>
       </c>
       <c r="C657" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D657" s="3">
-        <v>1.0328999999999999</v>
+        <v>0.94820000000000004</v>
       </c>
     </row>
     <row r="658" spans="1:4">
@@ -9593,10 +9593,10 @@
         <v>2025</v>
       </c>
       <c r="C658" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D658" s="3">
-        <v>1.0566</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="659" spans="1:4">
@@ -9607,10 +9607,10 @@
         <v>2025</v>
       </c>
       <c r="C659" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D659" s="3">
-        <v>1.0752999999999999</v>
+        <v>1.0746</v>
       </c>
     </row>
     <row r="660" spans="1:4">
@@ -9621,10 +9621,10 @@
         <v>2025</v>
       </c>
       <c r="C660" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D660" s="3">
-        <v>0.91410000000000002</v>
+        <v>1.1345000000000001</v>
       </c>
     </row>
     <row r="661" spans="1:4">
@@ -9635,10 +9635,10 @@
         <v>2025</v>
       </c>
       <c r="C661" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D661" s="3">
-        <v>1.083</v>
+        <v>0.96009999999999995</v>
       </c>
     </row>
     <row r="662" spans="1:4">
@@ -9646,13 +9646,13 @@
         <v>11</v>
       </c>
       <c r="B662" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C662" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D662" s="3">
-        <v>1.0168999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="663" spans="1:4">
@@ -9660,13 +9660,13 @@
         <v>11</v>
       </c>
       <c r="B663" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C663" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D663" s="3">
-        <v>0.9335</v>
+        <v>1.0889</v>
       </c>
     </row>
     <row r="664" spans="1:4">
@@ -9674,13 +9674,13 @@
         <v>11</v>
       </c>
       <c r="B664" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C664" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D664" s="3">
-        <v>0.96539999999999992</v>
+        <v>1.0328999999999999</v>
       </c>
     </row>
     <row r="665" spans="1:4">
@@ -9688,13 +9688,13 @@
         <v>11</v>
       </c>
       <c r="B665" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C665" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D665" s="3">
-        <v>0.9587</v>
+        <v>1.0566</v>
       </c>
     </row>
     <row r="666" spans="1:4">
@@ -9702,13 +9702,13 @@
         <v>11</v>
       </c>
       <c r="B666" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C666" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D666" s="3">
-        <v>1.1483000000000001</v>
+        <v>1.0752999999999999</v>
       </c>
     </row>
     <row r="667" spans="1:4">
@@ -9716,125 +9716,125 @@
         <v>11</v>
       </c>
       <c r="B667" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C667" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D667" s="3">
-        <v>1.2275</v>
+        <v>0.91410000000000002</v>
       </c>
     </row>
     <row r="668" spans="1:4">
       <c r="A668" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B668" s="2">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="C668" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D668" s="3">
-        <v>0.62870000000000004</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="669" spans="1:4">
       <c r="A669" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B669" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C669" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D669" s="3">
-        <v>0.97070000000000001</v>
+        <v>1.0168999999999999</v>
       </c>
     </row>
     <row r="670" spans="1:4">
       <c r="A670" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B670" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C670" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D670" s="3">
-        <v>0.71419999999999995</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="671" spans="1:4">
       <c r="A671" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B671" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C671" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D671" s="3">
-        <v>0.60429999999999995</v>
+        <v>0.98060000000000003</v>
       </c>
     </row>
     <row r="672" spans="1:4">
       <c r="A672" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B672" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C672" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D672" s="3">
-        <v>0.87819999999999998</v>
+        <v>0.95650000000000002</v>
       </c>
     </row>
     <row r="673" spans="1:4">
       <c r="A673" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B673" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C673" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D673" s="3">
-        <v>0.97710000000000008</v>
+        <v>1.2233000000000001</v>
       </c>
     </row>
     <row r="674" spans="1:4">
       <c r="A674" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B674" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C674" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D674" s="3">
-        <v>0.78180000000000005</v>
+        <v>1.2374000000000001</v>
       </c>
     </row>
     <row r="675" spans="1:4">
       <c r="A675" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B675" s="2">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="C675" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D675" s="3">
-        <v>0.88280000000000003</v>
+        <v>1.2229000000000001</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -9842,13 +9842,13 @@
         <v>12</v>
       </c>
       <c r="B676" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C676" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D676" s="3">
-        <v>0.84150000000000003</v>
+        <v>0.62870000000000004</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -9856,13 +9856,13 @@
         <v>12</v>
       </c>
       <c r="B677" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C677" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D677" s="3">
-        <v>3.6991000000000001</v>
+        <v>0.97070000000000001</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -9870,13 +9870,13 @@
         <v>12</v>
       </c>
       <c r="B678" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C678" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D678" s="3">
-        <v>0.63649999999999995</v>
+        <v>0.71419999999999995</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -9884,13 +9884,13 @@
         <v>12</v>
       </c>
       <c r="B679" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C679" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D679" s="3">
-        <v>0.63870000000000005</v>
+        <v>0.60429999999999995</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -9898,13 +9898,13 @@
         <v>12</v>
       </c>
       <c r="B680" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C680" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D680" s="3">
-        <v>0.58840000000000003</v>
+        <v>0.87819999999999998</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -9912,13 +9912,13 @@
         <v>12</v>
       </c>
       <c r="B681" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C681" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D681" s="3">
-        <v>0.83720000000000006</v>
+        <v>0.97710000000000008</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -9926,13 +9926,13 @@
         <v>12</v>
       </c>
       <c r="B682" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C682" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D682" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.78180000000000005</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -9940,13 +9940,13 @@
         <v>12</v>
       </c>
       <c r="B683" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C683" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D683" s="3">
-        <v>0.75119999999999998</v>
+        <v>0.88280000000000003</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -9957,10 +9957,10 @@
         <v>2020</v>
       </c>
       <c r="C684" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D684" s="3">
-        <v>0.76349999999999996</v>
+        <v>0.84150000000000003</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -9971,10 +9971,10 @@
         <v>2020</v>
       </c>
       <c r="C685" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D685" s="3">
-        <v>0.80579999999999996</v>
+        <v>3.6991000000000001</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -9985,10 +9985,10 @@
         <v>2020</v>
       </c>
       <c r="C686" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D686" s="3">
-        <v>0.75339999999999996</v>
+        <v>0.63649999999999995</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -9996,13 +9996,13 @@
         <v>12</v>
       </c>
       <c r="B687" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C687" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D687" s="3">
-        <v>0.83040000000000003</v>
+        <v>0.63870000000000005</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -10010,13 +10010,13 @@
         <v>12</v>
       </c>
       <c r="B688" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C688" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D688" s="3">
-        <v>0.85129999999999995</v>
+        <v>0.58840000000000003</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -10024,13 +10024,13 @@
         <v>12</v>
       </c>
       <c r="B689" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C689" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D689" s="3">
-        <v>0.8536999999999999</v>
+        <v>0.83720000000000006</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -10038,13 +10038,13 @@
         <v>12</v>
       </c>
       <c r="B690" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C690" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D690" s="3">
-        <v>0.93080000000000007</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -10052,13 +10052,13 @@
         <v>12</v>
       </c>
       <c r="B691" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C691" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D691" s="3">
-        <v>0.8980999999999999</v>
+        <v>0.75119999999999998</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -10066,13 +10066,13 @@
         <v>12</v>
       </c>
       <c r="B692" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C692" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D692" s="3">
-        <v>0.88049999999999984</v>
+        <v>0.76349999999999996</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -10080,13 +10080,13 @@
         <v>12</v>
       </c>
       <c r="B693" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C693" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D693" s="3">
-        <v>0.89779999999999993</v>
+        <v>0.80579999999999996</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -10094,13 +10094,13 @@
         <v>12</v>
       </c>
       <c r="B694" s="2">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C694" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D694" s="3">
-        <v>0.94299999999999995</v>
+        <v>0.75339999999999996</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -10111,10 +10111,10 @@
         <v>2021</v>
       </c>
       <c r="C695" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D695" s="3">
-        <v>0.87270000000000014</v>
+        <v>0.83040000000000003</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -10125,10 +10125,10 @@
         <v>2021</v>
       </c>
       <c r="C696" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D696" s="3">
-        <v>0.89249999999999985</v>
+        <v>0.85129999999999995</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -10139,10 +10139,10 @@
         <v>2021</v>
       </c>
       <c r="C697" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D697" s="3">
-        <v>0.90710000000000002</v>
+        <v>0.8536999999999999</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -10153,10 +10153,10 @@
         <v>2021</v>
       </c>
       <c r="C698" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D698" s="3">
-        <v>0.80330000000000001</v>
+        <v>0.93080000000000007</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -10164,13 +10164,13 @@
         <v>12</v>
       </c>
       <c r="B699" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C699" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D699" s="3">
-        <v>0.7107</v>
+        <v>0.8980999999999999</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -10178,13 +10178,13 @@
         <v>12</v>
       </c>
       <c r="B700" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C700" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D700" s="3">
-        <v>0.78610000000000002</v>
+        <v>0.88049999999999984</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -10192,13 +10192,13 @@
         <v>12</v>
       </c>
       <c r="B701" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C701" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D701" s="3">
-        <v>0.83389999999999997</v>
+        <v>0.89779999999999993</v>
       </c>
     </row>
     <row r="702" spans="1:4">
@@ -10206,13 +10206,13 @@
         <v>12</v>
       </c>
       <c r="B702" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C702" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D702" s="3">
-        <v>0.88970000000000005</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -10220,13 +10220,13 @@
         <v>12</v>
       </c>
       <c r="B703" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C703" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D703" s="3">
-        <v>0.83260000000000001</v>
+        <v>0.87270000000000014</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -10234,13 +10234,13 @@
         <v>12</v>
       </c>
       <c r="B704" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C704" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D704" s="3">
-        <v>0.84299999999999997</v>
+        <v>0.89249999999999985</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -10248,13 +10248,13 @@
         <v>12</v>
       </c>
       <c r="B705" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C705" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D705" s="3">
-        <v>0.90830000000000011</v>
+        <v>0.90710000000000002</v>
       </c>
     </row>
     <row r="706" spans="1:4">
@@ -10262,13 +10262,13 @@
         <v>12</v>
       </c>
       <c r="B706" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C706" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D706" s="3">
-        <v>0.80479999999999996</v>
+        <v>0.80330000000000001</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -10279,10 +10279,10 @@
         <v>2022</v>
       </c>
       <c r="C707" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D707" s="3">
-        <v>0.77749999999999997</v>
+        <v>0.7107</v>
       </c>
     </row>
     <row r="708" spans="1:4">
@@ -10293,10 +10293,10 @@
         <v>2022</v>
       </c>
       <c r="C708" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D708" s="3">
-        <v>0.81069999999999998</v>
+        <v>0.78610000000000002</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -10307,10 +10307,10 @@
         <v>2022</v>
       </c>
       <c r="C709" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D709" s="3">
-        <v>0.87409999999999999</v>
+        <v>0.83389999999999997</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -10321,10 +10321,10 @@
         <v>2022</v>
       </c>
       <c r="C710" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D710" s="3">
-        <v>0.86129999999999984</v>
+        <v>0.88970000000000005</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -10332,13 +10332,13 @@
         <v>12</v>
       </c>
       <c r="B711" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C711" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D711" s="3">
-        <v>0.78390000000000004</v>
+        <v>0.83260000000000001</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -10346,13 +10346,13 @@
         <v>12</v>
       </c>
       <c r="B712" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C712" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D712" s="3">
-        <v>0.84170000000000011</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -10360,13 +10360,13 @@
         <v>12</v>
       </c>
       <c r="B713" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C713" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D713" s="3">
-        <v>0.80769999999999986</v>
+        <v>0.90830000000000011</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -10374,13 +10374,13 @@
         <v>12</v>
       </c>
       <c r="B714" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C714" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D714" s="3">
-        <v>0.90670000000000006</v>
+        <v>0.80479999999999996</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -10388,13 +10388,13 @@
         <v>12</v>
       </c>
       <c r="B715" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C715" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D715" s="3">
-        <v>0.82020000000000004</v>
+        <v>0.77749999999999997</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -10402,13 +10402,13 @@
         <v>12</v>
       </c>
       <c r="B716" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C716" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D716" s="3">
-        <v>0.81120000000000014</v>
+        <v>0.81069999999999998</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -10416,13 +10416,13 @@
         <v>12</v>
       </c>
       <c r="B717" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C717" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D717" s="3">
-        <v>0.85009999999999997</v>
+        <v>0.87409999999999999</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -10430,13 +10430,13 @@
         <v>12</v>
       </c>
       <c r="B718" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C718" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D718" s="3">
-        <v>0.8327</v>
+        <v>0.86129999999999984</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -10447,10 +10447,10 @@
         <v>2023</v>
       </c>
       <c r="C719" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D719" s="3">
-        <v>0.90250000000000008</v>
+        <v>0.78390000000000004</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -10461,10 +10461,10 @@
         <v>2023</v>
       </c>
       <c r="C720" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D720" s="3">
-        <v>0.85660000000000003</v>
+        <v>0.84170000000000011</v>
       </c>
     </row>
     <row r="721" spans="1:4">
@@ -10475,10 +10475,10 @@
         <v>2023</v>
       </c>
       <c r="C721" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D721" s="3">
-        <v>0.92820000000000003</v>
+        <v>0.80769999999999986</v>
       </c>
     </row>
     <row r="722" spans="1:4">
@@ -10489,10 +10489,10 @@
         <v>2023</v>
       </c>
       <c r="C722" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D722" s="3">
-        <v>0.86169999999999991</v>
+        <v>0.90670000000000006</v>
       </c>
     </row>
     <row r="723" spans="1:4">
@@ -10500,13 +10500,13 @@
         <v>12</v>
       </c>
       <c r="B723" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C723" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D723" s="3">
-        <v>0.85750000000000004</v>
+        <v>0.82020000000000004</v>
       </c>
     </row>
     <row r="724" spans="1:4">
@@ -10514,13 +10514,13 @@
         <v>12</v>
       </c>
       <c r="B724" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C724" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D724" s="3">
-        <v>0.9355</v>
+        <v>0.81120000000000014</v>
       </c>
     </row>
     <row r="725" spans="1:4">
@@ -10528,13 +10528,13 @@
         <v>12</v>
       </c>
       <c r="B725" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C725" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D725" s="3">
-        <v>0.79620000000000002</v>
+        <v>0.85009999999999997</v>
       </c>
     </row>
     <row r="726" spans="1:4">
@@ -10542,13 +10542,13 @@
         <v>12</v>
       </c>
       <c r="B726" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C726" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D726" s="3">
-        <v>0.93479999999999996</v>
+        <v>0.8327</v>
       </c>
     </row>
     <row r="727" spans="1:4">
@@ -10556,13 +10556,13 @@
         <v>12</v>
       </c>
       <c r="B727" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C727" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D727" s="3">
-        <v>0.96489999999999998</v>
+        <v>0.90250000000000008</v>
       </c>
     </row>
     <row r="728" spans="1:4">
@@ -10570,13 +10570,13 @@
         <v>12</v>
       </c>
       <c r="B728" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C728" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D728" s="3">
-        <v>0.86809999999999998</v>
+        <v>0.85660000000000003</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -10584,13 +10584,13 @@
         <v>12</v>
       </c>
       <c r="B729" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C729" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D729" s="3">
-        <v>0.7752</v>
+        <v>0.92820000000000003</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -10598,13 +10598,13 @@
         <v>12</v>
       </c>
       <c r="B730" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C730" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D730" s="3">
-        <v>0.82489999999999997</v>
+        <v>0.86169999999999991</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -10615,10 +10615,10 @@
         <v>2024</v>
       </c>
       <c r="C731" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D731" s="3">
-        <v>0.91530000000000011</v>
+        <v>0.85750000000000004</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -10629,10 +10629,10 @@
         <v>2024</v>
       </c>
       <c r="C732" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D732" s="3">
-        <v>0.997</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -10643,10 +10643,10 @@
         <v>2024</v>
       </c>
       <c r="C733" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D733" s="3">
-        <v>1.0399</v>
+        <v>0.79620000000000002</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -10657,10 +10657,10 @@
         <v>2024</v>
       </c>
       <c r="C734" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D734" s="3">
-        <v>1.0548</v>
+        <v>0.93479999999999996</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -10668,13 +10668,13 @@
         <v>12</v>
       </c>
       <c r="B735" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C735" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D735" s="3">
-        <v>0.92949999999999999</v>
+        <v>0.96489999999999998</v>
       </c>
     </row>
     <row r="736" spans="1:4">
@@ -10682,13 +10682,13 @@
         <v>12</v>
       </c>
       <c r="B736" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C736" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D736" s="3">
-        <v>0.95120000000000016</v>
+        <v>0.86809999999999998</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -10696,13 +10696,13 @@
         <v>12</v>
       </c>
       <c r="B737" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C737" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D737" s="3">
-        <v>0.92459999999999998</v>
+        <v>0.7752</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -10710,13 +10710,13 @@
         <v>12</v>
       </c>
       <c r="B738" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C738" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D738" s="3">
-        <v>0.85740000000000005</v>
+        <v>0.82489999999999997</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -10724,13 +10724,13 @@
         <v>12</v>
       </c>
       <c r="B739" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C739" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D739" s="3">
-        <v>0.91100000000000003</v>
+        <v>0.91530000000000011</v>
       </c>
     </row>
     <row r="740" spans="1:4">
@@ -10738,13 +10738,13 @@
         <v>12</v>
       </c>
       <c r="B740" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C740" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D740" s="3">
-        <v>0.89139999999999986</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -10752,13 +10752,13 @@
         <v>12</v>
       </c>
       <c r="B741" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C741" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D741" s="3">
-        <v>0.92459999999999998</v>
+        <v>1.0399</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -10766,13 +10766,13 @@
         <v>12</v>
       </c>
       <c r="B742" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C742" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D742" s="3">
-        <v>0.98109999999999997</v>
+        <v>1.0548</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -10783,10 +10783,10 @@
         <v>2025</v>
       </c>
       <c r="C743" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D743" s="3">
-        <v>0.91020000000000001</v>
+        <v>0.92949999999999999</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -10797,10 +10797,10 @@
         <v>2025</v>
       </c>
       <c r="C744" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D744" s="3">
-        <v>0.89680000000000004</v>
+        <v>0.95120000000000016</v>
       </c>
     </row>
     <row r="745" spans="1:4">
@@ -10811,10 +10811,10 @@
         <v>2025</v>
       </c>
       <c r="C745" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D745" s="3">
-        <v>0.83699999999999997</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -10825,10 +10825,10 @@
         <v>2025</v>
       </c>
       <c r="C746" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D746" s="3">
-        <v>0.97820000000000007</v>
+        <v>0.85740000000000005</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -10836,13 +10836,13 @@
         <v>12</v>
       </c>
       <c r="B747" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C747" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D747" s="3">
-        <v>0.98019999999999996</v>
+        <v>0.91100000000000003</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -10850,13 +10850,13 @@
         <v>12</v>
       </c>
       <c r="B748" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C748" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D748" s="3">
-        <v>0.9</v>
+        <v>0.89139999999999986</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -10864,13 +10864,13 @@
         <v>12</v>
       </c>
       <c r="B749" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C749" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D749" s="3">
-        <v>1.0012000000000001</v>
+        <v>0.92459999999999998</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -10878,13 +10878,13 @@
         <v>12</v>
       </c>
       <c r="B750" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C750" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D750" s="3">
-        <v>0.93299999999999994</v>
+        <v>0.98109999999999997</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -10892,13 +10892,13 @@
         <v>12</v>
       </c>
       <c r="B751" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C751" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D751" s="3">
-        <v>0.8708999999999999</v>
+        <v>0.91020000000000001</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -10906,13 +10906,139 @@
         <v>12</v>
       </c>
       <c r="B752" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C752" s="2">
+        <v>10</v>
+      </c>
+      <c r="D752" s="3">
+        <v>0.89680000000000004</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4">
+      <c r="A753" t="s">
+        <v>12</v>
+      </c>
+      <c r="B753" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C753" s="2">
+        <v>11</v>
+      </c>
+      <c r="D753" s="3">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4">
+      <c r="A754" t="s">
+        <v>12</v>
+      </c>
+      <c r="B754" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C754" s="2">
+        <v>12</v>
+      </c>
+      <c r="D754" s="3">
+        <v>0.97820000000000007</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4">
+      <c r="A755" t="s">
+        <v>12</v>
+      </c>
+      <c r="B755" s="2">
         <v>2026</v>
       </c>
-      <c r="C752" s="2">
-        <v>6</v>
-      </c>
-      <c r="D752" s="3">
-        <v>0.89470000000000005</v>
+      <c r="C755" s="2">
+        <v>1</v>
+      </c>
+      <c r="D755" s="3">
+        <v>0.9658000000000001</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4">
+      <c r="A756" t="s">
+        <v>12</v>
+      </c>
+      <c r="B756" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C756" s="2">
+        <v>2</v>
+      </c>
+      <c r="D756" s="3">
+        <v>0.89919999999999989</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4">
+      <c r="A757" t="s">
+        <v>12</v>
+      </c>
+      <c r="B757" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C757" s="2">
+        <v>3</v>
+      </c>
+      <c r="D757" s="3">
+        <v>1.0006999999999999</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4">
+      <c r="A758" t="s">
+        <v>12</v>
+      </c>
+      <c r="B758" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C758" s="2">
+        <v>4</v>
+      </c>
+      <c r="D758" s="3">
+        <v>0.96489999999999998</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4">
+      <c r="A759" t="s">
+        <v>12</v>
+      </c>
+      <c r="B759" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C759" s="2">
+        <v>5</v>
+      </c>
+      <c r="D759" s="3">
+        <v>0.86739999999999995</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4">
+      <c r="A760" t="s">
+        <v>12</v>
+      </c>
+      <c r="B760" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C760" s="2">
+        <v>6</v>
+      </c>
+      <c r="D760" s="3">
+        <v>0.89370000000000005</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4">
+      <c r="A761" t="s">
+        <v>12</v>
+      </c>
+      <c r="B761" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C761" s="2">
+        <v>7</v>
+      </c>
+      <c r="D761" s="3">
+        <v>0.8629</v>
       </c>
     </row>
   </sheetData>
